--- a/artfynd/A 58003-2025 artfynd.xlsx
+++ b/artfynd/A 58003-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129973732</v>
+        <v>129969590</v>
       </c>
       <c r="B2" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461665</v>
+        <v>461816</v>
       </c>
       <c r="R2" t="n">
-        <v>6780925</v>
+        <v>6780978</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129969590</v>
+        <v>129973732</v>
       </c>
       <c r="B3" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,39 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461816</v>
+        <v>461665</v>
       </c>
       <c r="R3" t="n">
-        <v>6780978</v>
+        <v>6780925</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1001,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129972707</v>
+        <v>129970747</v>
       </c>
       <c r="B5" t="n">
         <v>79084</v>
@@ -1036,13 +1036,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461666</v>
+        <v>461799</v>
       </c>
       <c r="R5" t="n">
-        <v>6780902</v>
+        <v>6780979</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,11 +1082,6 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet 3 bilder, 2 ligger 12 bilder bakåt räknat från bohål</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,7 +1108,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129970747</v>
+        <v>129972707</v>
       </c>
       <c r="B6" t="n">
         <v>79084</v>
@@ -1148,13 +1143,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461799</v>
+        <v>461666</v>
       </c>
       <c r="R6" t="n">
-        <v>6780979</v>
+        <v>6780902</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1194,6 +1189,11 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter, synfältet 3 bilder, 2 ligger 12 bilder bakåt räknat från bohål</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1332,50 +1332,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129969658</v>
+        <v>129971802</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>79703</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461799</v>
+        <v>461709</v>
       </c>
       <c r="R8" t="n">
-        <v>6780979</v>
+        <v>6780921</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,45 +1439,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129971802</v>
+        <v>129969658</v>
       </c>
       <c r="B9" t="n">
-        <v>79703</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461709</v>
+        <v>461799</v>
       </c>
       <c r="R9" t="n">
-        <v>6780921</v>
+        <v>6780979</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1551,10 +1551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129971607</v>
+        <v>129973829</v>
       </c>
       <c r="B10" t="n">
-        <v>79674</v>
+        <v>57734</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1562,34 +1562,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461733</v>
+        <v>461730</v>
       </c>
       <c r="R10" t="n">
-        <v>6780958</v>
+        <v>6780969</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1658,50 +1663,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129971831</v>
+        <v>129971607</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>79674</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461686</v>
+        <v>461733</v>
       </c>
       <c r="R11" t="n">
-        <v>6780923</v>
+        <v>6780958</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1770,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129973829</v>
+        <v>129972961</v>
       </c>
       <c r="B12" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1781,39 +1781,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461730</v>
+        <v>461615</v>
       </c>
       <c r="R12" t="n">
-        <v>6780969</v>
+        <v>6780923</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1882,42 +1877,47 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129972961</v>
+        <v>129971831</v>
       </c>
       <c r="B13" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461615</v>
+        <v>461686</v>
       </c>
       <c r="R13" t="n">
         <v>6780923</v>
@@ -2417,10 +2417,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129971585</v>
+        <v>129971608</v>
       </c>
       <c r="B18" t="n">
-        <v>57734</v>
+        <v>79703</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2428,39 +2428,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461736</v>
+        <v>461733</v>
       </c>
       <c r="R18" t="n">
-        <v>6780931</v>
+        <v>6780958</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2529,10 +2524,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129971608</v>
+        <v>129971585</v>
       </c>
       <c r="B19" t="n">
-        <v>79703</v>
+        <v>57734</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2540,34 +2535,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461733</v>
+        <v>461736</v>
       </c>
       <c r="R19" t="n">
-        <v>6780958</v>
+        <v>6780931</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2743,53 +2743,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129972802</v>
+        <v>129971438</v>
       </c>
       <c r="B21" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461611</v>
+        <v>461737</v>
       </c>
       <c r="R21" t="n">
-        <v>6780900</v>
+        <v>6780944</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2829,6 +2824,11 @@
       <c r="AB21" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2 bilder, rikligt till måttligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2855,7 +2855,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129972800</v>
+        <v>129971589</v>
       </c>
       <c r="B22" t="n">
         <v>79084</v>
@@ -2890,10 +2890,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461611</v>
+        <v>461736</v>
       </c>
       <c r="R22" t="n">
-        <v>6780900</v>
+        <v>6780931</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2962,7 +2962,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129971438</v>
+        <v>129972800</v>
       </c>
       <c r="B23" t="n">
         <v>79084</v>
@@ -2997,13 +2997,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461737</v>
+        <v>461611</v>
       </c>
       <c r="R23" t="n">
-        <v>6780944</v>
+        <v>6780900</v>
       </c>
       <c r="S23" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3043,11 +3043,6 @@
       <c r="AB23" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>2 bilder, rikligt till måttligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3074,45 +3069,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129971589</v>
+        <v>129972802</v>
       </c>
       <c r="B24" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461736</v>
+        <v>461611</v>
       </c>
       <c r="R24" t="n">
-        <v>6780931</v>
+        <v>6780900</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3181,10 +3181,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129971741</v>
+        <v>129972538</v>
       </c>
       <c r="B25" t="n">
-        <v>79084</v>
+        <v>91623</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3192,21 +3192,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461741</v>
+        <v>461679</v>
       </c>
       <c r="R25" t="n">
-        <v>6780920</v>
+        <v>6780885</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3262,6 +3262,11 @@
       <c r="AB25" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>2 bilder, vid bohål</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3288,10 +3293,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129972538</v>
+        <v>129971741</v>
       </c>
       <c r="B26" t="n">
-        <v>91623</v>
+        <v>79084</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3299,21 +3304,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3323,10 +3328,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461679</v>
+        <v>461741</v>
       </c>
       <c r="R26" t="n">
-        <v>6780885</v>
+        <v>6780920</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3369,11 +3374,6 @@
       <c r="AB26" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>2 bilder, vid bohål</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3400,7 +3400,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129973842</v>
+        <v>129972234</v>
       </c>
       <c r="B27" t="n">
         <v>8450</v>
@@ -3440,10 +3440,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461730</v>
+        <v>461679</v>
       </c>
       <c r="R27" t="n">
-        <v>6780969</v>
+        <v>6780885</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3512,7 +3512,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129972234</v>
+        <v>129973842</v>
       </c>
       <c r="B28" t="n">
         <v>8450</v>
@@ -3552,10 +3552,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461679</v>
+        <v>461730</v>
       </c>
       <c r="R28" t="n">
-        <v>6780885</v>
+        <v>6780969</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3848,50 +3848,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129971289</v>
+        <v>129972394</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461751</v>
+        <v>461679</v>
       </c>
       <c r="R31" t="n">
-        <v>6780936</v>
+        <v>6780885</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3960,7 +3955,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129972394</v>
+        <v>129972457</v>
       </c>
       <c r="B32" t="n">
         <v>79084</v>
@@ -3995,10 +3990,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461679</v>
+        <v>461687</v>
       </c>
       <c r="R32" t="n">
-        <v>6780885</v>
+        <v>6780875</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4067,45 +4062,50 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129972457</v>
+        <v>129971289</v>
       </c>
       <c r="B33" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461687</v>
+        <v>461751</v>
       </c>
       <c r="R33" t="n">
-        <v>6780875</v>
+        <v>6780936</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4174,38 +4174,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129971587</v>
+        <v>129972793</v>
       </c>
       <c r="B34" t="n">
-        <v>8450</v>
+        <v>57734</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461736</v>
+        <v>461611</v>
       </c>
       <c r="R34" t="n">
-        <v>6780931</v>
+        <v>6780900</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4286,38 +4286,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129972793</v>
+        <v>129971587</v>
       </c>
       <c r="B35" t="n">
-        <v>57734</v>
+        <v>8450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4326,10 +4326,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461611</v>
+        <v>461736</v>
       </c>
       <c r="R35" t="n">
-        <v>6780900</v>
+        <v>6780931</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4510,10 +4510,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129970738</v>
+        <v>129971825</v>
       </c>
       <c r="B37" t="n">
-        <v>79703</v>
+        <v>57734</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4521,34 +4521,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461799</v>
+        <v>461686</v>
       </c>
       <c r="R37" t="n">
-        <v>6780979</v>
+        <v>6780923</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4617,10 +4622,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129971825</v>
+        <v>129971783</v>
       </c>
       <c r="B38" t="n">
-        <v>57734</v>
+        <v>79674</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4628,39 +4633,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461686</v>
+        <v>461741</v>
       </c>
       <c r="R38" t="n">
-        <v>6780923</v>
+        <v>6780920</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4703,6 +4703,11 @@
       <c r="AB38" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>2 bilder, högstubbe</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4729,10 +4734,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129971783</v>
+        <v>129970738</v>
       </c>
       <c r="B39" t="n">
-        <v>79674</v>
+        <v>79703</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4740,21 +4745,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4764,10 +4769,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461741</v>
+        <v>461799</v>
       </c>
       <c r="R39" t="n">
-        <v>6780920</v>
+        <v>6780979</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4810,11 +4815,6 @@
       <c r="AB39" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>2 bilder, högstubbe</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4841,10 +4841,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129970828</v>
+        <v>129971832</v>
       </c>
       <c r="B40" t="n">
-        <v>78841</v>
+        <v>79084</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4852,21 +4852,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4876,10 +4876,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461800</v>
+        <v>461686</v>
       </c>
       <c r="R40" t="n">
-        <v>6781016</v>
+        <v>6780923</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4948,7 +4948,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129971832</v>
+        <v>129969625</v>
       </c>
       <c r="B41" t="n">
         <v>79084</v>
@@ -4983,13 +4983,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461686</v>
+        <v>461814</v>
       </c>
       <c r="R41" t="n">
-        <v>6780923</v>
+        <v>6780993</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5029,6 +5029,11 @@
       <c r="AB41" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>3 bilder, rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5055,10 +5060,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129969625</v>
+        <v>129970828</v>
       </c>
       <c r="B42" t="n">
-        <v>79084</v>
+        <v>78841</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5066,21 +5071,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5090,13 +5095,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461814</v>
+        <v>461800</v>
       </c>
       <c r="R42" t="n">
-        <v>6780993</v>
+        <v>6781016</v>
       </c>
       <c r="S42" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5136,11 +5141,6 @@
       <c r="AB42" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>3 bilder, rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5279,10 +5279,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129971259</v>
+        <v>129973137</v>
       </c>
       <c r="B44" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5290,39 +5290,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461751</v>
+        <v>461609</v>
       </c>
       <c r="R44" t="n">
-        <v>6780936</v>
+        <v>6780949</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5365,6 +5360,11 @@
       <c r="AB44" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>3 bilder, rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5391,7 +5391,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129971804</v>
+        <v>129973978</v>
       </c>
       <c r="B45" t="n">
         <v>79084</v>
@@ -5426,10 +5426,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461709</v>
+        <v>461749</v>
       </c>
       <c r="R45" t="n">
-        <v>6780921</v>
+        <v>6780997</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5498,7 +5498,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129973978</v>
+        <v>129971804</v>
       </c>
       <c r="B46" t="n">
         <v>79084</v>
@@ -5533,10 +5533,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461749</v>
+        <v>461709</v>
       </c>
       <c r="R46" t="n">
-        <v>6780997</v>
+        <v>6780921</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5605,10 +5605,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129973137</v>
+        <v>129971259</v>
       </c>
       <c r="B47" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5616,34 +5616,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461609</v>
+        <v>461751</v>
       </c>
       <c r="R47" t="n">
-        <v>6780949</v>
+        <v>6780936</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5686,11 +5691,6 @@
       <c r="AB47" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>3 bilder, rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5717,7 +5717,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129972233</v>
+        <v>129969692</v>
       </c>
       <c r="B48" t="n">
         <v>57734</v>
@@ -5757,10 +5757,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461679</v>
+        <v>461799</v>
       </c>
       <c r="R48" t="n">
-        <v>6780885</v>
+        <v>6780979</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5834,7 +5834,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129969692</v>
+        <v>129972233</v>
       </c>
       <c r="B49" t="n">
         <v>57734</v>
@@ -5874,10 +5874,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>461799</v>
+        <v>461679</v>
       </c>
       <c r="R49" t="n">
-        <v>6780979</v>
+        <v>6780885</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6068,10 +6068,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129970961</v>
+        <v>129972983</v>
       </c>
       <c r="B51" t="n">
-        <v>79674</v>
+        <v>57734</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6079,34 +6079,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461789</v>
+        <v>461615</v>
       </c>
       <c r="R51" t="n">
-        <v>6780961</v>
+        <v>6780923</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6175,10 +6180,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129971290</v>
+        <v>129970813</v>
       </c>
       <c r="B52" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6186,21 +6191,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6210,10 +6215,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461751</v>
+        <v>461800</v>
       </c>
       <c r="R52" t="n">
-        <v>6780936</v>
+        <v>6781016</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6282,10 +6287,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129972983</v>
+        <v>129971290</v>
       </c>
       <c r="B53" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6293,39 +6298,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>461615</v>
+        <v>461751</v>
       </c>
       <c r="R53" t="n">
-        <v>6780923</v>
+        <v>6780936</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6394,10 +6394,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129970813</v>
+        <v>129970961</v>
       </c>
       <c r="B54" t="n">
-        <v>79703</v>
+        <v>79674</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6405,21 +6405,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6429,10 +6429,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>461800</v>
+        <v>461789</v>
       </c>
       <c r="R54" t="n">
-        <v>6781016</v>
+        <v>6780961</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>

--- a/artfynd/A 58003-2025 artfynd.xlsx
+++ b/artfynd/A 58003-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129969590</v>
       </c>
       <c r="B2" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>129973732</v>
       </c>
       <c r="B3" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>129971610</v>
       </c>
       <c r="B4" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>129970747</v>
       </c>
       <c r="B5" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>129972707</v>
       </c>
       <c r="B6" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129971066</v>
       </c>
       <c r="B7" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>129971802</v>
       </c>
       <c r="B8" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>129969658</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,10 +1551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129973829</v>
+        <v>129972961</v>
       </c>
       <c r="B10" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1562,39 +1562,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461730</v>
+        <v>461615</v>
       </c>
       <c r="R10" t="n">
-        <v>6780969</v>
+        <v>6780923</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1663,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129971607</v>
+        <v>129973829</v>
       </c>
       <c r="B11" t="n">
-        <v>79674</v>
+        <v>57737</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1674,34 +1669,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461733</v>
+        <v>461730</v>
       </c>
       <c r="R11" t="n">
-        <v>6780958</v>
+        <v>6780969</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1770,42 +1770,47 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129972961</v>
+        <v>129971831</v>
       </c>
       <c r="B12" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461615</v>
+        <v>461686</v>
       </c>
       <c r="R12" t="n">
         <v>6780923</v>
@@ -1877,50 +1882,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129971831</v>
+        <v>129971607</v>
       </c>
       <c r="B13" t="n">
-        <v>8450</v>
+        <v>79677</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461686</v>
+        <v>461733</v>
       </c>
       <c r="R13" t="n">
-        <v>6780923</v>
+        <v>6780958</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1992,7 +1992,7 @@
         <v>129970971</v>
       </c>
       <c r="B14" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2096,10 +2096,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129971115</v>
+        <v>129971787</v>
       </c>
       <c r="B15" t="n">
-        <v>79674</v>
+        <v>79706</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2107,21 +2107,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2131,10 +2131,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461762</v>
+        <v>461741</v>
       </c>
       <c r="R15" t="n">
-        <v>6780940</v>
+        <v>6780920</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2203,10 +2203,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129971787</v>
+        <v>129971115</v>
       </c>
       <c r="B16" t="n">
-        <v>79703</v>
+        <v>79677</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2214,21 +2214,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461741</v>
+        <v>461762</v>
       </c>
       <c r="R16" t="n">
-        <v>6780920</v>
+        <v>6780940</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2310,10 +2310,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129971127</v>
+        <v>129973851</v>
       </c>
       <c r="B17" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2345,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461762</v>
+        <v>461730</v>
       </c>
       <c r="R17" t="n">
-        <v>6780940</v>
+        <v>6780969</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2420,7 +2420,7 @@
         <v>129971608</v>
       </c>
       <c r="B18" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2524,10 +2524,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129971585</v>
+        <v>129971127</v>
       </c>
       <c r="B19" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2535,39 +2535,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461736</v>
+        <v>461762</v>
       </c>
       <c r="R19" t="n">
-        <v>6780931</v>
+        <v>6780940</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2636,10 +2631,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129973851</v>
+        <v>129971585</v>
       </c>
       <c r="B20" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2647,34 +2642,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461730</v>
+        <v>461736</v>
       </c>
       <c r="R20" t="n">
-        <v>6780969</v>
+        <v>6780931</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2746,7 +2746,7 @@
         <v>129971438</v>
       </c>
       <c r="B21" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>129971589</v>
       </c>
       <c r="B22" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>129972800</v>
       </c>
       <c r="B23" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>129972802</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3181,10 +3181,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129972538</v>
+        <v>129971741</v>
       </c>
       <c r="B25" t="n">
-        <v>91623</v>
+        <v>79087</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3192,21 +3192,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461679</v>
+        <v>461741</v>
       </c>
       <c r="R25" t="n">
-        <v>6780885</v>
+        <v>6780920</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3262,11 +3262,6 @@
       <c r="AB25" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>2 bilder, vid bohål</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3293,10 +3288,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129971741</v>
+        <v>129972538</v>
       </c>
       <c r="B26" t="n">
-        <v>79084</v>
+        <v>91626</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3304,21 +3299,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3328,10 +3323,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461741</v>
+        <v>461679</v>
       </c>
       <c r="R26" t="n">
-        <v>6780920</v>
+        <v>6780885</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3374,6 +3369,11 @@
       <c r="AB26" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>2 bilder, vid bohål</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3403,7 +3403,7 @@
         <v>129972234</v>
       </c>
       <c r="B27" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>129973842</v>
       </c>
       <c r="B28" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3624,10 +3624,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129972955</v>
+        <v>129970829</v>
       </c>
       <c r="B29" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3635,39 +3635,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461615</v>
+        <v>461800</v>
       </c>
       <c r="R29" t="n">
-        <v>6780923</v>
+        <v>6781016</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3710,11 +3705,6 @@
       <c r="AB29" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>1 bild</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3741,10 +3731,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129970829</v>
+        <v>129972955</v>
       </c>
       <c r="B30" t="n">
-        <v>79084</v>
+        <v>57740</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3752,34 +3742,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461800</v>
+        <v>461615</v>
       </c>
       <c r="R30" t="n">
-        <v>6781016</v>
+        <v>6780923</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3822,6 +3817,11 @@
       <c r="AB30" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3848,45 +3848,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129972394</v>
+        <v>129971289</v>
       </c>
       <c r="B31" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461679</v>
+        <v>461751</v>
       </c>
       <c r="R31" t="n">
-        <v>6780885</v>
+        <v>6780936</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3958,7 +3963,7 @@
         <v>129972457</v>
       </c>
       <c r="B32" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4062,50 +4067,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129971289</v>
+        <v>129972394</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461751</v>
+        <v>461679</v>
       </c>
       <c r="R33" t="n">
-        <v>6780936</v>
+        <v>6780885</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4174,38 +4174,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129972793</v>
+        <v>129971587</v>
       </c>
       <c r="B34" t="n">
-        <v>57734</v>
+        <v>8451</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461611</v>
+        <v>461736</v>
       </c>
       <c r="R34" t="n">
-        <v>6780900</v>
+        <v>6780931</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4286,10 +4286,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129971587</v>
+        <v>129972990</v>
       </c>
       <c r="B35" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4326,10 +4326,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461736</v>
+        <v>461615</v>
       </c>
       <c r="R35" t="n">
-        <v>6780931</v>
+        <v>6780923</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4398,38 +4398,38 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129972990</v>
+        <v>129972793</v>
       </c>
       <c r="B36" t="n">
-        <v>8450</v>
+        <v>57737</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4438,10 +4438,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461615</v>
+        <v>461611</v>
       </c>
       <c r="R36" t="n">
-        <v>6780923</v>
+        <v>6780900</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4510,10 +4510,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129971825</v>
+        <v>129970738</v>
       </c>
       <c r="B37" t="n">
-        <v>57734</v>
+        <v>79706</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4521,39 +4521,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461686</v>
+        <v>461799</v>
       </c>
       <c r="R37" t="n">
-        <v>6780923</v>
+        <v>6780979</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4625,7 +4620,7 @@
         <v>129971783</v>
       </c>
       <c r="B38" t="n">
-        <v>79674</v>
+        <v>79677</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4734,10 +4729,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129970738</v>
+        <v>129971825</v>
       </c>
       <c r="B39" t="n">
-        <v>79703</v>
+        <v>57737</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4745,34 +4740,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461799</v>
+        <v>461686</v>
       </c>
       <c r="R39" t="n">
-        <v>6780979</v>
+        <v>6780923</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4841,10 +4841,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129971832</v>
+        <v>129970828</v>
       </c>
       <c r="B40" t="n">
-        <v>79084</v>
+        <v>78844</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4852,21 +4852,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4876,10 +4876,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461686</v>
+        <v>461800</v>
       </c>
       <c r="R40" t="n">
-        <v>6780923</v>
+        <v>6781016</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4948,10 +4948,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129969625</v>
+        <v>129971832</v>
       </c>
       <c r="B41" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4983,13 +4983,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461814</v>
+        <v>461686</v>
       </c>
       <c r="R41" t="n">
-        <v>6780993</v>
+        <v>6780923</v>
       </c>
       <c r="S41" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5029,11 +5029,6 @@
       <c r="AB41" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>3 bilder, rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5060,10 +5055,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129970828</v>
+        <v>129969625</v>
       </c>
       <c r="B42" t="n">
-        <v>78841</v>
+        <v>79087</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5071,21 +5066,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5095,13 +5090,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461800</v>
+        <v>461814</v>
       </c>
       <c r="R42" t="n">
-        <v>6781016</v>
+        <v>6780993</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5141,6 +5136,11 @@
       <c r="AB42" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>3 bilder, rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5170,7 +5170,7 @@
         <v>129970888</v>
       </c>
       <c r="B43" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5279,10 +5279,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129973137</v>
+        <v>129971259</v>
       </c>
       <c r="B44" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5290,34 +5290,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461609</v>
+        <v>461751</v>
       </c>
       <c r="R44" t="n">
-        <v>6780949</v>
+        <v>6780936</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5360,11 +5365,6 @@
       <c r="AB44" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>3 bilder, rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5391,10 +5391,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129973978</v>
+        <v>129969692</v>
       </c>
       <c r="B45" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5402,34 +5402,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461749</v>
+        <v>461799</v>
       </c>
       <c r="R45" t="n">
-        <v>6780997</v>
+        <v>6780979</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5472,6 +5477,11 @@
       <c r="AB45" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5498,10 +5508,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129971804</v>
+        <v>129972233</v>
       </c>
       <c r="B46" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5509,34 +5519,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461709</v>
+        <v>461679</v>
       </c>
       <c r="R46" t="n">
-        <v>6780921</v>
+        <v>6780885</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5579,6 +5594,11 @@
       <c r="AB46" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5605,10 +5625,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129971259</v>
+        <v>129973978</v>
       </c>
       <c r="B47" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5616,39 +5636,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461751</v>
+        <v>461749</v>
       </c>
       <c r="R47" t="n">
-        <v>6780936</v>
+        <v>6780997</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5717,10 +5732,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129969692</v>
+        <v>129971804</v>
       </c>
       <c r="B48" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5728,39 +5743,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461799</v>
+        <v>461709</v>
       </c>
       <c r="R48" t="n">
-        <v>6780979</v>
+        <v>6780921</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5803,11 +5813,6 @@
       <c r="AB48" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>1 bild</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5834,10 +5839,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129972233</v>
+        <v>129973137</v>
       </c>
       <c r="B49" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5845,39 +5850,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>461679</v>
+        <v>461609</v>
       </c>
       <c r="R49" t="n">
-        <v>6780885</v>
+        <v>6780949</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>3 bilder, rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5954,7 +5954,7 @@
         <v>129972454</v>
       </c>
       <c r="B50" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6068,10 +6068,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129972983</v>
+        <v>129970813</v>
       </c>
       <c r="B51" t="n">
-        <v>57734</v>
+        <v>79706</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6079,39 +6079,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461615</v>
+        <v>461800</v>
       </c>
       <c r="R51" t="n">
-        <v>6780923</v>
+        <v>6781016</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6180,10 +6175,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129970813</v>
+        <v>129971290</v>
       </c>
       <c r="B52" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6191,21 +6186,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6215,10 +6210,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461800</v>
+        <v>461751</v>
       </c>
       <c r="R52" t="n">
-        <v>6781016</v>
+        <v>6780936</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6287,10 +6282,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129971290</v>
+        <v>129972983</v>
       </c>
       <c r="B53" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6298,34 +6293,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>461751</v>
+        <v>461615</v>
       </c>
       <c r="R53" t="n">
-        <v>6780936</v>
+        <v>6780923</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6397,7 +6397,7 @@
         <v>129970961</v>
       </c>
       <c r="B54" t="n">
-        <v>79674</v>
+        <v>79677</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 58003-2025 artfynd.xlsx
+++ b/artfynd/A 58003-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129969590</v>
+        <v>129973732</v>
       </c>
       <c r="B2" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461816</v>
+        <v>461665</v>
       </c>
       <c r="R2" t="n">
-        <v>6780978</v>
+        <v>6780925</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129973732</v>
+        <v>129969590</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461665</v>
+        <v>461816</v>
       </c>
       <c r="R3" t="n">
-        <v>6780925</v>
+        <v>6780978</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129972707</v>
+        <v>129971802</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461666</v>
+        <v>461709</v>
       </c>
       <c r="R6" t="n">
-        <v>6780902</v>
+        <v>6780921</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1189,11 +1189,6 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter, synfältet 3 bilder, 2 ligger 12 bilder bakåt räknat från bohål</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,45 +1215,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129971066</v>
+        <v>129969658</v>
       </c>
       <c r="B7" t="n">
-        <v>79706</v>
+        <v>8451</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461789</v>
+        <v>461799</v>
       </c>
       <c r="R7" t="n">
-        <v>6780961</v>
+        <v>6780979</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,11 +1301,6 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>1 bild, 2 stubbar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129971802</v>
+        <v>129972961</v>
       </c>
       <c r="B8" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1343,21 +1338,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1367,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461709</v>
+        <v>461615</v>
       </c>
       <c r="R8" t="n">
-        <v>6780921</v>
+        <v>6780923</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1439,38 +1434,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129969658</v>
+        <v>129973829</v>
       </c>
       <c r="B9" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1479,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461799</v>
+        <v>461730</v>
       </c>
       <c r="R9" t="n">
-        <v>6780979</v>
+        <v>6780969</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1551,42 +1546,47 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129972961</v>
+        <v>129971831</v>
       </c>
       <c r="B10" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461615</v>
+        <v>461686</v>
       </c>
       <c r="R10" t="n">
         <v>6780923</v>
@@ -1658,10 +1658,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129973829</v>
+        <v>129971607</v>
       </c>
       <c r="B11" t="n">
-        <v>57737</v>
+        <v>79677</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1669,39 +1669,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461730</v>
+        <v>461733</v>
       </c>
       <c r="R11" t="n">
-        <v>6780969</v>
+        <v>6780958</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1770,50 +1765,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129971831</v>
+        <v>129970971</v>
       </c>
       <c r="B12" t="n">
-        <v>8451</v>
+        <v>79087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461686</v>
+        <v>461789</v>
       </c>
       <c r="R12" t="n">
-        <v>6780923</v>
+        <v>6780961</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1882,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129971607</v>
+        <v>129971787</v>
       </c>
       <c r="B13" t="n">
-        <v>79677</v>
+        <v>79706</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1893,21 +1883,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1917,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461733</v>
+        <v>461741</v>
       </c>
       <c r="R13" t="n">
-        <v>6780958</v>
+        <v>6780920</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1989,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129970971</v>
+        <v>129971115</v>
       </c>
       <c r="B14" t="n">
-        <v>79087</v>
+        <v>79677</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2000,21 +1990,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2024,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461789</v>
+        <v>461762</v>
       </c>
       <c r="R14" t="n">
-        <v>6780961</v>
+        <v>6780940</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2096,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129971787</v>
+        <v>129973851</v>
       </c>
       <c r="B15" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2107,21 +2097,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2131,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461741</v>
+        <v>461730</v>
       </c>
       <c r="R15" t="n">
-        <v>6780920</v>
+        <v>6780969</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2203,10 +2193,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129971115</v>
+        <v>129971127</v>
       </c>
       <c r="B16" t="n">
-        <v>79677</v>
+        <v>79087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2214,21 +2204,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2310,10 +2300,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129973851</v>
+        <v>129971608</v>
       </c>
       <c r="B17" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2321,21 +2311,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2345,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461730</v>
+        <v>461733</v>
       </c>
       <c r="R17" t="n">
-        <v>6780969</v>
+        <v>6780958</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2417,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129971608</v>
+        <v>129971585</v>
       </c>
       <c r="B18" t="n">
-        <v>79706</v>
+        <v>57737</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2428,34 +2418,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461733</v>
+        <v>461736</v>
       </c>
       <c r="R18" t="n">
-        <v>6780958</v>
+        <v>6780931</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2524,7 +2519,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129971127</v>
+        <v>129971589</v>
       </c>
       <c r="B19" t="n">
         <v>79087</v>
@@ -2559,10 +2554,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461762</v>
+        <v>461736</v>
       </c>
       <c r="R19" t="n">
-        <v>6780940</v>
+        <v>6780931</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2631,10 +2626,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129971585</v>
+        <v>129972800</v>
       </c>
       <c r="B20" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2642,39 +2637,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461736</v>
+        <v>461611</v>
       </c>
       <c r="R20" t="n">
-        <v>6780931</v>
+        <v>6780900</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2743,48 +2733,53 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129971438</v>
+        <v>129972802</v>
       </c>
       <c r="B21" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461737</v>
+        <v>461611</v>
       </c>
       <c r="R21" t="n">
-        <v>6780944</v>
+        <v>6780900</v>
       </c>
       <c r="S21" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2824,11 +2819,6 @@
       <c r="AB21" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>2 bilder, rikligt till måttligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2855,7 +2845,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129971589</v>
+        <v>129971741</v>
       </c>
       <c r="B22" t="n">
         <v>79087</v>
@@ -2890,10 +2880,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461736</v>
+        <v>461741</v>
       </c>
       <c r="R22" t="n">
-        <v>6780931</v>
+        <v>6780920</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2962,7 +2952,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129972800</v>
+        <v>129970829</v>
       </c>
       <c r="B23" t="n">
         <v>79087</v>
@@ -2997,10 +2987,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461611</v>
+        <v>461800</v>
       </c>
       <c r="R23" t="n">
-        <v>6780900</v>
+        <v>6781016</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3069,7 +3059,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129972802</v>
+        <v>129972234</v>
       </c>
       <c r="B24" t="n">
         <v>8451</v>
@@ -3109,10 +3099,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461611</v>
+        <v>461679</v>
       </c>
       <c r="R24" t="n">
-        <v>6780900</v>
+        <v>6780885</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3181,45 +3171,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129971741</v>
+        <v>129973842</v>
       </c>
       <c r="B25" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461741</v>
+        <v>461730</v>
       </c>
       <c r="R25" t="n">
-        <v>6780920</v>
+        <v>6780969</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3288,10 +3283,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129972538</v>
+        <v>129972457</v>
       </c>
       <c r="B26" t="n">
-        <v>91626</v>
+        <v>79087</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3299,21 +3294,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3323,10 +3318,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461679</v>
+        <v>461687</v>
       </c>
       <c r="R26" t="n">
-        <v>6780885</v>
+        <v>6780875</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3369,11 +3364,6 @@
       <c r="AB26" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>2 bilder, vid bohål</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3400,40 +3390,35 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129972234</v>
+        <v>129972394</v>
       </c>
       <c r="B27" t="n">
-        <v>8451</v>
+        <v>79087</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
@@ -3512,7 +3497,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129973842</v>
+        <v>129971289</v>
       </c>
       <c r="B28" t="n">
         <v>8451</v>
@@ -3552,10 +3537,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461730</v>
+        <v>461751</v>
       </c>
       <c r="R28" t="n">
-        <v>6780969</v>
+        <v>6780936</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3624,45 +3609,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129970829</v>
+        <v>129971587</v>
       </c>
       <c r="B29" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461800</v>
+        <v>461736</v>
       </c>
       <c r="R29" t="n">
-        <v>6781016</v>
+        <v>6780931</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3731,38 +3721,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129972955</v>
+        <v>129972990</v>
       </c>
       <c r="B30" t="n">
-        <v>57740</v>
+        <v>8451</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3817,11 +3807,6 @@
       <c r="AB30" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>1 bild</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3848,50 +3833,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129971289</v>
+        <v>129970675</v>
       </c>
       <c r="B31" t="n">
-        <v>8451</v>
+        <v>79706</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461751</v>
+        <v>461789</v>
       </c>
       <c r="R31" t="n">
-        <v>6780936</v>
+        <v>6780961</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3960,10 +3940,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129972457</v>
+        <v>129972793</v>
       </c>
       <c r="B32" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3971,34 +3951,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461687</v>
+        <v>461611</v>
       </c>
       <c r="R32" t="n">
-        <v>6780875</v>
+        <v>6780900</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4067,10 +4052,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129972394</v>
+        <v>129970738</v>
       </c>
       <c r="B33" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4078,21 +4063,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4102,10 +4087,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461679</v>
+        <v>461799</v>
       </c>
       <c r="R33" t="n">
-        <v>6780885</v>
+        <v>6780979</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4174,38 +4159,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129971587</v>
+        <v>129971825</v>
       </c>
       <c r="B34" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4214,10 +4199,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461736</v>
+        <v>461686</v>
       </c>
       <c r="R34" t="n">
-        <v>6780931</v>
+        <v>6780923</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4286,47 +4271,42 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129972990</v>
+        <v>129971832</v>
       </c>
       <c r="B35" t="n">
-        <v>8451</v>
+        <v>79087</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461615</v>
+        <v>461686</v>
       </c>
       <c r="R35" t="n">
         <v>6780923</v>
@@ -4398,10 +4378,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129972793</v>
+        <v>129970828</v>
       </c>
       <c r="B36" t="n">
-        <v>57737</v>
+        <v>78844</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4409,39 +4389,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461611</v>
+        <v>461800</v>
       </c>
       <c r="R36" t="n">
-        <v>6780900</v>
+        <v>6781016</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4510,10 +4485,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129970738</v>
+        <v>129971259</v>
       </c>
       <c r="B37" t="n">
-        <v>79706</v>
+        <v>57737</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4521,34 +4496,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461799</v>
+        <v>461751</v>
       </c>
       <c r="R37" t="n">
-        <v>6780979</v>
+        <v>6780936</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4617,10 +4597,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129971783</v>
+        <v>129973978</v>
       </c>
       <c r="B38" t="n">
-        <v>79677</v>
+        <v>79087</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4628,21 +4608,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4652,10 +4632,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461741</v>
+        <v>461749</v>
       </c>
       <c r="R38" t="n">
-        <v>6780920</v>
+        <v>6780997</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4698,11 +4678,6 @@
       <c r="AB38" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>2 bilder, högstubbe</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4729,10 +4704,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129971825</v>
+        <v>129971804</v>
       </c>
       <c r="B39" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4740,39 +4715,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461686</v>
+        <v>461709</v>
       </c>
       <c r="R39" t="n">
-        <v>6780923</v>
+        <v>6780921</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4841,10 +4811,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129970828</v>
+        <v>129971739</v>
       </c>
       <c r="B40" t="n">
-        <v>78844</v>
+        <v>79677</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4852,21 +4822,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4876,10 +4846,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461800</v>
+        <v>461741</v>
       </c>
       <c r="R40" t="n">
-        <v>6781016</v>
+        <v>6780920</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4948,10 +4918,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129971832</v>
+        <v>129970813</v>
       </c>
       <c r="B41" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4959,21 +4929,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4983,10 +4953,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461686</v>
+        <v>461800</v>
       </c>
       <c r="R41" t="n">
-        <v>6780923</v>
+        <v>6781016</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5055,7 +5025,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129969625</v>
+        <v>129971290</v>
       </c>
       <c r="B42" t="n">
         <v>79087</v>
@@ -5090,13 +5060,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461814</v>
+        <v>461751</v>
       </c>
       <c r="R42" t="n">
-        <v>6780993</v>
+        <v>6780936</v>
       </c>
       <c r="S42" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5136,11 +5106,6 @@
       <c r="AB42" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>3 bilder, rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5167,10 +5132,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129970888</v>
+        <v>129972983</v>
       </c>
       <c r="B43" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5178,34 +5143,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461776</v>
+        <v>461615</v>
       </c>
       <c r="R43" t="n">
-        <v>6780976</v>
+        <v>6780923</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5248,11 +5218,6 @@
       <c r="AB43" t="inlineStr">
         <is>
           <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>3 bilder, rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5279,10 +5244,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129971259</v>
+        <v>129970961</v>
       </c>
       <c r="B44" t="n">
-        <v>57737</v>
+        <v>79677</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5290,39 +5255,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461751</v>
+        <v>461789</v>
       </c>
       <c r="R44" t="n">
-        <v>6780936</v>
+        <v>6780961</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5391,10 +5351,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129969692</v>
+        <v>129972707</v>
       </c>
       <c r="B45" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5402,42 +5362,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461799</v>
+        <v>461666</v>
       </c>
       <c r="R45" t="n">
-        <v>6780979</v>
+        <v>6780902</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5481,7 +5436,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Rikligt i en radie av ca 50 meter, synfältet 3 bilder, 2 ligger 12 bilder bakåt räknat från bohål</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5508,10 +5463,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129972233</v>
+        <v>129971438</v>
       </c>
       <c r="B46" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5519,42 +5474,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461679</v>
+        <v>461737</v>
       </c>
       <c r="R46" t="n">
-        <v>6780885</v>
+        <v>6780944</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5598,7 +5548,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>2 bilder, rikligt till måttligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5625,10 +5575,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129973978</v>
+        <v>129972538</v>
       </c>
       <c r="B47" t="n">
-        <v>79087</v>
+        <v>91626</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5636,21 +5586,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5660,10 +5610,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461749</v>
+        <v>461679</v>
       </c>
       <c r="R47" t="n">
-        <v>6780997</v>
+        <v>6780885</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5706,6 +5656,11 @@
       <c r="AB47" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>2 bilder, vid bohål</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5732,10 +5687,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129971804</v>
+        <v>129972955</v>
       </c>
       <c r="B48" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5743,34 +5698,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461709</v>
+        <v>461615</v>
       </c>
       <c r="R48" t="n">
-        <v>6780921</v>
+        <v>6780923</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5813,6 +5773,11 @@
       <c r="AB48" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5839,7 +5804,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129973137</v>
+        <v>129969625</v>
       </c>
       <c r="B49" t="n">
         <v>79087</v>
@@ -5874,13 +5839,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>461609</v>
+        <v>461814</v>
       </c>
       <c r="R49" t="n">
-        <v>6780949</v>
+        <v>6780993</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5924,7 +5889,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>3 bilder, rikligt i en radie av ca 50 meter</t>
+          <t>3 bilder, rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5951,10 +5916,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129972454</v>
+        <v>129970888</v>
       </c>
       <c r="B50" t="n">
-        <v>57740</v>
+        <v>79087</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5962,39 +5927,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>461687</v>
+        <v>461776</v>
       </c>
       <c r="R50" t="n">
-        <v>6780875</v>
+        <v>6780976</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6041,7 +6004,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>2 bilder</t>
+          <t>3 bilder, rikligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6050,6 +6013,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6068,10 +6032,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129970813</v>
+        <v>129973137</v>
       </c>
       <c r="B51" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6079,21 +6043,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6103,10 +6067,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461800</v>
+        <v>461609</v>
       </c>
       <c r="R51" t="n">
-        <v>6781016</v>
+        <v>6780949</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6149,6 +6113,11 @@
       <c r="AB51" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>3 bilder, rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6175,10 +6144,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129971290</v>
+        <v>129972233</v>
       </c>
       <c r="B52" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6186,34 +6155,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461751</v>
+        <v>461679</v>
       </c>
       <c r="R52" t="n">
-        <v>6780936</v>
+        <v>6780885</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6256,6 +6233,11 @@
       <c r="AB52" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6282,10 +6264,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129972983</v>
+        <v>129972454</v>
       </c>
       <c r="B53" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6293,16 +6275,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6313,7 +6295,7 @@
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6322,10 +6304,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>461615</v>
+        <v>461687</v>
       </c>
       <c r="R53" t="n">
-        <v>6780923</v>
+        <v>6780875</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6368,6 +6350,11 @@
       <c r="AB53" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>2 bilder</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6394,10 +6381,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129970961</v>
+        <v>129969692</v>
       </c>
       <c r="B54" t="n">
-        <v>79677</v>
+        <v>57737</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6405,34 +6392,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>461789</v>
+        <v>461799</v>
       </c>
       <c r="R54" t="n">
-        <v>6780961</v>
+        <v>6780979</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6475,6 +6467,11 @@
       <c r="AB54" t="inlineStr">
         <is>
           <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 58003-2025 artfynd.xlsx
+++ b/artfynd/A 58003-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129973732</v>
+        <v>129969590</v>
       </c>
       <c r="B2" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461665</v>
+        <v>461816</v>
       </c>
       <c r="R2" t="n">
-        <v>6780925</v>
+        <v>6780978</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129969590</v>
+        <v>129973732</v>
       </c>
       <c r="B3" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,39 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461816</v>
+        <v>461665</v>
       </c>
       <c r="R3" t="n">
-        <v>6780978</v>
+        <v>6780925</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -2193,10 +2193,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129971127</v>
+        <v>129971608</v>
       </c>
       <c r="B16" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2204,21 +2204,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461762</v>
+        <v>461733</v>
       </c>
       <c r="R16" t="n">
-        <v>6780940</v>
+        <v>6780958</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2300,10 +2300,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129971608</v>
+        <v>129971127</v>
       </c>
       <c r="B17" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2311,21 +2311,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461733</v>
+        <v>461762</v>
       </c>
       <c r="R17" t="n">
-        <v>6780958</v>
+        <v>6780940</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2519,45 +2519,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129971589</v>
+        <v>129972802</v>
       </c>
       <c r="B19" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461736</v>
+        <v>461611</v>
       </c>
       <c r="R19" t="n">
-        <v>6780931</v>
+        <v>6780900</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2626,7 +2631,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129972800</v>
+        <v>129971589</v>
       </c>
       <c r="B20" t="n">
         <v>79087</v>
@@ -2661,10 +2666,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461611</v>
+        <v>461736</v>
       </c>
       <c r="R20" t="n">
-        <v>6780900</v>
+        <v>6780931</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2733,40 +2738,35 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129972802</v>
+        <v>129972800</v>
       </c>
       <c r="B21" t="n">
-        <v>8451</v>
+        <v>79087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
@@ -3609,50 +3609,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129971587</v>
+        <v>129970675</v>
       </c>
       <c r="B29" t="n">
-        <v>8451</v>
+        <v>79706</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461736</v>
+        <v>461789</v>
       </c>
       <c r="R29" t="n">
-        <v>6780931</v>
+        <v>6780961</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3721,7 +3716,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129972990</v>
+        <v>129971587</v>
       </c>
       <c r="B30" t="n">
         <v>8451</v>
@@ -3761,10 +3756,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461615</v>
+        <v>461736</v>
       </c>
       <c r="R30" t="n">
-        <v>6780923</v>
+        <v>6780931</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3833,45 +3828,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129970675</v>
+        <v>129972990</v>
       </c>
       <c r="B31" t="n">
-        <v>79706</v>
+        <v>8451</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461789</v>
+        <v>461615</v>
       </c>
       <c r="R31" t="n">
-        <v>6780961</v>
+        <v>6780923</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4271,10 +4271,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129971832</v>
+        <v>129970828</v>
       </c>
       <c r="B35" t="n">
-        <v>79087</v>
+        <v>78844</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4282,21 +4282,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4306,10 +4306,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461686</v>
+        <v>461800</v>
       </c>
       <c r="R35" t="n">
-        <v>6780923</v>
+        <v>6781016</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4378,10 +4378,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129970828</v>
+        <v>129971832</v>
       </c>
       <c r="B36" t="n">
-        <v>78844</v>
+        <v>79087</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4389,21 +4389,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461800</v>
+        <v>461686</v>
       </c>
       <c r="R36" t="n">
-        <v>6781016</v>
+        <v>6780923</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4485,10 +4485,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129971259</v>
+        <v>129971739</v>
       </c>
       <c r="B37" t="n">
-        <v>57737</v>
+        <v>79677</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4496,39 +4496,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461751</v>
+        <v>461741</v>
       </c>
       <c r="R37" t="n">
-        <v>6780936</v>
+        <v>6780920</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4811,10 +4806,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129971739</v>
+        <v>129971259</v>
       </c>
       <c r="B40" t="n">
-        <v>79677</v>
+        <v>57737</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4822,34 +4817,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461741</v>
+        <v>461751</v>
       </c>
       <c r="R40" t="n">
-        <v>6780920</v>
+        <v>6780936</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -6032,10 +6032,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129973137</v>
+        <v>129969692</v>
       </c>
       <c r="B51" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6043,34 +6043,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461609</v>
+        <v>461799</v>
       </c>
       <c r="R51" t="n">
-        <v>6780949</v>
+        <v>6780979</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6117,7 +6122,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>3 bilder, rikligt i en radie av ca 50 meter</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6381,10 +6386,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129969692</v>
+        <v>129973137</v>
       </c>
       <c r="B54" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6392,39 +6397,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>461799</v>
+        <v>461609</v>
       </c>
       <c r="R54" t="n">
-        <v>6780979</v>
+        <v>6780949</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6471,7 +6471,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>3 bilder, rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 58003-2025 artfynd.xlsx
+++ b/artfynd/A 58003-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129969590</v>
+        <v>129973732</v>
       </c>
       <c r="B2" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461816</v>
+        <v>461665</v>
       </c>
       <c r="R2" t="n">
-        <v>6780978</v>
+        <v>6780925</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129973732</v>
+        <v>129969590</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461665</v>
+        <v>461816</v>
       </c>
       <c r="R3" t="n">
-        <v>6780925</v>
+        <v>6780978</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
         <v>129971610</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>129970747</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>129971802</v>
       </c>
       <c r="B6" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129972961</v>
+        <v>129971607</v>
       </c>
       <c r="B8" t="n">
-        <v>79087</v>
+        <v>79678</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,21 +1338,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461615</v>
+        <v>461733</v>
       </c>
       <c r="R8" t="n">
-        <v>6780923</v>
+        <v>6780958</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1546,47 +1546,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129971831</v>
+        <v>129972961</v>
       </c>
       <c r="B10" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461686</v>
+        <v>461615</v>
       </c>
       <c r="R10" t="n">
         <v>6780923</v>
@@ -1658,45 +1653,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129971607</v>
+        <v>129971831</v>
       </c>
       <c r="B11" t="n">
-        <v>79677</v>
+        <v>8451</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461733</v>
+        <v>461686</v>
       </c>
       <c r="R11" t="n">
-        <v>6780958</v>
+        <v>6780923</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1768,7 +1768,7 @@
         <v>129970971</v>
       </c>
       <c r="B12" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>129971787</v>
       </c>
       <c r="B13" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>129971115</v>
       </c>
       <c r="B14" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2086,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129973851</v>
+        <v>129971608</v>
       </c>
       <c r="B15" t="n">
-        <v>79087</v>
+        <v>79707</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,21 +2097,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461730</v>
+        <v>461733</v>
       </c>
       <c r="R15" t="n">
-        <v>6780969</v>
+        <v>6780958</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2193,10 +2193,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129971608</v>
+        <v>129971127</v>
       </c>
       <c r="B16" t="n">
-        <v>79706</v>
+        <v>79088</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2204,21 +2204,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461733</v>
+        <v>461762</v>
       </c>
       <c r="R16" t="n">
-        <v>6780958</v>
+        <v>6780940</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2300,10 +2300,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129971127</v>
+        <v>129973851</v>
       </c>
       <c r="B17" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461762</v>
+        <v>461730</v>
       </c>
       <c r="R17" t="n">
-        <v>6780940</v>
+        <v>6780969</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2519,50 +2519,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129972802</v>
+        <v>129971589</v>
       </c>
       <c r="B19" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461611</v>
+        <v>461736</v>
       </c>
       <c r="R19" t="n">
-        <v>6780900</v>
+        <v>6780931</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2631,10 +2626,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129971589</v>
+        <v>129972800</v>
       </c>
       <c r="B20" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2666,10 +2661,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461736</v>
+        <v>461611</v>
       </c>
       <c r="R20" t="n">
-        <v>6780931</v>
+        <v>6780900</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2738,35 +2733,40 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129972800</v>
+        <v>129972802</v>
       </c>
       <c r="B21" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
@@ -2848,7 +2848,7 @@
         <v>129971741</v>
       </c>
       <c r="B22" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>129970829</v>
       </c>
       <c r="B23" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3283,10 +3283,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129972457</v>
+        <v>129972394</v>
       </c>
       <c r="B26" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3318,10 +3318,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461687</v>
+        <v>461679</v>
       </c>
       <c r="R26" t="n">
-        <v>6780875</v>
+        <v>6780885</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3390,10 +3390,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129972394</v>
+        <v>129972457</v>
       </c>
       <c r="B27" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3425,10 +3425,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461679</v>
+        <v>461687</v>
       </c>
       <c r="R27" t="n">
-        <v>6780885</v>
+        <v>6780875</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3612,7 +3612,7 @@
         <v>129970675</v>
       </c>
       <c r="B29" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3716,38 +3716,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129971587</v>
+        <v>129972793</v>
       </c>
       <c r="B30" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3756,10 +3756,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461736</v>
+        <v>461611</v>
       </c>
       <c r="R30" t="n">
-        <v>6780931</v>
+        <v>6780900</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3828,7 +3828,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129972990</v>
+        <v>129971587</v>
       </c>
       <c r="B31" t="n">
         <v>8451</v>
@@ -3868,10 +3868,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461615</v>
+        <v>461736</v>
       </c>
       <c r="R31" t="n">
-        <v>6780923</v>
+        <v>6780931</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3940,38 +3940,38 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129972793</v>
+        <v>129972990</v>
       </c>
       <c r="B32" t="n">
-        <v>57737</v>
+        <v>8451</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3980,10 +3980,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461611</v>
+        <v>461615</v>
       </c>
       <c r="R32" t="n">
-        <v>6780900</v>
+        <v>6780923</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4055,7 +4055,7 @@
         <v>129970738</v>
       </c>
       <c r="B33" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4271,10 +4271,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129970828</v>
+        <v>129971832</v>
       </c>
       <c r="B35" t="n">
-        <v>78844</v>
+        <v>79088</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4282,21 +4282,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4306,10 +4306,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461800</v>
+        <v>461686</v>
       </c>
       <c r="R35" t="n">
-        <v>6781016</v>
+        <v>6780923</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4378,10 +4378,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129971832</v>
+        <v>129970828</v>
       </c>
       <c r="B36" t="n">
-        <v>79087</v>
+        <v>78845</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4389,21 +4389,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461686</v>
+        <v>461800</v>
       </c>
       <c r="R36" t="n">
-        <v>6780923</v>
+        <v>6781016</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4485,10 +4485,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129971739</v>
+        <v>129973978</v>
       </c>
       <c r="B37" t="n">
-        <v>79677</v>
+        <v>79088</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4496,21 +4496,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4520,10 +4520,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461741</v>
+        <v>461749</v>
       </c>
       <c r="R37" t="n">
-        <v>6780920</v>
+        <v>6780997</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4592,10 +4592,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129973978</v>
+        <v>129971804</v>
       </c>
       <c r="B38" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4627,10 +4627,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461749</v>
+        <v>461709</v>
       </c>
       <c r="R38" t="n">
-        <v>6780997</v>
+        <v>6780921</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4699,10 +4699,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129971804</v>
+        <v>129971259</v>
       </c>
       <c r="B39" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4710,34 +4710,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461709</v>
+        <v>461751</v>
       </c>
       <c r="R39" t="n">
-        <v>6780921</v>
+        <v>6780936</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4806,10 +4811,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129971259</v>
+        <v>129971739</v>
       </c>
       <c r="B40" t="n">
-        <v>57737</v>
+        <v>79678</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4817,39 +4822,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461751</v>
+        <v>461741</v>
       </c>
       <c r="R40" t="n">
-        <v>6780936</v>
+        <v>6780920</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4921,7 +4921,7 @@
         <v>129970813</v>
       </c>
       <c r="B41" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>129971290</v>
       </c>
       <c r="B42" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>129970961</v>
       </c>
       <c r="B44" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
         <v>129972707</v>
       </c>
       <c r="B45" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>129971438</v>
       </c>
       <c r="B46" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>129972538</v>
       </c>
       <c r="B47" t="n">
-        <v>91626</v>
+        <v>91627</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
         <v>129969625</v>
       </c>
       <c r="B49" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5919,7 +5919,7 @@
         <v>129970888</v>
       </c>
       <c r="B50" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6032,10 +6032,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129969692</v>
+        <v>129973137</v>
       </c>
       <c r="B51" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6043,39 +6043,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461799</v>
+        <v>461609</v>
       </c>
       <c r="R51" t="n">
-        <v>6780979</v>
+        <v>6780949</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6122,7 +6117,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>3 bilder, rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6269,10 +6264,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129972454</v>
+        <v>129969692</v>
       </c>
       <c r="B53" t="n">
-        <v>57740</v>
+        <v>57737</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6280,16 +6275,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6309,10 +6304,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>461687</v>
+        <v>461799</v>
       </c>
       <c r="R53" t="n">
-        <v>6780875</v>
+        <v>6780979</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6359,7 +6354,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>2 bilder</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6386,10 +6381,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129973137</v>
+        <v>129972454</v>
       </c>
       <c r="B54" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6397,34 +6392,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>461609</v>
+        <v>461687</v>
       </c>
       <c r="R54" t="n">
-        <v>6780949</v>
+        <v>6780875</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6471,7 +6471,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>3 bilder, rikligt i en radie av ca 50 meter</t>
+          <t>2 bilder</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 58003-2025 artfynd.xlsx
+++ b/artfynd/A 58003-2025 artfynd.xlsx
@@ -1434,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129973829</v>
+        <v>129972961</v>
       </c>
       <c r="B9" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,39 +1445,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461730</v>
+        <v>461615</v>
       </c>
       <c r="R9" t="n">
-        <v>6780969</v>
+        <v>6780923</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129972961</v>
+        <v>129973829</v>
       </c>
       <c r="B10" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,34 +1552,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461615</v>
+        <v>461730</v>
       </c>
       <c r="R10" t="n">
-        <v>6780923</v>
+        <v>6780969</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -4918,10 +4918,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129970813</v>
+        <v>129971290</v>
       </c>
       <c r="B41" t="n">
-        <v>79707</v>
+        <v>79088</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4929,21 +4929,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4953,10 +4953,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461800</v>
+        <v>461751</v>
       </c>
       <c r="R41" t="n">
-        <v>6781016</v>
+        <v>6780936</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5025,10 +5025,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129971290</v>
+        <v>129972983</v>
       </c>
       <c r="B42" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5036,34 +5036,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461751</v>
+        <v>461615</v>
       </c>
       <c r="R42" t="n">
-        <v>6780936</v>
+        <v>6780923</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5132,10 +5137,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129972983</v>
+        <v>129970813</v>
       </c>
       <c r="B43" t="n">
-        <v>57737</v>
+        <v>79707</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5143,39 +5148,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461615</v>
+        <v>461800</v>
       </c>
       <c r="R43" t="n">
-        <v>6780923</v>
+        <v>6781016</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 58003-2025 artfynd.xlsx
+++ b/artfynd/A 58003-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129973732</v>
       </c>
       <c r="B2" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>129971610</v>
       </c>
       <c r="B4" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>129970747</v>
       </c>
       <c r="B5" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>129971802</v>
       </c>
       <c r="B6" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129971607</v>
+        <v>129972961</v>
       </c>
       <c r="B8" t="n">
-        <v>79678</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,21 +1338,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461733</v>
+        <v>461615</v>
       </c>
       <c r="R8" t="n">
-        <v>6780958</v>
+        <v>6780923</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129972961</v>
+        <v>129971607</v>
       </c>
       <c r="B9" t="n">
-        <v>79088</v>
+        <v>79679</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,21 +1445,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461615</v>
+        <v>461733</v>
       </c>
       <c r="R9" t="n">
-        <v>6780923</v>
+        <v>6780958</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1768,7 +1768,7 @@
         <v>129970971</v>
       </c>
       <c r="B12" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129971787</v>
+        <v>129971115</v>
       </c>
       <c r="B13" t="n">
-        <v>79707</v>
+        <v>79679</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,21 +1883,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461741</v>
+        <v>461762</v>
       </c>
       <c r="R13" t="n">
-        <v>6780920</v>
+        <v>6780940</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1979,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129971115</v>
+        <v>129971787</v>
       </c>
       <c r="B14" t="n">
-        <v>79678</v>
+        <v>79708</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1990,21 +1990,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461762</v>
+        <v>461741</v>
       </c>
       <c r="R14" t="n">
-        <v>6780940</v>
+        <v>6780920</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2086,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129971608</v>
+        <v>129973851</v>
       </c>
       <c r="B15" t="n">
-        <v>79707</v>
+        <v>79089</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,21 +2097,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461733</v>
+        <v>461730</v>
       </c>
       <c r="R15" t="n">
-        <v>6780958</v>
+        <v>6780969</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2196,7 +2196,7 @@
         <v>129971127</v>
       </c>
       <c r="B16" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2300,10 +2300,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129973851</v>
+        <v>129971608</v>
       </c>
       <c r="B17" t="n">
-        <v>79088</v>
+        <v>79708</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2311,21 +2311,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461730</v>
+        <v>461733</v>
       </c>
       <c r="R17" t="n">
-        <v>6780969</v>
+        <v>6780958</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2519,10 +2519,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129971589</v>
+        <v>129972800</v>
       </c>
       <c r="B19" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2554,10 +2554,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461736</v>
+        <v>461611</v>
       </c>
       <c r="R19" t="n">
-        <v>6780931</v>
+        <v>6780900</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2626,10 +2626,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129972800</v>
+        <v>129971589</v>
       </c>
       <c r="B20" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461611</v>
+        <v>461736</v>
       </c>
       <c r="R20" t="n">
-        <v>6780900</v>
+        <v>6780931</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2848,7 +2848,7 @@
         <v>129971741</v>
       </c>
       <c r="B22" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2952,50 +2952,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129972234</v>
+        <v>129970829</v>
       </c>
       <c r="B23" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461679</v>
+        <v>461800</v>
       </c>
       <c r="R23" t="n">
-        <v>6780885</v>
+        <v>6781016</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3064,7 +3059,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129973842</v>
+        <v>129972234</v>
       </c>
       <c r="B24" t="n">
         <v>8451</v>
@@ -3104,10 +3099,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461730</v>
+        <v>461679</v>
       </c>
       <c r="R24" t="n">
-        <v>6780969</v>
+        <v>6780885</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3176,45 +3171,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129970829</v>
+        <v>129973842</v>
       </c>
       <c r="B25" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461800</v>
+        <v>461730</v>
       </c>
       <c r="R25" t="n">
-        <v>6781016</v>
+        <v>6780969</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3286,7 +3286,7 @@
         <v>129972394</v>
       </c>
       <c r="B26" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>129972457</v>
       </c>
       <c r="B27" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>129970675</v>
       </c>
       <c r="B29" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4052,10 +4052,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129970738</v>
+        <v>129971825</v>
       </c>
       <c r="B33" t="n">
-        <v>79707</v>
+        <v>57737</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4063,34 +4063,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461799</v>
+        <v>461686</v>
       </c>
       <c r="R33" t="n">
-        <v>6780979</v>
+        <v>6780923</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4159,10 +4164,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129971825</v>
+        <v>129970738</v>
       </c>
       <c r="B34" t="n">
-        <v>57737</v>
+        <v>79708</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4170,39 +4175,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461686</v>
+        <v>461799</v>
       </c>
       <c r="R34" t="n">
-        <v>6780923</v>
+        <v>6780979</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4271,10 +4271,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129971832</v>
+        <v>129970828</v>
       </c>
       <c r="B35" t="n">
-        <v>79088</v>
+        <v>78846</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4282,21 +4282,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4306,10 +4306,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461686</v>
+        <v>461800</v>
       </c>
       <c r="R35" t="n">
-        <v>6780923</v>
+        <v>6781016</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4378,10 +4378,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129970828</v>
+        <v>129971832</v>
       </c>
       <c r="B36" t="n">
-        <v>78845</v>
+        <v>79089</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4389,21 +4389,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461800</v>
+        <v>461686</v>
       </c>
       <c r="R36" t="n">
-        <v>6781016</v>
+        <v>6780923</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4488,7 +4488,7 @@
         <v>129973978</v>
       </c>
       <c r="B37" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>129971804</v>
       </c>
       <c r="B38" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>129971739</v>
       </c>
       <c r="B40" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4918,10 +4918,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129971290</v>
+        <v>129970813</v>
       </c>
       <c r="B41" t="n">
-        <v>79088</v>
+        <v>79708</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4929,21 +4929,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4953,10 +4953,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461751</v>
+        <v>461800</v>
       </c>
       <c r="R41" t="n">
-        <v>6780936</v>
+        <v>6781016</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5025,10 +5025,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129970961</v>
+        <v>129971290</v>
       </c>
       <c r="B42" t="n">
-        <v>79678</v>
+        <v>79089</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5036,21 +5036,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5060,10 +5060,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461789</v>
+        <v>461751</v>
       </c>
       <c r="R42" t="n">
-        <v>6780961</v>
+        <v>6780936</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5132,10 +5132,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129970813</v>
+        <v>129972983</v>
       </c>
       <c r="B43" t="n">
-        <v>79707</v>
+        <v>57737</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5143,34 +5143,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461800</v>
+        <v>461615</v>
       </c>
       <c r="R43" t="n">
-        <v>6781016</v>
+        <v>6780923</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5239,10 +5244,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129972983</v>
+        <v>129970961</v>
       </c>
       <c r="B44" t="n">
-        <v>57737</v>
+        <v>79679</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5250,39 +5255,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461615</v>
+        <v>461789</v>
       </c>
       <c r="R44" t="n">
-        <v>6780923</v>
+        <v>6780961</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5354,7 +5354,7 @@
         <v>129972707</v>
       </c>
       <c r="B45" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>129971438</v>
       </c>
       <c r="B46" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>129972538</v>
       </c>
       <c r="B47" t="n">
-        <v>91627</v>
+        <v>91644</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
         <v>129969625</v>
       </c>
       <c r="B49" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5919,7 +5919,7 @@
         <v>129970888</v>
       </c>
       <c r="B50" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
         <v>129973137</v>
       </c>
       <c r="B51" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129972233</v>
+        <v>129969692</v>
       </c>
       <c r="B52" t="n">
         <v>57737</v>
@@ -6173,24 +6173,21 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461679</v>
+        <v>461799</v>
       </c>
       <c r="R52" t="n">
-        <v>6780885</v>
+        <v>6780979</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6264,7 +6261,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129969692</v>
+        <v>129972233</v>
       </c>
       <c r="B53" t="n">
         <v>57737</v>
@@ -6293,21 +6290,24 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>461799</v>
+        <v>461679</v>
       </c>
       <c r="R53" t="n">
-        <v>6780979</v>
+        <v>6780885</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6605,7 +6605,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130087516</v>
+        <v>130087228</v>
       </c>
       <c r="B56" t="n">
         <v>8451</v>
@@ -6634,24 +6634,19 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461956</v>
+        <v>461948</v>
       </c>
       <c r="R56" t="n">
-        <v>6780787</v>
+        <v>6780740</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6829,7 +6824,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130087228</v>
+        <v>130087516</v>
       </c>
       <c r="B58" t="n">
         <v>8451</v>
@@ -6858,19 +6853,24 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461948</v>
+        <v>461956</v>
       </c>
       <c r="R58" t="n">
-        <v>6780740</v>
+        <v>6780787</v>
       </c>
       <c r="S58" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7043,53 +7043,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130092086</v>
+        <v>130084138</v>
       </c>
       <c r="B60" t="n">
-        <v>57740</v>
+        <v>91607</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>4660</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461986</v>
+        <v>461712</v>
       </c>
       <c r="R60" t="n">
-        <v>6780804</v>
+        <v>6780836</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7119,14 +7111,24 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7141,57 +7143,57 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130084138</v>
+        <v>130084991</v>
       </c>
       <c r="B61" t="n">
-        <v>91607</v>
+        <v>79121</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4660</v>
+        <v>185</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>461712</v>
+        <v>461840</v>
       </c>
       <c r="R61" t="n">
-        <v>6780836</v>
+        <v>6780854</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7223,7 +7225,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7233,12 +7235,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Sparsamt på gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7253,22 +7255,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130084991</v>
+        <v>130087559</v>
       </c>
       <c r="B62" t="n">
-        <v>79121</v>
+        <v>57737</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7276,34 +7278,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>461840</v>
+        <v>461970</v>
       </c>
       <c r="R62" t="n">
-        <v>6780854</v>
+        <v>6780823</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7335,7 +7342,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7345,12 +7352,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:27</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Sparsamt på gran</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7365,22 +7367,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130087559</v>
+        <v>130092086</v>
       </c>
       <c r="B63" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7388,16 +7390,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7406,21 +7408,24 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461970</v>
+        <v>461986</v>
       </c>
       <c r="R63" t="n">
-        <v>6780823</v>
+        <v>6780804</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7450,19 +7455,14 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>13:03</t>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7477,53 +7477,52 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130092205</v>
+        <v>130092209</v>
       </c>
       <c r="B64" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -7577,7 +7576,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7596,10 +7594,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130092209</v>
+        <v>130087919</v>
       </c>
       <c r="B65" t="n">
-        <v>57737</v>
+        <v>79089</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7607,42 +7605,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>461965</v>
+        <v>461853</v>
       </c>
       <c r="R65" t="n">
-        <v>6780759</v>
+        <v>6780990</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7672,9 +7662,19 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7689,12 +7689,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7808,45 +7808,54 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130087919</v>
+        <v>130092205</v>
       </c>
       <c r="B67" t="n">
-        <v>79089</v>
+        <v>8451</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>461853</v>
+        <v>461965</v>
       </c>
       <c r="R67" t="n">
-        <v>6780990</v>
+        <v>6780759</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7876,46 +7885,37 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130087669</v>
+        <v>130086991</v>
       </c>
       <c r="B68" t="n">
         <v>79089</v>
@@ -7950,13 +7950,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>461929</v>
+        <v>461939</v>
       </c>
       <c r="R68" t="n">
-        <v>6780891</v>
+        <v>6780857</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7996,6 +7996,11 @@
       <c r="AB68" t="inlineStr">
         <is>
           <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>2 bild. Rikligt till måttligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8022,10 +8027,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130087716</v>
+        <v>130092026</v>
       </c>
       <c r="B69" t="n">
-        <v>79708</v>
+        <v>78846</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8033,34 +8038,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>461894</v>
+        <v>461858</v>
       </c>
       <c r="R69" t="n">
-        <v>6780914</v>
+        <v>6780846</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8090,49 +8098,40 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130087512</v>
+        <v>130087492</v>
       </c>
       <c r="B70" t="n">
-        <v>57737</v>
+        <v>79089</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8140,39 +8139,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>461956</v>
+        <v>461944</v>
       </c>
       <c r="R70" t="n">
-        <v>6780787</v>
+        <v>6780796</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8241,7 +8235,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130087492</v>
+        <v>130087119</v>
       </c>
       <c r="B71" t="n">
         <v>79089</v>
@@ -8276,13 +8270,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>461944</v>
+        <v>461918</v>
       </c>
       <c r="R71" t="n">
-        <v>6780796</v>
+        <v>6780787</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8322,6 +8316,11 @@
       <c r="AB71" t="inlineStr">
         <is>
           <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8348,7 +8347,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130086991</v>
+        <v>130087669</v>
       </c>
       <c r="B72" t="n">
         <v>79089</v>
@@ -8383,13 +8382,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>461939</v>
+        <v>461929</v>
       </c>
       <c r="R72" t="n">
-        <v>6780857</v>
+        <v>6780891</v>
       </c>
       <c r="S72" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8429,11 +8428,6 @@
       <c r="AB72" t="inlineStr">
         <is>
           <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>2 bild. Rikligt till måttligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8460,10 +8454,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130087119</v>
+        <v>130087716</v>
       </c>
       <c r="B73" t="n">
-        <v>79089</v>
+        <v>79708</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8471,21 +8465,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8495,13 +8489,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>461918</v>
+        <v>461894</v>
       </c>
       <c r="R73" t="n">
-        <v>6780787</v>
+        <v>6780914</v>
       </c>
       <c r="S73" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8541,11 +8535,6 @@
       <c r="AB73" t="inlineStr">
         <is>
           <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8572,10 +8561,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130085288</v>
+        <v>130087512</v>
       </c>
       <c r="B74" t="n">
-        <v>92106</v>
+        <v>57737</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8583,37 +8572,42 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5467</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>461858</v>
+        <v>461956</v>
       </c>
       <c r="R74" t="n">
-        <v>6780876</v>
+        <v>6780787</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8642,7 +8636,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8652,7 +8646,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8667,22 +8661,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130092026</v>
+        <v>130085288</v>
       </c>
       <c r="B75" t="n">
-        <v>78846</v>
+        <v>92106</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8690,40 +8684,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>5467</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
         <v>461858</v>
       </c>
       <c r="R75" t="n">
-        <v>6780846</v>
+        <v>6780876</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8750,18 +8741,27 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8773,14 +8773,14 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130092389</v>
+        <v>130087222</v>
       </c>
       <c r="B76" t="n">
         <v>8451</v>
@@ -8809,25 +8809,21 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>461870</v>
+        <v>462001</v>
       </c>
       <c r="R76" t="n">
-        <v>6780967</v>
+        <v>6780764</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8857,18 +8853,32 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Äldre spår I tallåga</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8880,44 +8890,50 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130090003</v>
+        <v>130092389</v>
       </c>
       <c r="B77" t="n">
-        <v>91911</v>
+        <v>8451</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>71</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fomitopsis infirma</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Miettinen &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -8925,10 +8941,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>461851</v>
+        <v>461870</v>
       </c>
       <c r="R77" t="n">
-        <v>6780877</v>
+        <v>6780967</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8976,19 +8992,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130087222</v>
+        <v>130087245</v>
       </c>
       <c r="B78" t="n">
         <v>8451</v>
@@ -9017,24 +9033,19 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>462001</v>
+        <v>461946</v>
       </c>
       <c r="R78" t="n">
-        <v>6780764</v>
+        <v>6780867</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9063,7 +9074,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9073,12 +9084,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:46</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Äldre spår I tallåga</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9093,60 +9099,60 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130087245</v>
+        <v>130086767</v>
       </c>
       <c r="B79" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>461946</v>
+        <v>461850</v>
       </c>
       <c r="R79" t="n">
-        <v>6780867</v>
+        <v>6780913</v>
       </c>
       <c r="S79" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9175,7 +9181,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9185,7 +9191,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>2 bild. Rikligt till måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9200,12 +9211,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9324,10 +9335,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130086767</v>
+        <v>130087408</v>
       </c>
       <c r="B81" t="n">
-        <v>79089</v>
+        <v>57737</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9335,34 +9346,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>461850</v>
+        <v>462039</v>
       </c>
       <c r="R81" t="n">
-        <v>6780913</v>
+        <v>6780770</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9405,11 +9421,6 @@
       <c r="AB81" t="inlineStr">
         <is>
           <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>2 bild. Rikligt till måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9436,10 +9447,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130087408</v>
+        <v>130092215</v>
       </c>
       <c r="B82" t="n">
-        <v>57737</v>
+        <v>78847</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9447,39 +9458,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>462039</v>
+        <v>462002</v>
       </c>
       <c r="R82" t="n">
-        <v>6780770</v>
+        <v>6780772</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9509,39 +9518,30 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -9655,10 +9655,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130085198</v>
+        <v>130086966</v>
       </c>
       <c r="B84" t="n">
-        <v>81074</v>
+        <v>57740</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9666,37 +9666,42 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1049</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>461857</v>
+        <v>461946</v>
       </c>
       <c r="R84" t="n">
-        <v>6780842</v>
+        <v>6780867</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9725,7 +9730,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9735,7 +9740,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9750,62 +9760,57 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130086588</v>
+        <v>130085198</v>
       </c>
       <c r="B85" t="n">
-        <v>8451</v>
+        <v>81074</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>1049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>461880</v>
+        <v>461857</v>
       </c>
       <c r="R85" t="n">
-        <v>6780838</v>
+        <v>6780842</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9874,53 +9879,53 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130086966</v>
+        <v>130086588</v>
       </c>
       <c r="B86" t="n">
-        <v>57740</v>
+        <v>8451</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>461946</v>
+        <v>461880</v>
       </c>
       <c r="R86" t="n">
-        <v>6780867</v>
+        <v>6780838</v>
       </c>
       <c r="S86" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9949,7 +9954,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9959,12 +9964,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:17</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9979,22 +9979,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130092215</v>
+        <v>130091631</v>
       </c>
       <c r="B87" t="n">
-        <v>78847</v>
+        <v>79121</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10002,21 +10002,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10029,10 +10029,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>462002</v>
+        <v>461750</v>
       </c>
       <c r="R87" t="n">
-        <v>6780772</v>
+        <v>6781031</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10092,10 +10092,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130087832</v>
+        <v>130086497</v>
       </c>
       <c r="B88" t="n">
-        <v>79089</v>
+        <v>90655</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10103,34 +10103,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>461873</v>
+        <v>461865</v>
       </c>
       <c r="R88" t="n">
-        <v>6780961</v>
+        <v>6780909</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10162,7 +10162,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10172,7 +10172,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>På en bränd tallåga</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10187,66 +10192,57 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130091811</v>
+        <v>130085215</v>
       </c>
       <c r="B89" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>461716</v>
+        <v>461844</v>
       </c>
       <c r="R89" t="n">
-        <v>6780852</v>
+        <v>6780835</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10276,40 +10272,49 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>130091631</v>
+        <v>130087832</v>
       </c>
       <c r="B90" t="n">
-        <v>79121</v>
+        <v>79089</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10317,37 +10322,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>461750</v>
+        <v>461873</v>
       </c>
       <c r="R90" t="n">
-        <v>6781031</v>
+        <v>6780961</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10377,75 +10379,93 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>130086497</v>
+        <v>130091811</v>
       </c>
       <c r="B91" t="n">
-        <v>90655</v>
+        <v>8451</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1962</v>
+        <v>106545</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>461865</v>
+        <v>461716</v>
       </c>
       <c r="R91" t="n">
-        <v>6780909</v>
+        <v>6780852</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10475,54 +10495,40 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>12:38</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>På en bränd tallåga</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>130085215</v>
+        <v>130092368</v>
       </c>
       <c r="B92" t="n">
-        <v>79089</v>
+        <v>57737</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10530,34 +10536,42 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>461844</v>
+        <v>461867</v>
       </c>
       <c r="R92" t="n">
-        <v>6780835</v>
+        <v>6780956</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10587,19 +10601,9 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>10:14</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10614,62 +10618,65 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>130082759</v>
+        <v>130092059</v>
       </c>
       <c r="B93" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>461757</v>
+        <v>461946</v>
       </c>
       <c r="R93" t="n">
-        <v>6781096</v>
+        <v>6780839</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10699,19 +10706,9 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>10:14</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10726,65 +10723,62 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130092368</v>
+        <v>130082759</v>
       </c>
       <c r="B94" t="n">
-        <v>57737</v>
+        <v>8451</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>461867</v>
+        <v>461757</v>
       </c>
       <c r="R94" t="n">
-        <v>6780956</v>
+        <v>6781096</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10814,9 +10808,19 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10831,65 +10835,62 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>130092059</v>
+        <v>130086721</v>
       </c>
       <c r="B95" t="n">
-        <v>57737</v>
+        <v>8451</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>461946</v>
+        <v>461832</v>
       </c>
       <c r="R95" t="n">
-        <v>6780839</v>
+        <v>6780916</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10919,9 +10920,24 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Äldre spår i torrtall</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10936,62 +10952,66 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>130085149</v>
+        <v>130092063</v>
       </c>
       <c r="B96" t="n">
-        <v>57737</v>
+        <v>8451</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>461857</v>
+        <v>461946</v>
       </c>
       <c r="R96" t="n">
-        <v>6780859</v>
+        <v>6780839</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11021,89 +11041,80 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Äldre spår i torrtall</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>130083753</v>
+        <v>130087850</v>
       </c>
       <c r="B97" t="n">
-        <v>79089</v>
+        <v>8451</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>461711</v>
+        <v>461873</v>
       </c>
       <c r="R97" t="n">
-        <v>6780852</v>
+        <v>6780961</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11135,7 +11146,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11145,7 +11156,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11172,50 +11183,48 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>130087850</v>
+        <v>130091794</v>
       </c>
       <c r="B98" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>461873</v>
+        <v>461710</v>
       </c>
       <c r="R98" t="n">
-        <v>6780961</v>
+        <v>6780886</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11245,46 +11254,37 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>130087798</v>
+        <v>130092053</v>
       </c>
       <c r="B99" t="n">
         <v>79089</v>
@@ -11313,16 +11313,19 @@
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>461864</v>
+        <v>461926</v>
       </c>
       <c r="R99" t="n">
-        <v>6780951</v>
+        <v>6780853</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11352,89 +11355,75 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>130086721</v>
+        <v>130083753</v>
       </c>
       <c r="B100" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>461832</v>
+        <v>461711</v>
       </c>
       <c r="R100" t="n">
-        <v>6780916</v>
+        <v>6780852</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11466,7 +11455,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11476,12 +11465,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Äldre spår i torrtall</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11496,66 +11480,57 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>130092063</v>
+        <v>130087798</v>
       </c>
       <c r="B101" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>461946</v>
+        <v>461864</v>
       </c>
       <c r="R101" t="n">
-        <v>6780839</v>
+        <v>6780951</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11585,40 +11560,49 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>130091794</v>
+        <v>130085149</v>
       </c>
       <c r="B102" t="n">
-        <v>79089</v>
+        <v>57737</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11626,37 +11610,39 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>461710</v>
+        <v>461857</v>
       </c>
       <c r="R102" t="n">
-        <v>6780886</v>
+        <v>6780859</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11686,37 +11672,51 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Äldre spår i torrtall</t>
+        </is>
+      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>130092053</v>
+        <v>130087184</v>
       </c>
       <c r="B103" t="n">
         <v>79089</v>
@@ -11745,22 +11745,19 @@
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>461926</v>
+        <v>461948</v>
       </c>
       <c r="R103" t="n">
-        <v>6780853</v>
+        <v>6780740</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11787,30 +11784,44 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+        </is>
+      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -11929,10 +11940,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>130087915</v>
+        <v>130091832</v>
       </c>
       <c r="B105" t="n">
-        <v>79708</v>
+        <v>79089</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11940,34 +11951,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>461853</v>
+        <v>461738</v>
       </c>
       <c r="R105" t="n">
-        <v>6780990</v>
+        <v>6780825</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11997,49 +12011,40 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>130091832</v>
+        <v>130087915</v>
       </c>
       <c r="B106" t="n">
-        <v>79089</v>
+        <v>79708</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12047,37 +12052,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>461738</v>
+        <v>461853</v>
       </c>
       <c r="R106" t="n">
-        <v>6780825</v>
+        <v>6780990</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12107,30 +12109,39 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -12244,54 +12255,50 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>130091828</v>
+        <v>130087727</v>
       </c>
       <c r="B108" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>461736</v>
+        <v>461894</v>
       </c>
       <c r="R108" t="n">
-        <v>6780844</v>
+        <v>6780914</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12321,67 +12328,82 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>130092019</v>
+        <v>130091828</v>
       </c>
       <c r="B109" t="n">
-        <v>78847</v>
+        <v>8451</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
@@ -12389,10 +12411,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>461858</v>
+        <v>461736</v>
       </c>
       <c r="R109" t="n">
-        <v>6780846</v>
+        <v>6780844</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12452,10 +12474,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>130087727</v>
+        <v>130092019</v>
       </c>
       <c r="B110" t="n">
-        <v>57737</v>
+        <v>78847</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12463,39 +12485,37 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>461894</v>
+        <v>461858</v>
       </c>
       <c r="R110" t="n">
-        <v>6780914</v>
+        <v>6780846</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12525,87 +12545,87 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>130087184</v>
+        <v>130092018</v>
       </c>
       <c r="B111" t="n">
-        <v>79089</v>
+        <v>8451</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>461948</v>
+        <v>461858</v>
       </c>
       <c r="R111" t="n">
-        <v>6780740</v>
+        <v>6780846</v>
       </c>
       <c r="S111" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12632,51 +12652,37 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
-        </is>
-      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>130092199</v>
+        <v>130091806</v>
       </c>
       <c r="B112" t="n">
         <v>8451</v>
@@ -12720,10 +12726,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>461976</v>
+        <v>461715</v>
       </c>
       <c r="R112" t="n">
-        <v>6780775</v>
+        <v>6780868</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12783,7 +12789,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>130091806</v>
+        <v>130092199</v>
       </c>
       <c r="B113" t="n">
         <v>8451</v>
@@ -12827,10 +12833,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>461715</v>
+        <v>461976</v>
       </c>
       <c r="R113" t="n">
-        <v>6780868</v>
+        <v>6780775</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12890,7 +12896,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>130091785</v>
+        <v>130082682</v>
       </c>
       <c r="B114" t="n">
         <v>79089</v>
@@ -12919,22 +12925,19 @@
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>461710</v>
+        <v>461767</v>
       </c>
       <c r="R114" t="n">
-        <v>6780938</v>
+        <v>6781054</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12961,73 +12964,81 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>3 bilder. Rikligt i en radie av ca 50 meter</t>
+        </is>
+      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>130092018</v>
+        <v>130092042</v>
       </c>
       <c r="B115" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -13035,10 +13046,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>461858</v>
+        <v>461850</v>
       </c>
       <c r="R115" t="n">
-        <v>6780846</v>
+        <v>6780907</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13098,7 +13109,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>130092042</v>
+        <v>130091785</v>
       </c>
       <c r="B116" t="n">
         <v>79089</v>
@@ -13136,10 +13147,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>461850</v>
+        <v>461710</v>
       </c>
       <c r="R116" t="n">
-        <v>6780907</v>
+        <v>6780938</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13199,7 +13210,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>130082682</v>
+        <v>130082810</v>
       </c>
       <c r="B117" t="n">
         <v>79089</v>
@@ -13234,13 +13245,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>461767</v>
+        <v>461757</v>
       </c>
       <c r="R117" t="n">
-        <v>6781054</v>
+        <v>6781096</v>
       </c>
       <c r="S117" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13280,11 +13291,6 @@
       <c r="AB117" t="inlineStr">
         <is>
           <t>10:14</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>3 bilder. Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13311,7 +13317,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>130082810</v>
+        <v>130087616</v>
       </c>
       <c r="B118" t="n">
         <v>79089</v>
@@ -13346,10 +13352,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>461757</v>
+        <v>461970</v>
       </c>
       <c r="R118" t="n">
-        <v>6781096</v>
+        <v>6780823</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13381,7 +13387,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13391,7 +13397,12 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13418,10 +13429,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>130087616</v>
+        <v>130087271</v>
       </c>
       <c r="B119" t="n">
-        <v>79089</v>
+        <v>79708</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13429,21 +13440,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13453,10 +13464,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>461970</v>
+        <v>462051</v>
       </c>
       <c r="R119" t="n">
-        <v>6780823</v>
+        <v>6780727</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13499,11 +13510,6 @@
       <c r="AB119" t="inlineStr">
         <is>
           <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13530,53 +13536,53 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>130085157</v>
+        <v>130087227</v>
       </c>
       <c r="B120" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="M120" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>461859</v>
+        <v>461948</v>
       </c>
       <c r="R120" t="n">
-        <v>6780861</v>
+        <v>6780740</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13605,7 +13611,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13615,7 +13621,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13630,22 +13636,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>130087271</v>
+        <v>130087844</v>
       </c>
       <c r="B121" t="n">
-        <v>79708</v>
+        <v>57737</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13653,34 +13659,39 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>462051</v>
+        <v>461873</v>
       </c>
       <c r="R121" t="n">
-        <v>6780727</v>
+        <v>6780961</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13749,53 +13760,53 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>130087227</v>
+        <v>130085157</v>
       </c>
       <c r="B122" t="n">
-        <v>57737</v>
+        <v>8451</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="M122" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>461948</v>
+        <v>461859</v>
       </c>
       <c r="R122" t="n">
-        <v>6780740</v>
+        <v>6780861</v>
       </c>
       <c r="S122" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13824,7 +13835,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13834,7 +13845,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13849,22 +13860,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>130087844</v>
+        <v>130092071</v>
       </c>
       <c r="B123" t="n">
-        <v>57737</v>
+        <v>91921</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13872,39 +13883,37 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>461873</v>
+        <v>461946</v>
       </c>
       <c r="R123" t="n">
-        <v>6780961</v>
+        <v>6780863</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13934,39 +13943,30 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
@@ -14080,32 +14080,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>130092122</v>
+        <v>130091843</v>
       </c>
       <c r="B125" t="n">
-        <v>79113</v>
+        <v>79089</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14118,10 +14118,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>461986</v>
+        <v>461720</v>
       </c>
       <c r="R125" t="n">
-        <v>6780804</v>
+        <v>6780825</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14181,10 +14181,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>130092139</v>
+        <v>130092122</v>
       </c>
       <c r="B126" t="n">
-        <v>8451</v>
+        <v>79113</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14192,32 +14192,26 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>106545</v>
+        <v>6434</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
@@ -14225,10 +14219,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>461975</v>
+        <v>461986</v>
       </c>
       <c r="R126" t="n">
-        <v>6780791</v>
+        <v>6780804</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14288,37 +14282,43 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>130091843</v>
+        <v>130092139</v>
       </c>
       <c r="B127" t="n">
-        <v>79089</v>
+        <v>8451</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
@@ -14326,10 +14326,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>461720</v>
+        <v>461975</v>
       </c>
       <c r="R127" t="n">
-        <v>6780825</v>
+        <v>6780791</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14389,10 +14389,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>130092071</v>
+        <v>130092033</v>
       </c>
       <c r="B128" t="n">
-        <v>91921</v>
+        <v>78847</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14400,21 +14400,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>658</v>
+        <v>228912</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14427,10 +14427,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>461946</v>
+        <v>461871</v>
       </c>
       <c r="R128" t="n">
-        <v>6780863</v>
+        <v>6780851</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14490,10 +14490,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>130092033</v>
+        <v>130091751</v>
       </c>
       <c r="B129" t="n">
-        <v>78847</v>
+        <v>79121</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14501,21 +14501,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14528,10 +14528,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>461871</v>
+        <v>461737</v>
       </c>
       <c r="R129" t="n">
-        <v>6780851</v>
+        <v>6781057</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14591,45 +14591,48 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>130087075</v>
+        <v>130091628</v>
       </c>
       <c r="B130" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>461944</v>
+        <v>461750</v>
       </c>
       <c r="R130" t="n">
-        <v>6780796</v>
+        <v>6781031</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14659,46 +14662,37 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD130" t="b">
         <v>0</v>
       </c>
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>130091628</v>
+        <v>130091745</v>
       </c>
       <c r="B131" t="n">
         <v>79089</v>
@@ -14736,7 +14730,7 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>461750</v>
+        <v>461749</v>
       </c>
       <c r="R131" t="n">
         <v>6781031</v>
@@ -14799,7 +14793,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>130091745</v>
+        <v>130086831</v>
       </c>
       <c r="B132" t="n">
         <v>79089</v>
@@ -14828,19 +14822,16 @@
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>461749</v>
+        <v>461887</v>
       </c>
       <c r="R132" t="n">
-        <v>6781031</v>
+        <v>6780890</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14870,78 +14861,84 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>130091751</v>
+        <v>130087075</v>
       </c>
       <c r="B133" t="n">
-        <v>79121</v>
+        <v>8451</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>461737</v>
+        <v>461944</v>
       </c>
       <c r="R133" t="n">
-        <v>6781057</v>
+        <v>6780796</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14971,30 +14968,39 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
@@ -15108,10 +15114,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>130083972</v>
+        <v>130091780</v>
       </c>
       <c r="B135" t="n">
-        <v>57737</v>
+        <v>79089</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15119,39 +15125,37 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>461717</v>
+        <v>461742</v>
       </c>
       <c r="R135" t="n">
-        <v>6780842</v>
+        <v>6781010</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15181,49 +15185,40 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AD135" t="b">
         <v>0</v>
       </c>
       <c r="AE135" t="b">
         <v>0</v>
       </c>
+      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>130085089</v>
+        <v>130082967</v>
       </c>
       <c r="B136" t="n">
-        <v>78847</v>
+        <v>79089</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15231,37 +15226,37 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>461857</v>
+        <v>461749</v>
       </c>
       <c r="R136" t="n">
-        <v>6780866</v>
+        <v>6781117</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15290,7 +15285,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15300,7 +15295,12 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>2 bilder. Rikligt till måttligt i en radie av 40 meter</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15315,62 +15315,57 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>130085214</v>
+        <v>130087722</v>
       </c>
       <c r="B137" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>461844</v>
+        <v>461894</v>
       </c>
       <c r="R137" t="n">
-        <v>6780835</v>
+        <v>6780914</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15402,7 +15397,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15412,7 +15407,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15439,10 +15434,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>130085207</v>
+        <v>130087061</v>
       </c>
       <c r="B138" t="n">
-        <v>57737</v>
+        <v>79089</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15450,39 +15445,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>461844</v>
+        <v>461952</v>
       </c>
       <c r="R138" t="n">
-        <v>6780835</v>
+        <v>6780820</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15514,7 +15504,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15524,7 +15514,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15551,7 +15541,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>130091780</v>
+        <v>130087445</v>
       </c>
       <c r="B139" t="n">
         <v>79089</v>
@@ -15580,22 +15570,19 @@
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>461742</v>
+        <v>462022</v>
       </c>
       <c r="R139" t="n">
-        <v>6781010</v>
+        <v>6780775</v>
       </c>
       <c r="S139" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -15622,40 +15609,54 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+        </is>
+      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>130082967</v>
+        <v>130085207</v>
       </c>
       <c r="B140" t="n">
-        <v>79089</v>
+        <v>57737</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15663,37 +15664,42 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>461749</v>
+        <v>461844</v>
       </c>
       <c r="R140" t="n">
-        <v>6781117</v>
+        <v>6780835</v>
       </c>
       <c r="S140" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -15733,11 +15739,6 @@
       <c r="AB140" t="inlineStr">
         <is>
           <t>10:14</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>2 bilder. Rikligt till måttligt i en radie av 40 meter</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15764,10 +15765,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>130087445</v>
+        <v>130087794</v>
       </c>
       <c r="B141" t="n">
-        <v>79089</v>
+        <v>57737</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15775,37 +15776,42 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>462022</v>
+        <v>461864</v>
       </c>
       <c r="R141" t="n">
-        <v>6780775</v>
+        <v>6780951</v>
       </c>
       <c r="S141" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15845,11 +15851,6 @@
       <c r="AB141" t="inlineStr">
         <is>
           <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15876,10 +15877,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>130087061</v>
+        <v>130083972</v>
       </c>
       <c r="B142" t="n">
-        <v>79089</v>
+        <v>57737</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15887,34 +15888,39 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>461952</v>
+        <v>461717</v>
       </c>
       <c r="R142" t="n">
-        <v>6780820</v>
+        <v>6780842</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15946,7 +15952,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15956,7 +15962,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15983,45 +15989,50 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>130087722</v>
+        <v>130085214</v>
       </c>
       <c r="B143" t="n">
-        <v>79089</v>
+        <v>8451</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>461894</v>
+        <v>461844</v>
       </c>
       <c r="R143" t="n">
-        <v>6780914</v>
+        <v>6780835</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16053,7 +16064,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -16063,7 +16074,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16090,10 +16101,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>130087794</v>
+        <v>130085089</v>
       </c>
       <c r="B144" t="n">
-        <v>57737</v>
+        <v>78847</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16101,39 +16112,34 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>461864</v>
+        <v>461857</v>
       </c>
       <c r="R144" t="n">
-        <v>6780951</v>
+        <v>6780866</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16165,7 +16171,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16175,7 +16181,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16190,57 +16196,57 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>130086828</v>
+        <v>130087789</v>
       </c>
       <c r="B145" t="n">
-        <v>8451</v>
+        <v>79121</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>461887</v>
+        <v>461857</v>
       </c>
       <c r="R145" t="n">
-        <v>6780890</v>
+        <v>6780939</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16272,7 +16278,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16282,7 +16288,12 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>Sparsamt på gran</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16297,22 +16308,22 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>130087057</v>
+        <v>130083742</v>
       </c>
       <c r="B146" t="n">
-        <v>79708</v>
+        <v>79089</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16320,21 +16331,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16344,10 +16355,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>461952</v>
+        <v>461699</v>
       </c>
       <c r="R146" t="n">
-        <v>6780820</v>
+        <v>6780870</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16379,7 +16390,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16389,7 +16400,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16416,10 +16427,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>130087754</v>
+        <v>130087057</v>
       </c>
       <c r="B147" t="n">
-        <v>57737</v>
+        <v>79708</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16427,39 +16438,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>461879</v>
+        <v>461952</v>
       </c>
       <c r="R147" t="n">
-        <v>6780924</v>
+        <v>6780820</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16528,45 +16534,50 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>130087401</v>
+        <v>130087754</v>
       </c>
       <c r="B148" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>462039</v>
+        <v>461879</v>
       </c>
       <c r="R148" t="n">
-        <v>6780770</v>
+        <v>6780924</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16635,32 +16646,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>130083742</v>
+        <v>130087401</v>
       </c>
       <c r="B149" t="n">
-        <v>79089</v>
+        <v>8451</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16670,10 +16681,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>461699</v>
+        <v>462039</v>
       </c>
       <c r="R149" t="n">
-        <v>6780870</v>
+        <v>6780770</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16705,7 +16716,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16715,7 +16726,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16742,45 +16753,45 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>130087789</v>
+        <v>130086828</v>
       </c>
       <c r="B150" t="n">
-        <v>79121</v>
+        <v>8451</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>461857</v>
+        <v>461887</v>
       </c>
       <c r="R150" t="n">
-        <v>6780939</v>
+        <v>6780890</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16812,7 +16823,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16822,12 +16833,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>Sparsamt på gran</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16842,12 +16848,12 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
@@ -16955,54 +16961,45 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>130091989</v>
+        <v>130085304</v>
       </c>
       <c r="B152" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>461800</v>
+        <v>461880</v>
       </c>
       <c r="R152" t="n">
-        <v>6780830</v>
+        <v>6780838</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17032,40 +17029,49 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AD152" t="b">
         <v>0</v>
       </c>
       <c r="AE152" t="b">
         <v>0</v>
       </c>
-      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>130091819</v>
+        <v>130087667</v>
       </c>
       <c r="B153" t="n">
-        <v>57737</v>
+        <v>79708</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17073,42 +17079,34 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr"/>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>461716</v>
+        <v>461929</v>
       </c>
       <c r="R153" t="n">
-        <v>6780856</v>
+        <v>6780891</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17138,9 +17136,19 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17155,57 +17163,66 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>130087667</v>
+        <v>130091989</v>
       </c>
       <c r="B154" t="n">
-        <v>79708</v>
+        <v>8451</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>461929</v>
+        <v>461800</v>
       </c>
       <c r="R154" t="n">
-        <v>6780891</v>
+        <v>6780830</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17235,49 +17252,40 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD154" t="b">
         <v>0</v>
       </c>
       <c r="AE154" t="b">
         <v>0</v>
       </c>
+      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>130085309</v>
+        <v>130086869</v>
       </c>
       <c r="B155" t="n">
-        <v>57737</v>
+        <v>78847</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17285,39 +17293,34 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>461880</v>
+        <v>461922</v>
       </c>
       <c r="R155" t="n">
-        <v>6780838</v>
+        <v>6780874</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17349,7 +17352,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17359,7 +17362,12 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17374,22 +17382,22 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>130085304</v>
+        <v>130085309</v>
       </c>
       <c r="B156" t="n">
-        <v>79089</v>
+        <v>57737</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17397,24 +17405,29 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
@@ -17493,10 +17506,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>130086869</v>
+        <v>130091819</v>
       </c>
       <c r="B157" t="n">
-        <v>78847</v>
+        <v>57737</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17504,34 +17517,42 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>461922</v>
+        <v>461716</v>
       </c>
       <c r="R157" t="n">
-        <v>6780874</v>
+        <v>6780856</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17561,24 +17582,9 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>13:11</t>
-        </is>
-      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17593,19 +17599,19 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>130087153</v>
+        <v>130086826</v>
       </c>
       <c r="B158" t="n">
         <v>57737</v>
@@ -17636,19 +17642,19 @@
       <c r="I158" t="inlineStr"/>
       <c r="M158" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>461955</v>
+        <v>461887</v>
       </c>
       <c r="R158" t="n">
-        <v>6780741</v>
+        <v>6780890</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17678,14 +17684,19 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>Äldre spår I högstubbe</t>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17700,19 +17711,19 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>130086826</v>
+        <v>130092006</v>
       </c>
       <c r="B159" t="n">
         <v>57737</v>
@@ -17741,21 +17752,24 @@
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
       <c r="M159" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>461887</v>
+        <v>461808</v>
       </c>
       <c r="R159" t="n">
-        <v>6780890</v>
+        <v>6780861</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17785,19 +17799,9 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>13:03</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17812,19 +17816,19 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>130092006</v>
+        <v>130087153</v>
       </c>
       <c r="B160" t="n">
         <v>57737</v>
@@ -17853,24 +17857,21 @@
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
       <c r="M160" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>461808</v>
+        <v>461955</v>
       </c>
       <c r="R160" t="n">
-        <v>6780861</v>
+        <v>6780741</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17905,6 +17906,11 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>Äldre spår I högstubbe</t>
+        </is>
+      </c>
       <c r="AD160" t="b">
         <v>0</v>
       </c>
@@ -17917,22 +17923,22 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>130084608</v>
+        <v>130087527</v>
       </c>
       <c r="B161" t="n">
-        <v>78847</v>
+        <v>79089</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17940,34 +17946,34 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>461805</v>
+        <v>461956</v>
       </c>
       <c r="R161" t="n">
-        <v>6780835</v>
+        <v>6780787</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17999,7 +18005,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -18009,12 +18015,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>11:27</t>
-        </is>
-      </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18029,22 +18030,22 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>130087527</v>
+        <v>130084608</v>
       </c>
       <c r="B162" t="n">
-        <v>79089</v>
+        <v>78847</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18052,34 +18053,34 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>461956</v>
+        <v>461805</v>
       </c>
       <c r="R162" t="n">
-        <v>6780787</v>
+        <v>6780835</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18111,7 +18112,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -18121,7 +18122,12 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18136,12 +18142,12 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
@@ -18356,10 +18362,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>130085067</v>
+        <v>130092430</v>
       </c>
       <c r="B165" t="n">
-        <v>57737</v>
+        <v>78847</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18367,39 +18373,37 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>461857</v>
+        <v>461933</v>
       </c>
       <c r="R165" t="n">
-        <v>6780842</v>
+        <v>6780838</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18429,19 +18433,14 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z165" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB165" t="inlineStr">
-        <is>
-          <t>10:14</t>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18450,18 +18449,19 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
+      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
@@ -18575,32 +18575,32 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>130091789</v>
+        <v>130091747</v>
       </c>
       <c r="B167" t="n">
-        <v>91005</v>
+        <v>79089</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>5685</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18613,10 +18613,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>461710</v>
+        <v>461737</v>
       </c>
       <c r="R167" t="n">
-        <v>6780886</v>
+        <v>6781057</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18676,46 +18676,37 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>130091841</v>
+        <v>130091789</v>
       </c>
       <c r="B168" t="n">
-        <v>57740</v>
+        <v>91005</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>100109</v>
+        <v>5685</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
@@ -18723,10 +18714,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>461720</v>
+        <v>461710</v>
       </c>
       <c r="R168" t="n">
-        <v>6780825</v>
+        <v>6780886</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18761,17 +18752,13 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>hack födosök i gran och ringhackad gran intill</t>
-        </is>
-      </c>
       <c r="AD168" t="b">
         <v>0</v>
       </c>
       <c r="AE168" t="b">
         <v>0</v>
       </c>
+      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
@@ -18790,10 +18777,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>130091747</v>
+        <v>130085067</v>
       </c>
       <c r="B169" t="n">
-        <v>79089</v>
+        <v>57737</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18801,37 +18788,39 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P169" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>461737</v>
+        <v>461857</v>
       </c>
       <c r="R169" t="n">
-        <v>6781057</v>
+        <v>6780842</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18861,40 +18850,49 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AD169" t="b">
         <v>0</v>
       </c>
       <c r="AE169" t="b">
         <v>0</v>
       </c>
-      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>130092430</v>
+        <v>130091841</v>
       </c>
       <c r="B170" t="n">
-        <v>78847</v>
+        <v>57740</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18902,26 +18900,35 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
@@ -18929,10 +18936,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>461933</v>
+        <v>461720</v>
       </c>
       <c r="R170" t="n">
-        <v>6780838</v>
+        <v>6780825</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18969,7 +18976,7 @@
       </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>hack födosök i gran och ringhackad gran intill</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18978,19 +18985,18 @@
       <c r="AE170" t="b">
         <v>0</v>
       </c>
-      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>

--- a/artfynd/A 58003-2025 artfynd.xlsx
+++ b/artfynd/A 58003-2025 artfynd.xlsx
@@ -4485,10 +4485,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129971739</v>
+        <v>129973978</v>
       </c>
       <c r="B37" t="n">
-        <v>79685</v>
+        <v>79095</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4496,21 +4496,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4520,10 +4520,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461741</v>
+        <v>461749</v>
       </c>
       <c r="R37" t="n">
-        <v>6780920</v>
+        <v>6780997</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4592,10 +4592,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129971259</v>
+        <v>129971804</v>
       </c>
       <c r="B38" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4603,39 +4603,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461751</v>
+        <v>461709</v>
       </c>
       <c r="R38" t="n">
-        <v>6780936</v>
+        <v>6780921</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4704,10 +4699,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129973978</v>
+        <v>129971259</v>
       </c>
       <c r="B39" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4715,34 +4710,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461749</v>
+        <v>461751</v>
       </c>
       <c r="R39" t="n">
-        <v>6780997</v>
+        <v>6780936</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4811,10 +4811,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129971804</v>
+        <v>129971739</v>
       </c>
       <c r="B40" t="n">
-        <v>79095</v>
+        <v>79685</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4822,21 +4822,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4846,10 +4846,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461709</v>
+        <v>461741</v>
       </c>
       <c r="R40" t="n">
-        <v>6780921</v>
+        <v>6780920</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4918,10 +4918,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129972983</v>
+        <v>129970813</v>
       </c>
       <c r="B41" t="n">
-        <v>57738</v>
+        <v>79714</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4929,39 +4929,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461615</v>
+        <v>461800</v>
       </c>
       <c r="R41" t="n">
-        <v>6780923</v>
+        <v>6781016</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5244,10 +5239,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129970813</v>
+        <v>129972983</v>
       </c>
       <c r="B44" t="n">
-        <v>79714</v>
+        <v>57738</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5255,34 +5250,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461800</v>
+        <v>461615</v>
       </c>
       <c r="R44" t="n">
-        <v>6781016</v>
+        <v>6780923</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -7265,10 +7265,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130087919</v>
+        <v>130092209</v>
       </c>
       <c r="B62" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7276,34 +7276,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>461853</v>
+        <v>461965</v>
       </c>
       <c r="R62" t="n">
-        <v>6780990</v>
+        <v>6780759</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7333,19 +7341,9 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>13:03</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7360,52 +7358,53 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130092209</v>
+        <v>130091775</v>
       </c>
       <c r="B63" t="n">
-        <v>57738</v>
+        <v>8451</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -7415,10 +7414,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461965</v>
+        <v>461753</v>
       </c>
       <c r="R63" t="n">
-        <v>6780759</v>
+        <v>6781025</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7459,6 +7458,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7477,7 +7477,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130091775</v>
+        <v>130092205</v>
       </c>
       <c r="B64" t="n">
         <v>8451</v>
@@ -7521,10 +7521,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>461753</v>
+        <v>461965</v>
       </c>
       <c r="R64" t="n">
-        <v>6781025</v>
+        <v>6780759</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7584,54 +7584,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130092205</v>
+        <v>130087919</v>
       </c>
       <c r="B65" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>461965</v>
+        <v>461853</v>
       </c>
       <c r="R65" t="n">
-        <v>6780759</v>
+        <v>6780990</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7661,30 +7652,39 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -8999,10 +8999,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130086966</v>
+        <v>130087418</v>
       </c>
       <c r="B78" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9010,42 +9010,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>461946</v>
+        <v>462039</v>
       </c>
       <c r="R78" t="n">
-        <v>6780867</v>
+        <v>6780770</v>
       </c>
       <c r="S78" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9074,7 +9069,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9084,12 +9079,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:17</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9104,12 +9094,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -9329,10 +9319,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130087418</v>
+        <v>130086966</v>
       </c>
       <c r="B81" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9340,37 +9330,42 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>462039</v>
+        <v>461946</v>
       </c>
       <c r="R81" t="n">
-        <v>6780770</v>
+        <v>6780867</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9399,7 +9394,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9409,7 +9404,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9424,12 +9424,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -9970,53 +9970,50 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130092368</v>
+        <v>130082759</v>
       </c>
       <c r="B87" t="n">
-        <v>57738</v>
+        <v>8451</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>461867</v>
+        <v>461757</v>
       </c>
       <c r="R87" t="n">
-        <v>6780956</v>
+        <v>6781096</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10046,9 +10043,19 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10063,19 +10070,19 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130092059</v>
+        <v>130092368</v>
       </c>
       <c r="B88" t="n">
         <v>57738</v>
@@ -10118,10 +10125,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>461946</v>
+        <v>461867</v>
       </c>
       <c r="R88" t="n">
-        <v>6780839</v>
+        <v>6780956</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10168,62 +10175,65 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130082759</v>
+        <v>130092059</v>
       </c>
       <c r="B89" t="n">
-        <v>8451</v>
+        <v>57738</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>461757</v>
+        <v>461946</v>
       </c>
       <c r="R89" t="n">
-        <v>6781096</v>
+        <v>6780839</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10253,19 +10263,9 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>10:14</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10280,22 +10280,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>130083753</v>
+        <v>130085149</v>
       </c>
       <c r="B90" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10303,34 +10303,39 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>461711</v>
+        <v>461857</v>
       </c>
       <c r="R90" t="n">
-        <v>6780852</v>
+        <v>6780859</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10362,7 +10367,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10372,7 +10377,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Äldre spår i torrtall</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10387,19 +10397,19 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>130087798</v>
+        <v>130091794</v>
       </c>
       <c r="B91" t="n">
         <v>79095</v>
@@ -10428,16 +10438,19 @@
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>461864</v>
+        <v>461710</v>
       </c>
       <c r="R91" t="n">
-        <v>6780951</v>
+        <v>6780886</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10467,89 +10480,78 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>130086721</v>
+        <v>130092053</v>
       </c>
       <c r="B92" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>461832</v>
+        <v>461926</v>
       </c>
       <c r="R92" t="n">
-        <v>6780916</v>
+        <v>6780853</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10579,98 +10581,75 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Äldre spår i torrtall</t>
-        </is>
-      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>130092063</v>
+        <v>130083753</v>
       </c>
       <c r="B93" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>461946</v>
+        <v>461711</v>
       </c>
       <c r="R93" t="n">
-        <v>6780839</v>
+        <v>6780852</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10700,80 +10679,84 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130087850</v>
+        <v>130087798</v>
       </c>
       <c r="B94" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>461873</v>
+        <v>461864</v>
       </c>
       <c r="R94" t="n">
-        <v>6780961</v>
+        <v>6780951</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10842,38 +10825,38 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>130085149</v>
+        <v>130086721</v>
       </c>
       <c r="B95" t="n">
-        <v>57738</v>
+        <v>8451</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -10882,10 +10865,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>461857</v>
+        <v>461832</v>
       </c>
       <c r="R95" t="n">
-        <v>6780859</v>
+        <v>6780916</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10917,7 +10900,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10927,7 +10910,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
@@ -10959,37 +10942,43 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>130091794</v>
+        <v>130092063</v>
       </c>
       <c r="B96" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -10997,10 +10986,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>461710</v>
+        <v>461946</v>
       </c>
       <c r="R96" t="n">
-        <v>6780886</v>
+        <v>6780839</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11060,48 +11049,50 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>130092053</v>
+        <v>130087850</v>
       </c>
       <c r="B97" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>461926</v>
+        <v>461873</v>
       </c>
       <c r="R97" t="n">
-        <v>6780853</v>
+        <v>6780961</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11131,80 +11122,93 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>130087727</v>
+        <v>130091828</v>
       </c>
       <c r="B98" t="n">
-        <v>57738</v>
+        <v>8451</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>461894</v>
+        <v>461736</v>
       </c>
       <c r="R98" t="n">
-        <v>6780914</v>
+        <v>6780844</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11234,84 +11238,84 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>130087915</v>
+        <v>130091798</v>
       </c>
       <c r="B99" t="n">
-        <v>79714</v>
+        <v>8451</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>461853</v>
+        <v>461713</v>
       </c>
       <c r="R99" t="n">
-        <v>6780990</v>
+        <v>6780880</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11341,49 +11345,40 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>130091832</v>
+        <v>130087915</v>
       </c>
       <c r="B100" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11391,37 +11386,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>461738</v>
+        <v>461853</v>
       </c>
       <c r="R100" t="n">
-        <v>6780825</v>
+        <v>6780990</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11451,73 +11443,76 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>130091828</v>
+        <v>130091832</v>
       </c>
       <c r="B101" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -11525,10 +11520,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>461736</v>
+        <v>461738</v>
       </c>
       <c r="R101" t="n">
-        <v>6780844</v>
+        <v>6780825</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11588,57 +11583,48 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>130091798</v>
+        <v>130087184</v>
       </c>
       <c r="B102" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>461713</v>
+        <v>461948</v>
       </c>
       <c r="R102" t="n">
-        <v>6780880</v>
+        <v>6780740</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11665,40 +11651,54 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+        </is>
+      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>130092019</v>
+        <v>130087727</v>
       </c>
       <c r="B103" t="n">
-        <v>78853</v>
+        <v>57738</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11706,37 +11706,39 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>461858</v>
+        <v>461894</v>
       </c>
       <c r="R103" t="n">
-        <v>6780846</v>
+        <v>6780914</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11766,40 +11768,49 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>130087184</v>
+        <v>130092019</v>
       </c>
       <c r="B104" t="n">
-        <v>79095</v>
+        <v>78853</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11807,37 +11818,40 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>461948</v>
+        <v>461858</v>
       </c>
       <c r="R104" t="n">
-        <v>6780740</v>
+        <v>6780846</v>
       </c>
       <c r="S104" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11864,44 +11878,30 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
-        </is>
-      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
@@ -12650,53 +12650,53 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>130087227</v>
+        <v>130085157</v>
       </c>
       <c r="B112" t="n">
-        <v>57738</v>
+        <v>8451</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>461948</v>
+        <v>461859</v>
       </c>
       <c r="R112" t="n">
-        <v>6780740</v>
+        <v>6780861</v>
       </c>
       <c r="S112" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12725,7 +12725,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12735,7 +12735,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12750,19 +12750,19 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>130087844</v>
+        <v>130087227</v>
       </c>
       <c r="B113" t="n">
         <v>57738</v>
@@ -12802,13 +12802,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>461873</v>
+        <v>461948</v>
       </c>
       <c r="R113" t="n">
-        <v>6780961</v>
+        <v>6780740</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12874,50 +12874,50 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>130085157</v>
+        <v>130087844</v>
       </c>
       <c r="B114" t="n">
-        <v>8451</v>
+        <v>57738</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>461859</v>
+        <v>461873</v>
       </c>
       <c r="R114" t="n">
-        <v>6780861</v>
+        <v>6780961</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12949,7 +12949,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12959,7 +12959,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12974,12 +12974,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
@@ -13093,10 +13093,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>130087759</v>
+        <v>130092071</v>
       </c>
       <c r="B116" t="n">
-        <v>79095</v>
+        <v>91937</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13104,34 +13104,37 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>461879</v>
+        <v>461946</v>
       </c>
       <c r="R116" t="n">
-        <v>6780924</v>
+        <v>6780863</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13161,71 +13164,62 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>130091843</v>
+        <v>130092122</v>
       </c>
       <c r="B117" t="n">
-        <v>79095</v>
+        <v>79119</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13238,10 +13232,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>461720</v>
+        <v>461986</v>
       </c>
       <c r="R117" t="n">
-        <v>6780825</v>
+        <v>6780804</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13301,10 +13295,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>130092033</v>
+        <v>130091843</v>
       </c>
       <c r="B118" t="n">
-        <v>78853</v>
+        <v>79095</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13312,21 +13306,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13339,10 +13333,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>461871</v>
+        <v>461720</v>
       </c>
       <c r="R118" t="n">
-        <v>6780851</v>
+        <v>6780825</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13402,37 +13396,43 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>130092071</v>
+        <v>130092139</v>
       </c>
       <c r="B119" t="n">
-        <v>91937</v>
+        <v>8451</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>658</v>
+        <v>106545</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
@@ -13440,10 +13440,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>461946</v>
+        <v>461975</v>
       </c>
       <c r="R119" t="n">
-        <v>6780863</v>
+        <v>6780791</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13503,32 +13503,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>130092122</v>
+        <v>130092033</v>
       </c>
       <c r="B120" t="n">
-        <v>79119</v>
+        <v>78853</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6434</v>
+        <v>228912</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13541,10 +13541,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>461986</v>
+        <v>461871</v>
       </c>
       <c r="R120" t="n">
-        <v>6780804</v>
+        <v>6780851</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13604,54 +13604,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>130092139</v>
+        <v>130087759</v>
       </c>
       <c r="B121" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>461975</v>
+        <v>461879</v>
       </c>
       <c r="R121" t="n">
-        <v>6780791</v>
+        <v>6780924</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13681,30 +13672,39 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
@@ -15969,10 +15969,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>130085304</v>
+        <v>130085309</v>
       </c>
       <c r="B143" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15980,24 +15980,29 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
@@ -16076,7 +16081,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>130085309</v>
+        <v>130091819</v>
       </c>
       <c r="B144" t="n">
         <v>57738</v>
@@ -16105,21 +16110,24 @@
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
       <c r="M144" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>461880</v>
+        <v>461716</v>
       </c>
       <c r="R144" t="n">
-        <v>6780838</v>
+        <v>6780856</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16149,19 +16157,9 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z144" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>10:14</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16176,22 +16174,22 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>130091819</v>
+        <v>130087667</v>
       </c>
       <c r="B145" t="n">
-        <v>57738</v>
+        <v>79714</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16199,42 +16197,34 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>461716</v>
+        <v>461929</v>
       </c>
       <c r="R145" t="n">
-        <v>6780856</v>
+        <v>6780891</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16264,9 +16254,19 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16281,22 +16281,22 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>130087667</v>
+        <v>130085304</v>
       </c>
       <c r="B146" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16304,21 +16304,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16328,10 +16328,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>461929</v>
+        <v>461880</v>
       </c>
       <c r="R146" t="n">
-        <v>6780891</v>
+        <v>6780838</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16363,7 +16363,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17370,50 +17370,48 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>130085067</v>
+        <v>130091789</v>
       </c>
       <c r="B156" t="n">
-        <v>57738</v>
+        <v>91021</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100049</v>
+        <v>5685</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>461857</v>
+        <v>461710</v>
       </c>
       <c r="R156" t="n">
-        <v>6780842</v>
+        <v>6780886</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17443,76 +17441,73 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AD156" t="b">
         <v>0</v>
       </c>
       <c r="AE156" t="b">
         <v>0</v>
       </c>
+      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>130091747</v>
+        <v>130092010</v>
       </c>
       <c r="B157" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
@@ -17520,10 +17515,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>461737</v>
+        <v>461808</v>
       </c>
       <c r="R157" t="n">
-        <v>6781057</v>
+        <v>6780861</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17583,10 +17578,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>130091841</v>
+        <v>130085067</v>
       </c>
       <c r="B158" t="n">
-        <v>57741</v>
+        <v>57738</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17594,16 +17589,16 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -17611,29 +17606,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
       <c r="M158" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N158" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>461720</v>
+        <v>461857</v>
       </c>
       <c r="R158" t="n">
-        <v>6780825</v>
+        <v>6780842</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17663,14 +17651,19 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>hack födosök i gran och ringhackad gran intill</t>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17685,22 +17678,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>130092430</v>
+        <v>130091747</v>
       </c>
       <c r="B159" t="n">
-        <v>78853</v>
+        <v>79095</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17708,21 +17701,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17735,10 +17728,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>461933</v>
+        <v>461737</v>
       </c>
       <c r="R159" t="n">
-        <v>6780838</v>
+        <v>6781057</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17773,11 +17766,6 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
-        </is>
-      </c>
       <c r="AD159" t="b">
         <v>0</v>
       </c>
@@ -17791,49 +17779,58 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>130091789</v>
+        <v>130091841</v>
       </c>
       <c r="B160" t="n">
-        <v>91021</v>
+        <v>57741</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>5685</v>
+        <v>100109</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
@@ -17841,10 +17838,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>461710</v>
+        <v>461720</v>
       </c>
       <c r="R160" t="n">
-        <v>6780886</v>
+        <v>6780825</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17879,13 +17876,17 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>hack födosök i gran och ringhackad gran intill</t>
+        </is>
+      </c>
       <c r="AD160" t="b">
         <v>0</v>
       </c>
       <c r="AE160" t="b">
         <v>0</v>
       </c>
-      <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="b">
         <v>0</v>
       </c>
@@ -17904,43 +17905,37 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>130092010</v>
+        <v>130092430</v>
       </c>
       <c r="B161" t="n">
-        <v>8451</v>
+        <v>78853</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr"/>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
@@ -17948,10 +17943,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>461808</v>
+        <v>461933</v>
       </c>
       <c r="R161" t="n">
-        <v>6780861</v>
+        <v>6780838</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17986,6 +17981,11 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
+        </is>
+      </c>
       <c r="AD161" t="b">
         <v>0</v>
       </c>
@@ -17999,12 +17999,12 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>

--- a/artfynd/A 58003-2025 artfynd.xlsx
+++ b/artfynd/A 58003-2025 artfynd.xlsx
@@ -1108,50 +1108,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129969658</v>
+        <v>129971802</v>
       </c>
       <c r="B6" t="n">
-        <v>8451</v>
+        <v>79714</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461799</v>
+        <v>461709</v>
       </c>
       <c r="R6" t="n">
-        <v>6780979</v>
+        <v>6780921</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,45 +1215,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129971802</v>
+        <v>129969658</v>
       </c>
       <c r="B7" t="n">
-        <v>79714</v>
+        <v>8451</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461709</v>
+        <v>461799</v>
       </c>
       <c r="R7" t="n">
-        <v>6780921</v>
+        <v>6780979</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129973829</v>
+        <v>129972961</v>
       </c>
       <c r="B8" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,39 +1338,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461730</v>
+        <v>461615</v>
       </c>
       <c r="R8" t="n">
-        <v>6780969</v>
+        <v>6780923</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1439,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129972961</v>
+        <v>129971607</v>
       </c>
       <c r="B9" t="n">
-        <v>79095</v>
+        <v>79685</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,21 +1445,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1474,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461615</v>
+        <v>461733</v>
       </c>
       <c r="R9" t="n">
-        <v>6780923</v>
+        <v>6780958</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,38 +1541,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129971831</v>
+        <v>129973829</v>
       </c>
       <c r="B10" t="n">
-        <v>8451</v>
+        <v>57738</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1586,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461686</v>
+        <v>461730</v>
       </c>
       <c r="R10" t="n">
-        <v>6780923</v>
+        <v>6780969</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1658,45 +1653,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129971607</v>
+        <v>129971831</v>
       </c>
       <c r="B11" t="n">
-        <v>79685</v>
+        <v>8451</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461733</v>
+        <v>461686</v>
       </c>
       <c r="R11" t="n">
-        <v>6780958</v>
+        <v>6780923</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -3283,50 +3283,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129971289</v>
+        <v>129972394</v>
       </c>
       <c r="B26" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461751</v>
+        <v>461679</v>
       </c>
       <c r="R26" t="n">
-        <v>6780936</v>
+        <v>6780885</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3395,7 +3390,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129972394</v>
+        <v>129972457</v>
       </c>
       <c r="B27" t="n">
         <v>79095</v>
@@ -3430,10 +3425,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461679</v>
+        <v>461687</v>
       </c>
       <c r="R27" t="n">
-        <v>6780885</v>
+        <v>6780875</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3502,45 +3497,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129972457</v>
+        <v>129971289</v>
       </c>
       <c r="B28" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461687</v>
+        <v>461751</v>
       </c>
       <c r="R28" t="n">
-        <v>6780875</v>
+        <v>6780936</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4485,10 +4485,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129973978</v>
+        <v>129971259</v>
       </c>
       <c r="B37" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4496,34 +4496,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461749</v>
+        <v>461751</v>
       </c>
       <c r="R37" t="n">
-        <v>6780997</v>
+        <v>6780936</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4592,7 +4597,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129971804</v>
+        <v>129973978</v>
       </c>
       <c r="B38" t="n">
         <v>79095</v>
@@ -4627,10 +4632,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461709</v>
+        <v>461749</v>
       </c>
       <c r="R38" t="n">
-        <v>6780921</v>
+        <v>6780997</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4699,10 +4704,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129971259</v>
+        <v>129971804</v>
       </c>
       <c r="B39" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4710,39 +4715,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461751</v>
+        <v>461709</v>
       </c>
       <c r="R39" t="n">
-        <v>6780936</v>
+        <v>6780921</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5025,10 +5025,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129971290</v>
+        <v>129972983</v>
       </c>
       <c r="B42" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5036,34 +5036,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461751</v>
+        <v>461615</v>
       </c>
       <c r="R42" t="n">
-        <v>6780936</v>
+        <v>6780923</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5132,10 +5137,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129970961</v>
+        <v>129971290</v>
       </c>
       <c r="B43" t="n">
-        <v>79685</v>
+        <v>79095</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5143,21 +5148,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5167,10 +5172,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461789</v>
+        <v>461751</v>
       </c>
       <c r="R43" t="n">
-        <v>6780961</v>
+        <v>6780936</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5239,10 +5244,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129972983</v>
+        <v>129970961</v>
       </c>
       <c r="B44" t="n">
-        <v>57738</v>
+        <v>79685</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5250,39 +5255,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461615</v>
+        <v>461789</v>
       </c>
       <c r="R44" t="n">
-        <v>6780923</v>
+        <v>6780961</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6032,10 +6032,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129973137</v>
+        <v>129969692</v>
       </c>
       <c r="B51" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6043,34 +6043,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461609</v>
+        <v>461799</v>
       </c>
       <c r="R51" t="n">
-        <v>6780949</v>
+        <v>6780979</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6117,7 +6122,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>3 bilder, rikligt i en radie av ca 50 meter</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6144,10 +6149,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129969692</v>
+        <v>129973137</v>
       </c>
       <c r="B52" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6155,39 +6160,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461799</v>
+        <v>461609</v>
       </c>
       <c r="R52" t="n">
-        <v>6780979</v>
+        <v>6780949</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>3 bilder, rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6498,10 +6498,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130087273</v>
+        <v>130083775</v>
       </c>
       <c r="B55" t="n">
-        <v>78853</v>
+        <v>79095</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6509,21 +6509,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6533,10 +6533,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>462051</v>
+        <v>461717</v>
       </c>
       <c r="R55" t="n">
-        <v>6780727</v>
+        <v>6780842</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6605,32 +6605,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130083775</v>
+        <v>130087228</v>
       </c>
       <c r="B56" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6640,13 +6640,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461717</v>
+        <v>461948</v>
       </c>
       <c r="R56" t="n">
-        <v>6780842</v>
+        <v>6780740</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6712,7 +6712,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130087228</v>
+        <v>130087516</v>
       </c>
       <c r="B57" t="n">
         <v>8451</v>
@@ -6741,19 +6741,24 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461948</v>
+        <v>461956</v>
       </c>
       <c r="R57" t="n">
-        <v>6780740</v>
+        <v>6780787</v>
       </c>
       <c r="S57" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6819,50 +6824,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130087516</v>
+        <v>130087273</v>
       </c>
       <c r="B58" t="n">
-        <v>8451</v>
+        <v>78853</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461956</v>
+        <v>462051</v>
       </c>
       <c r="R58" t="n">
-        <v>6780787</v>
+        <v>6780727</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6931,10 +6931,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130084991</v>
+        <v>130087559</v>
       </c>
       <c r="B59" t="n">
-        <v>79127</v>
+        <v>57738</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6942,34 +6942,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>461840</v>
+        <v>461970</v>
       </c>
       <c r="R59" t="n">
-        <v>6780854</v>
+        <v>6780823</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7001,7 +7006,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7011,12 +7016,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:27</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Sparsamt på gran</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7031,22 +7031,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130087559</v>
+        <v>130084991</v>
       </c>
       <c r="B60" t="n">
-        <v>57738</v>
+        <v>79127</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7054,39 +7054,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461970</v>
+        <v>461840</v>
       </c>
       <c r="R60" t="n">
-        <v>6780823</v>
+        <v>6780854</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7118,7 +7113,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7128,7 +7123,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Sparsamt på gran</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7143,12 +7143,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7691,10 +7691,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130087492</v>
+        <v>130087512</v>
       </c>
       <c r="B66" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7702,34 +7702,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>461944</v>
+        <v>461956</v>
       </c>
       <c r="R66" t="n">
-        <v>6780796</v>
+        <v>6780787</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7798,10 +7803,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130087119</v>
+        <v>130092026</v>
       </c>
       <c r="B67" t="n">
-        <v>79095</v>
+        <v>78852</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7809,37 +7814,40 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>461918</v>
+        <v>461858</v>
       </c>
       <c r="R67" t="n">
-        <v>6780787</v>
+        <v>6780846</v>
       </c>
       <c r="S67" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7866,54 +7874,40 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130087669</v>
+        <v>130087716</v>
       </c>
       <c r="B68" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7921,21 +7915,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7945,10 +7939,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>461929</v>
+        <v>461894</v>
       </c>
       <c r="R68" t="n">
-        <v>6780891</v>
+        <v>6780914</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8017,10 +8011,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130087512</v>
+        <v>130085288</v>
       </c>
       <c r="B69" t="n">
-        <v>57738</v>
+        <v>92122</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8028,42 +8022,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>5467</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>461956</v>
+        <v>461858</v>
       </c>
       <c r="R69" t="n">
-        <v>6780787</v>
+        <v>6780876</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8092,7 +8081,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8102,7 +8091,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8117,60 +8106,62 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130092026</v>
+        <v>130087222</v>
       </c>
       <c r="B70" t="n">
-        <v>78852</v>
+        <v>8451</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>461858</v>
+        <v>462001</v>
       </c>
       <c r="R70" t="n">
-        <v>6780846</v>
+        <v>6780764</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8200,75 +8191,98 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Äldre spår I tallåga</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130087716</v>
+        <v>130092389</v>
       </c>
       <c r="B71" t="n">
-        <v>79714</v>
+        <v>8451</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>461894</v>
+        <v>461870</v>
       </c>
       <c r="R71" t="n">
-        <v>6780914</v>
+        <v>6780967</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8298,71 +8312,62 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130085288</v>
+        <v>130087245</v>
       </c>
       <c r="B72" t="n">
-        <v>92122</v>
+        <v>8451</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5467</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8372,13 +8377,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>461858</v>
+        <v>461946</v>
       </c>
       <c r="R72" t="n">
-        <v>6780876</v>
+        <v>6780867</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8407,7 +8412,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8417,7 +8422,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8444,50 +8449,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130087222</v>
+        <v>130087492</v>
       </c>
       <c r="B73" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>462001</v>
+        <v>461944</v>
       </c>
       <c r="R73" t="n">
-        <v>6780764</v>
+        <v>6780796</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8519,7 +8519,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8529,12 +8529,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:46</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Äldre spår I tallåga</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8549,69 +8544,60 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130092389</v>
+        <v>130087119</v>
       </c>
       <c r="B74" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>461870</v>
+        <v>461918</v>
       </c>
       <c r="R74" t="n">
-        <v>6780967</v>
+        <v>6780787</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8638,78 +8624,92 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130087245</v>
+        <v>130087669</v>
       </c>
       <c r="B75" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>461946</v>
+        <v>461929</v>
       </c>
       <c r="R75" t="n">
-        <v>6780867</v>
+        <v>6780891</v>
       </c>
       <c r="S75" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8748,7 +8748,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8763,22 +8763,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130086767</v>
+        <v>130087408</v>
       </c>
       <c r="B76" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8786,34 +8786,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>461850</v>
+        <v>462039</v>
       </c>
       <c r="R76" t="n">
-        <v>6780913</v>
+        <v>6780770</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8856,11 +8861,6 @@
       <c r="AB76" t="inlineStr">
         <is>
           <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>2 bild. Rikligt till måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8887,10 +8887,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130087408</v>
+        <v>130086767</v>
       </c>
       <c r="B77" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8898,39 +8898,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>462039</v>
+        <v>461850</v>
       </c>
       <c r="R77" t="n">
-        <v>6780770</v>
+        <v>6780913</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8973,6 +8968,11 @@
       <c r="AB77" t="inlineStr">
         <is>
           <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>2 bild. Rikligt till måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9970,50 +9970,53 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130082759</v>
+        <v>130092368</v>
       </c>
       <c r="B87" t="n">
-        <v>8451</v>
+        <v>57738</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>461757</v>
+        <v>461867</v>
       </c>
       <c r="R87" t="n">
-        <v>6781096</v>
+        <v>6780956</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10043,19 +10046,9 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>10:14</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10070,19 +10063,19 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130092368</v>
+        <v>130092059</v>
       </c>
       <c r="B88" t="n">
         <v>57738</v>
@@ -10125,10 +10118,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>461867</v>
+        <v>461946</v>
       </c>
       <c r="R88" t="n">
-        <v>6780956</v>
+        <v>6780839</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10175,65 +10168,62 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130092059</v>
+        <v>130082759</v>
       </c>
       <c r="B89" t="n">
-        <v>57738</v>
+        <v>8451</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>461946</v>
+        <v>461757</v>
       </c>
       <c r="R89" t="n">
-        <v>6780839</v>
+        <v>6781096</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10263,9 +10253,19 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10280,12 +10280,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -11161,54 +11161,50 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>130091828</v>
+        <v>130087727</v>
       </c>
       <c r="B98" t="n">
-        <v>8451</v>
+        <v>57738</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>461736</v>
+        <v>461894</v>
       </c>
       <c r="R98" t="n">
-        <v>6780844</v>
+        <v>6780914</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11238,84 +11234,84 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>130091798</v>
+        <v>130087915</v>
       </c>
       <c r="B99" t="n">
-        <v>8451</v>
+        <v>79714</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>461713</v>
+        <v>461853</v>
       </c>
       <c r="R99" t="n">
-        <v>6780880</v>
+        <v>6780990</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11345,40 +11341,49 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>130087915</v>
+        <v>130091832</v>
       </c>
       <c r="B100" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11386,34 +11391,37 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>461853</v>
+        <v>461738</v>
       </c>
       <c r="R100" t="n">
-        <v>6780990</v>
+        <v>6780825</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11443,76 +11451,73 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>130091832</v>
+        <v>130091828</v>
       </c>
       <c r="B101" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -11520,10 +11525,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>461738</v>
+        <v>461736</v>
       </c>
       <c r="R101" t="n">
-        <v>6780825</v>
+        <v>6780844</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11583,48 +11588,57 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>130087184</v>
+        <v>130091798</v>
       </c>
       <c r="B102" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>461948</v>
+        <v>461713</v>
       </c>
       <c r="R102" t="n">
-        <v>6780740</v>
+        <v>6780880</v>
       </c>
       <c r="S102" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11651,54 +11665,40 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
-        </is>
-      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>130087727</v>
+        <v>130092019</v>
       </c>
       <c r="B103" t="n">
-        <v>57738</v>
+        <v>78853</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11706,39 +11706,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>461894</v>
+        <v>461858</v>
       </c>
       <c r="R103" t="n">
-        <v>6780914</v>
+        <v>6780846</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11768,49 +11766,40 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>130092019</v>
+        <v>130087184</v>
       </c>
       <c r="B104" t="n">
-        <v>78853</v>
+        <v>79095</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11818,40 +11807,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>461858</v>
+        <v>461948</v>
       </c>
       <c r="R104" t="n">
-        <v>6780846</v>
+        <v>6780740</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11878,30 +11864,44 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+        </is>
+      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
@@ -12650,53 +12650,53 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>130085157</v>
+        <v>130087227</v>
       </c>
       <c r="B112" t="n">
-        <v>8451</v>
+        <v>57738</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>461859</v>
+        <v>461948</v>
       </c>
       <c r="R112" t="n">
-        <v>6780861</v>
+        <v>6780740</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12725,7 +12725,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12735,7 +12735,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12750,19 +12750,19 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>130087227</v>
+        <v>130087844</v>
       </c>
       <c r="B113" t="n">
         <v>57738</v>
@@ -12802,13 +12802,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>461948</v>
+        <v>461873</v>
       </c>
       <c r="R113" t="n">
-        <v>6780740</v>
+        <v>6780961</v>
       </c>
       <c r="S113" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12874,50 +12874,50 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>130087844</v>
+        <v>130085157</v>
       </c>
       <c r="B114" t="n">
-        <v>57738</v>
+        <v>8451</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>461873</v>
+        <v>461859</v>
       </c>
       <c r="R114" t="n">
-        <v>6780961</v>
+        <v>6780861</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12949,7 +12949,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12959,7 +12959,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12974,12 +12974,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
@@ -13711,10 +13711,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>130091751</v>
+        <v>130091745</v>
       </c>
       <c r="B122" t="n">
-        <v>79127</v>
+        <v>79095</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13722,21 +13722,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13749,10 +13749,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>461737</v>
+        <v>461749</v>
       </c>
       <c r="R122" t="n">
-        <v>6781057</v>
+        <v>6781031</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13812,7 +13812,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>130091745</v>
+        <v>130086831</v>
       </c>
       <c r="B123" t="n">
         <v>79095</v>
@@ -13841,19 +13841,16 @@
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>461749</v>
+        <v>461887</v>
       </c>
       <c r="R123" t="n">
-        <v>6781031</v>
+        <v>6780890</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13883,62 +13880,71 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>130086831</v>
+        <v>130087075</v>
       </c>
       <c r="B124" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13948,10 +13954,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>461887</v>
+        <v>461944</v>
       </c>
       <c r="R124" t="n">
-        <v>6780890</v>
+        <v>6780796</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14020,10 +14026,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>130091628</v>
+        <v>130083776</v>
       </c>
       <c r="B125" t="n">
-        <v>79095</v>
+        <v>78853</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14031,37 +14037,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>461750</v>
+        <v>461738</v>
       </c>
       <c r="R125" t="n">
-        <v>6781031</v>
+        <v>6780866</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14091,75 +14094,87 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>130087075</v>
+        <v>130091751</v>
       </c>
       <c r="B126" t="n">
-        <v>8451</v>
+        <v>79127</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>461944</v>
+        <v>461737</v>
       </c>
       <c r="R126" t="n">
-        <v>6780796</v>
+        <v>6781057</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14189,49 +14204,40 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD126" t="b">
         <v>0</v>
       </c>
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>130083776</v>
+        <v>130091628</v>
       </c>
       <c r="B127" t="n">
-        <v>78853</v>
+        <v>79095</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14239,34 +14245,37 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>461738</v>
+        <v>461750</v>
       </c>
       <c r="R127" t="n">
-        <v>6780866</v>
+        <v>6781031</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14296,49 +14305,40 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>10:54</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>10:54</t>
-        </is>
-      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>130085207</v>
+        <v>130087061</v>
       </c>
       <c r="B128" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14346,39 +14346,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>461844</v>
+        <v>461952</v>
       </c>
       <c r="R128" t="n">
-        <v>6780835</v>
+        <v>6780820</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14410,7 +14405,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14420,7 +14415,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14447,10 +14442,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>130087794</v>
+        <v>130087445</v>
       </c>
       <c r="B129" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14458,42 +14453,37 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>461864</v>
+        <v>462022</v>
       </c>
       <c r="R129" t="n">
-        <v>6780951</v>
+        <v>6780775</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14533,6 +14523,11 @@
       <c r="AB129" t="inlineStr">
         <is>
           <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14559,10 +14554,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>130083972</v>
+        <v>130087722</v>
       </c>
       <c r="B130" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14570,39 +14565,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>461717</v>
+        <v>461894</v>
       </c>
       <c r="R130" t="n">
-        <v>6780842</v>
+        <v>6780914</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14634,7 +14624,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14644,7 +14634,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14671,10 +14661,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>130091780</v>
+        <v>130085207</v>
       </c>
       <c r="B131" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14682,37 +14672,39 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>461742</v>
+        <v>461844</v>
       </c>
       <c r="R131" t="n">
-        <v>6781010</v>
+        <v>6780835</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14742,68 +14734,77 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AD131" t="b">
         <v>0</v>
       </c>
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>130085214</v>
+        <v>130087794</v>
       </c>
       <c r="B132" t="n">
-        <v>8451</v>
+        <v>57738</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="M132" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -14812,10 +14813,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>461844</v>
+        <v>461864</v>
       </c>
       <c r="R132" t="n">
-        <v>6780835</v>
+        <v>6780951</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14847,7 +14848,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14857,7 +14858,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14884,10 +14885,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>130085089</v>
+        <v>130083972</v>
       </c>
       <c r="B133" t="n">
-        <v>78853</v>
+        <v>57738</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14895,34 +14896,39 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>461857</v>
+        <v>461717</v>
       </c>
       <c r="R133" t="n">
-        <v>6780866</v>
+        <v>6780842</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14954,7 +14960,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14964,7 +14970,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14979,19 +14985,19 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>130087722</v>
+        <v>130091780</v>
       </c>
       <c r="B134" t="n">
         <v>79095</v>
@@ -15020,16 +15026,19 @@
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>461894</v>
+        <v>461742</v>
       </c>
       <c r="R134" t="n">
-        <v>6780914</v>
+        <v>6781010</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15059,84 +15068,80 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD134" t="b">
         <v>0</v>
       </c>
       <c r="AE134" t="b">
         <v>0</v>
       </c>
+      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>130087061</v>
+        <v>130085214</v>
       </c>
       <c r="B135" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>461952</v>
+        <v>461844</v>
       </c>
       <c r="R135" t="n">
-        <v>6780820</v>
+        <v>6780835</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15168,7 +15173,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15178,7 +15183,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15205,10 +15210,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>130087445</v>
+        <v>130085089</v>
       </c>
       <c r="B136" t="n">
-        <v>79095</v>
+        <v>78853</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15216,37 +15221,37 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>462022</v>
+        <v>461857</v>
       </c>
       <c r="R136" t="n">
-        <v>6780775</v>
+        <v>6780866</v>
       </c>
       <c r="S136" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15275,7 +15280,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15285,12 +15290,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15305,12 +15305,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
@@ -15969,10 +15969,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>130085309</v>
+        <v>130085304</v>
       </c>
       <c r="B143" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15980,29 +15980,24 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
@@ -16081,7 +16076,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>130091819</v>
+        <v>130085309</v>
       </c>
       <c r="B144" t="n">
         <v>57738</v>
@@ -16110,24 +16105,21 @@
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
       <c r="M144" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>461716</v>
+        <v>461880</v>
       </c>
       <c r="R144" t="n">
-        <v>6780856</v>
+        <v>6780838</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16157,9 +16149,19 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16174,22 +16176,22 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>130087667</v>
+        <v>130091819</v>
       </c>
       <c r="B145" t="n">
-        <v>79714</v>
+        <v>57738</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16197,34 +16199,42 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>461929</v>
+        <v>461716</v>
       </c>
       <c r="R145" t="n">
-        <v>6780891</v>
+        <v>6780856</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16254,19 +16264,9 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z145" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AB145" t="inlineStr">
-        <is>
-          <t>13:03</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16281,22 +16281,22 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>130085304</v>
+        <v>130087667</v>
       </c>
       <c r="B146" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16304,21 +16304,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16328,10 +16328,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>461880</v>
+        <v>461929</v>
       </c>
       <c r="R146" t="n">
-        <v>6780838</v>
+        <v>6780891</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16363,7 +16363,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -18241,10 +18241,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>130086991</v>
+        <v>130083774</v>
       </c>
       <c r="B164" t="n">
-        <v>79095</v>
+        <v>90671</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18252,37 +18252,40 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>461939</v>
+        <v>461717</v>
       </c>
       <c r="R164" t="n">
-        <v>6780857</v>
+        <v>6780842</v>
       </c>
       <c r="S164" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -18311,7 +18314,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -18321,12 +18324,12 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>2 bild. Rikligt till måttligt i en radie av ca 50 meter</t>
+          <t>2 bilder</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18335,6 +18338,7 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
+      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
@@ -18353,10 +18357,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>130083774</v>
+        <v>130086991</v>
       </c>
       <c r="B165" t="n">
-        <v>90671</v>
+        <v>79095</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18364,40 +18368,37 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>461717</v>
+        <v>461939</v>
       </c>
       <c r="R165" t="n">
-        <v>6780842</v>
+        <v>6780857</v>
       </c>
       <c r="S165" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -18426,7 +18427,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -18436,12 +18437,12 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>2 bilder</t>
+          <t>2 bild. Rikligt till måttligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18450,7 +18451,6 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
-      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58003-2025 artfynd.xlsx
+++ b/artfynd/A 58003-2025 artfynd.xlsx
@@ -1327,42 +1327,47 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129972961</v>
+        <v>129971831</v>
       </c>
       <c r="B8" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461615</v>
+        <v>461686</v>
       </c>
       <c r="R8" t="n">
         <v>6780923</v>
@@ -1434,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129971607</v>
+        <v>129972961</v>
       </c>
       <c r="B9" t="n">
-        <v>79685</v>
+        <v>79095</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,21 +1450,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461733</v>
+        <v>461615</v>
       </c>
       <c r="R9" t="n">
-        <v>6780958</v>
+        <v>6780923</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1653,50 +1658,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129971831</v>
+        <v>129971607</v>
       </c>
       <c r="B11" t="n">
-        <v>8451</v>
+        <v>79685</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461686</v>
+        <v>461733</v>
       </c>
       <c r="R11" t="n">
-        <v>6780923</v>
+        <v>6780958</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129971787</v>
+        <v>129971115</v>
       </c>
       <c r="B13" t="n">
-        <v>79714</v>
+        <v>79685</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,21 +1883,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461741</v>
+        <v>461762</v>
       </c>
       <c r="R13" t="n">
-        <v>6780920</v>
+        <v>6780940</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1979,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129971115</v>
+        <v>129971787</v>
       </c>
       <c r="B14" t="n">
-        <v>79685</v>
+        <v>79714</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1990,21 +1990,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461762</v>
+        <v>461741</v>
       </c>
       <c r="R14" t="n">
-        <v>6780940</v>
+        <v>6780920</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2519,45 +2519,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129971589</v>
+        <v>129972802</v>
       </c>
       <c r="B19" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461736</v>
+        <v>461611</v>
       </c>
       <c r="R19" t="n">
-        <v>6780931</v>
+        <v>6780900</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2626,7 +2631,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129972800</v>
+        <v>129971589</v>
       </c>
       <c r="B20" t="n">
         <v>79095</v>
@@ -2661,10 +2666,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461611</v>
+        <v>461736</v>
       </c>
       <c r="R20" t="n">
-        <v>6780900</v>
+        <v>6780931</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2733,40 +2738,35 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129972802</v>
+        <v>129972800</v>
       </c>
       <c r="B21" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
@@ -2952,45 +2952,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129970829</v>
+        <v>129972234</v>
       </c>
       <c r="B23" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461800</v>
+        <v>461679</v>
       </c>
       <c r="R23" t="n">
-        <v>6781016</v>
+        <v>6780885</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3059,7 +3064,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129972234</v>
+        <v>129973842</v>
       </c>
       <c r="B24" t="n">
         <v>8451</v>
@@ -3099,10 +3104,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461679</v>
+        <v>461730</v>
       </c>
       <c r="R24" t="n">
-        <v>6780885</v>
+        <v>6780969</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3171,50 +3176,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129973842</v>
+        <v>129970829</v>
       </c>
       <c r="B25" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461730</v>
+        <v>461800</v>
       </c>
       <c r="R25" t="n">
-        <v>6780969</v>
+        <v>6781016</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3283,7 +3283,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129972394</v>
+        <v>129972457</v>
       </c>
       <c r="B26" t="n">
         <v>79095</v>
@@ -3318,10 +3318,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461679</v>
+        <v>461687</v>
       </c>
       <c r="R26" t="n">
-        <v>6780885</v>
+        <v>6780875</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3390,45 +3390,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129972457</v>
+        <v>129971289</v>
       </c>
       <c r="B27" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461687</v>
+        <v>461751</v>
       </c>
       <c r="R27" t="n">
-        <v>6780875</v>
+        <v>6780936</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3497,50 +3502,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129971289</v>
+        <v>129972394</v>
       </c>
       <c r="B28" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461751</v>
+        <v>461679</v>
       </c>
       <c r="R28" t="n">
-        <v>6780936</v>
+        <v>6780885</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3721,45 +3721,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129970675</v>
+        <v>129971587</v>
       </c>
       <c r="B30" t="n">
-        <v>79714</v>
+        <v>8451</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461789</v>
+        <v>461736</v>
       </c>
       <c r="R30" t="n">
-        <v>6780961</v>
+        <v>6780931</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3828,7 +3833,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129971587</v>
+        <v>129972990</v>
       </c>
       <c r="B31" t="n">
         <v>8451</v>
@@ -3868,10 +3873,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461736</v>
+        <v>461615</v>
       </c>
       <c r="R31" t="n">
-        <v>6780931</v>
+        <v>6780923</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3940,50 +3945,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129972990</v>
+        <v>129970675</v>
       </c>
       <c r="B32" t="n">
-        <v>8451</v>
+        <v>79714</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461615</v>
+        <v>461789</v>
       </c>
       <c r="R32" t="n">
-        <v>6780923</v>
+        <v>6780961</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4052,10 +4052,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129970738</v>
+        <v>129971825</v>
       </c>
       <c r="B33" t="n">
-        <v>79714</v>
+        <v>57738</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4063,34 +4063,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461799</v>
+        <v>461686</v>
       </c>
       <c r="R33" t="n">
-        <v>6780979</v>
+        <v>6780923</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4159,10 +4164,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129971825</v>
+        <v>129970738</v>
       </c>
       <c r="B34" t="n">
-        <v>57738</v>
+        <v>79714</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4170,39 +4175,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461686</v>
+        <v>461799</v>
       </c>
       <c r="R34" t="n">
-        <v>6780923</v>
+        <v>6780979</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4271,10 +4271,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129970828</v>
+        <v>129971832</v>
       </c>
       <c r="B35" t="n">
-        <v>78852</v>
+        <v>79095</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4282,21 +4282,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4306,10 +4306,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461800</v>
+        <v>461686</v>
       </c>
       <c r="R35" t="n">
-        <v>6781016</v>
+        <v>6780923</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4378,10 +4378,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129971832</v>
+        <v>129970828</v>
       </c>
       <c r="B36" t="n">
-        <v>79095</v>
+        <v>78852</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4389,21 +4389,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461686</v>
+        <v>461800</v>
       </c>
       <c r="R36" t="n">
-        <v>6780923</v>
+        <v>6781016</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4485,10 +4485,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129971259</v>
+        <v>129971739</v>
       </c>
       <c r="B37" t="n">
-        <v>57738</v>
+        <v>79685</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4496,39 +4496,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461751</v>
+        <v>461741</v>
       </c>
       <c r="R37" t="n">
-        <v>6780936</v>
+        <v>6780920</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4704,10 +4699,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129971804</v>
+        <v>129971259</v>
       </c>
       <c r="B39" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4715,34 +4710,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461709</v>
+        <v>461751</v>
       </c>
       <c r="R39" t="n">
-        <v>6780921</v>
+        <v>6780936</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4811,10 +4811,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129971739</v>
+        <v>129971804</v>
       </c>
       <c r="B40" t="n">
-        <v>79685</v>
+        <v>79095</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4822,21 +4822,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4846,10 +4846,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461741</v>
+        <v>461709</v>
       </c>
       <c r="R40" t="n">
-        <v>6780920</v>
+        <v>6780921</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4918,10 +4918,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129970813</v>
+        <v>129971290</v>
       </c>
       <c r="B41" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4929,21 +4929,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4953,10 +4953,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461800</v>
+        <v>461751</v>
       </c>
       <c r="R41" t="n">
-        <v>6781016</v>
+        <v>6780936</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5025,10 +5025,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129972983</v>
+        <v>129970813</v>
       </c>
       <c r="B42" t="n">
-        <v>57738</v>
+        <v>79714</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5036,39 +5036,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461615</v>
+        <v>461800</v>
       </c>
       <c r="R42" t="n">
-        <v>6780923</v>
+        <v>6781016</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5137,10 +5132,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129971290</v>
+        <v>129972983</v>
       </c>
       <c r="B43" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5148,34 +5143,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461751</v>
+        <v>461615</v>
       </c>
       <c r="R43" t="n">
-        <v>6780936</v>
+        <v>6780923</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5578,7 +5578,7 @@
         <v>129972538</v>
       </c>
       <c r="B47" t="n">
-        <v>91660</v>
+        <v>91662</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6032,10 +6032,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129969692</v>
+        <v>129973137</v>
       </c>
       <c r="B51" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6043,39 +6043,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461799</v>
+        <v>461609</v>
       </c>
       <c r="R51" t="n">
-        <v>6780979</v>
+        <v>6780949</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6122,7 +6117,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>3 bilder, rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6149,10 +6144,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129973137</v>
+        <v>129972233</v>
       </c>
       <c r="B52" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6160,34 +6155,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461609</v>
+        <v>461679</v>
       </c>
       <c r="R52" t="n">
-        <v>6780949</v>
+        <v>6780885</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6234,7 +6237,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>3 bilder, rikligt i en radie av ca 50 meter</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6261,7 +6264,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129972233</v>
+        <v>129969692</v>
       </c>
       <c r="B53" t="n">
         <v>57738</v>
@@ -6290,24 +6293,21 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>461679</v>
+        <v>461799</v>
       </c>
       <c r="R53" t="n">
-        <v>6780885</v>
+        <v>6780979</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6498,10 +6498,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130083775</v>
+        <v>130087273</v>
       </c>
       <c r="B55" t="n">
-        <v>79095</v>
+        <v>78853</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6509,21 +6509,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6533,10 +6533,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>461717</v>
+        <v>462051</v>
       </c>
       <c r="R55" t="n">
-        <v>6780842</v>
+        <v>6780727</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6605,32 +6605,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130087228</v>
+        <v>130083775</v>
       </c>
       <c r="B56" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6640,13 +6640,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461948</v>
+        <v>461717</v>
       </c>
       <c r="R56" t="n">
-        <v>6780740</v>
+        <v>6780842</v>
       </c>
       <c r="S56" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6712,7 +6712,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130087516</v>
+        <v>130087228</v>
       </c>
       <c r="B57" t="n">
         <v>8451</v>
@@ -6741,24 +6741,19 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461956</v>
+        <v>461948</v>
       </c>
       <c r="R57" t="n">
-        <v>6780787</v>
+        <v>6780740</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6824,45 +6819,50 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130087273</v>
+        <v>130087516</v>
       </c>
       <c r="B58" t="n">
-        <v>78853</v>
+        <v>8451</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>462051</v>
+        <v>461956</v>
       </c>
       <c r="R58" t="n">
-        <v>6780727</v>
+        <v>6780787</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6931,10 +6931,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130087559</v>
+        <v>130084991</v>
       </c>
       <c r="B59" t="n">
-        <v>57738</v>
+        <v>79127</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6942,39 +6942,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>461970</v>
+        <v>461840</v>
       </c>
       <c r="R59" t="n">
-        <v>6780823</v>
+        <v>6780854</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7006,7 +7001,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7016,7 +7011,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Sparsamt på gran</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7031,22 +7031,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130084991</v>
+        <v>130092086</v>
       </c>
       <c r="B60" t="n">
-        <v>79127</v>
+        <v>57741</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7054,34 +7054,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461840</v>
+        <v>461986</v>
       </c>
       <c r="R60" t="n">
-        <v>6780854</v>
+        <v>6780804</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7111,24 +7119,14 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>11:27</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>11:27</t>
-        </is>
-      </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Sparsamt på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7143,22 +7141,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130092086</v>
+        <v>130087559</v>
       </c>
       <c r="B61" t="n">
-        <v>57741</v>
+        <v>57738</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7166,16 +7164,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7184,24 +7182,21 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>461986</v>
+        <v>461970</v>
       </c>
       <c r="R61" t="n">
-        <v>6780804</v>
+        <v>6780823</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7231,14 +7226,19 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7253,52 +7253,53 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130092209</v>
+        <v>130091775</v>
       </c>
       <c r="B62" t="n">
-        <v>57738</v>
+        <v>8451</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -7308,10 +7309,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>461965</v>
+        <v>461753</v>
       </c>
       <c r="R62" t="n">
-        <v>6780759</v>
+        <v>6781025</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7352,6 +7353,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7370,7 +7372,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130091775</v>
+        <v>130092205</v>
       </c>
       <c r="B63" t="n">
         <v>8451</v>
@@ -7414,10 +7416,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461753</v>
+        <v>461965</v>
       </c>
       <c r="R63" t="n">
-        <v>6781025</v>
+        <v>6780759</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7477,41 +7479,40 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130092205</v>
+        <v>130092209</v>
       </c>
       <c r="B64" t="n">
-        <v>8451</v>
+        <v>57738</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -7565,7 +7566,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7691,10 +7691,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130087512</v>
+        <v>130087492</v>
       </c>
       <c r="B66" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7702,39 +7702,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>461956</v>
+        <v>461944</v>
       </c>
       <c r="R66" t="n">
-        <v>6780787</v>
+        <v>6780796</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7803,10 +7798,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130092026</v>
+        <v>130087119</v>
       </c>
       <c r="B67" t="n">
-        <v>78852</v>
+        <v>79095</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7814,40 +7809,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>461858</v>
+        <v>461918</v>
       </c>
       <c r="R67" t="n">
-        <v>6780846</v>
+        <v>6780787</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7874,40 +7866,54 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130087716</v>
+        <v>130087669</v>
       </c>
       <c r="B68" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7915,21 +7921,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7939,10 +7945,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>461894</v>
+        <v>461929</v>
       </c>
       <c r="R68" t="n">
-        <v>6780914</v>
+        <v>6780891</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8011,10 +8017,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130085288</v>
+        <v>130087512</v>
       </c>
       <c r="B69" t="n">
-        <v>92122</v>
+        <v>57738</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8022,37 +8028,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5467</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>461858</v>
+        <v>461956</v>
       </c>
       <c r="R69" t="n">
-        <v>6780876</v>
+        <v>6780787</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8081,7 +8092,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8091,7 +8102,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8106,62 +8117,60 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130087222</v>
+        <v>130092026</v>
       </c>
       <c r="B70" t="n">
-        <v>8451</v>
+        <v>78852</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>462001</v>
+        <v>461858</v>
       </c>
       <c r="R70" t="n">
-        <v>6780764</v>
+        <v>6780846</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8191,98 +8200,75 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>13:46</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>13:46</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Äldre spår I tallåga</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130092389</v>
+        <v>130087716</v>
       </c>
       <c r="B71" t="n">
-        <v>8451</v>
+        <v>79714</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>461870</v>
+        <v>461894</v>
       </c>
       <c r="R71" t="n">
-        <v>6780967</v>
+        <v>6780914</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8312,62 +8298,71 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130087245</v>
+        <v>130085288</v>
       </c>
       <c r="B72" t="n">
-        <v>8451</v>
+        <v>92124</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>5467</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8377,13 +8372,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>461946</v>
+        <v>461858</v>
       </c>
       <c r="R72" t="n">
-        <v>6780867</v>
+        <v>6780876</v>
       </c>
       <c r="S72" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8412,7 +8407,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8422,7 +8417,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8449,45 +8444,50 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130087492</v>
+        <v>130087222</v>
       </c>
       <c r="B73" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>461944</v>
+        <v>462001</v>
       </c>
       <c r="R73" t="n">
-        <v>6780796</v>
+        <v>6780764</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8519,7 +8519,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8529,7 +8529,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Äldre spår I tallåga</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8544,60 +8549,69 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130087119</v>
+        <v>130092389</v>
       </c>
       <c r="B74" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>461918</v>
+        <v>461870</v>
       </c>
       <c r="R74" t="n">
-        <v>6780787</v>
+        <v>6780967</v>
       </c>
       <c r="S74" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8624,92 +8638,78 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130087669</v>
+        <v>130087245</v>
       </c>
       <c r="B75" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>461929</v>
+        <v>461946</v>
       </c>
       <c r="R75" t="n">
-        <v>6780891</v>
+        <v>6780867</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8748,7 +8748,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8763,22 +8763,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130087408</v>
+        <v>130086767</v>
       </c>
       <c r="B76" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8786,39 +8786,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>462039</v>
+        <v>461850</v>
       </c>
       <c r="R76" t="n">
-        <v>6780770</v>
+        <v>6780913</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8861,6 +8856,11 @@
       <c r="AB76" t="inlineStr">
         <is>
           <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>2 bild. Rikligt till måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8887,10 +8887,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130086767</v>
+        <v>130087408</v>
       </c>
       <c r="B77" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8898,34 +8898,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>461850</v>
+        <v>462039</v>
       </c>
       <c r="R77" t="n">
-        <v>6780913</v>
+        <v>6780770</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8968,11 +8973,6 @@
       <c r="AB77" t="inlineStr">
         <is>
           <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>2 bild. Rikligt till måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8999,10 +8999,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130087418</v>
+        <v>130086966</v>
       </c>
       <c r="B78" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9010,37 +9010,42 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>462039</v>
+        <v>461946</v>
       </c>
       <c r="R78" t="n">
-        <v>6780770</v>
+        <v>6780867</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9069,7 +9074,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9079,7 +9084,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9094,12 +9104,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -9218,10 +9228,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130092215</v>
+        <v>130087418</v>
       </c>
       <c r="B80" t="n">
-        <v>78853</v>
+        <v>79095</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9229,37 +9239,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>462002</v>
+        <v>462039</v>
       </c>
       <c r="R80" t="n">
-        <v>6780772</v>
+        <v>6780770</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9289,40 +9296,49 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130086966</v>
+        <v>130092215</v>
       </c>
       <c r="B81" t="n">
-        <v>57741</v>
+        <v>78853</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9330,42 +9346,40 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>461946</v>
+        <v>462002</v>
       </c>
       <c r="R81" t="n">
-        <v>6780867</v>
+        <v>6780772</v>
       </c>
       <c r="S81" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9392,32 +9406,18 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -9439,7 +9439,7 @@
         <v>130086497</v>
       </c>
       <c r="B82" t="n">
-        <v>90671</v>
+        <v>90673</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10409,48 +10409,50 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>130091794</v>
+        <v>130086721</v>
       </c>
       <c r="B91" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>461710</v>
+        <v>461832</v>
       </c>
       <c r="R91" t="n">
-        <v>6780886</v>
+        <v>6780916</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10480,67 +10482,87 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Äldre spår i torrtall</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>130092053</v>
+        <v>130092063</v>
       </c>
       <c r="B92" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -10548,10 +10570,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>461926</v>
+        <v>461946</v>
       </c>
       <c r="R92" t="n">
-        <v>6780853</v>
+        <v>6780839</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10611,45 +10633,50 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>130083753</v>
+        <v>130087850</v>
       </c>
       <c r="B93" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>461711</v>
+        <v>461873</v>
       </c>
       <c r="R93" t="n">
-        <v>6780852</v>
+        <v>6780961</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10681,7 +10708,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10691,7 +10718,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10718,7 +10745,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130087798</v>
+        <v>130091794</v>
       </c>
       <c r="B94" t="n">
         <v>79095</v>
@@ -10747,16 +10774,19 @@
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>461864</v>
+        <v>461710</v>
       </c>
       <c r="R94" t="n">
-        <v>6780951</v>
+        <v>6780886</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10786,89 +10816,78 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>130086721</v>
+        <v>130092053</v>
       </c>
       <c r="B95" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>461832</v>
+        <v>461926</v>
       </c>
       <c r="R95" t="n">
-        <v>6780916</v>
+        <v>6780853</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10898,98 +10917,75 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Äldre spår i torrtall</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>130092063</v>
+        <v>130083753</v>
       </c>
       <c r="B96" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>461946</v>
+        <v>461711</v>
       </c>
       <c r="R96" t="n">
-        <v>6780839</v>
+        <v>6780852</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11019,80 +11015,84 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>130087850</v>
+        <v>130087798</v>
       </c>
       <c r="B97" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>461873</v>
+        <v>461864</v>
       </c>
       <c r="R97" t="n">
-        <v>6780961</v>
+        <v>6780951</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11380,7 +11380,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>130091832</v>
+        <v>130087184</v>
       </c>
       <c r="B100" t="n">
         <v>79095</v>
@@ -11409,22 +11409,19 @@
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>461738</v>
+        <v>461948</v>
       </c>
       <c r="R100" t="n">
-        <v>6780825</v>
+        <v>6780740</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11451,73 +11448,81 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>130091828</v>
+        <v>130091832</v>
       </c>
       <c r="B101" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -11525,10 +11530,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>461736</v>
+        <v>461738</v>
       </c>
       <c r="R101" t="n">
-        <v>6780844</v>
+        <v>6780825</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11588,7 +11593,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>130091798</v>
+        <v>130091828</v>
       </c>
       <c r="B102" t="n">
         <v>8451</v>
@@ -11632,10 +11637,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>461713</v>
+        <v>461736</v>
       </c>
       <c r="R102" t="n">
-        <v>6780880</v>
+        <v>6780844</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11695,37 +11700,43 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>130092019</v>
+        <v>130091798</v>
       </c>
       <c r="B103" t="n">
-        <v>78853</v>
+        <v>8451</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
@@ -11733,10 +11744,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>461858</v>
+        <v>461713</v>
       </c>
       <c r="R103" t="n">
-        <v>6780846</v>
+        <v>6780880</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11796,10 +11807,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>130087184</v>
+        <v>130092019</v>
       </c>
       <c r="B104" t="n">
-        <v>79095</v>
+        <v>78853</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11807,37 +11818,40 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>461948</v>
+        <v>461858</v>
       </c>
       <c r="R104" t="n">
-        <v>6780740</v>
+        <v>6780846</v>
       </c>
       <c r="S104" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11864,44 +11878,30 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
-        </is>
-      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
@@ -12009,7 +12009,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>130082810</v>
+        <v>130091785</v>
       </c>
       <c r="B106" t="n">
         <v>79095</v>
@@ -12038,16 +12038,19 @@
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>461757</v>
+        <v>461710</v>
       </c>
       <c r="R106" t="n">
-        <v>6781096</v>
+        <v>6780938</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12077,46 +12080,37 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>130087616</v>
+        <v>130082810</v>
       </c>
       <c r="B107" t="n">
         <v>79095</v>
@@ -12151,10 +12145,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>461970</v>
+        <v>461757</v>
       </c>
       <c r="R107" t="n">
-        <v>6780823</v>
+        <v>6781096</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12186,7 +12180,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12196,12 +12190,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12228,7 +12217,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>130091785</v>
+        <v>130087616</v>
       </c>
       <c r="B108" t="n">
         <v>79095</v>
@@ -12257,19 +12246,16 @@
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>461710</v>
+        <v>461970</v>
       </c>
       <c r="R108" t="n">
-        <v>6780938</v>
+        <v>6780823</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12299,30 +12285,44 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter</t>
+        </is>
+      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -12650,10 +12650,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>130087227</v>
+        <v>130087271</v>
       </c>
       <c r="B112" t="n">
-        <v>57738</v>
+        <v>79714</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12661,42 +12661,37 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>461948</v>
+        <v>462051</v>
       </c>
       <c r="R112" t="n">
-        <v>6780740</v>
+        <v>6780727</v>
       </c>
       <c r="S112" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12762,7 +12757,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>130087844</v>
+        <v>130087227</v>
       </c>
       <c r="B113" t="n">
         <v>57738</v>
@@ -12802,13 +12797,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>461873</v>
+        <v>461948</v>
       </c>
       <c r="R113" t="n">
-        <v>6780961</v>
+        <v>6780740</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12874,50 +12869,50 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>130085157</v>
+        <v>130087844</v>
       </c>
       <c r="B114" t="n">
-        <v>8451</v>
+        <v>57738</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>461859</v>
+        <v>461873</v>
       </c>
       <c r="R114" t="n">
-        <v>6780861</v>
+        <v>6780961</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12949,7 +12944,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12959,7 +12954,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12974,57 +12969,62 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>130087271</v>
+        <v>130085157</v>
       </c>
       <c r="B115" t="n">
-        <v>79714</v>
+        <v>8451</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>462051</v>
+        <v>461859</v>
       </c>
       <c r="R115" t="n">
-        <v>6780727</v>
+        <v>6780861</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13056,7 +13056,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13081,12 +13081,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
@@ -13096,7 +13096,7 @@
         <v>130092071</v>
       </c>
       <c r="B116" t="n">
-        <v>91937</v>
+        <v>91939</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13194,10 +13194,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>130092122</v>
+        <v>130092139</v>
       </c>
       <c r="B117" t="n">
-        <v>79119</v>
+        <v>8451</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13205,26 +13205,32 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6434</v>
+        <v>106545</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -13232,10 +13238,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>461986</v>
+        <v>461975</v>
       </c>
       <c r="R117" t="n">
-        <v>6780804</v>
+        <v>6780791</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13295,10 +13301,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>130091843</v>
+        <v>130092033</v>
       </c>
       <c r="B118" t="n">
-        <v>79095</v>
+        <v>78853</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13306,21 +13312,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13333,10 +13339,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>461720</v>
+        <v>461871</v>
       </c>
       <c r="R118" t="n">
-        <v>6780825</v>
+        <v>6780851</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13396,10 +13402,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>130092139</v>
+        <v>130092122</v>
       </c>
       <c r="B119" t="n">
-        <v>8451</v>
+        <v>79119</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13407,32 +13413,26 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>106545</v>
+        <v>6434</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
@@ -13440,10 +13440,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>461975</v>
+        <v>461986</v>
       </c>
       <c r="R119" t="n">
-        <v>6780791</v>
+        <v>6780804</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13503,10 +13503,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>130092033</v>
+        <v>130087759</v>
       </c>
       <c r="B120" t="n">
-        <v>78853</v>
+        <v>79095</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13514,37 +13514,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>461871</v>
+        <v>461879</v>
       </c>
       <c r="R120" t="n">
-        <v>6780851</v>
+        <v>6780924</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13574,37 +13571,46 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>130087759</v>
+        <v>130091843</v>
       </c>
       <c r="B121" t="n">
         <v>79095</v>
@@ -13633,16 +13639,19 @@
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>461879</v>
+        <v>461720</v>
       </c>
       <c r="R121" t="n">
-        <v>6780924</v>
+        <v>6780825</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13672,87 +13681,75 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>130091745</v>
+        <v>130087075</v>
       </c>
       <c r="B122" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>461749</v>
+        <v>461944</v>
       </c>
       <c r="R122" t="n">
-        <v>6781031</v>
+        <v>6780796</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13782,40 +13779,49 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>130086831</v>
+        <v>130091751</v>
       </c>
       <c r="B123" t="n">
-        <v>79095</v>
+        <v>79127</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13823,34 +13829,37 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>461887</v>
+        <v>461737</v>
       </c>
       <c r="R123" t="n">
-        <v>6780890</v>
+        <v>6781057</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13880,84 +13889,78 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>130087075</v>
+        <v>130091628</v>
       </c>
       <c r="B124" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>461944</v>
+        <v>461750</v>
       </c>
       <c r="R124" t="n">
-        <v>6780796</v>
+        <v>6781031</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13987,49 +13990,40 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>130083776</v>
+        <v>130091745</v>
       </c>
       <c r="B125" t="n">
-        <v>78853</v>
+        <v>79095</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14037,34 +14031,37 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>461738</v>
+        <v>461749</v>
       </c>
       <c r="R125" t="n">
-        <v>6780866</v>
+        <v>6781031</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14094,49 +14091,40 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>10:54</t>
-        </is>
-      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>10:54</t>
-        </is>
-      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>130091751</v>
+        <v>130086831</v>
       </c>
       <c r="B126" t="n">
-        <v>79127</v>
+        <v>79095</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14144,37 +14132,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>461737</v>
+        <v>461887</v>
       </c>
       <c r="R126" t="n">
-        <v>6781057</v>
+        <v>6780890</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14204,40 +14189,49 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD126" t="b">
         <v>0</v>
       </c>
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>130091628</v>
+        <v>130083776</v>
       </c>
       <c r="B127" t="n">
-        <v>79095</v>
+        <v>78853</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14245,37 +14239,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>461750</v>
+        <v>461738</v>
       </c>
       <c r="R127" t="n">
-        <v>6781031</v>
+        <v>6780866</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14305,37 +14296,46 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>130087061</v>
+        <v>130091780</v>
       </c>
       <c r="B128" t="n">
         <v>79095</v>
@@ -14364,16 +14364,19 @@
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>461952</v>
+        <v>461742</v>
       </c>
       <c r="R128" t="n">
-        <v>6780820</v>
+        <v>6781010</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14403,46 +14406,37 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD128" t="b">
         <v>0</v>
       </c>
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>130087445</v>
+        <v>130087722</v>
       </c>
       <c r="B129" t="n">
         <v>79095</v>
@@ -14477,13 +14471,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>462022</v>
+        <v>461894</v>
       </c>
       <c r="R129" t="n">
-        <v>6780775</v>
+        <v>6780914</v>
       </c>
       <c r="S129" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14523,11 +14517,6 @@
       <c r="AB129" t="inlineStr">
         <is>
           <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14554,7 +14543,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>130087722</v>
+        <v>130087061</v>
       </c>
       <c r="B130" t="n">
         <v>79095</v>
@@ -14589,10 +14578,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>461894</v>
+        <v>461952</v>
       </c>
       <c r="R130" t="n">
-        <v>6780914</v>
+        <v>6780820</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14661,10 +14650,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>130085207</v>
+        <v>130087445</v>
       </c>
       <c r="B131" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14672,42 +14661,37 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>461844</v>
+        <v>462022</v>
       </c>
       <c r="R131" t="n">
-        <v>6780835</v>
+        <v>6780775</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14736,7 +14720,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14746,7 +14730,12 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14773,7 +14762,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>130087794</v>
+        <v>130085207</v>
       </c>
       <c r="B132" t="n">
         <v>57738</v>
@@ -14804,7 +14793,7 @@
       <c r="I132" t="inlineStr"/>
       <c r="M132" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -14813,10 +14802,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>461864</v>
+        <v>461844</v>
       </c>
       <c r="R132" t="n">
-        <v>6780951</v>
+        <v>6780835</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14848,7 +14837,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14858,7 +14847,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14885,7 +14874,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>130083972</v>
+        <v>130087794</v>
       </c>
       <c r="B133" t="n">
         <v>57738</v>
@@ -14916,7 +14905,7 @@
       <c r="I133" t="inlineStr"/>
       <c r="M133" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -14925,10 +14914,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>461717</v>
+        <v>461864</v>
       </c>
       <c r="R133" t="n">
-        <v>6780842</v>
+        <v>6780951</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14960,7 +14949,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14970,7 +14959,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14997,10 +14986,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>130091780</v>
+        <v>130083972</v>
       </c>
       <c r="B134" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15008,37 +14997,39 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>461742</v>
+        <v>461717</v>
       </c>
       <c r="R134" t="n">
-        <v>6781010</v>
+        <v>6780842</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15068,30 +15059,39 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AD134" t="b">
         <v>0</v>
       </c>
       <c r="AE134" t="b">
         <v>0</v>
       </c>
-      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
@@ -15317,10 +15317,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>130087789</v>
+        <v>130087057</v>
       </c>
       <c r="B137" t="n">
-        <v>79127</v>
+        <v>79714</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15328,34 +15328,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>461857</v>
+        <v>461952</v>
       </c>
       <c r="R137" t="n">
-        <v>6780939</v>
+        <v>6780820</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15387,7 +15387,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15397,12 +15397,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Sparsamt på gran</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15417,62 +15412,57 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>130087754</v>
+        <v>130087401</v>
       </c>
       <c r="B138" t="n">
-        <v>57738</v>
+        <v>8451</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>461879</v>
+        <v>462039</v>
       </c>
       <c r="R138" t="n">
-        <v>6780924</v>
+        <v>6780770</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15541,32 +15531,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>130083742</v>
+        <v>130086828</v>
       </c>
       <c r="B139" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15576,10 +15566,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>461699</v>
+        <v>461887</v>
       </c>
       <c r="R139" t="n">
-        <v>6780870</v>
+        <v>6780890</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15611,7 +15601,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15621,7 +15611,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15648,10 +15638,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>130087057</v>
+        <v>130087789</v>
       </c>
       <c r="B140" t="n">
-        <v>79714</v>
+        <v>79127</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15659,34 +15649,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>461952</v>
+        <v>461857</v>
       </c>
       <c r="R140" t="n">
-        <v>6780820</v>
+        <v>6780939</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15718,7 +15708,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15728,7 +15718,12 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Sparsamt på gran</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15743,44 +15738,44 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>130087401</v>
+        <v>130083742</v>
       </c>
       <c r="B141" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15790,10 +15785,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>462039</v>
+        <v>461699</v>
       </c>
       <c r="R141" t="n">
-        <v>6780770</v>
+        <v>6780870</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15825,7 +15820,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15835,7 +15830,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15862,45 +15857,50 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>130086828</v>
+        <v>130087754</v>
       </c>
       <c r="B142" t="n">
-        <v>8451</v>
+        <v>57738</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>461887</v>
+        <v>461879</v>
       </c>
       <c r="R142" t="n">
-        <v>6780890</v>
+        <v>6780924</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16293,45 +16293,54 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>130087667</v>
+        <v>130091989</v>
       </c>
       <c r="B146" t="n">
-        <v>79714</v>
+        <v>8451</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>461929</v>
+        <v>461800</v>
       </c>
       <c r="R146" t="n">
-        <v>6780891</v>
+        <v>6780830</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16361,93 +16370,75 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z146" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB146" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD146" t="b">
         <v>0</v>
       </c>
       <c r="AE146" t="b">
         <v>0</v>
       </c>
+      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>130091989</v>
+        <v>130086869</v>
       </c>
       <c r="B147" t="n">
-        <v>8451</v>
+        <v>78853</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>461800</v>
+        <v>461922</v>
       </c>
       <c r="R147" t="n">
-        <v>6780830</v>
+        <v>6780874</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16477,40 +16468,54 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
+        </is>
+      </c>
       <c r="AD147" t="b">
         <v>0</v>
       </c>
       <c r="AE147" t="b">
         <v>0</v>
       </c>
-      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
       </c>
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>130086869</v>
+        <v>130087667</v>
       </c>
       <c r="B148" t="n">
-        <v>78853</v>
+        <v>79714</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16518,34 +16523,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>461922</v>
+        <v>461929</v>
       </c>
       <c r="R148" t="n">
-        <v>6780874</v>
+        <v>6780891</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16577,7 +16582,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16587,12 +16592,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16607,22 +16607,22 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>130087527</v>
+        <v>130086826</v>
       </c>
       <c r="B149" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16630,34 +16630,39 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>461956</v>
+        <v>461887</v>
       </c>
       <c r="R149" t="n">
-        <v>6780787</v>
+        <v>6780890</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16726,7 +16731,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>130086826</v>
+        <v>130092006</v>
       </c>
       <c r="B150" t="n">
         <v>57738</v>
@@ -16755,21 +16760,24 @@
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
       <c r="M150" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>461887</v>
+        <v>461808</v>
       </c>
       <c r="R150" t="n">
-        <v>6780890</v>
+        <v>6780861</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16799,19 +16807,9 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z150" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AB150" t="inlineStr">
-        <is>
-          <t>13:03</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16826,19 +16824,19 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>130092006</v>
+        <v>130087153</v>
       </c>
       <c r="B151" t="n">
         <v>57738</v>
@@ -16867,24 +16865,21 @@
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
       <c r="M151" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>461808</v>
+        <v>461955</v>
       </c>
       <c r="R151" t="n">
-        <v>6780861</v>
+        <v>6780741</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16919,6 +16914,11 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Äldre spår I högstubbe</t>
+        </is>
+      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
@@ -16931,22 +16931,22 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>130087153</v>
+        <v>130084608</v>
       </c>
       <c r="B152" t="n">
-        <v>57738</v>
+        <v>78853</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16954,39 +16954,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>461955</v>
+        <v>461805</v>
       </c>
       <c r="R152" t="n">
-        <v>6780741</v>
+        <v>6780835</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17016,14 +17011,24 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Äldre spår I högstubbe</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17050,10 +17055,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>130084608</v>
+        <v>130087527</v>
       </c>
       <c r="B153" t="n">
-        <v>78853</v>
+        <v>79095</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17061,34 +17066,34 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>461805</v>
+        <v>461956</v>
       </c>
       <c r="R153" t="n">
-        <v>6780835</v>
+        <v>6780787</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17120,7 +17125,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17130,12 +17135,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>11:27</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17150,12 +17150,12 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
@@ -17370,37 +17370,46 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>130091789</v>
+        <v>130091841</v>
       </c>
       <c r="B156" t="n">
-        <v>91021</v>
+        <v>57741</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>5685</v>
+        <v>100109</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
@@ -17408,10 +17417,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>461710</v>
+        <v>461720</v>
       </c>
       <c r="R156" t="n">
-        <v>6780886</v>
+        <v>6780825</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17446,13 +17455,17 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>hack födosök i gran och ringhackad gran intill</t>
+        </is>
+      </c>
       <c r="AD156" t="b">
         <v>0</v>
       </c>
       <c r="AE156" t="b">
         <v>0</v>
       </c>
-      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
@@ -17471,54 +17484,50 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>130092010</v>
+        <v>130085067</v>
       </c>
       <c r="B157" t="n">
-        <v>8451</v>
+        <v>57738</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
       <c r="M157" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N157" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>461808</v>
+        <v>461857</v>
       </c>
       <c r="R157" t="n">
-        <v>6780861</v>
+        <v>6780842</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17548,40 +17557,49 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AD157" t="b">
         <v>0</v>
       </c>
       <c r="AE157" t="b">
         <v>0</v>
       </c>
-      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>130085067</v>
+        <v>130092430</v>
       </c>
       <c r="B158" t="n">
-        <v>57738</v>
+        <v>78853</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17589,39 +17607,37 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>461857</v>
+        <v>461933</v>
       </c>
       <c r="R158" t="n">
-        <v>6780842</v>
+        <v>6780838</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17651,19 +17667,14 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>10:14</t>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17672,18 +17683,19 @@
       <c r="AE158" t="b">
         <v>0</v>
       </c>
+      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
@@ -17791,46 +17803,37 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>130091841</v>
+        <v>130091789</v>
       </c>
       <c r="B160" t="n">
-        <v>57741</v>
+        <v>91023</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100109</v>
+        <v>5685</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
@@ -17838,10 +17841,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>461720</v>
+        <v>461710</v>
       </c>
       <c r="R160" t="n">
-        <v>6780825</v>
+        <v>6780886</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17876,17 +17879,13 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>hack födosök i gran och ringhackad gran intill</t>
-        </is>
-      </c>
       <c r="AD160" t="b">
         <v>0</v>
       </c>
       <c r="AE160" t="b">
         <v>0</v>
       </c>
+      <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="b">
         <v>0</v>
       </c>
@@ -17905,37 +17904,43 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>130092430</v>
+        <v>130092010</v>
       </c>
       <c r="B161" t="n">
-        <v>78853</v>
+        <v>8451</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
@@ -17943,10 +17948,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>461933</v>
+        <v>461808</v>
       </c>
       <c r="R161" t="n">
-        <v>6780838</v>
+        <v>6780861</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17981,11 +17986,6 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
-        </is>
-      </c>
       <c r="AD161" t="b">
         <v>0</v>
       </c>
@@ -17999,12 +17999,12 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
@@ -18132,7 +18132,7 @@
         <v>130084138</v>
       </c>
       <c r="B163" t="n">
-        <v>91623</v>
+        <v>91625</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>130083774</v>
       </c>
       <c r="B164" t="n">
-        <v>90671</v>
+        <v>90673</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19027,7 +19027,7 @@
         <v>130092045</v>
       </c>
       <c r="B171" t="n">
-        <v>91692</v>
+        <v>91694</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20374,43 +20374,37 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>130157677</v>
+        <v>130157446</v>
       </c>
       <c r="B184" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr"/>
-      <c r="L184" t="inlineStr"/>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
@@ -20418,10 +20412,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>461370</v>
+        <v>462162</v>
       </c>
       <c r="R184" t="n">
-        <v>6780963</v>
+        <v>6780616</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20462,7 +20456,6 @@
       <c r="AE184" t="b">
         <v>0</v>
       </c>
-      <c r="AF184" t="inlineStr"/>
       <c r="AG184" t="b">
         <v>0</v>
       </c>
@@ -20474,44 +20467,50 @@
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>130157446</v>
+        <v>130157677</v>
       </c>
       <c r="B185" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
@@ -20519,10 +20518,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>462162</v>
+        <v>461370</v>
       </c>
       <c r="R185" t="n">
-        <v>6780616</v>
+        <v>6780963</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20563,6 +20562,7 @@
       <c r="AE185" t="b">
         <v>0</v>
       </c>
+      <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="b">
         <v>0</v>
       </c>
@@ -20574,7 +20574,7 @@
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>

--- a/artfynd/A 58003-2025 artfynd.xlsx
+++ b/artfynd/A 58003-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129969590</v>
+        <v>129973732</v>
       </c>
       <c r="B2" t="n">
-        <v>57738</v>
+        <v>79180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461816</v>
+        <v>461665</v>
       </c>
       <c r="R2" t="n">
-        <v>6780978</v>
+        <v>6780925</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129973732</v>
+        <v>129969590</v>
       </c>
       <c r="B3" t="n">
-        <v>79095</v>
+        <v>57823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461665</v>
+        <v>461816</v>
       </c>
       <c r="R3" t="n">
-        <v>6780925</v>
+        <v>6780978</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
         <v>129971610</v>
       </c>
       <c r="B4" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>129970747</v>
       </c>
       <c r="B5" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>129971802</v>
       </c>
       <c r="B6" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1327,50 +1327,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129971831</v>
+        <v>129971607</v>
       </c>
       <c r="B8" t="n">
-        <v>8451</v>
+        <v>79770</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461686</v>
+        <v>461733</v>
       </c>
       <c r="R8" t="n">
-        <v>6780923</v>
+        <v>6780958</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1439,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129972961</v>
+        <v>129973829</v>
       </c>
       <c r="B9" t="n">
-        <v>79095</v>
+        <v>57823</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,34 +1445,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461615</v>
+        <v>461730</v>
       </c>
       <c r="R9" t="n">
-        <v>6780923</v>
+        <v>6780969</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129973829</v>
+        <v>129972961</v>
       </c>
       <c r="B10" t="n">
-        <v>57738</v>
+        <v>79180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,39 +1557,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461730</v>
+        <v>461615</v>
       </c>
       <c r="R10" t="n">
-        <v>6780969</v>
+        <v>6780923</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1658,45 +1653,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129971607</v>
+        <v>129971831</v>
       </c>
       <c r="B11" t="n">
-        <v>79685</v>
+        <v>8451</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461733</v>
+        <v>461686</v>
       </c>
       <c r="R11" t="n">
-        <v>6780958</v>
+        <v>6780923</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1768,7 +1768,7 @@
         <v>129970971</v>
       </c>
       <c r="B12" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>129971115</v>
       </c>
       <c r="B13" t="n">
-        <v>79685</v>
+        <v>79770</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>129971787</v>
       </c>
       <c r="B14" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2086,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129971585</v>
+        <v>129971127</v>
       </c>
       <c r="B15" t="n">
-        <v>57738</v>
+        <v>79180</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,39 +2097,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461736</v>
+        <v>461762</v>
       </c>
       <c r="R15" t="n">
-        <v>6780931</v>
+        <v>6780940</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2198,10 +2193,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129971127</v>
+        <v>129971585</v>
       </c>
       <c r="B16" t="n">
-        <v>79095</v>
+        <v>57823</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2209,34 +2204,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461762</v>
+        <v>461736</v>
       </c>
       <c r="R16" t="n">
-        <v>6780940</v>
+        <v>6780931</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2308,7 +2308,7 @@
         <v>129973851</v>
       </c>
       <c r="B17" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>129971608</v>
       </c>
       <c r="B18" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2631,10 +2631,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129971589</v>
+        <v>129972800</v>
       </c>
       <c r="B20" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461736</v>
+        <v>461611</v>
       </c>
       <c r="R20" t="n">
-        <v>6780931</v>
+        <v>6780900</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2738,10 +2738,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129972800</v>
+        <v>129971589</v>
       </c>
       <c r="B21" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461611</v>
+        <v>461736</v>
       </c>
       <c r="R21" t="n">
-        <v>6780900</v>
+        <v>6780931</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2848,7 +2848,7 @@
         <v>129971741</v>
       </c>
       <c r="B22" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3064,50 +3064,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129973842</v>
+        <v>129970829</v>
       </c>
       <c r="B24" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461730</v>
+        <v>461800</v>
       </c>
       <c r="R24" t="n">
-        <v>6780969</v>
+        <v>6781016</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3176,45 +3171,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129970829</v>
+        <v>129973842</v>
       </c>
       <c r="B25" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461800</v>
+        <v>461730</v>
       </c>
       <c r="R25" t="n">
-        <v>6781016</v>
+        <v>6780969</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3283,45 +3283,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129972457</v>
+        <v>129971289</v>
       </c>
       <c r="B26" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461687</v>
+        <v>461751</v>
       </c>
       <c r="R26" t="n">
-        <v>6780875</v>
+        <v>6780936</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3390,50 +3395,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129971289</v>
+        <v>129972394</v>
       </c>
       <c r="B27" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461751</v>
+        <v>461679</v>
       </c>
       <c r="R27" t="n">
-        <v>6780936</v>
+        <v>6780885</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3502,10 +3502,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129972394</v>
+        <v>129972457</v>
       </c>
       <c r="B28" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3537,10 +3537,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461679</v>
+        <v>461687</v>
       </c>
       <c r="R28" t="n">
-        <v>6780885</v>
+        <v>6780875</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3612,7 +3612,7 @@
         <v>129972793</v>
       </c>
       <c r="B29" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3721,50 +3721,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129971587</v>
+        <v>129970675</v>
       </c>
       <c r="B30" t="n">
-        <v>8451</v>
+        <v>79799</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461736</v>
+        <v>461789</v>
       </c>
       <c r="R30" t="n">
-        <v>6780931</v>
+        <v>6780961</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3833,7 +3828,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129972990</v>
+        <v>129971587</v>
       </c>
       <c r="B31" t="n">
         <v>8451</v>
@@ -3873,10 +3868,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461615</v>
+        <v>461736</v>
       </c>
       <c r="R31" t="n">
-        <v>6780923</v>
+        <v>6780931</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3945,45 +3940,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129970675</v>
+        <v>129972990</v>
       </c>
       <c r="B32" t="n">
-        <v>79714</v>
+        <v>8451</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461789</v>
+        <v>461615</v>
       </c>
       <c r="R32" t="n">
-        <v>6780961</v>
+        <v>6780923</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4055,7 +4055,7 @@
         <v>129971825</v>
       </c>
       <c r="B33" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>129970738</v>
       </c>
       <c r="B34" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>129971832</v>
       </c>
       <c r="B35" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>129970828</v>
       </c>
       <c r="B36" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4485,10 +4485,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129971739</v>
+        <v>129971259</v>
       </c>
       <c r="B37" t="n">
-        <v>79685</v>
+        <v>57823</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4496,34 +4496,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461741</v>
+        <v>461751</v>
       </c>
       <c r="R37" t="n">
-        <v>6780920</v>
+        <v>6780936</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4592,10 +4597,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129973978</v>
+        <v>129971739</v>
       </c>
       <c r="B38" t="n">
-        <v>79095</v>
+        <v>79770</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4603,21 +4608,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4627,10 +4632,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461749</v>
+        <v>461741</v>
       </c>
       <c r="R38" t="n">
-        <v>6780997</v>
+        <v>6780920</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4699,10 +4704,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129971259</v>
+        <v>129973978</v>
       </c>
       <c r="B39" t="n">
-        <v>57738</v>
+        <v>79180</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4710,39 +4715,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461751</v>
+        <v>461749</v>
       </c>
       <c r="R39" t="n">
-        <v>6780936</v>
+        <v>6780997</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4814,7 +4814,7 @@
         <v>129971804</v>
       </c>
       <c r="B40" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4918,10 +4918,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129971290</v>
+        <v>129972983</v>
       </c>
       <c r="B41" t="n">
-        <v>79095</v>
+        <v>57823</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4929,34 +4929,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461751</v>
+        <v>461615</v>
       </c>
       <c r="R41" t="n">
-        <v>6780936</v>
+        <v>6780923</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5025,10 +5030,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129970813</v>
+        <v>129970961</v>
       </c>
       <c r="B42" t="n">
-        <v>79714</v>
+        <v>79770</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5036,21 +5041,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5060,10 +5065,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461800</v>
+        <v>461789</v>
       </c>
       <c r="R42" t="n">
-        <v>6781016</v>
+        <v>6780961</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5132,10 +5137,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129972983</v>
+        <v>129971290</v>
       </c>
       <c r="B43" t="n">
-        <v>57738</v>
+        <v>79180</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5143,39 +5148,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461615</v>
+        <v>461751</v>
       </c>
       <c r="R43" t="n">
-        <v>6780923</v>
+        <v>6780936</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5244,10 +5244,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129970961</v>
+        <v>129970813</v>
       </c>
       <c r="B44" t="n">
-        <v>79685</v>
+        <v>79799</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5255,21 +5255,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5279,10 +5279,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461789</v>
+        <v>461800</v>
       </c>
       <c r="R44" t="n">
-        <v>6780961</v>
+        <v>6781016</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5354,7 +5354,7 @@
         <v>129972707</v>
       </c>
       <c r="B45" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>129971438</v>
       </c>
       <c r="B46" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>129972538</v>
       </c>
       <c r="B47" t="n">
-        <v>91662</v>
+        <v>91749</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         <v>129972955</v>
       </c>
       <c r="B48" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
         <v>129969625</v>
       </c>
       <c r="B49" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5919,7 +5919,7 @@
         <v>129970888</v>
       </c>
       <c r="B50" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6032,10 +6032,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129973137</v>
+        <v>129972454</v>
       </c>
       <c r="B51" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6043,34 +6043,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461609</v>
+        <v>461687</v>
       </c>
       <c r="R51" t="n">
-        <v>6780949</v>
+        <v>6780875</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6117,7 +6122,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>3 bilder, rikligt i en radie av ca 50 meter</t>
+          <t>2 bilder</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6144,10 +6149,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129972233</v>
+        <v>129973137</v>
       </c>
       <c r="B52" t="n">
-        <v>57738</v>
+        <v>79180</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6155,42 +6160,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461679</v>
+        <v>461609</v>
       </c>
       <c r="R52" t="n">
-        <v>6780885</v>
+        <v>6780949</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6237,7 +6234,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>3 bilder, rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6264,10 +6261,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129969692</v>
+        <v>129972233</v>
       </c>
       <c r="B53" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6293,21 +6290,24 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>461799</v>
+        <v>461679</v>
       </c>
       <c r="R53" t="n">
-        <v>6780979</v>
+        <v>6780885</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6381,10 +6381,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129972454</v>
+        <v>129969692</v>
       </c>
       <c r="B54" t="n">
-        <v>57741</v>
+        <v>57823</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6392,16 +6392,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6421,10 +6421,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>461687</v>
+        <v>461799</v>
       </c>
       <c r="R54" t="n">
-        <v>6780875</v>
+        <v>6780979</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6471,7 +6471,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>2 bilder</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6498,32 +6498,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130087273</v>
+        <v>130087228</v>
       </c>
       <c r="B55" t="n">
-        <v>78853</v>
+        <v>8451</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6533,13 +6533,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>462051</v>
+        <v>461948</v>
       </c>
       <c r="R55" t="n">
-        <v>6780727</v>
+        <v>6780740</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6605,10 +6605,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130083775</v>
+        <v>130087273</v>
       </c>
       <c r="B56" t="n">
-        <v>79095</v>
+        <v>78938</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6616,21 +6616,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6640,10 +6640,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461717</v>
+        <v>462051</v>
       </c>
       <c r="R56" t="n">
-        <v>6780842</v>
+        <v>6780727</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6675,7 +6675,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6712,7 +6712,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130087228</v>
+        <v>130087516</v>
       </c>
       <c r="B57" t="n">
         <v>8451</v>
@@ -6741,19 +6741,24 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461948</v>
+        <v>461956</v>
       </c>
       <c r="R57" t="n">
-        <v>6780740</v>
+        <v>6780787</v>
       </c>
       <c r="S57" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6819,50 +6824,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130087516</v>
+        <v>130083775</v>
       </c>
       <c r="B58" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461956</v>
+        <v>461717</v>
       </c>
       <c r="R58" t="n">
-        <v>6780787</v>
+        <v>6780842</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6934,7 +6934,7 @@
         <v>130084991</v>
       </c>
       <c r="B59" t="n">
-        <v>79127</v>
+        <v>79212</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7043,10 +7043,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130092086</v>
+        <v>130087559</v>
       </c>
       <c r="B60" t="n">
-        <v>57741</v>
+        <v>57823</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7054,16 +7054,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7072,24 +7072,21 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461986</v>
+        <v>461970</v>
       </c>
       <c r="R60" t="n">
-        <v>6780804</v>
+        <v>6780823</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7119,14 +7116,19 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7141,22 +7143,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130087559</v>
+        <v>130092086</v>
       </c>
       <c r="B61" t="n">
-        <v>57738</v>
+        <v>57826</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7164,16 +7166,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7182,21 +7184,24 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>461970</v>
+        <v>461986</v>
       </c>
       <c r="R61" t="n">
-        <v>6780823</v>
+        <v>6780804</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7226,19 +7231,14 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>13:03</t>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7253,66 +7253,57 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130091775</v>
+        <v>130087919</v>
       </c>
       <c r="B62" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>461753</v>
+        <v>461853</v>
       </c>
       <c r="R62" t="n">
-        <v>6781025</v>
+        <v>6780990</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7342,37 +7333,46 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130092205</v>
+        <v>130091775</v>
       </c>
       <c r="B63" t="n">
         <v>8451</v>
@@ -7416,10 +7416,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461965</v>
+        <v>461753</v>
       </c>
       <c r="R63" t="n">
-        <v>6780759</v>
+        <v>6781025</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7479,40 +7479,41 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130092209</v>
+        <v>130092205</v>
       </c>
       <c r="B64" t="n">
-        <v>57738</v>
+        <v>8451</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -7566,6 +7567,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7584,10 +7586,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130087919</v>
+        <v>130092209</v>
       </c>
       <c r="B65" t="n">
-        <v>79095</v>
+        <v>57823</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7595,34 +7597,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>461853</v>
+        <v>461965</v>
       </c>
       <c r="R65" t="n">
-        <v>6780990</v>
+        <v>6780759</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7652,19 +7662,9 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>13:03</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7679,12 +7679,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7694,7 +7694,7 @@
         <v>130087492</v>
       </c>
       <c r="B66" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7798,48 +7798,57 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130087119</v>
+        <v>130092389</v>
       </c>
       <c r="B67" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>461918</v>
+        <v>461870</v>
       </c>
       <c r="R67" t="n">
-        <v>6780787</v>
+        <v>6780967</v>
       </c>
       <c r="S67" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7866,89 +7875,80 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130087669</v>
+        <v>130087222</v>
       </c>
       <c r="B68" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>461929</v>
+        <v>462001</v>
       </c>
       <c r="R68" t="n">
-        <v>6780891</v>
+        <v>6780764</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7980,7 +7980,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7990,7 +7990,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Äldre spår I tallåga</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8005,22 +8010,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130087512</v>
+        <v>130087716</v>
       </c>
       <c r="B69" t="n">
-        <v>57738</v>
+        <v>79799</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8028,39 +8033,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>461956</v>
+        <v>461894</v>
       </c>
       <c r="R69" t="n">
-        <v>6780787</v>
+        <v>6780914</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8129,10 +8129,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130092026</v>
+        <v>130087119</v>
       </c>
       <c r="B70" t="n">
-        <v>78852</v>
+        <v>79180</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8140,40 +8140,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>461858</v>
+        <v>461918</v>
       </c>
       <c r="R70" t="n">
-        <v>6780846</v>
+        <v>6780787</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8200,40 +8197,54 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130087716</v>
+        <v>130087512</v>
       </c>
       <c r="B71" t="n">
-        <v>79714</v>
+        <v>57823</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8241,34 +8252,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>461894</v>
+        <v>461956</v>
       </c>
       <c r="R71" t="n">
-        <v>6780914</v>
+        <v>6780787</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8337,10 +8353,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130085288</v>
+        <v>130087669</v>
       </c>
       <c r="B72" t="n">
-        <v>92124</v>
+        <v>79180</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8348,37 +8364,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5467</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>461858</v>
+        <v>461929</v>
       </c>
       <c r="R72" t="n">
-        <v>6780876</v>
+        <v>6780891</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8407,7 +8423,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8417,7 +8433,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8432,65 +8448,60 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130087222</v>
+        <v>130085288</v>
       </c>
       <c r="B73" t="n">
-        <v>8451</v>
+        <v>92211</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>5467</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>462001</v>
+        <v>461858</v>
       </c>
       <c r="R73" t="n">
-        <v>6780764</v>
+        <v>6780876</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8519,7 +8530,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8529,12 +8540,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:46</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Äldre spår I tallåga</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8549,55 +8555,49 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130092389</v>
+        <v>130092026</v>
       </c>
       <c r="B74" t="n">
-        <v>8451</v>
+        <v>78937</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -8605,10 +8605,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>461870</v>
+        <v>461858</v>
       </c>
       <c r="R74" t="n">
-        <v>6780967</v>
+        <v>6780846</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8656,12 +8656,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8775,10 +8775,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130086767</v>
+        <v>130087408</v>
       </c>
       <c r="B76" t="n">
-        <v>79095</v>
+        <v>57823</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8786,34 +8786,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>461850</v>
+        <v>462039</v>
       </c>
       <c r="R76" t="n">
-        <v>6780913</v>
+        <v>6780770</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8856,11 +8861,6 @@
       <c r="AB76" t="inlineStr">
         <is>
           <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>2 bild. Rikligt till måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8887,10 +8887,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130087408</v>
+        <v>130086767</v>
       </c>
       <c r="B77" t="n">
-        <v>57738</v>
+        <v>79180</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8898,39 +8898,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>462039</v>
+        <v>461850</v>
       </c>
       <c r="R77" t="n">
-        <v>6780770</v>
+        <v>6780913</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8973,6 +8968,11 @@
       <c r="AB77" t="inlineStr">
         <is>
           <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>2 bild. Rikligt till måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8999,10 +8999,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130086966</v>
+        <v>130087418</v>
       </c>
       <c r="B78" t="n">
-        <v>57741</v>
+        <v>79180</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9010,42 +9010,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>461946</v>
+        <v>462039</v>
       </c>
       <c r="R78" t="n">
-        <v>6780867</v>
+        <v>6780770</v>
       </c>
       <c r="S78" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9074,7 +9069,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9084,12 +9079,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:17</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9104,12 +9094,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -9228,10 +9218,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130087418</v>
+        <v>130086966</v>
       </c>
       <c r="B80" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9239,37 +9229,42 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>462039</v>
+        <v>461946</v>
       </c>
       <c r="R80" t="n">
-        <v>6780770</v>
+        <v>6780867</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9298,7 +9293,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9308,7 +9303,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9323,12 +9323,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9338,7 +9338,7 @@
         <v>130092215</v>
       </c>
       <c r="B81" t="n">
-        <v>78853</v>
+        <v>78938</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9439,7 +9439,7 @@
         <v>130086497</v>
       </c>
       <c r="B82" t="n">
-        <v>90673</v>
+        <v>90760</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9551,7 +9551,7 @@
         <v>130091631</v>
       </c>
       <c r="B83" t="n">
-        <v>79127</v>
+        <v>79212</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9649,45 +9649,54 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130085215</v>
+        <v>130091811</v>
       </c>
       <c r="B84" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>461844</v>
+        <v>461716</v>
       </c>
       <c r="R84" t="n">
-        <v>6780835</v>
+        <v>6780852</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9717,49 +9726,40 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130087832</v>
+        <v>130085215</v>
       </c>
       <c r="B85" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9791,10 +9791,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>461873</v>
+        <v>461844</v>
       </c>
       <c r="R85" t="n">
-        <v>6780961</v>
+        <v>6780835</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9826,7 +9826,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9836,7 +9836,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9863,54 +9863,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130091811</v>
+        <v>130087832</v>
       </c>
       <c r="B86" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>461716</v>
+        <v>461873</v>
       </c>
       <c r="R86" t="n">
-        <v>6780852</v>
+        <v>6780961</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9940,30 +9931,39 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -9973,7 +9973,7 @@
         <v>130092368</v>
       </c>
       <c r="B87" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10075,53 +10075,50 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130092059</v>
+        <v>130082759</v>
       </c>
       <c r="B88" t="n">
-        <v>57738</v>
+        <v>8451</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>461946</v>
+        <v>461757</v>
       </c>
       <c r="R88" t="n">
-        <v>6780839</v>
+        <v>6781096</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10151,9 +10148,19 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10168,62 +10175,65 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130082759</v>
+        <v>130092059</v>
       </c>
       <c r="B89" t="n">
-        <v>8451</v>
+        <v>57823</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>461757</v>
+        <v>461946</v>
       </c>
       <c r="R89" t="n">
-        <v>6781096</v>
+        <v>6780839</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10253,19 +10263,9 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>10:14</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10280,50 +10280,50 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>130085149</v>
+        <v>130086721</v>
       </c>
       <c r="B90" t="n">
-        <v>57738</v>
+        <v>8451</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -10332,10 +10332,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>461857</v>
+        <v>461832</v>
       </c>
       <c r="R90" t="n">
-        <v>6780859</v>
+        <v>6780916</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10367,7 +10367,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10377,7 +10377,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
@@ -10409,38 +10409,38 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>130086721</v>
+        <v>130085149</v>
       </c>
       <c r="B91" t="n">
-        <v>8451</v>
+        <v>57823</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -10449,10 +10449,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>461832</v>
+        <v>461857</v>
       </c>
       <c r="R91" t="n">
-        <v>6780916</v>
+        <v>6780859</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10484,7 +10484,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10494,7 +10494,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
@@ -10526,54 +10526,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>130092063</v>
+        <v>130083753</v>
       </c>
       <c r="B92" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>461946</v>
+        <v>461711</v>
       </c>
       <c r="R92" t="n">
-        <v>6780839</v>
+        <v>6780852</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10603,30 +10594,39 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -10745,10 +10745,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130091794</v>
+        <v>130087798</v>
       </c>
       <c r="B94" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10774,19 +10774,16 @@
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>461710</v>
+        <v>461864</v>
       </c>
       <c r="R94" t="n">
-        <v>6780886</v>
+        <v>6780951</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10816,67 +10813,82 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>130092053</v>
+        <v>130092063</v>
       </c>
       <c r="B95" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -10884,10 +10896,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>461926</v>
+        <v>461946</v>
       </c>
       <c r="R95" t="n">
-        <v>6780853</v>
+        <v>6780839</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10947,10 +10959,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>130083753</v>
+        <v>130091794</v>
       </c>
       <c r="B96" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10976,16 +10988,19 @@
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>461711</v>
+        <v>461710</v>
       </c>
       <c r="R96" t="n">
-        <v>6780852</v>
+        <v>6780886</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11015,49 +11030,40 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>130087798</v>
+        <v>130092053</v>
       </c>
       <c r="B97" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11083,16 +11089,19 @@
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>461864</v>
+        <v>461926</v>
       </c>
       <c r="R97" t="n">
-        <v>6780951</v>
+        <v>6780853</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11122,49 +11131,40 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>130087727</v>
+        <v>130087184</v>
       </c>
       <c r="B98" t="n">
-        <v>57738</v>
+        <v>79180</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11172,42 +11172,37 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>461894</v>
+        <v>461948</v>
       </c>
       <c r="R98" t="n">
-        <v>6780914</v>
+        <v>6780740</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11247,6 +11242,11 @@
       <c r="AB98" t="inlineStr">
         <is>
           <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11273,10 +11273,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>130087915</v>
+        <v>130087727</v>
       </c>
       <c r="B99" t="n">
-        <v>79714</v>
+        <v>57823</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11284,34 +11284,39 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>461853</v>
+        <v>461894</v>
       </c>
       <c r="R99" t="n">
-        <v>6780990</v>
+        <v>6780914</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11380,10 +11385,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>130087184</v>
+        <v>130087915</v>
       </c>
       <c r="B100" t="n">
-        <v>79095</v>
+        <v>79799</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11391,21 +11396,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11415,13 +11420,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>461948</v>
+        <v>461853</v>
       </c>
       <c r="R100" t="n">
-        <v>6780740</v>
+        <v>6780990</v>
       </c>
       <c r="S100" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11461,11 +11466,6 @@
       <c r="AB100" t="inlineStr">
         <is>
           <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11492,37 +11492,43 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>130091832</v>
+        <v>130091828</v>
       </c>
       <c r="B101" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -11530,10 +11536,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>461738</v>
+        <v>461736</v>
       </c>
       <c r="R101" t="n">
-        <v>6780825</v>
+        <v>6780844</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11593,7 +11599,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>130091828</v>
+        <v>130091798</v>
       </c>
       <c r="B102" t="n">
         <v>8451</v>
@@ -11637,10 +11643,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>461736</v>
+        <v>461713</v>
       </c>
       <c r="R102" t="n">
-        <v>6780844</v>
+        <v>6780880</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11700,43 +11706,37 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>130091798</v>
+        <v>130091832</v>
       </c>
       <c r="B103" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
@@ -11744,10 +11744,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>461713</v>
+        <v>461738</v>
       </c>
       <c r="R103" t="n">
-        <v>6780880</v>
+        <v>6780825</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11810,7 +11810,7 @@
         <v>130092019</v>
       </c>
       <c r="B104" t="n">
-        <v>78853</v>
+        <v>78938</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11908,10 +11908,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>130092042</v>
+        <v>130082810</v>
       </c>
       <c r="B105" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11937,19 +11937,16 @@
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>461850</v>
+        <v>461757</v>
       </c>
       <c r="R105" t="n">
-        <v>6780907</v>
+        <v>6781096</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11979,40 +11976,49 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>130091785</v>
+        <v>130087616</v>
       </c>
       <c r="B106" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12038,19 +12044,16 @@
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>461710</v>
+        <v>461970</v>
       </c>
       <c r="R106" t="n">
-        <v>6780938</v>
+        <v>6780823</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12080,75 +12083,98 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter</t>
+        </is>
+      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>130082810</v>
+        <v>130092018</v>
       </c>
       <c r="B107" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>461757</v>
+        <v>461858</v>
       </c>
       <c r="R107" t="n">
-        <v>6781096</v>
+        <v>6780846</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12178,49 +12204,40 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>130087616</v>
+        <v>130092042</v>
       </c>
       <c r="B108" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12246,16 +12263,19 @@
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>461970</v>
+        <v>461850</v>
       </c>
       <c r="R108" t="n">
-        <v>6780823</v>
+        <v>6780907</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12285,87 +12305,67 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter</t>
-        </is>
-      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>130092018</v>
+        <v>130091785</v>
       </c>
       <c r="B109" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
@@ -12373,10 +12373,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>461858</v>
+        <v>461710</v>
       </c>
       <c r="R109" t="n">
-        <v>6780846</v>
+        <v>6780938</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12650,45 +12650,50 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>130087271</v>
+        <v>130085157</v>
       </c>
       <c r="B112" t="n">
-        <v>79714</v>
+        <v>8451</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>462051</v>
+        <v>461859</v>
       </c>
       <c r="R112" t="n">
-        <v>6780727</v>
+        <v>6780861</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12720,7 +12725,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12730,7 +12735,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12745,12 +12750,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
@@ -12760,7 +12765,7 @@
         <v>130087227</v>
       </c>
       <c r="B113" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12872,7 +12877,7 @@
         <v>130087844</v>
       </c>
       <c r="B114" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12981,50 +12986,45 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>130085157</v>
+        <v>130087271</v>
       </c>
       <c r="B115" t="n">
-        <v>8451</v>
+        <v>79799</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>461859</v>
+        <v>462051</v>
       </c>
       <c r="R115" t="n">
-        <v>6780861</v>
+        <v>6780727</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13056,7 +13056,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13081,22 +13081,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>130092071</v>
+        <v>130087759</v>
       </c>
       <c r="B116" t="n">
-        <v>91939</v>
+        <v>79180</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13104,37 +13104,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>461946</v>
+        <v>461879</v>
       </c>
       <c r="R116" t="n">
-        <v>6780863</v>
+        <v>6780924</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13164,73 +13161,76 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>130092139</v>
+        <v>130092033</v>
       </c>
       <c r="B117" t="n">
-        <v>8451</v>
+        <v>78938</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -13238,10 +13238,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>461975</v>
+        <v>461871</v>
       </c>
       <c r="R117" t="n">
-        <v>6780791</v>
+        <v>6780851</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13301,10 +13301,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>130092033</v>
+        <v>130091843</v>
       </c>
       <c r="B118" t="n">
-        <v>78853</v>
+        <v>79180</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13312,21 +13312,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13339,10 +13339,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>461871</v>
+        <v>461720</v>
       </c>
       <c r="R118" t="n">
-        <v>6780851</v>
+        <v>6780825</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13402,10 +13402,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>130092122</v>
+        <v>130092139</v>
       </c>
       <c r="B119" t="n">
-        <v>79119</v>
+        <v>8451</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13413,26 +13413,32 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6434</v>
+        <v>106545</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
@@ -13440,10 +13446,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>461986</v>
+        <v>461975</v>
       </c>
       <c r="R119" t="n">
-        <v>6780804</v>
+        <v>6780791</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13503,45 +13509,48 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>130087759</v>
+        <v>130092122</v>
       </c>
       <c r="B120" t="n">
-        <v>79095</v>
+        <v>79204</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>461879</v>
+        <v>461986</v>
       </c>
       <c r="R120" t="n">
-        <v>6780924</v>
+        <v>6780804</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13571,49 +13580,40 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>130091843</v>
+        <v>130092071</v>
       </c>
       <c r="B121" t="n">
-        <v>79095</v>
+        <v>92026</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13621,21 +13621,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13648,10 +13648,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>461720</v>
+        <v>461946</v>
       </c>
       <c r="R121" t="n">
-        <v>6780825</v>
+        <v>6780863</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13711,45 +13711,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>130087075</v>
+        <v>130083776</v>
       </c>
       <c r="B122" t="n">
-        <v>8451</v>
+        <v>78938</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>461944</v>
+        <v>461738</v>
       </c>
       <c r="R122" t="n">
-        <v>6780796</v>
+        <v>6780866</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13781,7 +13781,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13806,60 +13806,57 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>130091751</v>
+        <v>130087075</v>
       </c>
       <c r="B123" t="n">
-        <v>79127</v>
+        <v>8451</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>461737</v>
+        <v>461944</v>
       </c>
       <c r="R123" t="n">
-        <v>6781057</v>
+        <v>6780796</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13889,30 +13886,39 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
@@ -13922,7 +13928,7 @@
         <v>130091628</v>
       </c>
       <c r="B124" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14023,7 +14029,7 @@
         <v>130091745</v>
       </c>
       <c r="B125" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14121,10 +14127,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>130086831</v>
+        <v>130091751</v>
       </c>
       <c r="B126" t="n">
-        <v>79095</v>
+        <v>79212</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14132,34 +14138,37 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>461887</v>
+        <v>461737</v>
       </c>
       <c r="R126" t="n">
-        <v>6780890</v>
+        <v>6781057</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14189,49 +14198,40 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD126" t="b">
         <v>0</v>
       </c>
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>130083776</v>
+        <v>130086831</v>
       </c>
       <c r="B127" t="n">
-        <v>78853</v>
+        <v>79180</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14239,34 +14239,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>461738</v>
+        <v>461887</v>
       </c>
       <c r="R127" t="n">
-        <v>6780866</v>
+        <v>6780890</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14298,7 +14298,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14323,22 +14323,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>130091780</v>
+        <v>130085089</v>
       </c>
       <c r="B128" t="n">
-        <v>79095</v>
+        <v>78938</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14346,37 +14346,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>461742</v>
+        <v>461857</v>
       </c>
       <c r="R128" t="n">
-        <v>6781010</v>
+        <v>6780866</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14406,40 +14403,49 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
       <c r="AD128" t="b">
         <v>0</v>
       </c>
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>130087722</v>
+        <v>130085207</v>
       </c>
       <c r="B129" t="n">
-        <v>79095</v>
+        <v>57823</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14447,34 +14453,39 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>461894</v>
+        <v>461844</v>
       </c>
       <c r="R129" t="n">
-        <v>6780914</v>
+        <v>6780835</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14506,7 +14517,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14516,7 +14527,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14543,10 +14554,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>130087061</v>
+        <v>130087794</v>
       </c>
       <c r="B130" t="n">
-        <v>79095</v>
+        <v>57823</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14554,34 +14565,39 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>461952</v>
+        <v>461864</v>
       </c>
       <c r="R130" t="n">
-        <v>6780820</v>
+        <v>6780951</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14650,10 +14666,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>130087445</v>
+        <v>130087722</v>
       </c>
       <c r="B131" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14685,13 +14701,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>462022</v>
+        <v>461894</v>
       </c>
       <c r="R131" t="n">
-        <v>6780775</v>
+        <v>6780914</v>
       </c>
       <c r="S131" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14731,11 +14747,6 @@
       <c r="AB131" t="inlineStr">
         <is>
           <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14762,10 +14773,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>130085207</v>
+        <v>130087061</v>
       </c>
       <c r="B132" t="n">
-        <v>57738</v>
+        <v>79180</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14773,39 +14784,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>461844</v>
+        <v>461952</v>
       </c>
       <c r="R132" t="n">
-        <v>6780835</v>
+        <v>6780820</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14837,7 +14843,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14847,7 +14853,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14874,10 +14880,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>130087794</v>
+        <v>130083972</v>
       </c>
       <c r="B133" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14905,7 +14911,7 @@
       <c r="I133" t="inlineStr"/>
       <c r="M133" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -14914,10 +14920,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>461864</v>
+        <v>461717</v>
       </c>
       <c r="R133" t="n">
-        <v>6780951</v>
+        <v>6780842</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14949,7 +14955,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14959,7 +14965,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14986,38 +14992,38 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>130083972</v>
+        <v>130085214</v>
       </c>
       <c r="B134" t="n">
-        <v>57738</v>
+        <v>8451</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="M134" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -15026,10 +15032,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>461717</v>
+        <v>461844</v>
       </c>
       <c r="R134" t="n">
-        <v>6780842</v>
+        <v>6780835</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15098,53 +15104,48 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>130085214</v>
+        <v>130087445</v>
       </c>
       <c r="B135" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>461844</v>
+        <v>462022</v>
       </c>
       <c r="R135" t="n">
-        <v>6780835</v>
+        <v>6780775</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15173,7 +15174,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15183,7 +15184,12 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15210,10 +15216,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>130085089</v>
+        <v>130091780</v>
       </c>
       <c r="B136" t="n">
-        <v>78853</v>
+        <v>79180</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15221,34 +15227,37 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>461857</v>
+        <v>461742</v>
       </c>
       <c r="R136" t="n">
-        <v>6780866</v>
+        <v>6781010</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15278,39 +15287,30 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>11:27</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>11:27</t>
-        </is>
-      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
@@ -15320,7 +15320,7 @@
         <v>130087057</v>
       </c>
       <c r="B137" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15424,45 +15424,45 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>130087401</v>
+        <v>130087789</v>
       </c>
       <c r="B138" t="n">
-        <v>8451</v>
+        <v>79212</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>462039</v>
+        <v>461857</v>
       </c>
       <c r="R138" t="n">
-        <v>6780770</v>
+        <v>6780939</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15494,7 +15494,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15504,7 +15504,12 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>Sparsamt på gran</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15519,19 +15524,19 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>130086828</v>
+        <v>130087401</v>
       </c>
       <c r="B139" t="n">
         <v>8451</v>
@@ -15566,10 +15571,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>461887</v>
+        <v>462039</v>
       </c>
       <c r="R139" t="n">
-        <v>6780890</v>
+        <v>6780770</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15638,10 +15643,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>130087789</v>
+        <v>130083742</v>
       </c>
       <c r="B140" t="n">
-        <v>79127</v>
+        <v>79180</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15649,34 +15654,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>461857</v>
+        <v>461699</v>
       </c>
       <c r="R140" t="n">
-        <v>6780939</v>
+        <v>6780870</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15708,7 +15713,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15718,12 +15723,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Sparsamt på gran</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15738,22 +15738,22 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>130083742</v>
+        <v>130087754</v>
       </c>
       <c r="B141" t="n">
-        <v>79095</v>
+        <v>57823</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15761,34 +15761,39 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>461699</v>
+        <v>461879</v>
       </c>
       <c r="R141" t="n">
-        <v>6780870</v>
+        <v>6780924</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15820,7 +15825,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15830,7 +15835,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15857,50 +15862,45 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>130087754</v>
+        <v>130086828</v>
       </c>
       <c r="B142" t="n">
-        <v>57738</v>
+        <v>8451</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>461879</v>
+        <v>461887</v>
       </c>
       <c r="R142" t="n">
-        <v>6780924</v>
+        <v>6780890</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15972,7 +15972,7 @@
         <v>130085304</v>
       </c>
       <c r="B143" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16079,7 +16079,7 @@
         <v>130085309</v>
       </c>
       <c r="B144" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16188,10 +16188,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>130091819</v>
+        <v>130087667</v>
       </c>
       <c r="B145" t="n">
-        <v>57738</v>
+        <v>79799</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16199,42 +16199,34 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>461716</v>
+        <v>461929</v>
       </c>
       <c r="R145" t="n">
-        <v>6780856</v>
+        <v>6780891</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16264,9 +16256,19 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16281,12 +16283,12 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
@@ -16400,10 +16402,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>130086869</v>
+        <v>130091819</v>
       </c>
       <c r="B147" t="n">
-        <v>78853</v>
+        <v>57823</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16411,34 +16413,42 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>461922</v>
+        <v>461716</v>
       </c>
       <c r="R147" t="n">
-        <v>6780874</v>
+        <v>6780856</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16468,24 +16478,9 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z147" t="inlineStr">
-        <is>
-          <t>13:11</t>
-        </is>
-      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AB147" t="inlineStr">
-        <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16500,22 +16495,22 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>130087667</v>
+        <v>130086869</v>
       </c>
       <c r="B148" t="n">
-        <v>79714</v>
+        <v>78938</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16523,34 +16518,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>461929</v>
+        <v>461922</v>
       </c>
       <c r="R148" t="n">
-        <v>6780891</v>
+        <v>6780874</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16582,7 +16577,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16592,7 +16587,12 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16607,12 +16607,12 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
@@ -16622,7 +16622,7 @@
         <v>130086826</v>
       </c>
       <c r="B149" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16731,10 +16731,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>130092006</v>
+        <v>130087527</v>
       </c>
       <c r="B150" t="n">
-        <v>57738</v>
+        <v>79180</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16742,42 +16742,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>461808</v>
+        <v>461956</v>
       </c>
       <c r="R150" t="n">
-        <v>6780861</v>
+        <v>6780787</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16807,9 +16799,19 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16824,22 +16826,22 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>130087153</v>
+        <v>130092006</v>
       </c>
       <c r="B151" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16865,21 +16867,24 @@
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
       <c r="M151" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>461955</v>
+        <v>461808</v>
       </c>
       <c r="R151" t="n">
-        <v>6780741</v>
+        <v>6780861</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16914,11 +16919,6 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Äldre spår I högstubbe</t>
-        </is>
-      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
@@ -16931,12 +16931,12 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
@@ -16946,7 +16946,7 @@
         <v>130084608</v>
       </c>
       <c r="B152" t="n">
-        <v>78853</v>
+        <v>78938</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17055,10 +17055,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>130087527</v>
+        <v>130087153</v>
       </c>
       <c r="B153" t="n">
-        <v>79095</v>
+        <v>57823</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17066,34 +17066,39 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>461956</v>
+        <v>461955</v>
       </c>
       <c r="R153" t="n">
-        <v>6780787</v>
+        <v>6780741</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17123,19 +17128,14 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z153" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB153" t="inlineStr">
-        <is>
-          <t>13:03</t>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Äldre spår I högstubbe</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17150,12 +17150,12 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
@@ -17272,7 +17272,7 @@
         <v>130091626</v>
       </c>
       <c r="B155" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17373,7 +17373,7 @@
         <v>130091841</v>
       </c>
       <c r="B156" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17484,10 +17484,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>130085067</v>
+        <v>130092430</v>
       </c>
       <c r="B157" t="n">
-        <v>57738</v>
+        <v>78938</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17495,39 +17495,37 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>461857</v>
+        <v>461933</v>
       </c>
       <c r="R157" t="n">
-        <v>6780842</v>
+        <v>6780838</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17557,19 +17555,14 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>10:14</t>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17578,28 +17571,29 @@
       <c r="AE157" t="b">
         <v>0</v>
       </c>
+      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>130092430</v>
+        <v>130085067</v>
       </c>
       <c r="B158" t="n">
-        <v>78853</v>
+        <v>57823</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17607,37 +17601,39 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
-      <c r="N158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>461933</v>
+        <v>461857</v>
       </c>
       <c r="R158" t="n">
-        <v>6780838</v>
+        <v>6780842</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17667,14 +17663,19 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17683,19 +17684,18 @@
       <c r="AE158" t="b">
         <v>0</v>
       </c>
-      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
@@ -17705,7 +17705,7 @@
         <v>130091747</v>
       </c>
       <c r="B159" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17806,7 +17806,7 @@
         <v>130091789</v>
       </c>
       <c r="B160" t="n">
-        <v>91023</v>
+        <v>91110</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
         <v>130084138</v>
       </c>
       <c r="B163" t="n">
-        <v>91625</v>
+        <v>91712</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18241,10 +18241,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>130083774</v>
+        <v>130086991</v>
       </c>
       <c r="B164" t="n">
-        <v>90673</v>
+        <v>79180</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18252,40 +18252,37 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>461717</v>
+        <v>461939</v>
       </c>
       <c r="R164" t="n">
-        <v>6780842</v>
+        <v>6780857</v>
       </c>
       <c r="S164" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -18314,7 +18311,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -18324,12 +18321,12 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>2 bilder</t>
+          <t>2 bild. Rikligt till måttligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18338,7 +18335,6 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
-      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
@@ -18357,10 +18353,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>130086991</v>
+        <v>130083774</v>
       </c>
       <c r="B165" t="n">
-        <v>79095</v>
+        <v>90760</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18368,37 +18364,40 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>461939</v>
+        <v>461717</v>
       </c>
       <c r="R165" t="n">
-        <v>6780857</v>
+        <v>6780842</v>
       </c>
       <c r="S165" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -18427,7 +18426,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -18437,12 +18436,12 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>2 bild. Rikligt till måttligt i en radie av ca 50 meter</t>
+          <t>2 bilder</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18451,6 +18450,7 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
+      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
@@ -18472,7 +18472,7 @@
         <v>130084189</v>
       </c>
       <c r="B166" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18584,7 +18584,7 @@
         <v>130085198</v>
       </c>
       <c r="B167" t="n">
-        <v>81080</v>
+        <v>81165</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18691,7 +18691,7 @@
         <v>130084610</v>
       </c>
       <c r="B168" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18803,7 +18803,7 @@
         <v>130082682</v>
       </c>
       <c r="B169" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18915,7 +18915,7 @@
         <v>130082967</v>
       </c>
       <c r="B170" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19027,7 +19027,7 @@
         <v>130092045</v>
       </c>
       <c r="B171" t="n">
-        <v>91694</v>
+        <v>91781</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19133,7 +19133,7 @@
         <v>130157655</v>
       </c>
       <c r="B172" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19234,7 +19234,7 @@
         <v>130157740</v>
       </c>
       <c r="B173" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
         <v>130157437</v>
       </c>
       <c r="B174" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19436,37 +19436,39 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>130157644</v>
+        <v>130157422</v>
       </c>
       <c r="B175" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr"/>
       <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
@@ -19474,10 +19476,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>461439</v>
+        <v>462148</v>
       </c>
       <c r="R175" t="n">
-        <v>6780942</v>
+        <v>6780659</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19518,7 +19520,6 @@
       <c r="AE175" t="b">
         <v>0</v>
       </c>
-      <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="b">
         <v>0</v>
       </c>
@@ -19530,46 +19531,44 @@
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>130157422</v>
+        <v>130157644</v>
       </c>
       <c r="B176" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr"/>
-      <c r="L176" t="inlineStr"/>
-      <c r="M176" t="inlineStr"/>
       <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
@@ -19577,10 +19576,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>462148</v>
+        <v>461439</v>
       </c>
       <c r="R176" t="n">
-        <v>6780659</v>
+        <v>6780942</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19621,6 +19620,7 @@
       <c r="AE176" t="b">
         <v>0</v>
       </c>
+      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
@@ -19632,47 +19632,48 @@
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>130157723</v>
+        <v>130157683</v>
       </c>
       <c r="B177" t="n">
-        <v>57741</v>
+        <v>8451</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr"/>
       <c r="M177" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N177" t="inlineStr"/>
@@ -19682,10 +19683,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>461526</v>
+        <v>461363</v>
       </c>
       <c r="R177" t="n">
-        <v>6780870</v>
+        <v>6780957</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19720,17 +19721,13 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>Ringhack i en av de äldre tallarna (en av 5-6 äldre tallar som ej bandats av)</t>
-        </is>
-      </c>
       <c r="AD177" t="b">
         <v>0</v>
       </c>
       <c r="AE177" t="b">
         <v>0</v>
       </c>
+      <c r="AF177" t="inlineStr"/>
       <c r="AG177" t="b">
         <v>0</v>
       </c>
@@ -19749,41 +19746,40 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>130157683</v>
+        <v>130157723</v>
       </c>
       <c r="B178" t="n">
-        <v>8451</v>
+        <v>57826</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr"/>
       <c r="M178" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N178" t="inlineStr"/>
@@ -19793,10 +19789,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>461363</v>
+        <v>461526</v>
       </c>
       <c r="R178" t="n">
-        <v>6780957</v>
+        <v>6780870</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19831,13 +19827,17 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>Ringhack i en av de äldre tallarna (en av 5-6 äldre tallar som ej bandats av)</t>
+        </is>
+      </c>
       <c r="AD178" t="b">
         <v>0</v>
       </c>
       <c r="AE178" t="b">
         <v>0</v>
       </c>
-      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>
@@ -19859,7 +19859,7 @@
         <v>130157405</v>
       </c>
       <c r="B179" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19959,7 +19959,7 @@
         <v>130157430</v>
       </c>
       <c r="B180" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20059,7 +20059,7 @@
         <v>130157632</v>
       </c>
       <c r="B181" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20272,7 +20272,7 @@
         <v>130157699</v>
       </c>
       <c r="B183" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20374,37 +20374,43 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>130157446</v>
+        <v>130157677</v>
       </c>
       <c r="B184" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
@@ -20412,10 +20418,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>462162</v>
+        <v>461370</v>
       </c>
       <c r="R184" t="n">
-        <v>6780616</v>
+        <v>6780963</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20456,6 +20462,7 @@
       <c r="AE184" t="b">
         <v>0</v>
       </c>
+      <c r="AF184" t="inlineStr"/>
       <c r="AG184" t="b">
         <v>0</v>
       </c>
@@ -20467,50 +20474,44 @@
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>130157677</v>
+        <v>130157446</v>
       </c>
       <c r="B185" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr"/>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
@@ -20518,10 +20519,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>461370</v>
+        <v>462162</v>
       </c>
       <c r="R185" t="n">
-        <v>6780963</v>
+        <v>6780616</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20562,7 +20563,6 @@
       <c r="AE185" t="b">
         <v>0</v>
       </c>
-      <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="b">
         <v>0</v>
       </c>
@@ -20574,7 +20574,7 @@
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
@@ -20584,7 +20584,7 @@
         <v>130157638</v>
       </c>
       <c r="B186" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>

--- a/artfynd/A 58003-2025 artfynd.xlsx
+++ b/artfynd/A 58003-2025 artfynd.xlsx
@@ -4597,10 +4597,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129971739</v>
+        <v>129973978</v>
       </c>
       <c r="B38" t="n">
-        <v>79770</v>
+        <v>79180</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4608,21 +4608,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4632,10 +4632,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461741</v>
+        <v>461749</v>
       </c>
       <c r="R38" t="n">
-        <v>6780920</v>
+        <v>6780997</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4704,10 +4704,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129973978</v>
+        <v>129971739</v>
       </c>
       <c r="B39" t="n">
-        <v>79180</v>
+        <v>79770</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4715,21 +4715,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4739,10 +4739,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461749</v>
+        <v>461741</v>
       </c>
       <c r="R39" t="n">
-        <v>6780997</v>
+        <v>6780920</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -7691,7 +7691,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130087492</v>
+        <v>130087119</v>
       </c>
       <c r="B66" t="n">
         <v>79180</v>
@@ -7726,13 +7726,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>461944</v>
+        <v>461918</v>
       </c>
       <c r="R66" t="n">
-        <v>6780796</v>
+        <v>6780787</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7772,6 +7772,11 @@
       <c r="AB66" t="inlineStr">
         <is>
           <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7798,54 +7803,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130092389</v>
+        <v>130087669</v>
       </c>
       <c r="B67" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>461870</v>
+        <v>461929</v>
       </c>
       <c r="R67" t="n">
-        <v>6780967</v>
+        <v>6780891</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7875,37 +7871,46 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130087222</v>
+        <v>130092389</v>
       </c>
       <c r="B68" t="n">
         <v>8451</v>
@@ -7934,21 +7939,25 @@
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>462001</v>
+        <v>461870</v>
       </c>
       <c r="R68" t="n">
-        <v>6780764</v>
+        <v>6780967</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7978,32 +7987,18 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>13:46</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>13:46</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Äldre spår I tallåga</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8015,52 +8010,57 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130087716</v>
+        <v>130087222</v>
       </c>
       <c r="B69" t="n">
-        <v>79799</v>
+        <v>8451</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>461894</v>
+        <v>462001</v>
       </c>
       <c r="R69" t="n">
-        <v>6780914</v>
+        <v>6780764</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8092,7 +8092,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8102,7 +8102,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Äldre spår I tallåga</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8117,22 +8122,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130087119</v>
+        <v>130087716</v>
       </c>
       <c r="B70" t="n">
-        <v>79180</v>
+        <v>79799</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8140,21 +8145,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8164,13 +8169,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>461918</v>
+        <v>461894</v>
       </c>
       <c r="R70" t="n">
-        <v>6780787</v>
+        <v>6780914</v>
       </c>
       <c r="S70" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8210,11 +8215,6 @@
       <c r="AB70" t="inlineStr">
         <is>
           <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8241,10 +8241,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130087512</v>
+        <v>130087492</v>
       </c>
       <c r="B71" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8252,39 +8252,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>461956</v>
+        <v>461944</v>
       </c>
       <c r="R71" t="n">
-        <v>6780787</v>
+        <v>6780796</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8353,10 +8348,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130087669</v>
+        <v>130087512</v>
       </c>
       <c r="B72" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8364,34 +8359,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>461929</v>
+        <v>461956</v>
       </c>
       <c r="R72" t="n">
-        <v>6780891</v>
+        <v>6780787</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9970,53 +9970,50 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130092368</v>
+        <v>130082759</v>
       </c>
       <c r="B87" t="n">
-        <v>57823</v>
+        <v>8451</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>461867</v>
+        <v>461757</v>
       </c>
       <c r="R87" t="n">
-        <v>6780956</v>
+        <v>6781096</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10046,9 +10043,19 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10063,62 +10070,65 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130082759</v>
+        <v>130092059</v>
       </c>
       <c r="B88" t="n">
-        <v>8451</v>
+        <v>57823</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>461757</v>
+        <v>461946</v>
       </c>
       <c r="R88" t="n">
-        <v>6781096</v>
+        <v>6780839</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10148,19 +10158,9 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>10:14</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10175,19 +10175,19 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130092059</v>
+        <v>130092368</v>
       </c>
       <c r="B89" t="n">
         <v>57823</v>
@@ -10230,10 +10230,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>461946</v>
+        <v>461867</v>
       </c>
       <c r="R89" t="n">
-        <v>6780839</v>
+        <v>6780956</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10280,19 +10280,19 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>130086721</v>
+        <v>130087850</v>
       </c>
       <c r="B90" t="n">
         <v>8451</v>
@@ -10328,14 +10328,14 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>461832</v>
+        <v>461873</v>
       </c>
       <c r="R90" t="n">
-        <v>6780916</v>
+        <v>6780961</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10367,7 +10367,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10377,12 +10377,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Äldre spår i torrtall</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10397,50 +10392,50 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>130085149</v>
+        <v>130086721</v>
       </c>
       <c r="B91" t="n">
-        <v>57823</v>
+        <v>8451</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -10449,10 +10444,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>461857</v>
+        <v>461832</v>
       </c>
       <c r="R91" t="n">
-        <v>6780859</v>
+        <v>6780916</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10484,7 +10479,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10494,7 +10489,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
@@ -10526,10 +10521,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>130083753</v>
+        <v>130085149</v>
       </c>
       <c r="B92" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10537,34 +10532,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>461711</v>
+        <v>461857</v>
       </c>
       <c r="R92" t="n">
-        <v>6780852</v>
+        <v>6780859</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10606,7 +10606,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Äldre spår i torrtall</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10621,62 +10626,57 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>130087850</v>
+        <v>130083753</v>
       </c>
       <c r="B93" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>461873</v>
+        <v>461711</v>
       </c>
       <c r="R93" t="n">
-        <v>6780961</v>
+        <v>6780852</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10708,7 +10708,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10718,7 +10718,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11273,10 +11273,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>130087727</v>
+        <v>130087915</v>
       </c>
       <c r="B99" t="n">
-        <v>57823</v>
+        <v>79799</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11284,39 +11284,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>461894</v>
+        <v>461853</v>
       </c>
       <c r="R99" t="n">
-        <v>6780914</v>
+        <v>6780990</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11385,45 +11380,54 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>130087915</v>
+        <v>130091828</v>
       </c>
       <c r="B100" t="n">
-        <v>79799</v>
+        <v>8451</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>461853</v>
+        <v>461736</v>
       </c>
       <c r="R100" t="n">
-        <v>6780990</v>
+        <v>6780844</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11453,46 +11457,37 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>130091828</v>
+        <v>130091798</v>
       </c>
       <c r="B101" t="n">
         <v>8451</v>
@@ -11536,10 +11531,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>461736</v>
+        <v>461713</v>
       </c>
       <c r="R101" t="n">
-        <v>6780844</v>
+        <v>6780880</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11599,43 +11594,37 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>130091798</v>
+        <v>130091832</v>
       </c>
       <c r="B102" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
@@ -11643,10 +11632,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>461713</v>
+        <v>461738</v>
       </c>
       <c r="R102" t="n">
-        <v>6780880</v>
+        <v>6780825</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11706,10 +11695,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>130091832</v>
+        <v>130092019</v>
       </c>
       <c r="B103" t="n">
-        <v>79180</v>
+        <v>78938</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11717,21 +11706,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11744,10 +11733,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>461738</v>
+        <v>461858</v>
       </c>
       <c r="R103" t="n">
-        <v>6780825</v>
+        <v>6780846</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11807,10 +11796,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>130092019</v>
+        <v>130087727</v>
       </c>
       <c r="B104" t="n">
-        <v>78938</v>
+        <v>57823</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11818,37 +11807,39 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>461858</v>
+        <v>461894</v>
       </c>
       <c r="R104" t="n">
-        <v>6780846</v>
+        <v>6780914</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11878,30 +11869,39 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
@@ -13093,10 +13093,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>130087759</v>
+        <v>130092033</v>
       </c>
       <c r="B116" t="n">
-        <v>79180</v>
+        <v>78938</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13104,34 +13104,37 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>461879</v>
+        <v>461871</v>
       </c>
       <c r="R116" t="n">
-        <v>6780924</v>
+        <v>6780851</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13161,49 +13164,40 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>130092033</v>
+        <v>130091843</v>
       </c>
       <c r="B117" t="n">
-        <v>78938</v>
+        <v>79180</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13211,21 +13205,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13238,10 +13232,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>461871</v>
+        <v>461720</v>
       </c>
       <c r="R117" t="n">
-        <v>6780851</v>
+        <v>6780825</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13301,37 +13295,43 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>130091843</v>
+        <v>130092139</v>
       </c>
       <c r="B118" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
@@ -13339,10 +13339,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>461720</v>
+        <v>461975</v>
       </c>
       <c r="R118" t="n">
-        <v>6780825</v>
+        <v>6780791</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13402,10 +13402,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>130092139</v>
+        <v>130092122</v>
       </c>
       <c r="B119" t="n">
-        <v>8451</v>
+        <v>79204</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13413,32 +13413,26 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>106545</v>
+        <v>6434</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
@@ -13446,10 +13440,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>461975</v>
+        <v>461986</v>
       </c>
       <c r="R119" t="n">
-        <v>6780791</v>
+        <v>6780804</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13509,32 +13503,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>130092122</v>
+        <v>130092071</v>
       </c>
       <c r="B120" t="n">
-        <v>79204</v>
+        <v>92026</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6434</v>
+        <v>658</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13547,10 +13541,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>461986</v>
+        <v>461946</v>
       </c>
       <c r="R120" t="n">
-        <v>6780804</v>
+        <v>6780863</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13610,10 +13604,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>130092071</v>
+        <v>130087759</v>
       </c>
       <c r="B121" t="n">
-        <v>92026</v>
+        <v>79180</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13621,37 +13615,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>461946</v>
+        <v>461879</v>
       </c>
       <c r="R121" t="n">
-        <v>6780863</v>
+        <v>6780924</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13681,30 +13672,39 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>

--- a/artfynd/A 58003-2025 artfynd.xlsx
+++ b/artfynd/A 58003-2025 artfynd.xlsx
@@ -2519,50 +2519,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129972802</v>
+        <v>129971589</v>
       </c>
       <c r="B19" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461611</v>
+        <v>461736</v>
       </c>
       <c r="R19" t="n">
-        <v>6780900</v>
+        <v>6780931</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2738,45 +2733,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129971589</v>
+        <v>129972802</v>
       </c>
       <c r="B21" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461736</v>
+        <v>461611</v>
       </c>
       <c r="R21" t="n">
-        <v>6780931</v>
+        <v>6780900</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -4052,10 +4052,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129971825</v>
+        <v>129970738</v>
       </c>
       <c r="B33" t="n">
-        <v>57823</v>
+        <v>79799</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4063,39 +4063,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461686</v>
+        <v>461799</v>
       </c>
       <c r="R33" t="n">
-        <v>6780923</v>
+        <v>6780979</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4164,10 +4159,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129970738</v>
+        <v>129971825</v>
       </c>
       <c r="B34" t="n">
-        <v>79799</v>
+        <v>57823</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4175,34 +4170,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461799</v>
+        <v>461686</v>
       </c>
       <c r="R34" t="n">
-        <v>6780979</v>
+        <v>6780923</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -7691,7 +7691,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130087119</v>
+        <v>130087492</v>
       </c>
       <c r="B66" t="n">
         <v>79180</v>
@@ -7726,13 +7726,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>461918</v>
+        <v>461944</v>
       </c>
       <c r="R66" t="n">
-        <v>6780787</v>
+        <v>6780796</v>
       </c>
       <c r="S66" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7772,11 +7772,6 @@
       <c r="AB66" t="inlineStr">
         <is>
           <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7803,45 +7798,54 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130087669</v>
+        <v>130092389</v>
       </c>
       <c r="B67" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>461929</v>
+        <v>461870</v>
       </c>
       <c r="R67" t="n">
-        <v>6780891</v>
+        <v>6780967</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7871,46 +7875,37 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130092389</v>
+        <v>130087222</v>
       </c>
       <c r="B68" t="n">
         <v>8451</v>
@@ -7939,25 +7934,21 @@
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>461870</v>
+        <v>462001</v>
       </c>
       <c r="R68" t="n">
-        <v>6780967</v>
+        <v>6780764</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7987,18 +7978,32 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Äldre spår I tallåga</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8010,57 +8015,52 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130087222</v>
+        <v>130087716</v>
       </c>
       <c r="B69" t="n">
-        <v>8451</v>
+        <v>79799</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>462001</v>
+        <v>461894</v>
       </c>
       <c r="R69" t="n">
-        <v>6780764</v>
+        <v>6780914</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8092,7 +8092,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8102,12 +8102,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:46</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Äldre spår I tallåga</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8122,22 +8117,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130087716</v>
+        <v>130087119</v>
       </c>
       <c r="B70" t="n">
-        <v>79799</v>
+        <v>79180</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8145,21 +8140,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8169,13 +8164,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>461894</v>
+        <v>461918</v>
       </c>
       <c r="R70" t="n">
-        <v>6780914</v>
+        <v>6780787</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8215,6 +8210,11 @@
       <c r="AB70" t="inlineStr">
         <is>
           <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8241,10 +8241,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130087492</v>
+        <v>130087512</v>
       </c>
       <c r="B71" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8252,34 +8252,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>461944</v>
+        <v>461956</v>
       </c>
       <c r="R71" t="n">
-        <v>6780796</v>
+        <v>6780787</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8348,10 +8353,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130087512</v>
+        <v>130087669</v>
       </c>
       <c r="B72" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8359,39 +8364,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>461956</v>
+        <v>461929</v>
       </c>
       <c r="R72" t="n">
-        <v>6780787</v>
+        <v>6780891</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9970,50 +9970,53 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130082759</v>
+        <v>130092368</v>
       </c>
       <c r="B87" t="n">
-        <v>8451</v>
+        <v>57823</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>461757</v>
+        <v>461867</v>
       </c>
       <c r="R87" t="n">
-        <v>6781096</v>
+        <v>6780956</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10043,19 +10046,9 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>10:14</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10070,65 +10063,62 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130092059</v>
+        <v>130082759</v>
       </c>
       <c r="B88" t="n">
-        <v>57823</v>
+        <v>8451</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>461946</v>
+        <v>461757</v>
       </c>
       <c r="R88" t="n">
-        <v>6780839</v>
+        <v>6781096</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10158,9 +10148,19 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10175,19 +10175,19 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130092368</v>
+        <v>130092059</v>
       </c>
       <c r="B89" t="n">
         <v>57823</v>
@@ -10230,10 +10230,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>461867</v>
+        <v>461946</v>
       </c>
       <c r="R89" t="n">
-        <v>6780956</v>
+        <v>6780839</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10280,12 +10280,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -11273,10 +11273,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>130087915</v>
+        <v>130087727</v>
       </c>
       <c r="B99" t="n">
-        <v>79799</v>
+        <v>57823</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11284,34 +11284,39 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>461853</v>
+        <v>461894</v>
       </c>
       <c r="R99" t="n">
-        <v>6780990</v>
+        <v>6780914</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11380,54 +11385,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>130091828</v>
+        <v>130087915</v>
       </c>
       <c r="B100" t="n">
-        <v>8451</v>
+        <v>79799</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>461736</v>
+        <v>461853</v>
       </c>
       <c r="R100" t="n">
-        <v>6780844</v>
+        <v>6780990</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11457,37 +11453,46 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>130091798</v>
+        <v>130091828</v>
       </c>
       <c r="B101" t="n">
         <v>8451</v>
@@ -11531,10 +11536,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>461713</v>
+        <v>461736</v>
       </c>
       <c r="R101" t="n">
-        <v>6780880</v>
+        <v>6780844</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11594,37 +11599,43 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>130091832</v>
+        <v>130091798</v>
       </c>
       <c r="B102" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
@@ -11632,10 +11643,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>461738</v>
+        <v>461713</v>
       </c>
       <c r="R102" t="n">
-        <v>6780825</v>
+        <v>6780880</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11695,10 +11706,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>130092019</v>
+        <v>130091832</v>
       </c>
       <c r="B103" t="n">
-        <v>78938</v>
+        <v>79180</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11706,21 +11717,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11733,10 +11744,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>461858</v>
+        <v>461738</v>
       </c>
       <c r="R103" t="n">
-        <v>6780846</v>
+        <v>6780825</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11796,10 +11807,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>130087727</v>
+        <v>130092019</v>
       </c>
       <c r="B104" t="n">
-        <v>57823</v>
+        <v>78938</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11807,39 +11818,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>461894</v>
+        <v>461858</v>
       </c>
       <c r="R104" t="n">
-        <v>6780914</v>
+        <v>6780846</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11869,39 +11878,30 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
@@ -13093,10 +13093,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>130092033</v>
+        <v>130087759</v>
       </c>
       <c r="B116" t="n">
-        <v>78938</v>
+        <v>79180</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13104,37 +13104,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>461871</v>
+        <v>461879</v>
       </c>
       <c r="R116" t="n">
-        <v>6780851</v>
+        <v>6780924</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13164,40 +13161,49 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>130091843</v>
+        <v>130092033</v>
       </c>
       <c r="B117" t="n">
-        <v>79180</v>
+        <v>78938</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13205,21 +13211,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13232,10 +13238,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>461720</v>
+        <v>461871</v>
       </c>
       <c r="R117" t="n">
-        <v>6780825</v>
+        <v>6780851</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13295,43 +13301,37 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>130092139</v>
+        <v>130091843</v>
       </c>
       <c r="B118" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
@@ -13339,10 +13339,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>461975</v>
+        <v>461720</v>
       </c>
       <c r="R118" t="n">
-        <v>6780791</v>
+        <v>6780825</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13402,10 +13402,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>130092122</v>
+        <v>130092139</v>
       </c>
       <c r="B119" t="n">
-        <v>79204</v>
+        <v>8451</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13413,26 +13413,32 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6434</v>
+        <v>106545</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
@@ -13440,10 +13446,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>461986</v>
+        <v>461975</v>
       </c>
       <c r="R119" t="n">
-        <v>6780804</v>
+        <v>6780791</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13503,32 +13509,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>130092071</v>
+        <v>130092122</v>
       </c>
       <c r="B120" t="n">
-        <v>92026</v>
+        <v>79204</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>658</v>
+        <v>6434</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13541,10 +13547,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>461946</v>
+        <v>461986</v>
       </c>
       <c r="R120" t="n">
-        <v>6780863</v>
+        <v>6780804</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13604,10 +13610,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>130087759</v>
+        <v>130092071</v>
       </c>
       <c r="B121" t="n">
-        <v>79180</v>
+        <v>92026</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13615,34 +13621,37 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>461879</v>
+        <v>461946</v>
       </c>
       <c r="R121" t="n">
-        <v>6780924</v>
+        <v>6780863</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13672,49 +13681,40 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>130083776</v>
+        <v>130086831</v>
       </c>
       <c r="B122" t="n">
-        <v>78938</v>
+        <v>79180</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13722,34 +13722,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>461738</v>
+        <v>461887</v>
       </c>
       <c r="R122" t="n">
-        <v>6780866</v>
+        <v>6780890</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13781,7 +13781,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13806,57 +13806,57 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>130087075</v>
+        <v>130083776</v>
       </c>
       <c r="B123" t="n">
-        <v>8451</v>
+        <v>78938</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>461944</v>
+        <v>461738</v>
       </c>
       <c r="R123" t="n">
-        <v>6780796</v>
+        <v>6780866</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13888,7 +13888,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13898,7 +13898,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13913,60 +13913,57 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>130091628</v>
+        <v>130087075</v>
       </c>
       <c r="B124" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>461750</v>
+        <v>461944</v>
       </c>
       <c r="R124" t="n">
-        <v>6781031</v>
+        <v>6780796</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13996,37 +13993,46 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>130091745</v>
+        <v>130091628</v>
       </c>
       <c r="B125" t="n">
         <v>79180</v>
@@ -14064,7 +14070,7 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>461749</v>
+        <v>461750</v>
       </c>
       <c r="R125" t="n">
         <v>6781031</v>
@@ -14127,10 +14133,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>130091751</v>
+        <v>130091745</v>
       </c>
       <c r="B126" t="n">
-        <v>79212</v>
+        <v>79180</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14138,21 +14144,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14165,10 +14171,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>461737</v>
+        <v>461749</v>
       </c>
       <c r="R126" t="n">
-        <v>6781057</v>
+        <v>6781031</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14228,10 +14234,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>130086831</v>
+        <v>130091751</v>
       </c>
       <c r="B127" t="n">
-        <v>79180</v>
+        <v>79212</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14239,34 +14245,37 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>461887</v>
+        <v>461737</v>
       </c>
       <c r="R127" t="n">
-        <v>6780890</v>
+        <v>6781057</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14296,49 +14305,40 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>130085089</v>
+        <v>130085207</v>
       </c>
       <c r="B128" t="n">
-        <v>78938</v>
+        <v>57823</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14346,34 +14346,39 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>461857</v>
+        <v>461844</v>
       </c>
       <c r="R128" t="n">
-        <v>6780866</v>
+        <v>6780835</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14405,7 +14410,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14415,7 +14420,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14430,19 +14435,19 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>130085207</v>
+        <v>130087794</v>
       </c>
       <c r="B129" t="n">
         <v>57823</v>
@@ -14473,7 +14478,7 @@
       <c r="I129" t="inlineStr"/>
       <c r="M129" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
@@ -14482,10 +14487,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>461844</v>
+        <v>461864</v>
       </c>
       <c r="R129" t="n">
-        <v>6780835</v>
+        <v>6780951</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14517,7 +14522,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14527,7 +14532,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14554,10 +14559,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>130087794</v>
+        <v>130087061</v>
       </c>
       <c r="B130" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14565,39 +14570,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>461864</v>
+        <v>461952</v>
       </c>
       <c r="R130" t="n">
-        <v>6780951</v>
+        <v>6780820</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14666,7 +14666,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>130087722</v>
+        <v>130087445</v>
       </c>
       <c r="B131" t="n">
         <v>79180</v>
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>461894</v>
+        <v>462022</v>
       </c>
       <c r="R131" t="n">
-        <v>6780914</v>
+        <v>6780775</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14747,6 +14747,11 @@
       <c r="AB131" t="inlineStr">
         <is>
           <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14773,7 +14778,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>130087061</v>
+        <v>130091780</v>
       </c>
       <c r="B132" t="n">
         <v>79180</v>
@@ -14802,16 +14807,19 @@
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>461952</v>
+        <v>461742</v>
       </c>
       <c r="R132" t="n">
-        <v>6780820</v>
+        <v>6781010</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14841,49 +14849,40 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>130083972</v>
+        <v>130085089</v>
       </c>
       <c r="B133" t="n">
-        <v>57823</v>
+        <v>78938</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14891,39 +14890,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>461717</v>
+        <v>461857</v>
       </c>
       <c r="R133" t="n">
-        <v>6780842</v>
+        <v>6780866</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14955,7 +14949,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14965,7 +14959,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14980,62 +14974,57 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>130085214</v>
+        <v>130087722</v>
       </c>
       <c r="B134" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>461844</v>
+        <v>461894</v>
       </c>
       <c r="R134" t="n">
-        <v>6780835</v>
+        <v>6780914</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15067,7 +15056,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15077,7 +15066,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15104,10 +15093,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>130087445</v>
+        <v>130083972</v>
       </c>
       <c r="B135" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15115,37 +15104,42 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>462022</v>
+        <v>461717</v>
       </c>
       <c r="R135" t="n">
-        <v>6780775</v>
+        <v>6780842</v>
       </c>
       <c r="S135" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15174,7 +15168,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15184,12 +15178,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15216,48 +15205,50 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>130091780</v>
+        <v>130085214</v>
       </c>
       <c r="B136" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>461742</v>
+        <v>461844</v>
       </c>
       <c r="R136" t="n">
-        <v>6781010</v>
+        <v>6780835</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15287,40 +15278,49 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>130087057</v>
+        <v>130087789</v>
       </c>
       <c r="B137" t="n">
-        <v>79799</v>
+        <v>79212</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15328,34 +15328,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>461952</v>
+        <v>461857</v>
       </c>
       <c r="R137" t="n">
-        <v>6780820</v>
+        <v>6780939</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15387,7 +15387,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15397,7 +15397,12 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Sparsamt på gran</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15412,57 +15417,57 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>130087789</v>
+        <v>130087401</v>
       </c>
       <c r="B138" t="n">
-        <v>79212</v>
+        <v>8451</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>461857</v>
+        <v>462039</v>
       </c>
       <c r="R138" t="n">
-        <v>6780939</v>
+        <v>6780770</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15494,7 +15499,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15504,12 +15509,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>Sparsamt på gran</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15524,44 +15524,44 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>130087401</v>
+        <v>130083742</v>
       </c>
       <c r="B139" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15571,10 +15571,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>462039</v>
+        <v>461699</v>
       </c>
       <c r="R139" t="n">
-        <v>6780770</v>
+        <v>6780870</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15606,7 +15606,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15616,7 +15616,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15643,10 +15643,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>130083742</v>
+        <v>130087057</v>
       </c>
       <c r="B140" t="n">
-        <v>79180</v>
+        <v>79799</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15654,21 +15654,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15678,10 +15678,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>461699</v>
+        <v>461952</v>
       </c>
       <c r="R140" t="n">
-        <v>6780870</v>
+        <v>6780820</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15713,7 +15713,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15723,7 +15723,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15969,45 +15969,54 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>130085304</v>
+        <v>130091989</v>
       </c>
       <c r="B143" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>461880</v>
+        <v>461800</v>
       </c>
       <c r="R143" t="n">
-        <v>6780838</v>
+        <v>6780830</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16037,49 +16046,40 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AD143" t="b">
         <v>0</v>
       </c>
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>130085309</v>
+        <v>130086869</v>
       </c>
       <c r="B144" t="n">
-        <v>57823</v>
+        <v>78938</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16087,39 +16087,34 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>461880</v>
+        <v>461922</v>
       </c>
       <c r="R144" t="n">
-        <v>6780838</v>
+        <v>6780874</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16151,7 +16146,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16161,7 +16156,12 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16176,22 +16176,22 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>130087667</v>
+        <v>130085304</v>
       </c>
       <c r="B145" t="n">
-        <v>79799</v>
+        <v>79180</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16199,21 +16199,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16223,10 +16223,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>461929</v>
+        <v>461880</v>
       </c>
       <c r="R145" t="n">
-        <v>6780891</v>
+        <v>6780838</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16258,7 +16258,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16268,7 +16268,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16295,54 +16295,50 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>130091989</v>
+        <v>130085309</v>
       </c>
       <c r="B146" t="n">
-        <v>8451</v>
+        <v>57823</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr"/>
       <c r="M146" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N146" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>461800</v>
+        <v>461880</v>
       </c>
       <c r="R146" t="n">
-        <v>6780830</v>
+        <v>6780838</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16372,40 +16368,49 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AD146" t="b">
         <v>0</v>
       </c>
       <c r="AE146" t="b">
         <v>0</v>
       </c>
-      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>130091819</v>
+        <v>130087667</v>
       </c>
       <c r="B147" t="n">
-        <v>57823</v>
+        <v>79799</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16413,42 +16418,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>461716</v>
+        <v>461929</v>
       </c>
       <c r="R147" t="n">
-        <v>6780856</v>
+        <v>6780891</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16478,9 +16475,19 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16495,22 +16502,22 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>130086869</v>
+        <v>130091819</v>
       </c>
       <c r="B148" t="n">
-        <v>78938</v>
+        <v>57823</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16518,34 +16525,42 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>461922</v>
+        <v>461716</v>
       </c>
       <c r="R148" t="n">
-        <v>6780874</v>
+        <v>6780856</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16575,24 +16590,9 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>13:11</t>
-        </is>
-      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16607,19 +16607,19 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>130086826</v>
+        <v>130087153</v>
       </c>
       <c r="B149" t="n">
         <v>57823</v>
@@ -16650,19 +16650,19 @@
       <c r="I149" t="inlineStr"/>
       <c r="M149" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>461887</v>
+        <v>461955</v>
       </c>
       <c r="R149" t="n">
-        <v>6780890</v>
+        <v>6780741</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16692,19 +16692,14 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z149" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB149" t="inlineStr">
-        <is>
-          <t>13:03</t>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Äldre spår I högstubbe</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16719,22 +16714,22 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>130087527</v>
+        <v>130086826</v>
       </c>
       <c r="B150" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16742,34 +16737,39 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>461956</v>
+        <v>461887</v>
       </c>
       <c r="R150" t="n">
-        <v>6780787</v>
+        <v>6780890</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16838,10 +16838,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>130092006</v>
+        <v>130087527</v>
       </c>
       <c r="B151" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16849,42 +16849,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>461808</v>
+        <v>461956</v>
       </c>
       <c r="R151" t="n">
-        <v>6780861</v>
+        <v>6780787</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16914,9 +16906,19 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16931,22 +16933,22 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>130084608</v>
+        <v>130092006</v>
       </c>
       <c r="B152" t="n">
-        <v>78938</v>
+        <v>57823</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16954,34 +16956,42 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>461805</v>
+        <v>461808</v>
       </c>
       <c r="R152" t="n">
-        <v>6780835</v>
+        <v>6780861</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17011,24 +17021,9 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z152" t="inlineStr">
-        <is>
-          <t>11:27</t>
-        </is>
-      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AB152" t="inlineStr">
-        <is>
-          <t>11:27</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17043,22 +17038,22 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>130087153</v>
+        <v>130084608</v>
       </c>
       <c r="B153" t="n">
-        <v>57823</v>
+        <v>78938</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17066,39 +17061,34 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>461955</v>
+        <v>461805</v>
       </c>
       <c r="R153" t="n">
-        <v>6780741</v>
+        <v>6780835</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17128,14 +17118,24 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>Äldre spår I högstubbe</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17370,10 +17370,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>130091841</v>
+        <v>130085067</v>
       </c>
       <c r="B156" t="n">
-        <v>57826</v>
+        <v>57823</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17381,16 +17381,16 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -17398,29 +17398,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
       <c r="M156" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N156" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>461720</v>
+        <v>461857</v>
       </c>
       <c r="R156" t="n">
-        <v>6780825</v>
+        <v>6780842</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17450,14 +17443,19 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>hack födosök i gran och ringhackad gran intill</t>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17472,22 +17470,22 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>130092430</v>
+        <v>130091747</v>
       </c>
       <c r="B157" t="n">
-        <v>78938</v>
+        <v>79180</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17495,21 +17493,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17522,10 +17520,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>461933</v>
+        <v>461737</v>
       </c>
       <c r="R157" t="n">
-        <v>6780838</v>
+        <v>6781057</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17560,11 +17558,6 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
-        </is>
-      </c>
       <c r="AD157" t="b">
         <v>0</v>
       </c>
@@ -17578,62 +17571,60 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>130085067</v>
+        <v>130091789</v>
       </c>
       <c r="B158" t="n">
-        <v>57823</v>
+        <v>91110</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100049</v>
+        <v>5685</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>461857</v>
+        <v>461710</v>
       </c>
       <c r="R158" t="n">
-        <v>6780842</v>
+        <v>6780886</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17663,49 +17654,40 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AD158" t="b">
         <v>0</v>
       </c>
       <c r="AE158" t="b">
         <v>0</v>
       </c>
+      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>130091747</v>
+        <v>130091841</v>
       </c>
       <c r="B159" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17713,26 +17695,35 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
@@ -17740,10 +17731,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>461737</v>
+        <v>461720</v>
       </c>
       <c r="R159" t="n">
-        <v>6781057</v>
+        <v>6780825</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17778,13 +17769,17 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>hack födosök i gran och ringhackad gran intill</t>
+        </is>
+      </c>
       <c r="AD159" t="b">
         <v>0</v>
       </c>
       <c r="AE159" t="b">
         <v>0</v>
       </c>
-      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
@@ -17803,10 +17798,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>130091789</v>
+        <v>130092010</v>
       </c>
       <c r="B160" t="n">
-        <v>91110</v>
+        <v>8451</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17814,26 +17809,32 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>5685</v>
+        <v>106545</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
@@ -17841,10 +17842,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>461710</v>
+        <v>461808</v>
       </c>
       <c r="R160" t="n">
-        <v>6780886</v>
+        <v>6780861</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17904,43 +17905,37 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>130092010</v>
+        <v>130092430</v>
       </c>
       <c r="B161" t="n">
-        <v>8451</v>
+        <v>78938</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr"/>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
@@ -17948,10 +17943,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>461808</v>
+        <v>461933</v>
       </c>
       <c r="R161" t="n">
-        <v>6780861</v>
+        <v>6780838</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17986,6 +17981,11 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
+        </is>
+      </c>
       <c r="AD161" t="b">
         <v>0</v>
       </c>
@@ -17999,12 +17999,12 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>

--- a/artfynd/A 58003-2025 artfynd.xlsx
+++ b/artfynd/A 58003-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY186"/>
+  <dimension ref="A1:AY187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129971607</v>
+        <v>129972961</v>
       </c>
       <c r="B8" t="n">
-        <v>79770</v>
+        <v>79180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,21 +1338,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461733</v>
+        <v>461615</v>
       </c>
       <c r="R8" t="n">
-        <v>6780958</v>
+        <v>6780923</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1546,42 +1546,47 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129972961</v>
+        <v>129971831</v>
       </c>
       <c r="B10" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461615</v>
+        <v>461686</v>
       </c>
       <c r="R10" t="n">
         <v>6780923</v>
@@ -1653,50 +1658,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129971831</v>
+        <v>129971607</v>
       </c>
       <c r="B11" t="n">
-        <v>8451</v>
+        <v>79770</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461686</v>
+        <v>461733</v>
       </c>
       <c r="R11" t="n">
-        <v>6780923</v>
+        <v>6780958</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129971115</v>
+        <v>129971787</v>
       </c>
       <c r="B13" t="n">
-        <v>79770</v>
+        <v>79799</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,21 +1883,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461762</v>
+        <v>461741</v>
       </c>
       <c r="R13" t="n">
-        <v>6780940</v>
+        <v>6780920</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1979,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129971787</v>
+        <v>129971115</v>
       </c>
       <c r="B14" t="n">
-        <v>79799</v>
+        <v>79770</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1990,21 +1990,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461741</v>
+        <v>461762</v>
       </c>
       <c r="R14" t="n">
-        <v>6780920</v>
+        <v>6780940</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2086,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129971127</v>
+        <v>129971608</v>
       </c>
       <c r="B15" t="n">
-        <v>79180</v>
+        <v>79799</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,21 +2097,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461762</v>
+        <v>461733</v>
       </c>
       <c r="R15" t="n">
-        <v>6780940</v>
+        <v>6780958</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2193,10 +2193,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129971585</v>
+        <v>129971127</v>
       </c>
       <c r="B16" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2204,39 +2204,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461736</v>
+        <v>461762</v>
       </c>
       <c r="R16" t="n">
-        <v>6780931</v>
+        <v>6780940</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2412,10 +2407,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129971608</v>
+        <v>129971585</v>
       </c>
       <c r="B18" t="n">
-        <v>79799</v>
+        <v>57823</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2423,34 +2418,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461733</v>
+        <v>461736</v>
       </c>
       <c r="R18" t="n">
-        <v>6780958</v>
+        <v>6780931</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2952,50 +2952,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129972234</v>
+        <v>129970829</v>
       </c>
       <c r="B23" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461679</v>
+        <v>461800</v>
       </c>
       <c r="R23" t="n">
-        <v>6780885</v>
+        <v>6781016</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3064,45 +3059,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129970829</v>
+        <v>129972234</v>
       </c>
       <c r="B24" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461800</v>
+        <v>461679</v>
       </c>
       <c r="R24" t="n">
-        <v>6781016</v>
+        <v>6780885</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3283,50 +3283,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129971289</v>
+        <v>129972394</v>
       </c>
       <c r="B26" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461751</v>
+        <v>461679</v>
       </c>
       <c r="R26" t="n">
-        <v>6780936</v>
+        <v>6780885</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3395,7 +3390,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129972394</v>
+        <v>129972457</v>
       </c>
       <c r="B27" t="n">
         <v>79180</v>
@@ -3430,10 +3425,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461679</v>
+        <v>461687</v>
       </c>
       <c r="R27" t="n">
-        <v>6780885</v>
+        <v>6780875</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3502,45 +3497,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129972457</v>
+        <v>129971289</v>
       </c>
       <c r="B28" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461687</v>
+        <v>461751</v>
       </c>
       <c r="R28" t="n">
-        <v>6780875</v>
+        <v>6780936</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3721,45 +3721,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129970675</v>
+        <v>129971587</v>
       </c>
       <c r="B30" t="n">
-        <v>79799</v>
+        <v>8451</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461789</v>
+        <v>461736</v>
       </c>
       <c r="R30" t="n">
-        <v>6780961</v>
+        <v>6780931</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3828,7 +3833,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129971587</v>
+        <v>129972990</v>
       </c>
       <c r="B31" t="n">
         <v>8451</v>
@@ -3868,10 +3873,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461736</v>
+        <v>461615</v>
       </c>
       <c r="R31" t="n">
-        <v>6780931</v>
+        <v>6780923</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3940,50 +3945,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129972990</v>
+        <v>129970675</v>
       </c>
       <c r="B32" t="n">
-        <v>8451</v>
+        <v>79799</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461615</v>
+        <v>461789</v>
       </c>
       <c r="R32" t="n">
-        <v>6780923</v>
+        <v>6780961</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4271,10 +4271,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129971832</v>
+        <v>129970828</v>
       </c>
       <c r="B35" t="n">
-        <v>79180</v>
+        <v>78937</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4282,21 +4282,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4306,10 +4306,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461686</v>
+        <v>461800</v>
       </c>
       <c r="R35" t="n">
-        <v>6780923</v>
+        <v>6781016</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4378,10 +4378,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129970828</v>
+        <v>129971832</v>
       </c>
       <c r="B36" t="n">
-        <v>78937</v>
+        <v>79180</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4389,21 +4389,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461800</v>
+        <v>461686</v>
       </c>
       <c r="R36" t="n">
-        <v>6781016</v>
+        <v>6780923</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4485,10 +4485,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129971259</v>
+        <v>129971804</v>
       </c>
       <c r="B37" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4496,39 +4496,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461751</v>
+        <v>461709</v>
       </c>
       <c r="R37" t="n">
-        <v>6780936</v>
+        <v>6780921</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4704,10 +4699,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129971739</v>
+        <v>129971259</v>
       </c>
       <c r="B39" t="n">
-        <v>79770</v>
+        <v>57823</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4715,34 +4710,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461741</v>
+        <v>461751</v>
       </c>
       <c r="R39" t="n">
-        <v>6780920</v>
+        <v>6780936</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4811,10 +4811,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129971804</v>
+        <v>129971739</v>
       </c>
       <c r="B40" t="n">
-        <v>79180</v>
+        <v>79770</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4822,21 +4822,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4846,10 +4846,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461709</v>
+        <v>461741</v>
       </c>
       <c r="R40" t="n">
-        <v>6780921</v>
+        <v>6780920</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4918,10 +4918,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129972983</v>
+        <v>129970961</v>
       </c>
       <c r="B41" t="n">
-        <v>57823</v>
+        <v>79770</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4929,39 +4929,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461615</v>
+        <v>461789</v>
       </c>
       <c r="R41" t="n">
-        <v>6780923</v>
+        <v>6780961</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5030,10 +5025,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129970961</v>
+        <v>129970813</v>
       </c>
       <c r="B42" t="n">
-        <v>79770</v>
+        <v>79799</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5041,21 +5036,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5065,10 +5060,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461789</v>
+        <v>461800</v>
       </c>
       <c r="R42" t="n">
-        <v>6780961</v>
+        <v>6781016</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5244,10 +5239,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129970813</v>
+        <v>129972983</v>
       </c>
       <c r="B44" t="n">
-        <v>79799</v>
+        <v>57823</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5255,34 +5250,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461800</v>
+        <v>461615</v>
       </c>
       <c r="R44" t="n">
-        <v>6781016</v>
+        <v>6780923</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6032,10 +6032,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129972454</v>
+        <v>129973137</v>
       </c>
       <c r="B51" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6043,39 +6043,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461687</v>
+        <v>461609</v>
       </c>
       <c r="R51" t="n">
-        <v>6780875</v>
+        <v>6780949</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6122,7 +6117,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>2 bilder</t>
+          <t>3 bilder, rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6149,10 +6144,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129973137</v>
+        <v>129969692</v>
       </c>
       <c r="B52" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6160,34 +6155,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461609</v>
+        <v>461799</v>
       </c>
       <c r="R52" t="n">
-        <v>6780949</v>
+        <v>6780979</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>3 bilder, rikligt i en radie av ca 50 meter</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6261,10 +6261,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129972233</v>
+        <v>129972454</v>
       </c>
       <c r="B53" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6272,16 +6272,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6290,24 +6290,21 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>461679</v>
+        <v>461687</v>
       </c>
       <c r="R53" t="n">
-        <v>6780885</v>
+        <v>6780875</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6354,7 +6351,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>2 bilder</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6381,7 +6378,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129969692</v>
+        <v>129972233</v>
       </c>
       <c r="B54" t="n">
         <v>57823</v>
@@ -6410,21 +6407,24 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>461799</v>
+        <v>461679</v>
       </c>
       <c r="R54" t="n">
-        <v>6780979</v>
+        <v>6780885</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6498,32 +6498,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130087228</v>
+        <v>130087273</v>
       </c>
       <c r="B55" t="n">
-        <v>8451</v>
+        <v>78938</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6533,13 +6533,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>461948</v>
+        <v>462051</v>
       </c>
       <c r="R55" t="n">
-        <v>6780740</v>
+        <v>6780727</v>
       </c>
       <c r="S55" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6605,10 +6605,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130087273</v>
+        <v>130083775</v>
       </c>
       <c r="B56" t="n">
-        <v>78938</v>
+        <v>79180</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6616,21 +6616,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6640,10 +6640,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>462051</v>
+        <v>461717</v>
       </c>
       <c r="R56" t="n">
-        <v>6780727</v>
+        <v>6780842</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6675,7 +6675,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6712,7 +6712,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130087516</v>
+        <v>130087228</v>
       </c>
       <c r="B57" t="n">
         <v>8451</v>
@@ -6741,24 +6741,19 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461956</v>
+        <v>461948</v>
       </c>
       <c r="R57" t="n">
-        <v>6780787</v>
+        <v>6780740</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6824,45 +6819,50 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130083775</v>
+        <v>130087516</v>
       </c>
       <c r="B58" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461717</v>
+        <v>461956</v>
       </c>
       <c r="R58" t="n">
-        <v>6780842</v>
+        <v>6780787</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7372,41 +7372,40 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130091775</v>
+        <v>130092209</v>
       </c>
       <c r="B63" t="n">
-        <v>8451</v>
+        <v>57823</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -7416,10 +7415,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461753</v>
+        <v>461965</v>
       </c>
       <c r="R63" t="n">
-        <v>6781025</v>
+        <v>6780759</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7460,7 +7459,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7479,7 +7477,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130092205</v>
+        <v>130091775</v>
       </c>
       <c r="B64" t="n">
         <v>8451</v>
@@ -7523,10 +7521,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>461965</v>
+        <v>461753</v>
       </c>
       <c r="R64" t="n">
-        <v>6780759</v>
+        <v>6781025</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7579,47 +7577,48 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander, Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130092209</v>
+        <v>130092205</v>
       </c>
       <c r="B65" t="n">
-        <v>57823</v>
+        <v>8451</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -7673,6 +7672,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7691,10 +7691,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130087492</v>
+        <v>130085288</v>
       </c>
       <c r="B66" t="n">
-        <v>79180</v>
+        <v>92211</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7702,37 +7702,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>5467</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>461944</v>
+        <v>461858</v>
       </c>
       <c r="R66" t="n">
-        <v>6780796</v>
+        <v>6780876</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7786,66 +7786,57 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130092389</v>
+        <v>130087716</v>
       </c>
       <c r="B67" t="n">
-        <v>8451</v>
+        <v>79799</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>461870</v>
+        <v>461894</v>
       </c>
       <c r="R67" t="n">
-        <v>6780967</v>
+        <v>6780914</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7875,80 +7866,87 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130087222</v>
+        <v>130092026</v>
       </c>
       <c r="B68" t="n">
-        <v>8451</v>
+        <v>78937</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>462001</v>
+        <v>461858</v>
       </c>
       <c r="R68" t="n">
-        <v>6780764</v>
+        <v>6780846</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7978,54 +7976,40 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>13:46</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>13:46</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Äldre spår I tallåga</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130087716</v>
+        <v>130087492</v>
       </c>
       <c r="B69" t="n">
-        <v>79799</v>
+        <v>79180</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8033,21 +8017,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8057,10 +8041,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>461894</v>
+        <v>461944</v>
       </c>
       <c r="R69" t="n">
-        <v>6780914</v>
+        <v>6780796</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8241,10 +8225,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130087512</v>
+        <v>130087669</v>
       </c>
       <c r="B71" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8252,39 +8236,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>461956</v>
+        <v>461929</v>
       </c>
       <c r="R71" t="n">
-        <v>6780787</v>
+        <v>6780891</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8353,10 +8332,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130087669</v>
+        <v>130087512</v>
       </c>
       <c r="B72" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8364,34 +8343,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>461929</v>
+        <v>461956</v>
       </c>
       <c r="R72" t="n">
-        <v>6780891</v>
+        <v>6780787</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8460,48 +8444,53 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130085288</v>
+        <v>130087222</v>
       </c>
       <c r="B73" t="n">
-        <v>92211</v>
+        <v>8451</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5467</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>461858</v>
+        <v>462001</v>
       </c>
       <c r="R73" t="n">
-        <v>6780876</v>
+        <v>6780764</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8530,7 +8519,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8540,7 +8529,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Äldre spår I tallåga</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8555,49 +8549,55 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130092026</v>
+        <v>130092389</v>
       </c>
       <c r="B74" t="n">
-        <v>78937</v>
+        <v>8451</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -8605,10 +8605,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>461858</v>
+        <v>461870</v>
       </c>
       <c r="R74" t="n">
-        <v>6780846</v>
+        <v>6780967</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8656,12 +8656,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8775,10 +8775,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130087408</v>
+        <v>130086767</v>
       </c>
       <c r="B76" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8786,39 +8786,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>462039</v>
+        <v>461850</v>
       </c>
       <c r="R76" t="n">
-        <v>6780770</v>
+        <v>6780913</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8861,6 +8856,11 @@
       <c r="AB76" t="inlineStr">
         <is>
           <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>2 bild. Rikligt till måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8887,10 +8887,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130086767</v>
+        <v>130087408</v>
       </c>
       <c r="B77" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8898,34 +8898,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>461850</v>
+        <v>462039</v>
       </c>
       <c r="R77" t="n">
-        <v>6780913</v>
+        <v>6780770</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8968,11 +8973,6 @@
       <c r="AB77" t="inlineStr">
         <is>
           <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>2 bild. Rikligt till måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9106,53 +9106,53 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130086588</v>
+        <v>130086966</v>
       </c>
       <c r="B79" t="n">
-        <v>8451</v>
+        <v>57826</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>461880</v>
+        <v>461946</v>
       </c>
       <c r="R79" t="n">
-        <v>6780838</v>
+        <v>6780867</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9191,7 +9191,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9206,65 +9211,65 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Birgitta Kvist, Håkan Thenander, Peter Turander, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130086966</v>
+        <v>130086588</v>
       </c>
       <c r="B80" t="n">
-        <v>57826</v>
+        <v>8451</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>461946</v>
+        <v>461880</v>
       </c>
       <c r="R80" t="n">
-        <v>6780867</v>
+        <v>6780838</v>
       </c>
       <c r="S80" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9293,7 +9298,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9303,12 +9308,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:17</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9323,12 +9323,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9436,45 +9436,54 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130086497</v>
+        <v>130091811</v>
       </c>
       <c r="B82" t="n">
-        <v>90760</v>
+        <v>8451</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1962</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>461865</v>
+        <v>461716</v>
       </c>
       <c r="R82" t="n">
-        <v>6780909</v>
+        <v>6780852</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9504,54 +9513,40 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>12:38</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>På en bränd tallåga</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130091631</v>
+        <v>130085215</v>
       </c>
       <c r="B83" t="n">
-        <v>79212</v>
+        <v>79180</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9559,37 +9554,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>461750</v>
+        <v>461844</v>
       </c>
       <c r="R83" t="n">
-        <v>6781031</v>
+        <v>6780835</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9619,84 +9611,84 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130091811</v>
+        <v>130087832</v>
       </c>
       <c r="B84" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>461716</v>
+        <v>461873</v>
       </c>
       <c r="R84" t="n">
-        <v>6780852</v>
+        <v>6780961</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9726,40 +9718,49 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130085215</v>
+        <v>130091631</v>
       </c>
       <c r="B85" t="n">
-        <v>79180</v>
+        <v>79212</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9767,34 +9768,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>461844</v>
+        <v>461750</v>
       </c>
       <c r="R85" t="n">
-        <v>6780835</v>
+        <v>6781031</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9824,49 +9828,40 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130087832</v>
+        <v>130086497</v>
       </c>
       <c r="B86" t="n">
-        <v>79180</v>
+        <v>90760</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9874,34 +9869,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>461873</v>
+        <v>461865</v>
       </c>
       <c r="R86" t="n">
-        <v>6780961</v>
+        <v>6780909</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9933,7 +9928,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9943,7 +9938,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>På en bränd tallåga</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9958,19 +9958,19 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130092368</v>
+        <v>130092059</v>
       </c>
       <c r="B87" t="n">
         <v>57823</v>
@@ -10013,10 +10013,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>461867</v>
+        <v>461946</v>
       </c>
       <c r="R87" t="n">
-        <v>6780956</v>
+        <v>6780839</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10063,62 +10063,65 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130082759</v>
+        <v>130092368</v>
       </c>
       <c r="B88" t="n">
-        <v>8451</v>
+        <v>57823</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>461757</v>
+        <v>461867</v>
       </c>
       <c r="R88" t="n">
-        <v>6781096</v>
+        <v>6780956</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10148,19 +10151,9 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>10:14</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10175,65 +10168,62 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130092059</v>
+        <v>130082759</v>
       </c>
       <c r="B89" t="n">
-        <v>57823</v>
+        <v>8451</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>461946</v>
+        <v>461757</v>
       </c>
       <c r="R89" t="n">
-        <v>6780839</v>
+        <v>6781096</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10263,9 +10253,19 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10280,19 +10280,19 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>130087850</v>
+        <v>130086721</v>
       </c>
       <c r="B90" t="n">
         <v>8451</v>
@@ -10328,14 +10328,14 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>461873</v>
+        <v>461832</v>
       </c>
       <c r="R90" t="n">
-        <v>6780961</v>
+        <v>6780916</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10367,7 +10367,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10377,7 +10377,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Äldre spår i torrtall</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10392,19 +10397,19 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>130086721</v>
+        <v>130092063</v>
       </c>
       <c r="B91" t="n">
         <v>8451</v>
@@ -10433,21 +10438,25 @@
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>461832</v>
+        <v>461946</v>
       </c>
       <c r="R91" t="n">
-        <v>6780916</v>
+        <v>6780839</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10477,94 +10486,80 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Äldre spår i torrtall</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>130085149</v>
+        <v>130087850</v>
       </c>
       <c r="B92" t="n">
-        <v>57823</v>
+        <v>8451</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>461857</v>
+        <v>461873</v>
       </c>
       <c r="R92" t="n">
-        <v>6780859</v>
+        <v>6780961</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10596,7 +10591,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10606,12 +10601,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Äldre spår i torrtall</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10626,19 +10616,19 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>130083753</v>
+        <v>130091794</v>
       </c>
       <c r="B93" t="n">
         <v>79180</v>
@@ -10667,16 +10657,19 @@
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>461711</v>
+        <v>461710</v>
       </c>
       <c r="R93" t="n">
-        <v>6780852</v>
+        <v>6780886</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10706,46 +10699,37 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130087798</v>
+        <v>130092053</v>
       </c>
       <c r="B94" t="n">
         <v>79180</v>
@@ -10774,16 +10758,19 @@
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>461864</v>
+        <v>461926</v>
       </c>
       <c r="R94" t="n">
-        <v>6780951</v>
+        <v>6780853</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10813,93 +10800,75 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>130092063</v>
+        <v>130083753</v>
       </c>
       <c r="B95" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>461946</v>
+        <v>461711</v>
       </c>
       <c r="R95" t="n">
-        <v>6780839</v>
+        <v>6780852</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10929,37 +10898,46 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>130091794</v>
+        <v>130087798</v>
       </c>
       <c r="B96" t="n">
         <v>79180</v>
@@ -10988,19 +10966,16 @@
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>461710</v>
+        <v>461864</v>
       </c>
       <c r="R96" t="n">
-        <v>6780886</v>
+        <v>6780951</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11030,40 +11005,49 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>130092053</v>
+        <v>130085149</v>
       </c>
       <c r="B97" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11071,37 +11055,39 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>461926</v>
+        <v>461857</v>
       </c>
       <c r="R97" t="n">
-        <v>6780853</v>
+        <v>6780859</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11131,40 +11117,54 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Äldre spår i torrtall</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>130087184</v>
+        <v>130092019</v>
       </c>
       <c r="B98" t="n">
-        <v>79180</v>
+        <v>78938</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11172,37 +11172,40 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>461948</v>
+        <v>461858</v>
       </c>
       <c r="R98" t="n">
-        <v>6780740</v>
+        <v>6780846</v>
       </c>
       <c r="S98" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11229,54 +11232,40 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
-        </is>
-      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>130087727</v>
+        <v>130091832</v>
       </c>
       <c r="B99" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11284,39 +11273,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>461894</v>
+        <v>461738</v>
       </c>
       <c r="R99" t="n">
-        <v>6780914</v>
+        <v>6780825</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11346,49 +11333,40 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>130087915</v>
+        <v>130087184</v>
       </c>
       <c r="B100" t="n">
-        <v>79799</v>
+        <v>79180</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11396,21 +11374,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11420,13 +11398,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>461853</v>
+        <v>461948</v>
       </c>
       <c r="R100" t="n">
-        <v>6780990</v>
+        <v>6780740</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11466,6 +11444,11 @@
       <c r="AB100" t="inlineStr">
         <is>
           <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11492,54 +11475,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>130091828</v>
+        <v>130087915</v>
       </c>
       <c r="B101" t="n">
-        <v>8451</v>
+        <v>79799</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>461736</v>
+        <v>461853</v>
       </c>
       <c r="R101" t="n">
-        <v>6780844</v>
+        <v>6780990</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11569,84 +11543,89 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>130091798</v>
+        <v>130087727</v>
       </c>
       <c r="B102" t="n">
-        <v>8451</v>
+        <v>57823</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>461713</v>
+        <v>461894</v>
       </c>
       <c r="R102" t="n">
-        <v>6780880</v>
+        <v>6780914</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11676,67 +11655,82 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>130091832</v>
+        <v>130091828</v>
       </c>
       <c r="B103" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
@@ -11744,10 +11738,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>461738</v>
+        <v>461736</v>
       </c>
       <c r="R103" t="n">
-        <v>6780825</v>
+        <v>6780844</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11807,37 +11801,43 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>130092019</v>
+        <v>130091798</v>
       </c>
       <c r="B104" t="n">
-        <v>78938</v>
+        <v>8451</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
@@ -11845,10 +11845,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>461858</v>
+        <v>461713</v>
       </c>
       <c r="R104" t="n">
-        <v>6780846</v>
+        <v>6780880</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11908,7 +11908,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>130082810</v>
+        <v>130091785</v>
       </c>
       <c r="B105" t="n">
         <v>79180</v>
@@ -11937,16 +11937,19 @@
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>461757</v>
+        <v>461710</v>
       </c>
       <c r="R105" t="n">
-        <v>6781096</v>
+        <v>6780938</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11976,46 +11979,37 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>130087616</v>
+        <v>130092042</v>
       </c>
       <c r="B106" t="n">
         <v>79180</v>
@@ -12044,16 +12038,19 @@
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>461970</v>
+        <v>461850</v>
       </c>
       <c r="R106" t="n">
-        <v>6780823</v>
+        <v>6780907</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12083,98 +12080,75 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter</t>
-        </is>
-      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>130092018</v>
+        <v>130082810</v>
       </c>
       <c r="B107" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>461858</v>
+        <v>461757</v>
       </c>
       <c r="R107" t="n">
-        <v>6780846</v>
+        <v>6781096</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12204,37 +12178,46 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>130092042</v>
+        <v>130087616</v>
       </c>
       <c r="B108" t="n">
         <v>79180</v>
@@ -12263,19 +12246,16 @@
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>461850</v>
+        <v>461970</v>
       </c>
       <c r="R108" t="n">
-        <v>6780907</v>
+        <v>6780823</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12305,67 +12285,87 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter</t>
+        </is>
+      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>130091785</v>
+        <v>130092018</v>
       </c>
       <c r="B109" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
@@ -12373,10 +12373,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>461710</v>
+        <v>461858</v>
       </c>
       <c r="R109" t="n">
-        <v>6780938</v>
+        <v>6780846</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12650,53 +12650,53 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>130085157</v>
+        <v>130087227</v>
       </c>
       <c r="B112" t="n">
-        <v>8451</v>
+        <v>57823</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>461859</v>
+        <v>461948</v>
       </c>
       <c r="R112" t="n">
-        <v>6780861</v>
+        <v>6780740</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12725,7 +12725,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12735,7 +12735,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12750,19 +12750,19 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>130087227</v>
+        <v>130087844</v>
       </c>
       <c r="B113" t="n">
         <v>57823</v>
@@ -12802,13 +12802,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>461948</v>
+        <v>461873</v>
       </c>
       <c r="R113" t="n">
-        <v>6780740</v>
+        <v>6780961</v>
       </c>
       <c r="S113" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12874,10 +12874,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>130087844</v>
+        <v>130087271</v>
       </c>
       <c r="B114" t="n">
-        <v>57823</v>
+        <v>79799</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12885,39 +12885,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>461873</v>
+        <v>462051</v>
       </c>
       <c r="R114" t="n">
-        <v>6780961</v>
+        <v>6780727</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12986,45 +12981,50 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>130087271</v>
+        <v>130085157</v>
       </c>
       <c r="B115" t="n">
-        <v>79799</v>
+        <v>8451</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>462051</v>
+        <v>461859</v>
       </c>
       <c r="R115" t="n">
-        <v>6780727</v>
+        <v>6780861</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13056,7 +13056,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13081,22 +13081,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>130087759</v>
+        <v>130092071</v>
       </c>
       <c r="B116" t="n">
-        <v>79180</v>
+        <v>92026</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13104,34 +13104,37 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>461879</v>
+        <v>461946</v>
       </c>
       <c r="R116" t="n">
-        <v>6780924</v>
+        <v>6780863</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13161,49 +13164,40 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>130092033</v>
+        <v>130087759</v>
       </c>
       <c r="B117" t="n">
-        <v>78938</v>
+        <v>79180</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13211,37 +13205,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>461871</v>
+        <v>461879</v>
       </c>
       <c r="R117" t="n">
-        <v>6780851</v>
+        <v>6780924</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13271,30 +13262,39 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -13402,10 +13402,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>130092139</v>
+        <v>130092122</v>
       </c>
       <c r="B119" t="n">
-        <v>8451</v>
+        <v>79204</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13413,32 +13413,26 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>106545</v>
+        <v>6434</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
@@ -13446,10 +13440,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>461975</v>
+        <v>461986</v>
       </c>
       <c r="R119" t="n">
-        <v>6780791</v>
+        <v>6780804</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13509,10 +13503,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>130092122</v>
+        <v>130092139</v>
       </c>
       <c r="B120" t="n">
-        <v>79204</v>
+        <v>8451</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13520,26 +13514,32 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6434</v>
+        <v>106545</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
@@ -13547,10 +13547,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>461986</v>
+        <v>461975</v>
       </c>
       <c r="R120" t="n">
-        <v>6780804</v>
+        <v>6780791</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13610,10 +13610,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>130092071</v>
+        <v>130092033</v>
       </c>
       <c r="B121" t="n">
-        <v>92026</v>
+        <v>78938</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13621,21 +13621,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>658</v>
+        <v>228912</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13648,10 +13648,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>461946</v>
+        <v>461871</v>
       </c>
       <c r="R121" t="n">
-        <v>6780863</v>
+        <v>6780851</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13711,10 +13711,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>130086831</v>
+        <v>130091751</v>
       </c>
       <c r="B122" t="n">
-        <v>79180</v>
+        <v>79212</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13722,34 +13722,37 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>461887</v>
+        <v>461737</v>
       </c>
       <c r="R122" t="n">
-        <v>6780890</v>
+        <v>6781057</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13779,49 +13782,40 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>130083776</v>
+        <v>130091745</v>
       </c>
       <c r="B123" t="n">
-        <v>78938</v>
+        <v>79180</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13829,34 +13823,37 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>461738</v>
+        <v>461749</v>
       </c>
       <c r="R123" t="n">
-        <v>6780866</v>
+        <v>6781031</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13886,84 +13883,78 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>10:54</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>10:54</t>
-        </is>
-      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>130087075</v>
+        <v>130091628</v>
       </c>
       <c r="B124" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>461944</v>
+        <v>461750</v>
       </c>
       <c r="R124" t="n">
-        <v>6780796</v>
+        <v>6781031</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13993,46 +13984,37 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>130091628</v>
+        <v>130086831</v>
       </c>
       <c r="B125" t="n">
         <v>79180</v>
@@ -14061,19 +14043,16 @@
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>461750</v>
+        <v>461887</v>
       </c>
       <c r="R125" t="n">
-        <v>6781031</v>
+        <v>6780890</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14103,78 +14082,84 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>130091745</v>
+        <v>130087075</v>
       </c>
       <c r="B126" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>461749</v>
+        <v>461944</v>
       </c>
       <c r="R126" t="n">
-        <v>6781031</v>
+        <v>6780796</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14204,40 +14189,49 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD126" t="b">
         <v>0</v>
       </c>
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>130091751</v>
+        <v>130083776</v>
       </c>
       <c r="B127" t="n">
-        <v>79212</v>
+        <v>78938</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14245,37 +14239,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>461737</v>
+        <v>461738</v>
       </c>
       <c r="R127" t="n">
-        <v>6781057</v>
+        <v>6780866</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14305,40 +14296,49 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>130085207</v>
+        <v>130091780</v>
       </c>
       <c r="B128" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14346,39 +14346,37 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>461844</v>
+        <v>461742</v>
       </c>
       <c r="R128" t="n">
-        <v>6780835</v>
+        <v>6781010</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14408,49 +14406,40 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AD128" t="b">
         <v>0</v>
       </c>
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>130087794</v>
+        <v>130087722</v>
       </c>
       <c r="B129" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14458,39 +14447,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>461864</v>
+        <v>461894</v>
       </c>
       <c r="R129" t="n">
-        <v>6780951</v>
+        <v>6780914</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14778,10 +14762,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>130091780</v>
+        <v>130085207</v>
       </c>
       <c r="B132" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14789,37 +14773,39 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>461742</v>
+        <v>461844</v>
       </c>
       <c r="R132" t="n">
-        <v>6781010</v>
+        <v>6780835</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14849,40 +14835,49 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>130085089</v>
+        <v>130087794</v>
       </c>
       <c r="B133" t="n">
-        <v>78938</v>
+        <v>57823</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14890,34 +14885,39 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>461857</v>
+        <v>461864</v>
       </c>
       <c r="R133" t="n">
-        <v>6780866</v>
+        <v>6780951</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14949,7 +14949,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14959,7 +14959,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14974,22 +14974,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>130087722</v>
+        <v>130083972</v>
       </c>
       <c r="B134" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14997,34 +14997,39 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>461894</v>
+        <v>461717</v>
       </c>
       <c r="R134" t="n">
-        <v>6780914</v>
+        <v>6780842</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15056,7 +15061,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15066,7 +15071,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15093,38 +15098,38 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>130083972</v>
+        <v>130085214</v>
       </c>
       <c r="B135" t="n">
-        <v>57823</v>
+        <v>8451</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="M135" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -15133,10 +15138,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>461717</v>
+        <v>461844</v>
       </c>
       <c r="R135" t="n">
-        <v>6780842</v>
+        <v>6780835</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15205,50 +15210,45 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>130085214</v>
+        <v>130085089</v>
       </c>
       <c r="B136" t="n">
-        <v>8451</v>
+        <v>78938</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>461844</v>
+        <v>461857</v>
       </c>
       <c r="R136" t="n">
-        <v>6780835</v>
+        <v>6780866</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15280,7 +15280,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15290,7 +15290,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15305,22 +15305,22 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>130087789</v>
+        <v>130083742</v>
       </c>
       <c r="B137" t="n">
-        <v>79212</v>
+        <v>79180</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15328,34 +15328,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>461857</v>
+        <v>461699</v>
       </c>
       <c r="R137" t="n">
-        <v>6780939</v>
+        <v>6780870</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15387,7 +15387,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15397,12 +15397,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Sparsamt på gran</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15417,44 +15412,44 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>130087401</v>
+        <v>130087057</v>
       </c>
       <c r="B138" t="n">
-        <v>8451</v>
+        <v>79799</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15464,10 +15459,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>462039</v>
+        <v>461952</v>
       </c>
       <c r="R138" t="n">
-        <v>6780770</v>
+        <v>6780820</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15536,32 +15531,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>130083742</v>
+        <v>130087401</v>
       </c>
       <c r="B139" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15571,10 +15566,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>461699</v>
+        <v>462039</v>
       </c>
       <c r="R139" t="n">
-        <v>6780870</v>
+        <v>6780770</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15606,7 +15601,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15616,7 +15611,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15643,32 +15638,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>130087057</v>
+        <v>130086828</v>
       </c>
       <c r="B140" t="n">
-        <v>79799</v>
+        <v>8451</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15678,10 +15673,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>461952</v>
+        <v>461887</v>
       </c>
       <c r="R140" t="n">
-        <v>6780820</v>
+        <v>6780890</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15750,10 +15745,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>130087754</v>
+        <v>130087789</v>
       </c>
       <c r="B141" t="n">
-        <v>57823</v>
+        <v>79212</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15761,39 +15756,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>461879</v>
+        <v>461857</v>
       </c>
       <c r="R141" t="n">
-        <v>6780924</v>
+        <v>6780939</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15825,7 +15815,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15835,7 +15825,12 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Sparsamt på gran</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15850,57 +15845,62 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>130086828</v>
+        <v>130087754</v>
       </c>
       <c r="B142" t="n">
-        <v>8451</v>
+        <v>57823</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>461887</v>
+        <v>461879</v>
       </c>
       <c r="R142" t="n">
-        <v>6780890</v>
+        <v>6780924</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16295,10 +16295,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>130085309</v>
+        <v>130087667</v>
       </c>
       <c r="B146" t="n">
-        <v>57823</v>
+        <v>79799</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16306,39 +16306,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>461880</v>
+        <v>461929</v>
       </c>
       <c r="R146" t="n">
-        <v>6780838</v>
+        <v>6780891</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16370,7 +16365,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16380,7 +16375,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16407,10 +16402,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>130087667</v>
+        <v>130085309</v>
       </c>
       <c r="B147" t="n">
-        <v>79799</v>
+        <v>57823</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16418,34 +16413,39 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>461929</v>
+        <v>461880</v>
       </c>
       <c r="R147" t="n">
-        <v>6780891</v>
+        <v>6780838</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16477,7 +16477,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16487,7 +16487,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16619,10 +16619,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>130087153</v>
+        <v>130084608</v>
       </c>
       <c r="B149" t="n">
-        <v>57823</v>
+        <v>78938</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16630,39 +16630,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>461955</v>
+        <v>461805</v>
       </c>
       <c r="R149" t="n">
-        <v>6780741</v>
+        <v>6780835</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16692,14 +16687,24 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>Äldre spår I högstubbe</t>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16726,10 +16731,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>130086826</v>
+        <v>130087527</v>
       </c>
       <c r="B150" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16737,39 +16742,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>461887</v>
+        <v>461956</v>
       </c>
       <c r="R150" t="n">
-        <v>6780890</v>
+        <v>6780787</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16838,10 +16838,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>130087527</v>
+        <v>130092006</v>
       </c>
       <c r="B151" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16849,34 +16849,42 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>461956</v>
+        <v>461808</v>
       </c>
       <c r="R151" t="n">
-        <v>6780787</v>
+        <v>6780861</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16906,19 +16914,9 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AB151" t="inlineStr">
-        <is>
-          <t>13:03</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16933,19 +16931,19 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>130092006</v>
+        <v>130087153</v>
       </c>
       <c r="B152" t="n">
         <v>57823</v>
@@ -16974,24 +16972,21 @@
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
       <c r="M152" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>461808</v>
+        <v>461955</v>
       </c>
       <c r="R152" t="n">
-        <v>6780861</v>
+        <v>6780741</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17026,6 +17021,11 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>Äldre spår I högstubbe</t>
+        </is>
+      </c>
       <c r="AD152" t="b">
         <v>0</v>
       </c>
@@ -17038,22 +17038,22 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>130084608</v>
+        <v>130086826</v>
       </c>
       <c r="B153" t="n">
-        <v>78938</v>
+        <v>57823</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17061,34 +17061,39 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>461805</v>
+        <v>461887</v>
       </c>
       <c r="R153" t="n">
-        <v>6780835</v>
+        <v>6780890</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17120,7 +17125,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17130,12 +17135,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>11:27</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17150,55 +17150,49 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>130092162</v>
+        <v>130091626</v>
       </c>
       <c r="B154" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr"/>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
@@ -17206,10 +17200,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>461969</v>
+        <v>461775</v>
       </c>
       <c r="R154" t="n">
-        <v>6780801</v>
+        <v>6781049</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17269,37 +17263,43 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>130091626</v>
+        <v>130092162</v>
       </c>
       <c r="B155" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
@@ -17307,10 +17307,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>461775</v>
+        <v>461969</v>
       </c>
       <c r="R155" t="n">
-        <v>6781049</v>
+        <v>6780801</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17370,10 +17370,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>130085067</v>
+        <v>130092430</v>
       </c>
       <c r="B156" t="n">
-        <v>57823</v>
+        <v>78938</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17381,39 +17381,37 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>461857</v>
+        <v>461933</v>
       </c>
       <c r="R156" t="n">
-        <v>6780842</v>
+        <v>6780838</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17443,19 +17441,14 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>10:14</t>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17464,55 +17457,62 @@
       <c r="AE156" t="b">
         <v>0</v>
       </c>
+      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>130091747</v>
+        <v>130092010</v>
       </c>
       <c r="B157" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
@@ -17520,10 +17520,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>461737</v>
+        <v>461808</v>
       </c>
       <c r="R157" t="n">
-        <v>6781057</v>
+        <v>6780861</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17684,10 +17684,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>130091841</v>
+        <v>130091747</v>
       </c>
       <c r="B159" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17695,35 +17695,26 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
@@ -17731,10 +17722,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>461720</v>
+        <v>461737</v>
       </c>
       <c r="R159" t="n">
-        <v>6780825</v>
+        <v>6781057</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17769,17 +17760,13 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>hack födosök i gran och ringhackad gran intill</t>
-        </is>
-      </c>
       <c r="AD159" t="b">
         <v>0</v>
       </c>
       <c r="AE159" t="b">
         <v>0</v>
       </c>
+      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
@@ -17798,54 +17785,50 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>130092010</v>
+        <v>130085067</v>
       </c>
       <c r="B160" t="n">
-        <v>8451</v>
+        <v>57823</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
       <c r="M160" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N160" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>461808</v>
+        <v>461857</v>
       </c>
       <c r="R160" t="n">
-        <v>6780861</v>
+        <v>6780842</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17875,40 +17858,49 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AD160" t="b">
         <v>0</v>
       </c>
       <c r="AE160" t="b">
         <v>0</v>
       </c>
-      <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="b">
         <v>0</v>
       </c>
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>130092430</v>
+        <v>130091841</v>
       </c>
       <c r="B161" t="n">
-        <v>78938</v>
+        <v>57826</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17916,26 +17908,35 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
@@ -17943,10 +17944,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>461933</v>
+        <v>461720</v>
       </c>
       <c r="R161" t="n">
-        <v>6780838</v>
+        <v>6780825</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17983,7 +17984,7 @@
       </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>hack födosök i gran och ringhackad gran intill</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17992,19 +17993,18 @@
       <c r="AE161" t="b">
         <v>0</v>
       </c>
-      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
@@ -18241,10 +18241,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>130086991</v>
+        <v>130083774</v>
       </c>
       <c r="B164" t="n">
-        <v>79180</v>
+        <v>90760</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18252,37 +18252,40 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>461939</v>
+        <v>461717</v>
       </c>
       <c r="R164" t="n">
-        <v>6780857</v>
+        <v>6780842</v>
       </c>
       <c r="S164" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -18311,7 +18314,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -18321,12 +18324,12 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>2 bild. Rikligt till måttligt i en radie av ca 50 meter</t>
+          <t>2 bilder</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18335,6 +18338,7 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
+      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
@@ -18353,10 +18357,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>130083774</v>
+        <v>130086991</v>
       </c>
       <c r="B165" t="n">
-        <v>90760</v>
+        <v>79180</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18364,40 +18368,37 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>461717</v>
+        <v>461939</v>
       </c>
       <c r="R165" t="n">
-        <v>6780842</v>
+        <v>6780857</v>
       </c>
       <c r="S165" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -18426,7 +18427,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -18436,12 +18437,12 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>2 bilder</t>
+          <t>2 bild. Rikligt till måttligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18450,7 +18451,6 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
-      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
@@ -20374,43 +20374,37 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>130157677</v>
+        <v>130157446</v>
       </c>
       <c r="B184" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr"/>
-      <c r="L184" t="inlineStr"/>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
@@ -20418,10 +20412,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>461370</v>
+        <v>462162</v>
       </c>
       <c r="R184" t="n">
-        <v>6780963</v>
+        <v>6780616</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20462,7 +20456,6 @@
       <c r="AE184" t="b">
         <v>0</v>
       </c>
-      <c r="AF184" t="inlineStr"/>
       <c r="AG184" t="b">
         <v>0</v>
       </c>
@@ -20474,44 +20467,50 @@
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>130157446</v>
+        <v>130157677</v>
       </c>
       <c r="B185" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
@@ -20519,10 +20518,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>462162</v>
+        <v>461370</v>
       </c>
       <c r="R185" t="n">
-        <v>6780616</v>
+        <v>6780963</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20563,6 +20562,7 @@
       <c r="AE185" t="b">
         <v>0</v>
       </c>
+      <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="b">
         <v>0</v>
       </c>
@@ -20574,7 +20574,7 @@
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
@@ -20680,6 +20680,126 @@
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>129972392</v>
+      </c>
+      <c r="B187" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr"/>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>Rävhällsdammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q187" t="n">
+        <v>461679</v>
+      </c>
+      <c r="R187" t="n">
+        <v>6780885</v>
+      </c>
+      <c r="S187" t="n">
+        <v>10</v>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>4 bilder, 10 hackhål/bohål, 4 till 8 meter upp, 3 till 6 cm i diameter</t>
+        </is>
+      </c>
+      <c r="AD187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT187" t="inlineStr"/>
+      <c r="AW187" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX187" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY187" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58003-2025 artfynd.xlsx
+++ b/artfynd/A 58003-2025 artfynd.xlsx
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129971787</v>
+        <v>129971115</v>
       </c>
       <c r="B13" t="n">
-        <v>79799</v>
+        <v>79770</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,21 +1883,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461741</v>
+        <v>461762</v>
       </c>
       <c r="R13" t="n">
-        <v>6780920</v>
+        <v>6780940</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1979,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129971115</v>
+        <v>129971787</v>
       </c>
       <c r="B14" t="n">
-        <v>79770</v>
+        <v>79799</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1990,21 +1990,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461762</v>
+        <v>461741</v>
       </c>
       <c r="R14" t="n">
-        <v>6780940</v>
+        <v>6780920</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2086,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129971608</v>
+        <v>129971127</v>
       </c>
       <c r="B15" t="n">
-        <v>79799</v>
+        <v>79180</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,21 +2097,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461733</v>
+        <v>461762</v>
       </c>
       <c r="R15" t="n">
-        <v>6780958</v>
+        <v>6780940</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2193,7 +2193,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129971127</v>
+        <v>129973851</v>
       </c>
       <c r="B16" t="n">
         <v>79180</v>
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461762</v>
+        <v>461730</v>
       </c>
       <c r="R16" t="n">
-        <v>6780940</v>
+        <v>6780969</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2300,10 +2300,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129973851</v>
+        <v>129971585</v>
       </c>
       <c r="B17" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2311,34 +2311,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461730</v>
+        <v>461736</v>
       </c>
       <c r="R17" t="n">
-        <v>6780969</v>
+        <v>6780931</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2407,10 +2412,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129971585</v>
+        <v>129971608</v>
       </c>
       <c r="B18" t="n">
-        <v>57823</v>
+        <v>79799</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2418,39 +2423,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461736</v>
+        <v>461733</v>
       </c>
       <c r="R18" t="n">
-        <v>6780931</v>
+        <v>6780958</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2519,45 +2519,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129971589</v>
+        <v>129972802</v>
       </c>
       <c r="B19" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461736</v>
+        <v>461611</v>
       </c>
       <c r="R19" t="n">
-        <v>6780931</v>
+        <v>6780900</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2626,7 +2631,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129972800</v>
+        <v>129971589</v>
       </c>
       <c r="B20" t="n">
         <v>79180</v>
@@ -2661,10 +2666,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461611</v>
+        <v>461736</v>
       </c>
       <c r="R20" t="n">
-        <v>6780900</v>
+        <v>6780931</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2733,40 +2738,35 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129972802</v>
+        <v>129972800</v>
       </c>
       <c r="B21" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
@@ -3609,10 +3609,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129972793</v>
+        <v>129970675</v>
       </c>
       <c r="B29" t="n">
-        <v>57823</v>
+        <v>79799</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3620,39 +3620,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461611</v>
+        <v>461789</v>
       </c>
       <c r="R29" t="n">
-        <v>6780900</v>
+        <v>6780961</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3721,38 +3716,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129971587</v>
+        <v>129972793</v>
       </c>
       <c r="B30" t="n">
-        <v>8451</v>
+        <v>57823</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3761,10 +3756,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461736</v>
+        <v>461611</v>
       </c>
       <c r="R30" t="n">
-        <v>6780931</v>
+        <v>6780900</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3833,7 +3828,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129972990</v>
+        <v>129971587</v>
       </c>
       <c r="B31" t="n">
         <v>8451</v>
@@ -3873,10 +3868,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461615</v>
+        <v>461736</v>
       </c>
       <c r="R31" t="n">
-        <v>6780923</v>
+        <v>6780931</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3945,45 +3940,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129970675</v>
+        <v>129972990</v>
       </c>
       <c r="B32" t="n">
-        <v>79799</v>
+        <v>8451</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461789</v>
+        <v>461615</v>
       </c>
       <c r="R32" t="n">
-        <v>6780961</v>
+        <v>6780923</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4052,10 +4052,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129970738</v>
+        <v>129971825</v>
       </c>
       <c r="B33" t="n">
-        <v>79799</v>
+        <v>57823</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4063,34 +4063,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461799</v>
+        <v>461686</v>
       </c>
       <c r="R33" t="n">
-        <v>6780979</v>
+        <v>6780923</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4159,10 +4164,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129971825</v>
+        <v>129970738</v>
       </c>
       <c r="B34" t="n">
-        <v>57823</v>
+        <v>79799</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4170,39 +4175,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461686</v>
+        <v>461799</v>
       </c>
       <c r="R34" t="n">
-        <v>6780923</v>
+        <v>6780979</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4271,10 +4271,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129970828</v>
+        <v>129971832</v>
       </c>
       <c r="B35" t="n">
-        <v>78937</v>
+        <v>79180</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4282,21 +4282,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4306,10 +4306,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461800</v>
+        <v>461686</v>
       </c>
       <c r="R35" t="n">
-        <v>6781016</v>
+        <v>6780923</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4378,10 +4378,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129971832</v>
+        <v>129970828</v>
       </c>
       <c r="B36" t="n">
-        <v>79180</v>
+        <v>78937</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4389,21 +4389,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461686</v>
+        <v>461800</v>
       </c>
       <c r="R36" t="n">
-        <v>6780923</v>
+        <v>6781016</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4485,7 +4485,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129971804</v>
+        <v>129973978</v>
       </c>
       <c r="B37" t="n">
         <v>79180</v>
@@ -4520,10 +4520,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461709</v>
+        <v>461749</v>
       </c>
       <c r="R37" t="n">
-        <v>6780921</v>
+        <v>6780997</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4592,10 +4592,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129973978</v>
+        <v>129971739</v>
       </c>
       <c r="B38" t="n">
-        <v>79180</v>
+        <v>79770</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4603,21 +4603,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4627,10 +4627,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461749</v>
+        <v>461741</v>
       </c>
       <c r="R38" t="n">
-        <v>6780997</v>
+        <v>6780920</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4699,10 +4699,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129971259</v>
+        <v>129971804</v>
       </c>
       <c r="B39" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4710,39 +4710,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461751</v>
+        <v>461709</v>
       </c>
       <c r="R39" t="n">
-        <v>6780936</v>
+        <v>6780921</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4811,10 +4806,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129971739</v>
+        <v>129971259</v>
       </c>
       <c r="B40" t="n">
-        <v>79770</v>
+        <v>57823</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4822,34 +4817,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461741</v>
+        <v>461751</v>
       </c>
       <c r="R40" t="n">
-        <v>6780920</v>
+        <v>6780936</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -6032,10 +6032,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129973137</v>
+        <v>129972454</v>
       </c>
       <c r="B51" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6043,34 +6043,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461609</v>
+        <v>461687</v>
       </c>
       <c r="R51" t="n">
-        <v>6780949</v>
+        <v>6780875</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6117,7 +6122,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>3 bilder, rikligt i en radie av ca 50 meter</t>
+          <t>2 bilder</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6144,10 +6149,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129969692</v>
+        <v>129973137</v>
       </c>
       <c r="B52" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6155,39 +6160,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461799</v>
+        <v>461609</v>
       </c>
       <c r="R52" t="n">
-        <v>6780979</v>
+        <v>6780949</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>3 bilder, rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6261,10 +6261,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129972454</v>
+        <v>129969692</v>
       </c>
       <c r="B53" t="n">
-        <v>57826</v>
+        <v>57823</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6272,16 +6272,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6301,10 +6301,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>461687</v>
+        <v>461799</v>
       </c>
       <c r="R53" t="n">
-        <v>6780875</v>
+        <v>6780979</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>2 bilder</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6498,10 +6498,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130087273</v>
+        <v>130083775</v>
       </c>
       <c r="B55" t="n">
-        <v>78938</v>
+        <v>79180</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6509,21 +6509,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6533,10 +6533,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>462051</v>
+        <v>461717</v>
       </c>
       <c r="R55" t="n">
-        <v>6780727</v>
+        <v>6780842</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6605,32 +6605,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130083775</v>
+        <v>130087228</v>
       </c>
       <c r="B56" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6640,13 +6640,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461717</v>
+        <v>461948</v>
       </c>
       <c r="R56" t="n">
-        <v>6780842</v>
+        <v>6780740</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6712,7 +6712,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130087228</v>
+        <v>130087516</v>
       </c>
       <c r="B57" t="n">
         <v>8451</v>
@@ -6741,19 +6741,24 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461948</v>
+        <v>461956</v>
       </c>
       <c r="R57" t="n">
-        <v>6780740</v>
+        <v>6780787</v>
       </c>
       <c r="S57" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6819,50 +6824,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130087516</v>
+        <v>130087273</v>
       </c>
       <c r="B58" t="n">
-        <v>8451</v>
+        <v>78938</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461956</v>
+        <v>462051</v>
       </c>
       <c r="R58" t="n">
-        <v>6780787</v>
+        <v>6780727</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7577,7 +7577,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7798,10 +7798,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130087716</v>
+        <v>130087492</v>
       </c>
       <c r="B67" t="n">
-        <v>79799</v>
+        <v>79180</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7809,21 +7809,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7833,10 +7833,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>461894</v>
+        <v>461944</v>
       </c>
       <c r="R67" t="n">
-        <v>6780914</v>
+        <v>6780796</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7905,10 +7905,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130092026</v>
+        <v>130087119</v>
       </c>
       <c r="B68" t="n">
-        <v>78937</v>
+        <v>79180</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7916,40 +7916,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>461858</v>
+        <v>461918</v>
       </c>
       <c r="R68" t="n">
-        <v>6780846</v>
+        <v>6780787</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7976,37 +7973,51 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130087492</v>
+        <v>130087669</v>
       </c>
       <c r="B69" t="n">
         <v>79180</v>
@@ -8041,10 +8052,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>461944</v>
+        <v>461929</v>
       </c>
       <c r="R69" t="n">
-        <v>6780796</v>
+        <v>6780891</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8113,10 +8124,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130087119</v>
+        <v>130087716</v>
       </c>
       <c r="B70" t="n">
-        <v>79180</v>
+        <v>79799</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8124,21 +8135,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8148,13 +8159,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>461918</v>
+        <v>461894</v>
       </c>
       <c r="R70" t="n">
-        <v>6780787</v>
+        <v>6780914</v>
       </c>
       <c r="S70" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8194,11 +8205,6 @@
       <c r="AB70" t="inlineStr">
         <is>
           <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8225,10 +8231,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130087669</v>
+        <v>130092026</v>
       </c>
       <c r="B71" t="n">
-        <v>79180</v>
+        <v>78937</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8236,34 +8242,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>461929</v>
+        <v>461858</v>
       </c>
       <c r="R71" t="n">
-        <v>6780891</v>
+        <v>6780846</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8293,39 +8302,30 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -8999,45 +8999,50 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130087418</v>
+        <v>130086588</v>
       </c>
       <c r="B78" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>462039</v>
+        <v>461880</v>
       </c>
       <c r="R78" t="n">
-        <v>6780770</v>
+        <v>6780838</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9069,7 +9074,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9079,7 +9084,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9106,10 +9111,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130086966</v>
+        <v>130092215</v>
       </c>
       <c r="B79" t="n">
-        <v>57826</v>
+        <v>78938</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9117,42 +9122,40 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>461946</v>
+        <v>462002</v>
       </c>
       <c r="R79" t="n">
-        <v>6780867</v>
+        <v>6780772</v>
       </c>
       <c r="S79" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9179,32 +9182,18 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -9216,57 +9205,52 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Håkan Thenander, Peter Turander, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130086588</v>
+        <v>130087418</v>
       </c>
       <c r="B80" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>461880</v>
+        <v>462039</v>
       </c>
       <c r="R80" t="n">
-        <v>6780838</v>
+        <v>6780770</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9298,7 +9282,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9308,7 +9292,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9335,10 +9319,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130092215</v>
+        <v>130086966</v>
       </c>
       <c r="B81" t="n">
-        <v>78938</v>
+        <v>57826</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9346,40 +9330,42 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>462002</v>
+        <v>461946</v>
       </c>
       <c r="R81" t="n">
-        <v>6780772</v>
+        <v>6780867</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9406,18 +9392,32 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9429,61 +9429,52 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130091811</v>
+        <v>130086497</v>
       </c>
       <c r="B82" t="n">
-        <v>8451</v>
+        <v>90760</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>1962</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>461716</v>
+        <v>461865</v>
       </c>
       <c r="R82" t="n">
-        <v>6780852</v>
+        <v>6780909</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9513,40 +9504,54 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På en bränd tallåga</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130085215</v>
+        <v>130091631</v>
       </c>
       <c r="B83" t="n">
-        <v>79180</v>
+        <v>79212</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9554,34 +9559,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>461844</v>
+        <v>461750</v>
       </c>
       <c r="R83" t="n">
-        <v>6780835</v>
+        <v>6781031</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9611,46 +9619,37 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130087832</v>
+        <v>130085215</v>
       </c>
       <c r="B84" t="n">
         <v>79180</v>
@@ -9685,10 +9684,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>461873</v>
+        <v>461844</v>
       </c>
       <c r="R84" t="n">
-        <v>6780961</v>
+        <v>6780835</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9720,7 +9719,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9730,7 +9729,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9757,10 +9756,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130091631</v>
+        <v>130087832</v>
       </c>
       <c r="B85" t="n">
-        <v>79212</v>
+        <v>79180</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9768,37 +9767,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>461750</v>
+        <v>461873</v>
       </c>
       <c r="R85" t="n">
-        <v>6781031</v>
+        <v>6780961</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9828,75 +9824,93 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130086497</v>
+        <v>130091811</v>
       </c>
       <c r="B86" t="n">
-        <v>90760</v>
+        <v>8451</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1962</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>461865</v>
+        <v>461716</v>
       </c>
       <c r="R86" t="n">
-        <v>6780909</v>
+        <v>6780852</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9926,51 +9940,37 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>12:38</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>På en bränd tallåga</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130092059</v>
+        <v>130092368</v>
       </c>
       <c r="B87" t="n">
         <v>57823</v>
@@ -10013,10 +10013,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>461946</v>
+        <v>461867</v>
       </c>
       <c r="R87" t="n">
-        <v>6780839</v>
+        <v>6780956</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10063,19 +10063,19 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130092368</v>
+        <v>130092059</v>
       </c>
       <c r="B88" t="n">
         <v>57823</v>
@@ -10118,10 +10118,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>461867</v>
+        <v>461946</v>
       </c>
       <c r="R88" t="n">
-        <v>6780956</v>
+        <v>6780839</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10168,12 +10168,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -10292,50 +10292,48 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>130086721</v>
+        <v>130091794</v>
       </c>
       <c r="B90" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>461832</v>
+        <v>461710</v>
       </c>
       <c r="R90" t="n">
-        <v>6780916</v>
+        <v>6780886</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10365,87 +10363,67 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Äldre spår i torrtall</t>
-        </is>
-      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>130092063</v>
+        <v>130092053</v>
       </c>
       <c r="B91" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -10453,10 +10431,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>461946</v>
+        <v>461926</v>
       </c>
       <c r="R91" t="n">
-        <v>6780839</v>
+        <v>6780853</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10516,50 +10494,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>130087850</v>
+        <v>130083753</v>
       </c>
       <c r="B92" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>461873</v>
+        <v>461711</v>
       </c>
       <c r="R92" t="n">
-        <v>6780961</v>
+        <v>6780852</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10591,7 +10564,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10601,7 +10574,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10628,7 +10601,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>130091794</v>
+        <v>130087798</v>
       </c>
       <c r="B93" t="n">
         <v>79180</v>
@@ -10657,19 +10630,16 @@
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>461710</v>
+        <v>461864</v>
       </c>
       <c r="R93" t="n">
-        <v>6780886</v>
+        <v>6780951</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10699,40 +10669,49 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130092053</v>
+        <v>130085149</v>
       </c>
       <c r="B94" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10740,37 +10719,39 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>461926</v>
+        <v>461857</v>
       </c>
       <c r="R94" t="n">
-        <v>6780853</v>
+        <v>6780859</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10800,75 +10781,94 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Äldre spår i torrtall</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>130083753</v>
+        <v>130086721</v>
       </c>
       <c r="B95" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>461711</v>
+        <v>461832</v>
       </c>
       <c r="R95" t="n">
-        <v>6780852</v>
+        <v>6780916</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10900,7 +10900,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10910,7 +10910,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Äldre spår i torrtall</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10925,57 +10930,66 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>130087798</v>
+        <v>130092063</v>
       </c>
       <c r="B96" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>461864</v>
+        <v>461946</v>
       </c>
       <c r="R96" t="n">
-        <v>6780951</v>
+        <v>6780839</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11005,89 +11019,80 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>130085149</v>
+        <v>130087850</v>
       </c>
       <c r="B97" t="n">
-        <v>57823</v>
+        <v>8451</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>461857</v>
+        <v>461873</v>
       </c>
       <c r="R97" t="n">
-        <v>6780859</v>
+        <v>6780961</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11119,7 +11124,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11129,12 +11134,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Äldre spår i torrtall</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11149,49 +11149,55 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>130092019</v>
+        <v>130091828</v>
       </c>
       <c r="B98" t="n">
-        <v>78938</v>
+        <v>8451</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
@@ -11199,10 +11205,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>461858</v>
+        <v>461736</v>
       </c>
       <c r="R98" t="n">
-        <v>6780846</v>
+        <v>6780844</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11262,37 +11268,43 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>130091832</v>
+        <v>130091798</v>
       </c>
       <c r="B99" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
@@ -11300,10 +11312,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>461738</v>
+        <v>461713</v>
       </c>
       <c r="R99" t="n">
-        <v>6780825</v>
+        <v>6780880</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11363,10 +11375,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>130087184</v>
+        <v>130092019</v>
       </c>
       <c r="B100" t="n">
-        <v>79180</v>
+        <v>78938</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11374,37 +11386,40 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>461948</v>
+        <v>461858</v>
       </c>
       <c r="R100" t="n">
-        <v>6780740</v>
+        <v>6780846</v>
       </c>
       <c r="S100" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11431,54 +11446,40 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>130087915</v>
+        <v>130087184</v>
       </c>
       <c r="B101" t="n">
-        <v>79799</v>
+        <v>79180</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11486,21 +11487,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11510,13 +11511,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>461853</v>
+        <v>461948</v>
       </c>
       <c r="R101" t="n">
-        <v>6780990</v>
+        <v>6780740</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11556,6 +11557,11 @@
       <c r="AB101" t="inlineStr">
         <is>
           <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11582,10 +11588,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>130087727</v>
+        <v>130091832</v>
       </c>
       <c r="B102" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11593,39 +11599,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>461894</v>
+        <v>461738</v>
       </c>
       <c r="R102" t="n">
-        <v>6780914</v>
+        <v>6780825</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11655,93 +11659,75 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>130091828</v>
+        <v>130087915</v>
       </c>
       <c r="B103" t="n">
-        <v>8451</v>
+        <v>79799</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>461736</v>
+        <v>461853</v>
       </c>
       <c r="R103" t="n">
-        <v>6780844</v>
+        <v>6780990</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11771,84 +11757,89 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>130091798</v>
+        <v>130087727</v>
       </c>
       <c r="B104" t="n">
-        <v>8451</v>
+        <v>57823</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>461713</v>
+        <v>461894</v>
       </c>
       <c r="R104" t="n">
-        <v>6780880</v>
+        <v>6780914</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11878,37 +11869,46 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>130091785</v>
+        <v>130092042</v>
       </c>
       <c r="B105" t="n">
         <v>79180</v>
@@ -11946,10 +11946,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>461710</v>
+        <v>461850</v>
       </c>
       <c r="R105" t="n">
-        <v>6780938</v>
+        <v>6780907</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12009,7 +12009,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>130092042</v>
+        <v>130091785</v>
       </c>
       <c r="B106" t="n">
         <v>79180</v>
@@ -12047,10 +12047,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>461850</v>
+        <v>461710</v>
       </c>
       <c r="R106" t="n">
-        <v>6780907</v>
+        <v>6780938</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13194,45 +13194,48 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>130087759</v>
+        <v>130092122</v>
       </c>
       <c r="B117" t="n">
-        <v>79180</v>
+        <v>79204</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>461879</v>
+        <v>461986</v>
       </c>
       <c r="R117" t="n">
-        <v>6780924</v>
+        <v>6780804</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13262,46 +13265,37 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>130091843</v>
+        <v>130087759</v>
       </c>
       <c r="B118" t="n">
         <v>79180</v>
@@ -13330,19 +13324,16 @@
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>461720</v>
+        <v>461879</v>
       </c>
       <c r="R118" t="n">
-        <v>6780825</v>
+        <v>6780924</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13372,62 +13363,71 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>130092122</v>
+        <v>130091843</v>
       </c>
       <c r="B119" t="n">
-        <v>79204</v>
+        <v>79180</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13440,10 +13440,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>461986</v>
+        <v>461720</v>
       </c>
       <c r="R119" t="n">
-        <v>6780804</v>
+        <v>6780825</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13711,48 +13711,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>130091751</v>
+        <v>130087075</v>
       </c>
       <c r="B122" t="n">
-        <v>79212</v>
+        <v>8451</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>461737</v>
+        <v>461944</v>
       </c>
       <c r="R122" t="n">
-        <v>6781057</v>
+        <v>6780796</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13782,37 +13779,46 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>130091745</v>
+        <v>130091628</v>
       </c>
       <c r="B123" t="n">
         <v>79180</v>
@@ -13850,7 +13856,7 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>461749</v>
+        <v>461750</v>
       </c>
       <c r="R123" t="n">
         <v>6781031</v>
@@ -13913,7 +13919,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>130091628</v>
+        <v>130091745</v>
       </c>
       <c r="B124" t="n">
         <v>79180</v>
@@ -13951,7 +13957,7 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>461750</v>
+        <v>461749</v>
       </c>
       <c r="R124" t="n">
         <v>6781031</v>
@@ -14121,45 +14127,48 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>130087075</v>
+        <v>130091751</v>
       </c>
       <c r="B126" t="n">
-        <v>8451</v>
+        <v>79212</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>461944</v>
+        <v>461737</v>
       </c>
       <c r="R126" t="n">
-        <v>6780796</v>
+        <v>6781057</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14189,39 +14198,30 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD126" t="b">
         <v>0</v>
       </c>
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
@@ -15531,45 +15531,50 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>130087401</v>
+        <v>130087754</v>
       </c>
       <c r="B139" t="n">
-        <v>8451</v>
+        <v>57823</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>462039</v>
+        <v>461879</v>
       </c>
       <c r="R139" t="n">
-        <v>6780770</v>
+        <v>6780924</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15638,45 +15643,45 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>130086828</v>
+        <v>130087789</v>
       </c>
       <c r="B140" t="n">
-        <v>8451</v>
+        <v>79212</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>461887</v>
+        <v>461857</v>
       </c>
       <c r="R140" t="n">
-        <v>6780890</v>
+        <v>6780939</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15708,7 +15713,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15718,7 +15723,12 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Sparsamt på gran</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15733,57 +15743,57 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>130087789</v>
+        <v>130087401</v>
       </c>
       <c r="B141" t="n">
-        <v>79212</v>
+        <v>8451</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>461857</v>
+        <v>462039</v>
       </c>
       <c r="R141" t="n">
-        <v>6780939</v>
+        <v>6780770</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15815,7 +15825,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15825,12 +15835,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Sparsamt på gran</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15845,62 +15850,57 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>130087754</v>
+        <v>130086828</v>
       </c>
       <c r="B142" t="n">
-        <v>57823</v>
+        <v>8451</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>461879</v>
+        <v>461887</v>
       </c>
       <c r="R142" t="n">
-        <v>6780924</v>
+        <v>6780890</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15969,54 +15969,45 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>130091989</v>
+        <v>130085304</v>
       </c>
       <c r="B143" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>461800</v>
+        <v>461880</v>
       </c>
       <c r="R143" t="n">
-        <v>6780830</v>
+        <v>6780838</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16046,40 +16037,49 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AD143" t="b">
         <v>0</v>
       </c>
       <c r="AE143" t="b">
         <v>0</v>
       </c>
-      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>130086869</v>
+        <v>130087667</v>
       </c>
       <c r="B144" t="n">
-        <v>78938</v>
+        <v>79799</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16087,34 +16087,34 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>461922</v>
+        <v>461929</v>
       </c>
       <c r="R144" t="n">
-        <v>6780874</v>
+        <v>6780891</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16146,7 +16146,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16156,12 +16156,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16176,22 +16171,22 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>130085304</v>
+        <v>130085309</v>
       </c>
       <c r="B145" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16199,24 +16194,29 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
@@ -16295,10 +16295,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>130087667</v>
+        <v>130091819</v>
       </c>
       <c r="B146" t="n">
-        <v>79799</v>
+        <v>57823</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16306,34 +16306,42 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>461929</v>
+        <v>461716</v>
       </c>
       <c r="R146" t="n">
-        <v>6780891</v>
+        <v>6780856</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16363,19 +16371,9 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z146" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AB146" t="inlineStr">
-        <is>
-          <t>13:03</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16390,62 +16388,66 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>130085309</v>
+        <v>130091989</v>
       </c>
       <c r="B147" t="n">
-        <v>57823</v>
+        <v>8451</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>461880</v>
+        <v>461800</v>
       </c>
       <c r="R147" t="n">
-        <v>6780838</v>
+        <v>6780830</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16475,49 +16477,40 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z147" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB147" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AD147" t="b">
         <v>0</v>
       </c>
       <c r="AE147" t="b">
         <v>0</v>
       </c>
+      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
       </c>
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>130091819</v>
+        <v>130086869</v>
       </c>
       <c r="B148" t="n">
-        <v>57823</v>
+        <v>78938</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16525,42 +16518,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>461716</v>
+        <v>461922</v>
       </c>
       <c r="R148" t="n">
-        <v>6780856</v>
+        <v>6780874</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16590,9 +16575,24 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16607,12 +16607,12 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
@@ -17583,32 +17583,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>130091789</v>
+        <v>130091747</v>
       </c>
       <c r="B158" t="n">
-        <v>91110</v>
+        <v>79180</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>5685</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17621,10 +17621,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>461710</v>
+        <v>461737</v>
       </c>
       <c r="R158" t="n">
-        <v>6780886</v>
+        <v>6781057</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17684,10 +17684,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>130091747</v>
+        <v>130085067</v>
       </c>
       <c r="B159" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17695,37 +17695,39 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
-      <c r="N159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>461737</v>
+        <v>461857</v>
       </c>
       <c r="R159" t="n">
-        <v>6781057</v>
+        <v>6780842</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17755,80 +17757,87 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AD159" t="b">
         <v>0</v>
       </c>
       <c r="AE159" t="b">
         <v>0</v>
       </c>
-      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>130085067</v>
+        <v>130091789</v>
       </c>
       <c r="B160" t="n">
-        <v>57823</v>
+        <v>91110</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100049</v>
+        <v>5685</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>461857</v>
+        <v>461710</v>
       </c>
       <c r="R160" t="n">
-        <v>6780842</v>
+        <v>6780886</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17858,39 +17867,30 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AD160" t="b">
         <v>0</v>
       </c>
       <c r="AE160" t="b">
         <v>0</v>
       </c>
+      <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="b">
         <v>0</v>
       </c>
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
@@ -19436,39 +19436,37 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>130157422</v>
+        <v>130157644</v>
       </c>
       <c r="B175" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr"/>
-      <c r="M175" t="inlineStr"/>
       <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
@@ -19476,10 +19474,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>462148</v>
+        <v>461439</v>
       </c>
       <c r="R175" t="n">
-        <v>6780659</v>
+        <v>6780942</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19520,6 +19518,7 @@
       <c r="AE175" t="b">
         <v>0</v>
       </c>
+      <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="b">
         <v>0</v>
       </c>
@@ -19531,44 +19530,46 @@
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>130157644</v>
+        <v>130157422</v>
       </c>
       <c r="B176" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr"/>
       <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
@@ -19576,10 +19577,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>461439</v>
+        <v>462148</v>
       </c>
       <c r="R176" t="n">
-        <v>6780942</v>
+        <v>6780659</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19620,7 +19621,6 @@
       <c r="AE176" t="b">
         <v>0</v>
       </c>
-      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
@@ -19632,48 +19632,47 @@
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>130157683</v>
+        <v>130157723</v>
       </c>
       <c r="B177" t="n">
-        <v>8451</v>
+        <v>57826</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
-      <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr"/>
       <c r="M177" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N177" t="inlineStr"/>
@@ -19683,10 +19682,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>461363</v>
+        <v>461526</v>
       </c>
       <c r="R177" t="n">
-        <v>6780957</v>
+        <v>6780870</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19721,13 +19720,17 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>Ringhack i en av de äldre tallarna (en av 5-6 äldre tallar som ej bandats av)</t>
+        </is>
+      </c>
       <c r="AD177" t="b">
         <v>0</v>
       </c>
       <c r="AE177" t="b">
         <v>0</v>
       </c>
-      <c r="AF177" t="inlineStr"/>
       <c r="AG177" t="b">
         <v>0</v>
       </c>
@@ -19746,40 +19749,41 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>130157723</v>
+        <v>130157683</v>
       </c>
       <c r="B178" t="n">
-        <v>57826</v>
+        <v>8451</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr"/>
       <c r="M178" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N178" t="inlineStr"/>
@@ -19789,10 +19793,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>461526</v>
+        <v>461363</v>
       </c>
       <c r="R178" t="n">
-        <v>6780870</v>
+        <v>6780957</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19827,17 +19831,13 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="AC178" t="inlineStr">
-        <is>
-          <t>Ringhack i en av de äldre tallarna (en av 5-6 äldre tallar som ej bandats av)</t>
-        </is>
-      </c>
       <c r="AD178" t="b">
         <v>0</v>
       </c>
       <c r="AE178" t="b">
         <v>0</v>
       </c>
+      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58003-2025 artfynd.xlsx
+++ b/artfynd/A 58003-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129973732</v>
+        <v>129969590</v>
       </c>
       <c r="B2" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461665</v>
+        <v>461816</v>
       </c>
       <c r="R2" t="n">
-        <v>6780925</v>
+        <v>6780978</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129969590</v>
+        <v>129973732</v>
       </c>
       <c r="B3" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,39 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461816</v>
+        <v>461665</v>
       </c>
       <c r="R3" t="n">
-        <v>6780978</v>
+        <v>6780925</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1108,45 +1108,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129971802</v>
+        <v>129969658</v>
       </c>
       <c r="B6" t="n">
-        <v>79799</v>
+        <v>8451</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461709</v>
+        <v>461799</v>
       </c>
       <c r="R6" t="n">
-        <v>6780921</v>
+        <v>6780979</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,50 +1220,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129969658</v>
+        <v>129971802</v>
       </c>
       <c r="B7" t="n">
-        <v>8451</v>
+        <v>79799</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461799</v>
+        <v>461709</v>
       </c>
       <c r="R7" t="n">
-        <v>6780979</v>
+        <v>6780921</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,42 +1327,47 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129972961</v>
+        <v>129971831</v>
       </c>
       <c r="B8" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461615</v>
+        <v>461686</v>
       </c>
       <c r="R8" t="n">
         <v>6780923</v>
@@ -1546,47 +1551,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129971831</v>
+        <v>129972961</v>
       </c>
       <c r="B10" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461686</v>
+        <v>461615</v>
       </c>
       <c r="R10" t="n">
         <v>6780923</v>
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129971115</v>
+        <v>129971787</v>
       </c>
       <c r="B13" t="n">
-        <v>79770</v>
+        <v>79799</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,21 +1883,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461762</v>
+        <v>461741</v>
       </c>
       <c r="R13" t="n">
-        <v>6780940</v>
+        <v>6780920</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1979,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129971787</v>
+        <v>129971115</v>
       </c>
       <c r="B14" t="n">
-        <v>79799</v>
+        <v>79770</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1990,21 +1990,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461741</v>
+        <v>461762</v>
       </c>
       <c r="R14" t="n">
-        <v>6780920</v>
+        <v>6780940</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2086,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129971127</v>
+        <v>129971585</v>
       </c>
       <c r="B15" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,34 +2097,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461762</v>
+        <v>461736</v>
       </c>
       <c r="R15" t="n">
-        <v>6780940</v>
+        <v>6780931</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2193,10 +2198,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129973851</v>
+        <v>129971608</v>
       </c>
       <c r="B16" t="n">
-        <v>79180</v>
+        <v>79799</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2204,21 +2209,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2228,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461730</v>
+        <v>461733</v>
       </c>
       <c r="R16" t="n">
-        <v>6780969</v>
+        <v>6780958</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2300,10 +2305,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129971585</v>
+        <v>129971127</v>
       </c>
       <c r="B17" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2311,39 +2316,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461736</v>
+        <v>461762</v>
       </c>
       <c r="R17" t="n">
-        <v>6780931</v>
+        <v>6780940</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129971608</v>
+        <v>129973851</v>
       </c>
       <c r="B18" t="n">
-        <v>79799</v>
+        <v>79180</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2423,21 +2423,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2447,10 +2447,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461733</v>
+        <v>461730</v>
       </c>
       <c r="R18" t="n">
-        <v>6780958</v>
+        <v>6780969</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2519,50 +2519,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129972802</v>
+        <v>129971589</v>
       </c>
       <c r="B19" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461611</v>
+        <v>461736</v>
       </c>
       <c r="R19" t="n">
-        <v>6780900</v>
+        <v>6780931</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2631,7 +2626,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129971589</v>
+        <v>129972800</v>
       </c>
       <c r="B20" t="n">
         <v>79180</v>
@@ -2666,10 +2661,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461736</v>
+        <v>461611</v>
       </c>
       <c r="R20" t="n">
-        <v>6780931</v>
+        <v>6780900</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2738,35 +2733,40 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129972800</v>
+        <v>129972802</v>
       </c>
       <c r="B21" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
@@ -2952,45 +2952,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129970829</v>
+        <v>129972234</v>
       </c>
       <c r="B23" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461800</v>
+        <v>461679</v>
       </c>
       <c r="R23" t="n">
-        <v>6781016</v>
+        <v>6780885</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3059,7 +3064,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129972234</v>
+        <v>129973842</v>
       </c>
       <c r="B24" t="n">
         <v>8451</v>
@@ -3099,10 +3104,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461679</v>
+        <v>461730</v>
       </c>
       <c r="R24" t="n">
-        <v>6780885</v>
+        <v>6780969</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3171,50 +3176,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129973842</v>
+        <v>129970829</v>
       </c>
       <c r="B25" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461730</v>
+        <v>461800</v>
       </c>
       <c r="R25" t="n">
-        <v>6780969</v>
+        <v>6781016</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3609,45 +3609,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129970675</v>
+        <v>129971587</v>
       </c>
       <c r="B29" t="n">
-        <v>79799</v>
+        <v>8451</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461789</v>
+        <v>461736</v>
       </c>
       <c r="R29" t="n">
-        <v>6780961</v>
+        <v>6780931</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3716,38 +3721,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129972793</v>
+        <v>129972990</v>
       </c>
       <c r="B30" t="n">
-        <v>57823</v>
+        <v>8451</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3756,10 +3761,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461611</v>
+        <v>461615</v>
       </c>
       <c r="R30" t="n">
-        <v>6780900</v>
+        <v>6780923</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3828,50 +3833,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129971587</v>
+        <v>129970675</v>
       </c>
       <c r="B31" t="n">
-        <v>8451</v>
+        <v>79799</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461736</v>
+        <v>461789</v>
       </c>
       <c r="R31" t="n">
-        <v>6780931</v>
+        <v>6780961</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3940,38 +3940,38 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129972990</v>
+        <v>129972793</v>
       </c>
       <c r="B32" t="n">
-        <v>8451</v>
+        <v>57823</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3980,10 +3980,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461615</v>
+        <v>461611</v>
       </c>
       <c r="R32" t="n">
-        <v>6780923</v>
+        <v>6780900</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4052,10 +4052,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129971825</v>
+        <v>129970738</v>
       </c>
       <c r="B33" t="n">
-        <v>57823</v>
+        <v>79799</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4063,39 +4063,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461686</v>
+        <v>461799</v>
       </c>
       <c r="R33" t="n">
-        <v>6780923</v>
+        <v>6780979</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4164,10 +4159,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129970738</v>
+        <v>129971825</v>
       </c>
       <c r="B34" t="n">
-        <v>79799</v>
+        <v>57823</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4175,34 +4170,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461799</v>
+        <v>461686</v>
       </c>
       <c r="R34" t="n">
-        <v>6780979</v>
+        <v>6780923</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4271,10 +4271,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129971832</v>
+        <v>129970828</v>
       </c>
       <c r="B35" t="n">
-        <v>79180</v>
+        <v>78937</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4282,21 +4282,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4306,10 +4306,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461686</v>
+        <v>461800</v>
       </c>
       <c r="R35" t="n">
-        <v>6780923</v>
+        <v>6781016</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4378,10 +4378,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129970828</v>
+        <v>129971832</v>
       </c>
       <c r="B36" t="n">
-        <v>78937</v>
+        <v>79180</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4389,21 +4389,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461800</v>
+        <v>461686</v>
       </c>
       <c r="R36" t="n">
-        <v>6781016</v>
+        <v>6780923</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4592,10 +4592,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129971739</v>
+        <v>129971804</v>
       </c>
       <c r="B38" t="n">
-        <v>79770</v>
+        <v>79180</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4603,21 +4603,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4627,10 +4627,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461741</v>
+        <v>461709</v>
       </c>
       <c r="R38" t="n">
-        <v>6780920</v>
+        <v>6780921</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4699,10 +4699,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129971804</v>
+        <v>129971739</v>
       </c>
       <c r="B39" t="n">
-        <v>79180</v>
+        <v>79770</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4710,21 +4710,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4734,10 +4734,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461709</v>
+        <v>461741</v>
       </c>
       <c r="R39" t="n">
-        <v>6780921</v>
+        <v>6780920</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4918,10 +4918,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129970961</v>
+        <v>129972983</v>
       </c>
       <c r="B41" t="n">
-        <v>79770</v>
+        <v>57823</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4929,34 +4929,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461789</v>
+        <v>461615</v>
       </c>
       <c r="R41" t="n">
-        <v>6780961</v>
+        <v>6780923</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5025,10 +5030,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129970813</v>
+        <v>129971290</v>
       </c>
       <c r="B42" t="n">
-        <v>79799</v>
+        <v>79180</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5036,21 +5041,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5060,10 +5065,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461800</v>
+        <v>461751</v>
       </c>
       <c r="R42" t="n">
-        <v>6781016</v>
+        <v>6780936</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5132,10 +5137,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129971290</v>
+        <v>129970961</v>
       </c>
       <c r="B43" t="n">
-        <v>79180</v>
+        <v>79770</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5143,21 +5148,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5167,10 +5172,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461751</v>
+        <v>461789</v>
       </c>
       <c r="R43" t="n">
-        <v>6780936</v>
+        <v>6780961</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5239,10 +5244,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129972983</v>
+        <v>129970813</v>
       </c>
       <c r="B44" t="n">
-        <v>57823</v>
+        <v>79799</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5250,39 +5255,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461615</v>
+        <v>461800</v>
       </c>
       <c r="R44" t="n">
-        <v>6780923</v>
+        <v>6781016</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6032,10 +6032,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129972454</v>
+        <v>129973137</v>
       </c>
       <c r="B51" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6043,39 +6043,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461687</v>
+        <v>461609</v>
       </c>
       <c r="R51" t="n">
-        <v>6780875</v>
+        <v>6780949</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6122,7 +6117,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>2 bilder</t>
+          <t>3 bilder, rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6149,10 +6144,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129973137</v>
+        <v>129969692</v>
       </c>
       <c r="B52" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6160,34 +6155,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461609</v>
+        <v>461799</v>
       </c>
       <c r="R52" t="n">
-        <v>6780949</v>
+        <v>6780979</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>3 bilder, rikligt i en radie av ca 50 meter</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6261,7 +6261,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129969692</v>
+        <v>129972233</v>
       </c>
       <c r="B53" t="n">
         <v>57823</v>
@@ -6290,21 +6290,24 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>461799</v>
+        <v>461679</v>
       </c>
       <c r="R53" t="n">
-        <v>6780979</v>
+        <v>6780885</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6378,10 +6381,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129972233</v>
+        <v>129972454</v>
       </c>
       <c r="B54" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6389,16 +6392,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6407,24 +6410,21 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>461679</v>
+        <v>461687</v>
       </c>
       <c r="R54" t="n">
-        <v>6780885</v>
+        <v>6780875</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6471,7 +6471,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>2 bilder</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6605,32 +6605,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130087228</v>
+        <v>130087273</v>
       </c>
       <c r="B56" t="n">
-        <v>8451</v>
+        <v>78938</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6640,13 +6640,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461948</v>
+        <v>462051</v>
       </c>
       <c r="R56" t="n">
-        <v>6780740</v>
+        <v>6780727</v>
       </c>
       <c r="S56" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6712,7 +6712,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130087516</v>
+        <v>130087228</v>
       </c>
       <c r="B57" t="n">
         <v>8451</v>
@@ -6741,24 +6741,19 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461956</v>
+        <v>461948</v>
       </c>
       <c r="R57" t="n">
-        <v>6780787</v>
+        <v>6780740</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6824,45 +6819,50 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130087273</v>
+        <v>130087516</v>
       </c>
       <c r="B58" t="n">
-        <v>78938</v>
+        <v>8451</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>462051</v>
+        <v>461956</v>
       </c>
       <c r="R58" t="n">
-        <v>6780727</v>
+        <v>6780787</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6931,10 +6931,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130084991</v>
+        <v>130092086</v>
       </c>
       <c r="B59" t="n">
-        <v>79212</v>
+        <v>57826</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6942,34 +6942,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>461840</v>
+        <v>461986</v>
       </c>
       <c r="R59" t="n">
-        <v>6780854</v>
+        <v>6780804</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6999,24 +7007,14 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>11:27</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>11:27</t>
-        </is>
-      </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Sparsamt på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7031,22 +7029,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130087559</v>
+        <v>130084991</v>
       </c>
       <c r="B60" t="n">
-        <v>57823</v>
+        <v>79212</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7054,39 +7052,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461970</v>
+        <v>461840</v>
       </c>
       <c r="R60" t="n">
-        <v>6780823</v>
+        <v>6780854</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7118,7 +7111,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7128,7 +7121,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Sparsamt på gran</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7143,22 +7141,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130092086</v>
+        <v>130087559</v>
       </c>
       <c r="B61" t="n">
-        <v>57826</v>
+        <v>57823</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7166,16 +7164,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7184,24 +7182,21 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>461986</v>
+        <v>461970</v>
       </c>
       <c r="R61" t="n">
-        <v>6780804</v>
+        <v>6780823</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7231,14 +7226,19 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7253,12 +7253,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander, Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7684,17 +7684,17 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander, Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130085288</v>
+        <v>130087716</v>
       </c>
       <c r="B66" t="n">
-        <v>92211</v>
+        <v>79799</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7702,37 +7702,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5467</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>461858</v>
+        <v>461894</v>
       </c>
       <c r="R66" t="n">
-        <v>6780876</v>
+        <v>6780914</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7786,22 +7786,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130087492</v>
+        <v>130092026</v>
       </c>
       <c r="B67" t="n">
-        <v>79180</v>
+        <v>78937</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7809,34 +7809,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>461944</v>
+        <v>461858</v>
       </c>
       <c r="R67" t="n">
-        <v>6780796</v>
+        <v>6780846</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7866,46 +7869,37 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130087119</v>
+        <v>130087669</v>
       </c>
       <c r="B68" t="n">
         <v>79180</v>
@@ -7940,13 +7934,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>461918</v>
+        <v>461929</v>
       </c>
       <c r="R68" t="n">
-        <v>6780787</v>
+        <v>6780891</v>
       </c>
       <c r="S68" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7986,11 +7980,6 @@
       <c r="AB68" t="inlineStr">
         <is>
           <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8017,10 +8006,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130087669</v>
+        <v>130085288</v>
       </c>
       <c r="B69" t="n">
-        <v>79180</v>
+        <v>92211</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8028,37 +8017,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>5467</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>461929</v>
+        <v>461858</v>
       </c>
       <c r="R69" t="n">
-        <v>6780891</v>
+        <v>6780876</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8087,7 +8076,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8097,7 +8086,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8112,22 +8101,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130087716</v>
+        <v>130087492</v>
       </c>
       <c r="B70" t="n">
-        <v>79799</v>
+        <v>79180</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8135,21 +8124,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8159,10 +8148,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>461894</v>
+        <v>461944</v>
       </c>
       <c r="R70" t="n">
-        <v>6780914</v>
+        <v>6780796</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8231,10 +8220,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130092026</v>
+        <v>130087119</v>
       </c>
       <c r="B71" t="n">
-        <v>78937</v>
+        <v>79180</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8242,40 +8231,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>461858</v>
+        <v>461918</v>
       </c>
       <c r="R71" t="n">
-        <v>6780846</v>
+        <v>6780787</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8302,30 +8288,44 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -8999,50 +8999,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130086588</v>
+        <v>130087418</v>
       </c>
       <c r="B78" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>461880</v>
+        <v>462039</v>
       </c>
       <c r="R78" t="n">
-        <v>6780838</v>
+        <v>6780770</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9074,7 +9069,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9084,7 +9079,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9111,10 +9106,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130092215</v>
+        <v>130086966</v>
       </c>
       <c r="B79" t="n">
-        <v>78938</v>
+        <v>57826</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9122,40 +9117,42 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>462002</v>
+        <v>461946</v>
       </c>
       <c r="R79" t="n">
-        <v>6780772</v>
+        <v>6780867</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9182,18 +9179,32 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -9205,52 +9216,57 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130087418</v>
+        <v>130086588</v>
       </c>
       <c r="B80" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>462039</v>
+        <v>461880</v>
       </c>
       <c r="R80" t="n">
-        <v>6780770</v>
+        <v>6780838</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9282,7 +9298,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9292,7 +9308,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9319,10 +9335,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130086966</v>
+        <v>130092215</v>
       </c>
       <c r="B81" t="n">
-        <v>57826</v>
+        <v>78938</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9330,42 +9346,40 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>461946</v>
+        <v>462002</v>
       </c>
       <c r="R81" t="n">
-        <v>6780867</v>
+        <v>6780772</v>
       </c>
       <c r="S81" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9392,32 +9406,18 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9429,17 +9429,17 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
+          <t>Håkan Thenander, Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130086497</v>
+        <v>130087832</v>
       </c>
       <c r="B82" t="n">
-        <v>90760</v>
+        <v>79180</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9447,34 +9447,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>461865</v>
+        <v>461873</v>
       </c>
       <c r="R82" t="n">
-        <v>6780909</v>
+        <v>6780961</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9506,7 +9506,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9516,12 +9516,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>På en bränd tallåga</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9536,12 +9531,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -9649,10 +9644,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130085215</v>
+        <v>130086497</v>
       </c>
       <c r="B84" t="n">
-        <v>79180</v>
+        <v>90760</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9660,34 +9655,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>461844</v>
+        <v>461865</v>
       </c>
       <c r="R84" t="n">
-        <v>6780835</v>
+        <v>6780909</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9719,7 +9714,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9729,7 +9724,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>På en bränd tallåga</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9744,19 +9744,19 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130087832</v>
+        <v>130085215</v>
       </c>
       <c r="B85" t="n">
         <v>79180</v>
@@ -9791,10 +9791,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>461873</v>
+        <v>461844</v>
       </c>
       <c r="R85" t="n">
-        <v>6780961</v>
+        <v>6780835</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9826,7 +9826,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9836,7 +9836,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11161,54 +11161,50 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>130091828</v>
+        <v>130087727</v>
       </c>
       <c r="B98" t="n">
-        <v>8451</v>
+        <v>57823</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>461736</v>
+        <v>461894</v>
       </c>
       <c r="R98" t="n">
-        <v>6780844</v>
+        <v>6780914</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11238,73 +11234,76 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>130091798</v>
+        <v>130092019</v>
       </c>
       <c r="B99" t="n">
-        <v>8451</v>
+        <v>78938</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
@@ -11312,10 +11311,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>461713</v>
+        <v>461858</v>
       </c>
       <c r="R99" t="n">
-        <v>6780880</v>
+        <v>6780846</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11375,37 +11374,43 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>130092019</v>
+        <v>130091828</v>
       </c>
       <c r="B100" t="n">
-        <v>78938</v>
+        <v>8451</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -11413,10 +11418,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>461858</v>
+        <v>461736</v>
       </c>
       <c r="R100" t="n">
-        <v>6780846</v>
+        <v>6780844</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11476,48 +11481,57 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>130087184</v>
+        <v>130091798</v>
       </c>
       <c r="B101" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>461948</v>
+        <v>461713</v>
       </c>
       <c r="R101" t="n">
-        <v>6780740</v>
+        <v>6780880</v>
       </c>
       <c r="S101" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11544,51 +11558,37 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
-        </is>
-      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>130091832</v>
+        <v>130087184</v>
       </c>
       <c r="B102" t="n">
         <v>79180</v>
@@ -11617,22 +11617,19 @@
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>461738</v>
+        <v>461948</v>
       </c>
       <c r="R102" t="n">
-        <v>6780825</v>
+        <v>6780740</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11659,30 +11656,44 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+        </is>
+      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
@@ -11796,10 +11807,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>130087727</v>
+        <v>130091832</v>
       </c>
       <c r="B104" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11807,39 +11818,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>461894</v>
+        <v>461738</v>
       </c>
       <c r="R104" t="n">
-        <v>6780914</v>
+        <v>6780825</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11869,39 +11878,30 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
@@ -12110,45 +12110,54 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>130082810</v>
+        <v>130092018</v>
       </c>
       <c r="B107" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>461757</v>
+        <v>461858</v>
       </c>
       <c r="R107" t="n">
-        <v>6781096</v>
+        <v>6780846</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12178,84 +12187,84 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>130087616</v>
+        <v>130091806</v>
       </c>
       <c r="B108" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>461970</v>
+        <v>461715</v>
       </c>
       <c r="R108" t="n">
-        <v>6780823</v>
+        <v>6780868</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12285,51 +12294,37 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter</t>
-        </is>
-      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>130092018</v>
+        <v>130092199</v>
       </c>
       <c r="B109" t="n">
         <v>8451</v>
@@ -12373,10 +12368,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>461858</v>
+        <v>461976</v>
       </c>
       <c r="R109" t="n">
-        <v>6780846</v>
+        <v>6780775</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12429,61 +12424,52 @@
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander, Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>130091806</v>
+        <v>130082810</v>
       </c>
       <c r="B110" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>461715</v>
+        <v>461757</v>
       </c>
       <c r="R110" t="n">
-        <v>6780868</v>
+        <v>6781096</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12513,84 +12499,84 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>130092199</v>
+        <v>130087616</v>
       </c>
       <c r="B111" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>461976</v>
+        <v>461970</v>
       </c>
       <c r="R111" t="n">
-        <v>6780775</v>
+        <v>6780823</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12620,40 +12606,54 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter</t>
+        </is>
+      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>130087227</v>
+        <v>130087271</v>
       </c>
       <c r="B112" t="n">
-        <v>57823</v>
+        <v>79799</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12661,42 +12661,37 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>461948</v>
+        <v>462051</v>
       </c>
       <c r="R112" t="n">
-        <v>6780740</v>
+        <v>6780727</v>
       </c>
       <c r="S112" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12762,50 +12757,50 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>130087844</v>
+        <v>130085157</v>
       </c>
       <c r="B113" t="n">
-        <v>57823</v>
+        <v>8451</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>461873</v>
+        <v>461859</v>
       </c>
       <c r="R113" t="n">
-        <v>6780961</v>
+        <v>6780861</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12837,7 +12832,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12847,7 +12842,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12862,22 +12857,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>130087271</v>
+        <v>130087227</v>
       </c>
       <c r="B114" t="n">
-        <v>79799</v>
+        <v>57823</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12885,37 +12880,42 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>462051</v>
+        <v>461948</v>
       </c>
       <c r="R114" t="n">
-        <v>6780727</v>
+        <v>6780740</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12981,50 +12981,50 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>130085157</v>
+        <v>130087844</v>
       </c>
       <c r="B115" t="n">
-        <v>8451</v>
+        <v>57823</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>461859</v>
+        <v>461873</v>
       </c>
       <c r="R115" t="n">
-        <v>6780861</v>
+        <v>6780961</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13056,7 +13056,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13081,12 +13081,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
@@ -13194,48 +13194,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>130092122</v>
+        <v>130087759</v>
       </c>
       <c r="B117" t="n">
-        <v>79204</v>
+        <v>79180</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>461986</v>
+        <v>461879</v>
       </c>
       <c r="R117" t="n">
-        <v>6780804</v>
+        <v>6780924</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13265,37 +13262,46 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>130087759</v>
+        <v>130091843</v>
       </c>
       <c r="B118" t="n">
         <v>79180</v>
@@ -13324,16 +13330,19 @@
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>461879</v>
+        <v>461720</v>
       </c>
       <c r="R118" t="n">
-        <v>6780924</v>
+        <v>6780825</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13363,71 +13372,62 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>130091843</v>
+        <v>130092122</v>
       </c>
       <c r="B119" t="n">
-        <v>79180</v>
+        <v>79204</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13440,10 +13440,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>461720</v>
+        <v>461986</v>
       </c>
       <c r="R119" t="n">
-        <v>6780825</v>
+        <v>6780804</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13603,7 +13603,7 @@
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander, Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
@@ -13711,45 +13711,48 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>130087075</v>
+        <v>130091628</v>
       </c>
       <c r="B122" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>461944</v>
+        <v>461750</v>
       </c>
       <c r="R122" t="n">
-        <v>6780796</v>
+        <v>6781031</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13779,46 +13782,37 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>130091628</v>
+        <v>130091745</v>
       </c>
       <c r="B123" t="n">
         <v>79180</v>
@@ -13856,7 +13850,7 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>461750</v>
+        <v>461749</v>
       </c>
       <c r="R123" t="n">
         <v>6781031</v>
@@ -13919,48 +13913,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>130091745</v>
+        <v>130087075</v>
       </c>
       <c r="B124" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>461749</v>
+        <v>461944</v>
       </c>
       <c r="R124" t="n">
-        <v>6781031</v>
+        <v>6780796</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13990,40 +13981,49 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>130086831</v>
+        <v>130083776</v>
       </c>
       <c r="B125" t="n">
-        <v>79180</v>
+        <v>78938</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14031,34 +14031,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>461887</v>
+        <v>461738</v>
       </c>
       <c r="R125" t="n">
-        <v>6780890</v>
+        <v>6780866</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14090,7 +14090,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14100,7 +14100,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14115,12 +14115,12 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
@@ -14228,10 +14228,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>130083776</v>
+        <v>130086831</v>
       </c>
       <c r="B127" t="n">
-        <v>78938</v>
+        <v>79180</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14239,34 +14239,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>461738</v>
+        <v>461887</v>
       </c>
       <c r="R127" t="n">
-        <v>6780866</v>
+        <v>6780890</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14298,7 +14298,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14323,22 +14323,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>130091780</v>
+        <v>130085207</v>
       </c>
       <c r="B128" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14346,37 +14346,39 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>461742</v>
+        <v>461844</v>
       </c>
       <c r="R128" t="n">
-        <v>6781010</v>
+        <v>6780835</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14406,40 +14408,49 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AD128" t="b">
         <v>0</v>
       </c>
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>130087722</v>
+        <v>130087794</v>
       </c>
       <c r="B129" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14447,34 +14458,39 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>461894</v>
+        <v>461864</v>
       </c>
       <c r="R129" t="n">
-        <v>6780914</v>
+        <v>6780951</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14543,10 +14559,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>130087061</v>
+        <v>130083972</v>
       </c>
       <c r="B130" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14554,34 +14570,39 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>461952</v>
+        <v>461717</v>
       </c>
       <c r="R130" t="n">
-        <v>6780820</v>
+        <v>6780842</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14613,7 +14634,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14623,7 +14644,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14650,48 +14671,53 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>130087445</v>
+        <v>130085214</v>
       </c>
       <c r="B131" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>462022</v>
+        <v>461844</v>
       </c>
       <c r="R131" t="n">
-        <v>6780775</v>
+        <v>6780835</v>
       </c>
       <c r="S131" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14720,7 +14746,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14730,12 +14756,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14762,10 +14783,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>130085207</v>
+        <v>130085089</v>
       </c>
       <c r="B132" t="n">
-        <v>57823</v>
+        <v>78938</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14773,39 +14794,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>461844</v>
+        <v>461857</v>
       </c>
       <c r="R132" t="n">
-        <v>6780835</v>
+        <v>6780866</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14837,7 +14853,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14847,7 +14863,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14862,22 +14878,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>130087794</v>
+        <v>130091780</v>
       </c>
       <c r="B133" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14885,39 +14901,37 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>461864</v>
+        <v>461742</v>
       </c>
       <c r="R133" t="n">
-        <v>6780951</v>
+        <v>6781010</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14947,49 +14961,40 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z133" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB133" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>130083972</v>
+        <v>130087722</v>
       </c>
       <c r="B134" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14997,39 +15002,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>461717</v>
+        <v>461894</v>
       </c>
       <c r="R134" t="n">
-        <v>6780842</v>
+        <v>6780914</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15061,7 +15061,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15071,7 +15071,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15098,50 +15098,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>130085214</v>
+        <v>130087061</v>
       </c>
       <c r="B135" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>461844</v>
+        <v>461952</v>
       </c>
       <c r="R135" t="n">
-        <v>6780835</v>
+        <v>6780820</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15173,7 +15168,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15183,7 +15178,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15210,10 +15205,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>130085089</v>
+        <v>130087445</v>
       </c>
       <c r="B136" t="n">
-        <v>78938</v>
+        <v>79180</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15221,37 +15216,37 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>461857</v>
+        <v>462022</v>
       </c>
       <c r="R136" t="n">
-        <v>6780866</v>
+        <v>6780775</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15280,7 +15275,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15290,7 +15285,12 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15305,12 +15305,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
@@ -15424,10 +15424,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>130087057</v>
+        <v>130087754</v>
       </c>
       <c r="B138" t="n">
-        <v>79799</v>
+        <v>57823</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15435,34 +15435,39 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>461952</v>
+        <v>461879</v>
       </c>
       <c r="R138" t="n">
-        <v>6780820</v>
+        <v>6780924</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15531,50 +15536,45 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>130087754</v>
+        <v>130087401</v>
       </c>
       <c r="B139" t="n">
-        <v>57823</v>
+        <v>8451</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>461879</v>
+        <v>462039</v>
       </c>
       <c r="R139" t="n">
-        <v>6780924</v>
+        <v>6780770</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15643,45 +15643,45 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>130087789</v>
+        <v>130086828</v>
       </c>
       <c r="B140" t="n">
-        <v>79212</v>
+        <v>8451</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>185</v>
+        <v>106545</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>461857</v>
+        <v>461887</v>
       </c>
       <c r="R140" t="n">
-        <v>6780939</v>
+        <v>6780890</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15713,7 +15713,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15723,12 +15723,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Sparsamt på gran</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15743,57 +15738,57 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>130087401</v>
+        <v>130087789</v>
       </c>
       <c r="B141" t="n">
-        <v>8451</v>
+        <v>79212</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>462039</v>
+        <v>461857</v>
       </c>
       <c r="R141" t="n">
-        <v>6780770</v>
+        <v>6780939</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15825,7 +15820,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15835,7 +15830,12 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Sparsamt på gran</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15850,44 +15850,44 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>130086828</v>
+        <v>130087057</v>
       </c>
       <c r="B142" t="n">
-        <v>8451</v>
+        <v>79799</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15897,10 +15897,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>461887</v>
+        <v>461952</v>
       </c>
       <c r="R142" t="n">
-        <v>6780890</v>
+        <v>6780820</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15969,10 +15969,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>130085304</v>
+        <v>130087667</v>
       </c>
       <c r="B143" t="n">
-        <v>79180</v>
+        <v>79799</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15980,21 +15980,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -16004,10 +16004,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>461880</v>
+        <v>461929</v>
       </c>
       <c r="R143" t="n">
-        <v>6780838</v>
+        <v>6780891</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16039,7 +16039,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -16049,7 +16049,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16076,10 +16076,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>130087667</v>
+        <v>130085304</v>
       </c>
       <c r="B144" t="n">
-        <v>79799</v>
+        <v>79180</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16087,21 +16087,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16111,10 +16111,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>461929</v>
+        <v>461880</v>
       </c>
       <c r="R144" t="n">
-        <v>6780891</v>
+        <v>6780838</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16146,7 +16146,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16156,7 +16156,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16400,54 +16400,45 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>130091989</v>
+        <v>130086869</v>
       </c>
       <c r="B147" t="n">
-        <v>8451</v>
+        <v>78938</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>461800</v>
+        <v>461922</v>
       </c>
       <c r="R147" t="n">
-        <v>6780830</v>
+        <v>6780874</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16477,75 +16468,98 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
+        </is>
+      </c>
       <c r="AD147" t="b">
         <v>0</v>
       </c>
       <c r="AE147" t="b">
         <v>0</v>
       </c>
-      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
       </c>
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>130086869</v>
+        <v>130091989</v>
       </c>
       <c r="B148" t="n">
-        <v>78938</v>
+        <v>8451</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>461922</v>
+        <v>461800</v>
       </c>
       <c r="R148" t="n">
-        <v>6780874</v>
+        <v>6780830</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16575,54 +16589,40 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>13:11</t>
-        </is>
-      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
-        </is>
-      </c>
       <c r="AD148" t="b">
         <v>0</v>
       </c>
       <c r="AE148" t="b">
         <v>0</v>
       </c>
+      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>130084608</v>
+        <v>130087527</v>
       </c>
       <c r="B149" t="n">
-        <v>78938</v>
+        <v>79180</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16630,34 +16630,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>461805</v>
+        <v>461956</v>
       </c>
       <c r="R149" t="n">
-        <v>6780835</v>
+        <v>6780787</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16689,7 +16689,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16699,12 +16699,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>11:27</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16719,22 +16714,22 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>130087527</v>
+        <v>130086826</v>
       </c>
       <c r="B150" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16742,34 +16737,39 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>461956</v>
+        <v>461887</v>
       </c>
       <c r="R150" t="n">
-        <v>6780787</v>
+        <v>6780890</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17050,10 +17050,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>130086826</v>
+        <v>130084608</v>
       </c>
       <c r="B153" t="n">
-        <v>57823</v>
+        <v>78938</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17061,39 +17061,34 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>461887</v>
+        <v>461805</v>
       </c>
       <c r="R153" t="n">
-        <v>6780890</v>
+        <v>6780835</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17125,7 +17120,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17135,7 +17130,12 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17150,12 +17150,12 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
@@ -17363,17 +17363,17 @@
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander, Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>130092430</v>
+        <v>130091747</v>
       </c>
       <c r="B156" t="n">
-        <v>78938</v>
+        <v>79180</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17381,21 +17381,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17408,10 +17408,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>461933</v>
+        <v>461737</v>
       </c>
       <c r="R156" t="n">
-        <v>6780838</v>
+        <v>6781057</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17446,11 +17446,6 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
-        </is>
-      </c>
       <c r="AD156" t="b">
         <v>0</v>
       </c>
@@ -17464,22 +17459,22 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>130092010</v>
+        <v>130091789</v>
       </c>
       <c r="B157" t="n">
-        <v>8451</v>
+        <v>91110</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17487,32 +17482,26 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>106545</v>
+        <v>5685</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
@@ -17520,10 +17509,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>461808</v>
+        <v>461710</v>
       </c>
       <c r="R157" t="n">
-        <v>6780861</v>
+        <v>6780886</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17583,10 +17572,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>130091747</v>
+        <v>130091841</v>
       </c>
       <c r="B158" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17594,26 +17583,35 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
@@ -17621,10 +17619,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>461737</v>
+        <v>461720</v>
       </c>
       <c r="R158" t="n">
-        <v>6781057</v>
+        <v>6780825</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17659,13 +17657,17 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>hack födosök i gran och ringhackad gran intill</t>
+        </is>
+      </c>
       <c r="AD158" t="b">
         <v>0</v>
       </c>
       <c r="AE158" t="b">
         <v>0</v>
       </c>
-      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
@@ -17796,32 +17798,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>130091789</v>
+        <v>130092430</v>
       </c>
       <c r="B160" t="n">
-        <v>91110</v>
+        <v>78938</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>5685</v>
+        <v>228912</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17834,10 +17836,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>461710</v>
+        <v>461933</v>
       </c>
       <c r="R160" t="n">
-        <v>6780886</v>
+        <v>6780838</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17872,6 +17874,11 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
+        </is>
+      </c>
       <c r="AD160" t="b">
         <v>0</v>
       </c>
@@ -17885,56 +17892,53 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>130091841</v>
+        <v>130092010</v>
       </c>
       <c r="B161" t="n">
-        <v>57826</v>
+        <v>8451</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr"/>
       <c r="M161" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N161" t="inlineStr"/>
@@ -17944,10 +17948,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>461720</v>
+        <v>461808</v>
       </c>
       <c r="R161" t="n">
-        <v>6780825</v>
+        <v>6780861</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17982,17 +17986,13 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>hack födosök i gran och ringhackad gran intill</t>
-        </is>
-      </c>
       <c r="AD161" t="b">
         <v>0</v>
       </c>
       <c r="AE161" t="b">
         <v>0</v>
       </c>
+      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
@@ -18241,10 +18241,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>130083774</v>
+        <v>130086991</v>
       </c>
       <c r="B164" t="n">
-        <v>90760</v>
+        <v>79180</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18252,40 +18252,37 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>461717</v>
+        <v>461939</v>
       </c>
       <c r="R164" t="n">
-        <v>6780842</v>
+        <v>6780857</v>
       </c>
       <c r="S164" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -18314,7 +18311,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -18324,12 +18321,12 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>2 bilder</t>
+          <t>2 bild. Rikligt till måttligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18338,7 +18335,6 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
-      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
@@ -18357,10 +18353,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>130086991</v>
+        <v>130083774</v>
       </c>
       <c r="B165" t="n">
-        <v>79180</v>
+        <v>90760</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18368,37 +18364,40 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>461939</v>
+        <v>461717</v>
       </c>
       <c r="R165" t="n">
-        <v>6780857</v>
+        <v>6780842</v>
       </c>
       <c r="S165" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -18427,7 +18426,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -18437,20 +18436,21 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>2 bild. Rikligt till måttligt i en radie av ca 50 meter</t>
+          <t>2 bilder</t>
         </is>
       </c>
       <c r="AD165" t="b">
         <v>0</v>
       </c>
       <c r="AE165" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
@@ -19109,7 +19109,7 @@
         <v>0</v>
       </c>
       <c r="AE171" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
@@ -19436,37 +19436,39 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>130157644</v>
+        <v>130157422</v>
       </c>
       <c r="B175" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr"/>
       <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
@@ -19474,10 +19476,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>461439</v>
+        <v>462148</v>
       </c>
       <c r="R175" t="n">
-        <v>6780942</v>
+        <v>6780659</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19518,7 +19520,6 @@
       <c r="AE175" t="b">
         <v>0</v>
       </c>
-      <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="b">
         <v>0</v>
       </c>
@@ -19530,46 +19531,44 @@
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>130157422</v>
+        <v>130157644</v>
       </c>
       <c r="B176" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr"/>
-      <c r="L176" t="inlineStr"/>
-      <c r="M176" t="inlineStr"/>
       <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
@@ -19577,10 +19576,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>462148</v>
+        <v>461439</v>
       </c>
       <c r="R176" t="n">
-        <v>6780659</v>
+        <v>6780942</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19621,6 +19620,7 @@
       <c r="AE176" t="b">
         <v>0</v>
       </c>
+      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
@@ -19632,47 +19632,48 @@
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>130157723</v>
+        <v>130157683</v>
       </c>
       <c r="B177" t="n">
-        <v>57826</v>
+        <v>8451</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr"/>
       <c r="M177" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N177" t="inlineStr"/>
@@ -19682,10 +19683,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>461526</v>
+        <v>461363</v>
       </c>
       <c r="R177" t="n">
-        <v>6780870</v>
+        <v>6780957</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19720,17 +19721,13 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>Ringhack i en av de äldre tallarna (en av 5-6 äldre tallar som ej bandats av)</t>
-        </is>
-      </c>
       <c r="AD177" t="b">
         <v>0</v>
       </c>
       <c r="AE177" t="b">
         <v>0</v>
       </c>
+      <c r="AF177" t="inlineStr"/>
       <c r="AG177" t="b">
         <v>0</v>
       </c>
@@ -19749,41 +19746,40 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>130157683</v>
+        <v>130157723</v>
       </c>
       <c r="B178" t="n">
-        <v>8451</v>
+        <v>57826</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr"/>
       <c r="M178" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N178" t="inlineStr"/>
@@ -19793,10 +19789,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>461363</v>
+        <v>461526</v>
       </c>
       <c r="R178" t="n">
-        <v>6780957</v>
+        <v>6780870</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19831,13 +19827,17 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>Ringhack i en av de äldre tallarna (en av 5-6 äldre tallar som ej bandats av)</t>
+        </is>
+      </c>
       <c r="AD178" t="b">
         <v>0</v>
       </c>
       <c r="AE178" t="b">
         <v>0</v>
       </c>
-      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>
@@ -20374,37 +20374,43 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>130157446</v>
+        <v>130157677</v>
       </c>
       <c r="B184" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
@@ -20412,10 +20418,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>462162</v>
+        <v>461370</v>
       </c>
       <c r="R184" t="n">
-        <v>6780616</v>
+        <v>6780963</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20456,6 +20462,7 @@
       <c r="AE184" t="b">
         <v>0</v>
       </c>
+      <c r="AF184" t="inlineStr"/>
       <c r="AG184" t="b">
         <v>0</v>
       </c>
@@ -20467,50 +20474,44 @@
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>130157677</v>
+        <v>130157446</v>
       </c>
       <c r="B185" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr"/>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
@@ -20518,10 +20519,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>461370</v>
+        <v>462162</v>
       </c>
       <c r="R185" t="n">
-        <v>6780963</v>
+        <v>6780616</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20562,7 +20563,6 @@
       <c r="AE185" t="b">
         <v>0</v>
       </c>
-      <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="b">
         <v>0</v>
       </c>
@@ -20574,7 +20574,7 @@
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>

--- a/artfynd/A 58003-2025 artfynd.xlsx
+++ b/artfynd/A 58003-2025 artfynd.xlsx
@@ -6931,10 +6931,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130092086</v>
+        <v>130084991</v>
       </c>
       <c r="B59" t="n">
-        <v>57826</v>
+        <v>79212</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6942,42 +6942,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>461986</v>
+        <v>461840</v>
       </c>
       <c r="R59" t="n">
-        <v>6780804</v>
+        <v>6780854</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7007,14 +6999,24 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Sparsamt på gran</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7029,22 +7031,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130084991</v>
+        <v>130087559</v>
       </c>
       <c r="B60" t="n">
-        <v>79212</v>
+        <v>57823</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7052,34 +7054,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461840</v>
+        <v>461970</v>
       </c>
       <c r="R60" t="n">
-        <v>6780854</v>
+        <v>6780823</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7111,7 +7118,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7121,12 +7128,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:27</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Sparsamt på gran</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7141,22 +7143,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130087559</v>
+        <v>130092086</v>
       </c>
       <c r="B61" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7164,16 +7166,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7182,21 +7184,24 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>461970</v>
+        <v>461986</v>
       </c>
       <c r="R61" t="n">
-        <v>6780823</v>
+        <v>6780804</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7226,19 +7231,14 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>13:03</t>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7253,12 +7253,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -11161,57 +11161,48 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>130091828</v>
+        <v>130087184</v>
       </c>
       <c r="B98" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>461736</v>
+        <v>461948</v>
       </c>
       <c r="R98" t="n">
-        <v>6780844</v>
+        <v>6780740</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11238,73 +11229,81 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>130091798</v>
+        <v>130091832</v>
       </c>
       <c r="B99" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
@@ -11312,10 +11311,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>461713</v>
+        <v>461738</v>
       </c>
       <c r="R99" t="n">
-        <v>6780880</v>
+        <v>6780825</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11375,10 +11374,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>130091832</v>
+        <v>130087915</v>
       </c>
       <c r="B100" t="n">
-        <v>79180</v>
+        <v>79799</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11386,37 +11385,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>461738</v>
+        <v>461853</v>
       </c>
       <c r="R100" t="n">
-        <v>6780825</v>
+        <v>6780990</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11446,40 +11442,49 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>130087184</v>
+        <v>130092019</v>
       </c>
       <c r="B101" t="n">
-        <v>79180</v>
+        <v>78938</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11487,37 +11492,40 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>461948</v>
+        <v>461858</v>
       </c>
       <c r="R101" t="n">
-        <v>6780740</v>
+        <v>6780846</v>
       </c>
       <c r="S101" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11544,54 +11552,40 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
-        </is>
-      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>130092019</v>
+        <v>130087727</v>
       </c>
       <c r="B102" t="n">
-        <v>78938</v>
+        <v>57823</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11599,37 +11593,39 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>461858</v>
+        <v>461894</v>
       </c>
       <c r="R102" t="n">
-        <v>6780846</v>
+        <v>6780914</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11659,75 +11655,93 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>130087915</v>
+        <v>130091828</v>
       </c>
       <c r="B103" t="n">
-        <v>79799</v>
+        <v>8451</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>461853</v>
+        <v>461736</v>
       </c>
       <c r="R103" t="n">
-        <v>6780990</v>
+        <v>6780844</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11757,89 +11771,84 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>130087727</v>
+        <v>130091798</v>
       </c>
       <c r="B104" t="n">
-        <v>57823</v>
+        <v>8451</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>461894</v>
+        <v>461713</v>
       </c>
       <c r="R104" t="n">
-        <v>6780914</v>
+        <v>6780880</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11869,39 +11878,30 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
@@ -12650,10 +12650,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>130087271</v>
+        <v>130087844</v>
       </c>
       <c r="B112" t="n">
-        <v>79799</v>
+        <v>57823</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12661,34 +12661,39 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>462051</v>
+        <v>461873</v>
       </c>
       <c r="R112" t="n">
-        <v>6780727</v>
+        <v>6780961</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12757,10 +12762,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>130087227</v>
+        <v>130087271</v>
       </c>
       <c r="B113" t="n">
-        <v>57823</v>
+        <v>79799</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12768,42 +12773,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>461948</v>
+        <v>462051</v>
       </c>
       <c r="R113" t="n">
-        <v>6780740</v>
+        <v>6780727</v>
       </c>
       <c r="S113" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12869,7 +12869,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>130087844</v>
+        <v>130087227</v>
       </c>
       <c r="B114" t="n">
         <v>57823</v>
@@ -12909,13 +12909,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>461873</v>
+        <v>461948</v>
       </c>
       <c r="R114" t="n">
-        <v>6780961</v>
+        <v>6780740</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -14650,10 +14650,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>130083972</v>
+        <v>130087445</v>
       </c>
       <c r="B131" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14661,42 +14661,37 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>461717</v>
+        <v>462022</v>
       </c>
       <c r="R131" t="n">
-        <v>6780842</v>
+        <v>6780775</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14725,7 +14720,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14735,7 +14730,12 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14762,38 +14762,38 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>130085214</v>
+        <v>130085207</v>
       </c>
       <c r="B132" t="n">
-        <v>8451</v>
+        <v>57823</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="M132" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -14874,10 +14874,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>130085089</v>
+        <v>130087794</v>
       </c>
       <c r="B133" t="n">
-        <v>78938</v>
+        <v>57823</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14885,34 +14885,39 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>461857</v>
+        <v>461864</v>
       </c>
       <c r="R133" t="n">
-        <v>6780866</v>
+        <v>6780951</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14944,7 +14949,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14954,7 +14959,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14969,22 +14974,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>130087445</v>
+        <v>130083972</v>
       </c>
       <c r="B134" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14992,37 +14997,42 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>462022</v>
+        <v>461717</v>
       </c>
       <c r="R134" t="n">
-        <v>6780775</v>
+        <v>6780842</v>
       </c>
       <c r="S134" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -15051,7 +15061,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15061,12 +15071,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15093,10 +15098,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>130085207</v>
+        <v>130085089</v>
       </c>
       <c r="B135" t="n">
-        <v>57823</v>
+        <v>78938</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15104,39 +15109,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>461844</v>
+        <v>461857</v>
       </c>
       <c r="R135" t="n">
-        <v>6780835</v>
+        <v>6780866</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15168,7 +15168,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15178,7 +15178,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15193,50 +15193,50 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>130087794</v>
+        <v>130085214</v>
       </c>
       <c r="B136" t="n">
-        <v>57823</v>
+        <v>8451</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="M136" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -15245,10 +15245,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>461864</v>
+        <v>461844</v>
       </c>
       <c r="R136" t="n">
-        <v>6780951</v>
+        <v>6780835</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15280,7 +15280,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15290,7 +15290,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15317,10 +15317,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>130087057</v>
+        <v>130083742</v>
       </c>
       <c r="B137" t="n">
-        <v>79799</v>
+        <v>79180</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15328,21 +15328,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15352,10 +15352,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>461952</v>
+        <v>461699</v>
       </c>
       <c r="R137" t="n">
-        <v>6780820</v>
+        <v>6780870</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15387,7 +15387,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15424,10 +15424,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>130087789</v>
+        <v>130087754</v>
       </c>
       <c r="B138" t="n">
-        <v>79212</v>
+        <v>57823</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15435,34 +15435,39 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>461857</v>
+        <v>461879</v>
       </c>
       <c r="R138" t="n">
-        <v>6780939</v>
+        <v>6780924</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15494,7 +15499,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15504,12 +15509,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>Sparsamt på gran</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15524,22 +15524,22 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>130083742</v>
+        <v>130087789</v>
       </c>
       <c r="B139" t="n">
-        <v>79180</v>
+        <v>79212</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15547,34 +15547,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>461699</v>
+        <v>461857</v>
       </c>
       <c r="R139" t="n">
-        <v>6780870</v>
+        <v>6780939</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15606,7 +15606,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15616,7 +15616,12 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Sparsamt på gran</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15631,22 +15636,22 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>130087754</v>
+        <v>130087057</v>
       </c>
       <c r="B140" t="n">
-        <v>57823</v>
+        <v>79799</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15654,39 +15659,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>461879</v>
+        <v>461952</v>
       </c>
       <c r="R140" t="n">
-        <v>6780924</v>
+        <v>6780820</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15969,50 +15969,54 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>130085309</v>
+        <v>130091989</v>
       </c>
       <c r="B143" t="n">
-        <v>57823</v>
+        <v>8451</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>461880</v>
+        <v>461800</v>
       </c>
       <c r="R143" t="n">
-        <v>6780838</v>
+        <v>6780830</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16042,49 +16046,40 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AD143" t="b">
         <v>0</v>
       </c>
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>130091819</v>
+        <v>130085304</v>
       </c>
       <c r="B144" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16092,42 +16087,34 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>461716</v>
+        <v>461880</v>
       </c>
       <c r="R144" t="n">
-        <v>6780856</v>
+        <v>6780838</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16157,9 +16144,19 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16174,22 +16171,22 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>130085304</v>
+        <v>130085309</v>
       </c>
       <c r="B145" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16197,24 +16194,29 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
@@ -16293,10 +16295,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>130087667</v>
+        <v>130091819</v>
       </c>
       <c r="B146" t="n">
-        <v>79799</v>
+        <v>57823</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16304,34 +16306,42 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>461929</v>
+        <v>461716</v>
       </c>
       <c r="R146" t="n">
-        <v>6780891</v>
+        <v>6780856</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16361,19 +16371,9 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z146" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AB146" t="inlineStr">
-        <is>
-          <t>13:03</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16388,66 +16388,57 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>130091989</v>
+        <v>130086869</v>
       </c>
       <c r="B147" t="n">
-        <v>8451</v>
+        <v>78938</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>461800</v>
+        <v>461922</v>
       </c>
       <c r="R147" t="n">
-        <v>6780830</v>
+        <v>6780874</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16477,40 +16468,54 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
+        </is>
+      </c>
       <c r="AD147" t="b">
         <v>0</v>
       </c>
       <c r="AE147" t="b">
         <v>0</v>
       </c>
-      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
       </c>
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>130086869</v>
+        <v>130087667</v>
       </c>
       <c r="B148" t="n">
-        <v>78938</v>
+        <v>79799</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16518,34 +16523,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>461922</v>
+        <v>461929</v>
       </c>
       <c r="R148" t="n">
-        <v>6780874</v>
+        <v>6780891</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16577,7 +16582,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16587,12 +16592,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16607,12 +16607,12 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
@@ -19639,41 +19639,40 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>130157683</v>
+        <v>130157723</v>
       </c>
       <c r="B177" t="n">
-        <v>8451</v>
+        <v>57826</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
-      <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr"/>
       <c r="M177" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N177" t="inlineStr"/>
@@ -19683,10 +19682,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>461363</v>
+        <v>461526</v>
       </c>
       <c r="R177" t="n">
-        <v>6780957</v>
+        <v>6780870</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19721,13 +19720,17 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>Ringhack i en av de äldre tallarna (en av 5-6 äldre tallar som ej bandats av)</t>
+        </is>
+      </c>
       <c r="AD177" t="b">
         <v>0</v>
       </c>
       <c r="AE177" t="b">
         <v>0</v>
       </c>
-      <c r="AF177" t="inlineStr"/>
       <c r="AG177" t="b">
         <v>0</v>
       </c>
@@ -19746,40 +19749,41 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>130157723</v>
+        <v>130157683</v>
       </c>
       <c r="B178" t="n">
-        <v>57826</v>
+        <v>8451</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr"/>
       <c r="M178" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N178" t="inlineStr"/>
@@ -19789,10 +19793,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>461526</v>
+        <v>461363</v>
       </c>
       <c r="R178" t="n">
-        <v>6780870</v>
+        <v>6780957</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19827,17 +19831,13 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="AC178" t="inlineStr">
-        <is>
-          <t>Ringhack i en av de äldre tallarna (en av 5-6 äldre tallar som ej bandats av)</t>
-        </is>
-      </c>
       <c r="AD178" t="b">
         <v>0</v>
       </c>
       <c r="AE178" t="b">
         <v>0</v>
       </c>
+      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58003-2025 artfynd.xlsx
+++ b/artfynd/A 58003-2025 artfynd.xlsx
@@ -8225,50 +8225,50 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130087222</v>
+        <v>130087512</v>
       </c>
       <c r="B71" t="n">
-        <v>8451</v>
+        <v>57823</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>462001</v>
+        <v>461956</v>
       </c>
       <c r="R71" t="n">
-        <v>6780764</v>
+        <v>6780787</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8300,7 +8300,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8310,12 +8310,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:46</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Äldre spår I tallåga</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8330,19 +8325,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130092389</v>
+        <v>130087245</v>
       </c>
       <c r="B72" t="n">
         <v>8451</v>
@@ -8371,28 +8366,19 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>461870</v>
+        <v>461946</v>
       </c>
       <c r="R72" t="n">
-        <v>6780967</v>
+        <v>6780867</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8419,37 +8405,46 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Håkan Thenander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130087245</v>
+        <v>130087222</v>
       </c>
       <c r="B73" t="n">
         <v>8451</v>
@@ -8478,19 +8473,24 @@
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>461946</v>
+        <v>462001</v>
       </c>
       <c r="R73" t="n">
-        <v>6780867</v>
+        <v>6780764</v>
       </c>
       <c r="S73" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8519,7 +8519,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8529,7 +8529,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Äldre spår I tallåga</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8544,57 +8549,66 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130087716</v>
+        <v>130092389</v>
       </c>
       <c r="B74" t="n">
-        <v>79799</v>
+        <v>8451</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>461894</v>
+        <v>461870</v>
       </c>
       <c r="R74" t="n">
-        <v>6780914</v>
+        <v>6780967</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8624,49 +8638,40 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130087512</v>
+        <v>130087716</v>
       </c>
       <c r="B75" t="n">
-        <v>57823</v>
+        <v>79799</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8674,39 +8679,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>461956</v>
+        <v>461894</v>
       </c>
       <c r="R75" t="n">
-        <v>6780787</v>
+        <v>6780914</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9116,10 +9116,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130087418</v>
+        <v>130092215</v>
       </c>
       <c r="B79" t="n">
-        <v>79180</v>
+        <v>78938</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9127,34 +9127,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>462039</v>
+        <v>462002</v>
       </c>
       <c r="R79" t="n">
-        <v>6780770</v>
+        <v>6780772</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9184,39 +9187,30 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9335,10 +9329,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130092215</v>
+        <v>130087418</v>
       </c>
       <c r="B81" t="n">
-        <v>78938</v>
+        <v>79180</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9346,37 +9340,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>462002</v>
+        <v>462039</v>
       </c>
       <c r="R81" t="n">
-        <v>6780772</v>
+        <v>6780770</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9406,40 +9397,49 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130087832</v>
+        <v>130091631</v>
       </c>
       <c r="B82" t="n">
-        <v>79180</v>
+        <v>79212</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9447,34 +9447,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>461873</v>
+        <v>461750</v>
       </c>
       <c r="R82" t="n">
-        <v>6780961</v>
+        <v>6781031</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9504,49 +9507,40 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130085215</v>
+        <v>130086497</v>
       </c>
       <c r="B83" t="n">
-        <v>79180</v>
+        <v>90760</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9554,34 +9548,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>461844</v>
+        <v>461865</v>
       </c>
       <c r="R83" t="n">
-        <v>6780835</v>
+        <v>6780909</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9613,7 +9607,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9623,7 +9617,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>På en bränd tallåga</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9638,66 +9637,57 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130091811</v>
+        <v>130087832</v>
       </c>
       <c r="B84" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>461716</v>
+        <v>461873</v>
       </c>
       <c r="R84" t="n">
-        <v>6780852</v>
+        <v>6780961</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9727,40 +9717,49 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130091631</v>
+        <v>130085215</v>
       </c>
       <c r="B85" t="n">
-        <v>79212</v>
+        <v>79180</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9768,37 +9767,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>461750</v>
+        <v>461844</v>
       </c>
       <c r="R85" t="n">
-        <v>6781031</v>
+        <v>6780835</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9828,75 +9824,93 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130086497</v>
+        <v>130091811</v>
       </c>
       <c r="B86" t="n">
-        <v>90760</v>
+        <v>8451</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1962</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>461865</v>
+        <v>461716</v>
       </c>
       <c r="R86" t="n">
-        <v>6780909</v>
+        <v>6780852</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9926,44 +9940,30 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>12:38</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>På en bränd tallåga</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -10292,48 +10292,50 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>130091794</v>
+        <v>130086721</v>
       </c>
       <c r="B90" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>461710</v>
+        <v>461832</v>
       </c>
       <c r="R90" t="n">
-        <v>6780886</v>
+        <v>6780916</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10363,75 +10365,98 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Äldre spår i torrtall</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>130083753</v>
+        <v>130092063</v>
       </c>
       <c r="B91" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>461711</v>
+        <v>461946</v>
       </c>
       <c r="R91" t="n">
-        <v>6780852</v>
+        <v>6780839</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10461,87 +10486,80 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>130092053</v>
+        <v>130087850</v>
       </c>
       <c r="B92" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>461926</v>
+        <v>461873</v>
       </c>
       <c r="R92" t="n">
-        <v>6780853</v>
+        <v>6780961</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10571,40 +10589,49 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>130087798</v>
+        <v>130085149</v>
       </c>
       <c r="B93" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10612,34 +10639,39 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>461864</v>
+        <v>461857</v>
       </c>
       <c r="R93" t="n">
-        <v>6780951</v>
+        <v>6780859</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10671,7 +10703,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10681,7 +10713,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Äldre spår i torrtall</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10696,22 +10733,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130085149</v>
+        <v>130091794</v>
       </c>
       <c r="B94" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10719,39 +10756,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>461857</v>
+        <v>461710</v>
       </c>
       <c r="R94" t="n">
-        <v>6780859</v>
+        <v>6780886</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10781,94 +10816,75 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Äldre spår i torrtall</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>130086721</v>
+        <v>130083753</v>
       </c>
       <c r="B95" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>461832</v>
+        <v>461711</v>
       </c>
       <c r="R95" t="n">
-        <v>6780916</v>
+        <v>6780852</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10900,7 +10916,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10910,12 +10926,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Äldre spår i torrtall</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10930,55 +10941,49 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>130092063</v>
+        <v>130092053</v>
       </c>
       <c r="B96" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -10986,10 +10991,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>461946</v>
+        <v>461926</v>
       </c>
       <c r="R96" t="n">
-        <v>6780839</v>
+        <v>6780853</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11049,50 +11054,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>130087850</v>
+        <v>130087798</v>
       </c>
       <c r="B97" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>461873</v>
+        <v>461864</v>
       </c>
       <c r="R97" t="n">
-        <v>6780961</v>
+        <v>6780951</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -13301,10 +13301,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>130092071</v>
+        <v>130087759</v>
       </c>
       <c r="B118" t="n">
-        <v>92026</v>
+        <v>79180</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13312,37 +13312,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>461946</v>
+        <v>461879</v>
       </c>
       <c r="R118" t="n">
-        <v>6780863</v>
+        <v>6780924</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13372,37 +13369,46 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>130087759</v>
+        <v>130091843</v>
       </c>
       <c r="B119" t="n">
         <v>79180</v>
@@ -13431,16 +13437,19 @@
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>461879</v>
+        <v>461720</v>
       </c>
       <c r="R119" t="n">
-        <v>6780924</v>
+        <v>6780825</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13470,49 +13479,40 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
       <c r="AE119" t="b">
         <v>0</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>130091843</v>
+        <v>130092071</v>
       </c>
       <c r="B120" t="n">
-        <v>79180</v>
+        <v>92026</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13520,21 +13520,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13547,10 +13547,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>461720</v>
+        <v>461946</v>
       </c>
       <c r="R120" t="n">
-        <v>6780825</v>
+        <v>6780863</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13925,10 +13925,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>130091751</v>
+        <v>130091628</v>
       </c>
       <c r="B124" t="n">
-        <v>79212</v>
+        <v>79180</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13936,21 +13936,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13963,10 +13963,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>461737</v>
+        <v>461750</v>
       </c>
       <c r="R124" t="n">
-        <v>6781057</v>
+        <v>6781031</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14026,7 +14026,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>130091628</v>
+        <v>130086831</v>
       </c>
       <c r="B125" t="n">
         <v>79180</v>
@@ -14055,19 +14055,16 @@
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>461750</v>
+        <v>461887</v>
       </c>
       <c r="R125" t="n">
-        <v>6781031</v>
+        <v>6780890</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14097,37 +14094,46 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>130086831</v>
+        <v>130091745</v>
       </c>
       <c r="B126" t="n">
         <v>79180</v>
@@ -14156,16 +14162,19 @@
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>461887</v>
+        <v>461749</v>
       </c>
       <c r="R126" t="n">
-        <v>6780890</v>
+        <v>6781031</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14195,49 +14204,40 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD126" t="b">
         <v>0</v>
       </c>
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>130091745</v>
+        <v>130091751</v>
       </c>
       <c r="B127" t="n">
-        <v>79180</v>
+        <v>79212</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14245,21 +14245,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14272,10 +14272,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>461749</v>
+        <v>461737</v>
       </c>
       <c r="R127" t="n">
-        <v>6781031</v>
+        <v>6781057</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14650,10 +14650,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>130087445</v>
+        <v>130083972</v>
       </c>
       <c r="B131" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14661,37 +14661,42 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>462022</v>
+        <v>461717</v>
       </c>
       <c r="R131" t="n">
-        <v>6780775</v>
+        <v>6780842</v>
       </c>
       <c r="S131" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14720,7 +14725,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14730,12 +14735,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>13:03</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14762,38 +14762,38 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>130085207</v>
+        <v>130085214</v>
       </c>
       <c r="B132" t="n">
-        <v>57823</v>
+        <v>8451</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="M132" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -14874,10 +14874,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>130087794</v>
+        <v>130085089</v>
       </c>
       <c r="B133" t="n">
-        <v>57823</v>
+        <v>78938</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14885,39 +14885,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>461864</v>
+        <v>461857</v>
       </c>
       <c r="R133" t="n">
-        <v>6780951</v>
+        <v>6780866</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14949,7 +14944,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14959,7 +14954,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14974,22 +14969,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>130083972</v>
+        <v>130087445</v>
       </c>
       <c r="B134" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14997,42 +14992,37 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>461717</v>
+        <v>462022</v>
       </c>
       <c r="R134" t="n">
-        <v>6780842</v>
+        <v>6780775</v>
       </c>
       <c r="S134" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -15061,7 +15051,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15071,7 +15061,12 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15098,10 +15093,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>130085089</v>
+        <v>130085207</v>
       </c>
       <c r="B135" t="n">
-        <v>78938</v>
+        <v>57823</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15109,34 +15104,39 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>461857</v>
+        <v>461844</v>
       </c>
       <c r="R135" t="n">
-        <v>6780866</v>
+        <v>6780835</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15168,7 +15168,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15178,7 +15178,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15193,50 +15193,50 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>130085214</v>
+        <v>130087794</v>
       </c>
       <c r="B136" t="n">
-        <v>8451</v>
+        <v>57823</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="M136" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -15245,10 +15245,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>461844</v>
+        <v>461864</v>
       </c>
       <c r="R136" t="n">
-        <v>6780835</v>
+        <v>6780951</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15280,7 +15280,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15290,7 +15290,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15317,10 +15317,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>130083742</v>
+        <v>130087057</v>
       </c>
       <c r="B137" t="n">
-        <v>79180</v>
+        <v>79799</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15328,21 +15328,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15352,10 +15352,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>461699</v>
+        <v>461952</v>
       </c>
       <c r="R137" t="n">
-        <v>6780870</v>
+        <v>6780820</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15387,7 +15387,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15424,10 +15424,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>130087754</v>
+        <v>130087789</v>
       </c>
       <c r="B138" t="n">
-        <v>57823</v>
+        <v>79212</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15435,39 +15435,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>461879</v>
+        <v>461857</v>
       </c>
       <c r="R138" t="n">
-        <v>6780924</v>
+        <v>6780939</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15499,7 +15494,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15509,7 +15504,12 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>Sparsamt på gran</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15524,22 +15524,22 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>130087789</v>
+        <v>130083742</v>
       </c>
       <c r="B139" t="n">
-        <v>79212</v>
+        <v>79180</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15547,34 +15547,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>461857</v>
+        <v>461699</v>
       </c>
       <c r="R139" t="n">
-        <v>6780939</v>
+        <v>6780870</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15606,7 +15606,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15616,12 +15616,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Sparsamt på gran</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15636,22 +15631,22 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>130087057</v>
+        <v>130087754</v>
       </c>
       <c r="B140" t="n">
-        <v>79799</v>
+        <v>57823</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15659,34 +15654,39 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>461952</v>
+        <v>461879</v>
       </c>
       <c r="R140" t="n">
-        <v>6780820</v>
+        <v>6780924</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16619,10 +16619,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>130086826</v>
+        <v>130084608</v>
       </c>
       <c r="B149" t="n">
-        <v>57823</v>
+        <v>78938</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16630,39 +16630,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>461887</v>
+        <v>461805</v>
       </c>
       <c r="R149" t="n">
-        <v>6780890</v>
+        <v>6780835</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16694,7 +16689,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16704,7 +16699,12 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16719,22 +16719,22 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>130092006</v>
+        <v>130087527</v>
       </c>
       <c r="B150" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16742,42 +16742,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>461808</v>
+        <v>461956</v>
       </c>
       <c r="R150" t="n">
-        <v>6780861</v>
+        <v>6780787</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16807,9 +16799,19 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16824,19 +16826,19 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>130087153</v>
+        <v>130086826</v>
       </c>
       <c r="B151" t="n">
         <v>57823</v>
@@ -16867,19 +16869,19 @@
       <c r="I151" t="inlineStr"/>
       <c r="M151" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>461955</v>
+        <v>461887</v>
       </c>
       <c r="R151" t="n">
-        <v>6780741</v>
+        <v>6780890</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16909,14 +16911,19 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Äldre spår I högstubbe</t>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16931,22 +16938,22 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>130087527</v>
+        <v>130092006</v>
       </c>
       <c r="B152" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16954,34 +16961,42 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>461956</v>
+        <v>461808</v>
       </c>
       <c r="R152" t="n">
-        <v>6780787</v>
+        <v>6780861</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17011,19 +17026,9 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z152" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AB152" t="inlineStr">
-        <is>
-          <t>13:03</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17038,22 +17043,22 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>130084608</v>
+        <v>130087153</v>
       </c>
       <c r="B153" t="n">
-        <v>78938</v>
+        <v>57823</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17061,34 +17066,39 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>461805</v>
+        <v>461955</v>
       </c>
       <c r="R153" t="n">
-        <v>6780835</v>
+        <v>6780741</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17118,24 +17128,14 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z153" t="inlineStr">
-        <is>
-          <t>11:27</t>
-        </is>
-      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB153" t="inlineStr">
-        <is>
-          <t>11:27</t>
-        </is>
-      </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>På en brandstubbe</t>
+          <t>Äldre spår I högstubbe</t>
         </is>
       </c>
       <c r="AD153" t="b">

--- a/artfynd/A 58003-2025 artfynd.xlsx
+++ b/artfynd/A 58003-2025 artfynd.xlsx
@@ -6931,10 +6931,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130084991</v>
+        <v>130092086</v>
       </c>
       <c r="B59" t="n">
-        <v>79212</v>
+        <v>57826</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6942,34 +6942,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>461840</v>
+        <v>461986</v>
       </c>
       <c r="R59" t="n">
-        <v>6780854</v>
+        <v>6780804</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6999,24 +7007,14 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>11:27</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>11:27</t>
-        </is>
-      </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Sparsamt på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7031,22 +7029,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130087559</v>
+        <v>130084991</v>
       </c>
       <c r="B60" t="n">
-        <v>57823</v>
+        <v>79212</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7054,39 +7052,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461970</v>
+        <v>461840</v>
       </c>
       <c r="R60" t="n">
-        <v>6780823</v>
+        <v>6780854</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7118,7 +7111,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7128,7 +7121,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Sparsamt på gran</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7143,22 +7141,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130092086</v>
+        <v>130087559</v>
       </c>
       <c r="B61" t="n">
-        <v>57826</v>
+        <v>57823</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7166,16 +7164,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7184,24 +7182,21 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>461986</v>
+        <v>461970</v>
       </c>
       <c r="R61" t="n">
-        <v>6780804</v>
+        <v>6780823</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7231,14 +7226,19 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7253,57 +7253,66 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130087919</v>
+        <v>130091775</v>
       </c>
       <c r="B62" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>461853</v>
+        <v>461753</v>
       </c>
       <c r="R62" t="n">
-        <v>6780990</v>
+        <v>6781025</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7333,79 +7342,71 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130092209</v>
+        <v>130092205</v>
       </c>
       <c r="B63" t="n">
-        <v>57823</v>
+        <v>8451</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -7459,6 +7460,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7477,54 +7479,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130091775</v>
+        <v>130087919</v>
       </c>
       <c r="B64" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>461753</v>
+        <v>461853</v>
       </c>
       <c r="R64" t="n">
-        <v>6781025</v>
+        <v>6780990</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7554,71 +7547,79 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130092205</v>
+        <v>130092209</v>
       </c>
       <c r="B65" t="n">
-        <v>8451</v>
+        <v>57823</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -7672,7 +7673,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -8225,50 +8225,50 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130087512</v>
+        <v>130087222</v>
       </c>
       <c r="B71" t="n">
-        <v>57823</v>
+        <v>8451</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>461956</v>
+        <v>462001</v>
       </c>
       <c r="R71" t="n">
-        <v>6780787</v>
+        <v>6780764</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8300,7 +8300,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8310,7 +8310,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Äldre spår I tallåga</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8325,19 +8330,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130087245</v>
+        <v>130092389</v>
       </c>
       <c r="B72" t="n">
         <v>8451</v>
@@ -8366,19 +8371,28 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>461946</v>
+        <v>461870</v>
       </c>
       <c r="R72" t="n">
-        <v>6780867</v>
+        <v>6780967</v>
       </c>
       <c r="S72" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8405,46 +8419,37 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130087222</v>
+        <v>130087245</v>
       </c>
       <c r="B73" t="n">
         <v>8451</v>
@@ -8473,24 +8478,19 @@
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>462001</v>
+        <v>461946</v>
       </c>
       <c r="R73" t="n">
-        <v>6780764</v>
+        <v>6780867</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8519,7 +8519,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8529,12 +8529,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:46</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Äldre spår I tallåga</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8549,66 +8544,57 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Peter Turander, Håkan Thenander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130092389</v>
+        <v>130087716</v>
       </c>
       <c r="B74" t="n">
-        <v>8451</v>
+        <v>79799</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>461870</v>
+        <v>461894</v>
       </c>
       <c r="R74" t="n">
-        <v>6780967</v>
+        <v>6780914</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8638,40 +8624,49 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130087716</v>
+        <v>130087512</v>
       </c>
       <c r="B75" t="n">
-        <v>79799</v>
+        <v>57823</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8679,34 +8674,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>461894</v>
+        <v>461956</v>
       </c>
       <c r="R75" t="n">
-        <v>6780914</v>
+        <v>6780787</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10292,50 +10292,48 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>130086721</v>
+        <v>130091794</v>
       </c>
       <c r="B90" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>461832</v>
+        <v>461710</v>
       </c>
       <c r="R90" t="n">
-        <v>6780916</v>
+        <v>6780886</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10365,98 +10363,75 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Äldre spår i torrtall</t>
-        </is>
-      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>130092063</v>
+        <v>130083753</v>
       </c>
       <c r="B91" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>461946</v>
+        <v>461711</v>
       </c>
       <c r="R91" t="n">
-        <v>6780839</v>
+        <v>6780852</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10486,80 +10461,87 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>130087850</v>
+        <v>130092053</v>
       </c>
       <c r="B92" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>461873</v>
+        <v>461926</v>
       </c>
       <c r="R92" t="n">
-        <v>6780961</v>
+        <v>6780853</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10589,49 +10571,40 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>130085149</v>
+        <v>130087798</v>
       </c>
       <c r="B93" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10639,39 +10612,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>461857</v>
+        <v>461864</v>
       </c>
       <c r="R93" t="n">
-        <v>6780859</v>
+        <v>6780951</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10703,7 +10671,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10713,12 +10681,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Äldre spår i torrtall</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10733,22 +10696,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130091794</v>
+        <v>130085149</v>
       </c>
       <c r="B94" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10756,37 +10719,39 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>461710</v>
+        <v>461857</v>
       </c>
       <c r="R94" t="n">
-        <v>6780886</v>
+        <v>6780859</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10816,75 +10781,94 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Äldre spår i torrtall</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>130083753</v>
+        <v>130086721</v>
       </c>
       <c r="B95" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>461711</v>
+        <v>461832</v>
       </c>
       <c r="R95" t="n">
-        <v>6780852</v>
+        <v>6780916</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10916,7 +10900,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10926,7 +10910,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Äldre spår i torrtall</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10941,49 +10930,55 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>130092053</v>
+        <v>130092063</v>
       </c>
       <c r="B96" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -10991,10 +10986,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>461926</v>
+        <v>461946</v>
       </c>
       <c r="R96" t="n">
-        <v>6780853</v>
+        <v>6780839</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11054,45 +11049,50 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>130087798</v>
+        <v>130087850</v>
       </c>
       <c r="B97" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>461864</v>
+        <v>461873</v>
       </c>
       <c r="R97" t="n">
-        <v>6780951</v>
+        <v>6780961</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -13301,10 +13301,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>130087759</v>
+        <v>130092071</v>
       </c>
       <c r="B118" t="n">
-        <v>79180</v>
+        <v>92026</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13312,34 +13312,37 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>461879</v>
+        <v>461946</v>
       </c>
       <c r="R118" t="n">
-        <v>6780924</v>
+        <v>6780863</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13369,46 +13372,37 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>130091843</v>
+        <v>130087759</v>
       </c>
       <c r="B119" t="n">
         <v>79180</v>
@@ -13437,19 +13431,16 @@
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>461720</v>
+        <v>461879</v>
       </c>
       <c r="R119" t="n">
-        <v>6780825</v>
+        <v>6780924</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13479,40 +13470,49 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
       <c r="AE119" t="b">
         <v>0</v>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>130092071</v>
+        <v>130091843</v>
       </c>
       <c r="B120" t="n">
-        <v>92026</v>
+        <v>79180</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13520,21 +13520,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13547,10 +13547,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>461946</v>
+        <v>461720</v>
       </c>
       <c r="R120" t="n">
-        <v>6780863</v>
+        <v>6780825</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15969,54 +15969,50 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>130091989</v>
+        <v>130085309</v>
       </c>
       <c r="B143" t="n">
-        <v>8451</v>
+        <v>57823</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N143" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>461800</v>
+        <v>461880</v>
       </c>
       <c r="R143" t="n">
-        <v>6780830</v>
+        <v>6780838</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16046,40 +16042,49 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AD143" t="b">
         <v>0</v>
       </c>
       <c r="AE143" t="b">
         <v>0</v>
       </c>
-      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>130085304</v>
+        <v>130091819</v>
       </c>
       <c r="B144" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16087,34 +16092,42 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>461880</v>
+        <v>461716</v>
       </c>
       <c r="R144" t="n">
-        <v>6780838</v>
+        <v>6780856</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16144,19 +16157,9 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z144" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>10:14</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16171,22 +16174,22 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>130085309</v>
+        <v>130085304</v>
       </c>
       <c r="B145" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16194,29 +16197,24 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
@@ -16295,10 +16293,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>130091819</v>
+        <v>130087667</v>
       </c>
       <c r="B146" t="n">
-        <v>57823</v>
+        <v>79799</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16306,42 +16304,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr"/>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>461716</v>
+        <v>461929</v>
       </c>
       <c r="R146" t="n">
-        <v>6780856</v>
+        <v>6780891</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16371,9 +16361,19 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16388,57 +16388,66 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>130086869</v>
+        <v>130091989</v>
       </c>
       <c r="B147" t="n">
-        <v>78938</v>
+        <v>8451</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>461922</v>
+        <v>461800</v>
       </c>
       <c r="R147" t="n">
-        <v>6780874</v>
+        <v>6780830</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16468,54 +16477,40 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z147" t="inlineStr">
-        <is>
-          <t>13:11</t>
-        </is>
-      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB147" t="inlineStr">
-        <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>På en brandstubbe</t>
-        </is>
-      </c>
       <c r="AD147" t="b">
         <v>0</v>
       </c>
       <c r="AE147" t="b">
         <v>0</v>
       </c>
+      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
       </c>
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>130087667</v>
+        <v>130086869</v>
       </c>
       <c r="B148" t="n">
-        <v>79799</v>
+        <v>78938</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16523,34 +16518,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Rävhällsdammen, Dlr</t>
+          <t>Rävhällsdammen, Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>461929</v>
+        <v>461922</v>
       </c>
       <c r="R148" t="n">
-        <v>6780891</v>
+        <v>6780874</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16582,7 +16577,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16592,7 +16587,12 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>På en brandstubbe</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16607,12 +16607,12 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
@@ -17370,46 +17370,37 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>130091841</v>
+        <v>130091789</v>
       </c>
       <c r="B156" t="n">
-        <v>57826</v>
+        <v>91110</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100109</v>
+        <v>5685</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
@@ -17417,10 +17408,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>461720</v>
+        <v>461710</v>
       </c>
       <c r="R156" t="n">
-        <v>6780825</v>
+        <v>6780886</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17455,17 +17446,13 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>hack födosök i gran och ringhackad gran intill</t>
-        </is>
-      </c>
       <c r="AD156" t="b">
         <v>0</v>
       </c>
       <c r="AE156" t="b">
         <v>0</v>
       </c>
+      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
@@ -17484,32 +17471,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>130091789</v>
+        <v>130091747</v>
       </c>
       <c r="B157" t="n">
-        <v>91110</v>
+        <v>79180</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>5685</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17522,10 +17509,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>461710</v>
+        <v>461737</v>
       </c>
       <c r="R157" t="n">
-        <v>6780886</v>
+        <v>6781057</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17585,10 +17572,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>130091747</v>
+        <v>130085067</v>
       </c>
       <c r="B158" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17596,37 +17583,39 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
-      <c r="N158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>461737</v>
+        <v>461857</v>
       </c>
       <c r="R158" t="n">
-        <v>6781057</v>
+        <v>6780842</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17656,40 +17645,49 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AD158" t="b">
         <v>0</v>
       </c>
       <c r="AE158" t="b">
         <v>0</v>
       </c>
-      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>130085067</v>
+        <v>130091841</v>
       </c>
       <c r="B159" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17697,16 +17695,16 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -17714,22 +17712,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr"/>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
       <c r="M159" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>461857</v>
+        <v>461720</v>
       </c>
       <c r="R159" t="n">
-        <v>6780842</v>
+        <v>6780825</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17759,19 +17764,14 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>10:14</t>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>hack födosök i gran och ringhackad gran intill</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17786,12 +17786,12 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander, Håkan Thenander</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
@@ -19639,40 +19639,41 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>130157723</v>
+        <v>130157683</v>
       </c>
       <c r="B177" t="n">
-        <v>57826</v>
+        <v>8451</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr"/>
       <c r="M177" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N177" t="inlineStr"/>
@@ -19682,10 +19683,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>461526</v>
+        <v>461363</v>
       </c>
       <c r="R177" t="n">
-        <v>6780870</v>
+        <v>6780957</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19720,17 +19721,13 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>Ringhack i en av de äldre tallarna (en av 5-6 äldre tallar som ej bandats av)</t>
-        </is>
-      </c>
       <c r="AD177" t="b">
         <v>0</v>
       </c>
       <c r="AE177" t="b">
         <v>0</v>
       </c>
+      <c r="AF177" t="inlineStr"/>
       <c r="AG177" t="b">
         <v>0</v>
       </c>
@@ -19749,41 +19746,40 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>130157683</v>
+        <v>130157723</v>
       </c>
       <c r="B178" t="n">
-        <v>8451</v>
+        <v>57826</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr"/>
       <c r="M178" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N178" t="inlineStr"/>
@@ -19793,10 +19789,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>461363</v>
+        <v>461526</v>
       </c>
       <c r="R178" t="n">
-        <v>6780957</v>
+        <v>6780870</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19831,13 +19827,17 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>Ringhack i en av de äldre tallarna (en av 5-6 äldre tallar som ej bandats av)</t>
+        </is>
+      </c>
       <c r="AD178" t="b">
         <v>0</v>
       </c>
       <c r="AE178" t="b">
         <v>0</v>
       </c>
-      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58003-2025 artfynd.xlsx
+++ b/artfynd/A 58003-2025 artfynd.xlsx
@@ -18132,7 +18132,7 @@
         <v>130084138</v>
       </c>
       <c r="B163" t="n">
-        <v>91712</v>
+        <v>91715</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18241,10 +18241,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>130086991</v>
+        <v>130083774</v>
       </c>
       <c r="B164" t="n">
-        <v>79180</v>
+        <v>90763</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18252,37 +18252,40 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>461939</v>
+        <v>461717</v>
       </c>
       <c r="R164" t="n">
-        <v>6780857</v>
+        <v>6780842</v>
       </c>
       <c r="S164" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -18311,7 +18314,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -18321,20 +18324,21 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>2 bild. Rikligt till måttligt i en radie av ca 50 meter</t>
+          <t>2 bilder</t>
         </is>
       </c>
       <c r="AD164" t="b">
         <v>0</v>
       </c>
       <c r="AE164" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
@@ -18353,10 +18357,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>130083774</v>
+        <v>130086991</v>
       </c>
       <c r="B165" t="n">
-        <v>90760</v>
+        <v>79183</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18364,40 +18368,37 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>461717</v>
+        <v>461939</v>
       </c>
       <c r="R165" t="n">
-        <v>6780842</v>
+        <v>6780857</v>
       </c>
       <c r="S165" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -18426,7 +18427,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -18436,21 +18437,20 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>2 bilder</t>
+          <t>2 bild. Rikligt till måttligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD165" t="b">
         <v>0</v>
       </c>
       <c r="AE165" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF165" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
@@ -18472,7 +18472,7 @@
         <v>130084189</v>
       </c>
       <c r="B166" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18584,7 +18584,7 @@
         <v>130085198</v>
       </c>
       <c r="B167" t="n">
-        <v>81165</v>
+        <v>81168</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18691,7 +18691,7 @@
         <v>130084610</v>
       </c>
       <c r="B168" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18803,7 +18803,7 @@
         <v>130082682</v>
       </c>
       <c r="B169" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18915,7 +18915,7 @@
         <v>130082967</v>
       </c>
       <c r="B170" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19027,7 +19027,7 @@
         <v>130092045</v>
       </c>
       <c r="B171" t="n">
-        <v>91781</v>
+        <v>91784</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19133,7 +19133,7 @@
         <v>130157655</v>
       </c>
       <c r="B172" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
         <v>130157437</v>
       </c>
       <c r="B174" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19439,7 +19439,7 @@
         <v>130157644</v>
       </c>
       <c r="B175" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19639,41 +19639,40 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>130157683</v>
+        <v>130157723</v>
       </c>
       <c r="B177" t="n">
-        <v>8451</v>
+        <v>57826</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
-      <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr"/>
       <c r="M177" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N177" t="inlineStr"/>
@@ -19683,10 +19682,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>461363</v>
+        <v>461526</v>
       </c>
       <c r="R177" t="n">
-        <v>6780957</v>
+        <v>6780870</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19721,13 +19720,17 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>Ringhack i en av de äldre tallarna (en av 5-6 äldre tallar som ej bandats av)</t>
+        </is>
+      </c>
       <c r="AD177" t="b">
         <v>0</v>
       </c>
       <c r="AE177" t="b">
         <v>0</v>
       </c>
-      <c r="AF177" t="inlineStr"/>
       <c r="AG177" t="b">
         <v>0</v>
       </c>
@@ -19746,40 +19749,41 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>130157723</v>
+        <v>130157683</v>
       </c>
       <c r="B178" t="n">
-        <v>57826</v>
+        <v>8451</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr"/>
       <c r="M178" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N178" t="inlineStr"/>
@@ -19789,10 +19793,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>461526</v>
+        <v>461363</v>
       </c>
       <c r="R178" t="n">
-        <v>6780870</v>
+        <v>6780957</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19827,17 +19831,13 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="AC178" t="inlineStr">
-        <is>
-          <t>Ringhack i en av de äldre tallarna (en av 5-6 äldre tallar som ej bandats av)</t>
-        </is>
-      </c>
       <c r="AD178" t="b">
         <v>0</v>
       </c>
       <c r="AE178" t="b">
         <v>0</v>
       </c>
+      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>
@@ -19859,7 +19859,7 @@
         <v>130157405</v>
       </c>
       <c r="B179" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19959,7 +19959,7 @@
         <v>130157430</v>
       </c>
       <c r="B180" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20059,7 +20059,7 @@
         <v>130157632</v>
       </c>
       <c r="B181" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20374,37 +20374,43 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>130157446</v>
+        <v>130157677</v>
       </c>
       <c r="B184" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
@@ -20412,10 +20418,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>462162</v>
+        <v>461370</v>
       </c>
       <c r="R184" t="n">
-        <v>6780616</v>
+        <v>6780963</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20456,6 +20462,7 @@
       <c r="AE184" t="b">
         <v>0</v>
       </c>
+      <c r="AF184" t="inlineStr"/>
       <c r="AG184" t="b">
         <v>0</v>
       </c>
@@ -20467,50 +20474,44 @@
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>130157677</v>
+        <v>130157446</v>
       </c>
       <c r="B185" t="n">
-        <v>8451</v>
+        <v>79183</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr"/>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
@@ -20518,10 +20519,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>461370</v>
+        <v>462162</v>
       </c>
       <c r="R185" t="n">
-        <v>6780963</v>
+        <v>6780616</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20562,7 +20563,6 @@
       <c r="AE185" t="b">
         <v>0</v>
       </c>
-      <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="b">
         <v>0</v>
       </c>
@@ -20574,7 +20574,7 @@
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
@@ -20584,7 +20584,7 @@
         <v>130157638</v>
       </c>
       <c r="B186" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>

--- a/artfynd/A 58003-2025 artfynd.xlsx
+++ b/artfynd/A 58003-2025 artfynd.xlsx
@@ -18132,7 +18132,7 @@
         <v>130084138</v>
       </c>
       <c r="B163" t="n">
-        <v>91715</v>
+        <v>91741</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18241,10 +18241,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>130083774</v>
+        <v>130086991</v>
       </c>
       <c r="B164" t="n">
-        <v>90763</v>
+        <v>79209</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18252,40 +18252,37 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>461717</v>
+        <v>461939</v>
       </c>
       <c r="R164" t="n">
-        <v>6780842</v>
+        <v>6780857</v>
       </c>
       <c r="S164" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -18314,7 +18311,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -18324,21 +18321,20 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>2 bilder</t>
+          <t>2 bild. Rikligt till måttligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD164" t="b">
         <v>0</v>
       </c>
       <c r="AE164" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF164" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
@@ -18357,10 +18353,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>130086991</v>
+        <v>130083774</v>
       </c>
       <c r="B165" t="n">
-        <v>79183</v>
+        <v>90789</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18368,37 +18364,40 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Rävhällsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>461939</v>
+        <v>461717</v>
       </c>
       <c r="R165" t="n">
-        <v>6780857</v>
+        <v>6780842</v>
       </c>
       <c r="S165" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -18427,7 +18426,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -18437,20 +18436,21 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>2 bild. Rikligt till måttligt i en radie av ca 50 meter</t>
+          <t>2 bilder</t>
         </is>
       </c>
       <c r="AD165" t="b">
         <v>0</v>
       </c>
       <c r="AE165" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
@@ -18472,7 +18472,7 @@
         <v>130084189</v>
       </c>
       <c r="B166" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18584,7 +18584,7 @@
         <v>130085198</v>
       </c>
       <c r="B167" t="n">
-        <v>81168</v>
+        <v>81194</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18691,7 +18691,7 @@
         <v>130084610</v>
       </c>
       <c r="B168" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18803,7 +18803,7 @@
         <v>130082682</v>
       </c>
       <c r="B169" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18915,7 +18915,7 @@
         <v>130082967</v>
       </c>
       <c r="B170" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19027,7 +19027,7 @@
         <v>130092045</v>
       </c>
       <c r="B171" t="n">
-        <v>91784</v>
+        <v>91810</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19133,7 +19133,7 @@
         <v>130157655</v>
       </c>
       <c r="B172" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19234,7 +19234,7 @@
         <v>130157740</v>
       </c>
       <c r="B173" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
         <v>130157437</v>
       </c>
       <c r="B174" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19439,7 +19439,7 @@
         <v>130157644</v>
       </c>
       <c r="B175" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19642,7 +19642,7 @@
         <v>130157723</v>
       </c>
       <c r="B177" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19859,7 +19859,7 @@
         <v>130157405</v>
       </c>
       <c r="B179" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19959,7 +19959,7 @@
         <v>130157430</v>
       </c>
       <c r="B180" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20059,7 +20059,7 @@
         <v>130157632</v>
       </c>
       <c r="B181" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20272,7 +20272,7 @@
         <v>130157699</v>
       </c>
       <c r="B183" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20374,43 +20374,37 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>130157677</v>
+        <v>130157446</v>
       </c>
       <c r="B184" t="n">
-        <v>8451</v>
+        <v>79209</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr"/>
-      <c r="L184" t="inlineStr"/>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
@@ -20418,10 +20412,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>461370</v>
+        <v>462162</v>
       </c>
       <c r="R184" t="n">
-        <v>6780963</v>
+        <v>6780616</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20462,7 +20456,6 @@
       <c r="AE184" t="b">
         <v>0</v>
       </c>
-      <c r="AF184" t="inlineStr"/>
       <c r="AG184" t="b">
         <v>0</v>
       </c>
@@ -20474,44 +20467,50 @@
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>130157446</v>
+        <v>130157677</v>
       </c>
       <c r="B185" t="n">
-        <v>79183</v>
+        <v>8451</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
@@ -20519,10 +20518,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>462162</v>
+        <v>461370</v>
       </c>
       <c r="R185" t="n">
-        <v>6780616</v>
+        <v>6780963</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20563,6 +20562,7 @@
       <c r="AE185" t="b">
         <v>0</v>
       </c>
+      <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="b">
         <v>0</v>
       </c>
@@ -20574,7 +20574,7 @@
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
@@ -20584,7 +20584,7 @@
         <v>130157638</v>
       </c>
       <c r="B186" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20685,7 +20685,7 @@
         <v>129972392</v>
       </c>
       <c r="B187" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>

--- a/artfynd/A 58003-2025 artfynd.xlsx
+++ b/artfynd/A 58003-2025 artfynd.xlsx
@@ -19639,40 +19639,41 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>130157723</v>
+        <v>130157683</v>
       </c>
       <c r="B177" t="n">
-        <v>57852</v>
+        <v>8451</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr"/>
       <c r="M177" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N177" t="inlineStr"/>
@@ -19682,10 +19683,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>461526</v>
+        <v>461363</v>
       </c>
       <c r="R177" t="n">
-        <v>6780870</v>
+        <v>6780957</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19720,17 +19721,13 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>Ringhack i en av de äldre tallarna (en av 5-6 äldre tallar som ej bandats av)</t>
-        </is>
-      </c>
       <c r="AD177" t="b">
         <v>0</v>
       </c>
       <c r="AE177" t="b">
         <v>0</v>
       </c>
+      <c r="AF177" t="inlineStr"/>
       <c r="AG177" t="b">
         <v>0</v>
       </c>
@@ -19749,41 +19746,40 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>130157683</v>
+        <v>130157723</v>
       </c>
       <c r="B178" t="n">
-        <v>8451</v>
+        <v>57852</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr"/>
       <c r="M178" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N178" t="inlineStr"/>
@@ -19793,10 +19789,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>461363</v>
+        <v>461526</v>
       </c>
       <c r="R178" t="n">
-        <v>6780957</v>
+        <v>6780870</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19831,13 +19827,17 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>Ringhack i en av de äldre tallarna (en av 5-6 äldre tallar som ej bandats av)</t>
+        </is>
+      </c>
       <c r="AD178" t="b">
         <v>0</v>
       </c>
       <c r="AE178" t="b">
         <v>0</v>
       </c>
-      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58003-2025 artfynd.xlsx
+++ b/artfynd/A 58003-2025 artfynd.xlsx
@@ -19639,41 +19639,40 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>130157683</v>
+        <v>130157723</v>
       </c>
       <c r="B177" t="n">
-        <v>8451</v>
+        <v>57852</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
-      <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr"/>
       <c r="M177" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N177" t="inlineStr"/>
@@ -19683,10 +19682,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>461363</v>
+        <v>461526</v>
       </c>
       <c r="R177" t="n">
-        <v>6780957</v>
+        <v>6780870</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19721,13 +19720,17 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>Ringhack i en av de äldre tallarna (en av 5-6 äldre tallar som ej bandats av)</t>
+        </is>
+      </c>
       <c r="AD177" t="b">
         <v>0</v>
       </c>
       <c r="AE177" t="b">
         <v>0</v>
       </c>
-      <c r="AF177" t="inlineStr"/>
       <c r="AG177" t="b">
         <v>0</v>
       </c>
@@ -19746,40 +19749,41 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>130157723</v>
+        <v>130157683</v>
       </c>
       <c r="B178" t="n">
-        <v>57852</v>
+        <v>8451</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr"/>
       <c r="M178" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N178" t="inlineStr"/>
@@ -19789,10 +19793,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>461526</v>
+        <v>461363</v>
       </c>
       <c r="R178" t="n">
-        <v>6780870</v>
+        <v>6780957</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19827,17 +19831,13 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="AC178" t="inlineStr">
-        <is>
-          <t>Ringhack i en av de äldre tallarna (en av 5-6 äldre tallar som ej bandats av)</t>
-        </is>
-      </c>
       <c r="AD178" t="b">
         <v>0</v>
       </c>
       <c r="AE178" t="b">
         <v>0</v>
       </c>
+      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58003-2025 artfynd.xlsx
+++ b/artfynd/A 58003-2025 artfynd.xlsx
@@ -19436,37 +19436,39 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>130157644</v>
+        <v>130157422</v>
       </c>
       <c r="B175" t="n">
-        <v>79209</v>
+        <v>8451</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr"/>
       <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
@@ -19474,10 +19476,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>461439</v>
+        <v>462148</v>
       </c>
       <c r="R175" t="n">
-        <v>6780942</v>
+        <v>6780659</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19518,7 +19520,6 @@
       <c r="AE175" t="b">
         <v>0</v>
       </c>
-      <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="b">
         <v>0</v>
       </c>
@@ -19530,46 +19531,44 @@
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>130157422</v>
+        <v>130157644</v>
       </c>
       <c r="B176" t="n">
-        <v>8451</v>
+        <v>79209</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr"/>
-      <c r="L176" t="inlineStr"/>
-      <c r="M176" t="inlineStr"/>
       <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
@@ -19577,10 +19576,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>462148</v>
+        <v>461439</v>
       </c>
       <c r="R176" t="n">
-        <v>6780659</v>
+        <v>6780942</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19621,6 +19620,7 @@
       <c r="AE176" t="b">
         <v>0</v>
       </c>
+      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
@@ -19632,7 +19632,7 @@
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>

--- a/artfynd/A 58003-2025 artfynd.xlsx
+++ b/artfynd/A 58003-2025 artfynd.xlsx
@@ -20685,7 +20685,7 @@
         <v>129972392</v>
       </c>
       <c r="B187" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>

--- a/artfynd/A 58003-2025 artfynd.xlsx
+++ b/artfynd/A 58003-2025 artfynd.xlsx
@@ -20685,7 +20685,7 @@
         <v>129972392</v>
       </c>
       <c r="B187" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>

--- a/artfynd/A 58003-2025 artfynd.xlsx
+++ b/artfynd/A 58003-2025 artfynd.xlsx
@@ -20685,7 +20685,7 @@
         <v>129972392</v>
       </c>
       <c r="B187" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>

--- a/artfynd/A 58003-2025 artfynd.xlsx
+++ b/artfynd/A 58003-2025 artfynd.xlsx
@@ -20685,7 +20685,7 @@
         <v>129972392</v>
       </c>
       <c r="B187" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>

--- a/artfynd/A 58003-2025 artfynd.xlsx
+++ b/artfynd/A 58003-2025 artfynd.xlsx
@@ -20805,7 +20805,7 @@
         <v>131048623</v>
       </c>
       <c r="B188" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
         <v>131048622</v>
       </c>
       <c r="B189" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>

--- a/artfynd/A 58003-2025 artfynd.xlsx
+++ b/artfynd/A 58003-2025 artfynd.xlsx
@@ -20805,7 +20805,7 @@
         <v>131048623</v>
       </c>
       <c r="B188" t="n">
-        <v>57075</v>
+        <v>57076</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
         <v>131048622</v>
       </c>
       <c r="B189" t="n">
-        <v>57075</v>
+        <v>57076</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>

--- a/artfynd/A 58003-2025 artfynd.xlsx
+++ b/artfynd/A 58003-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY225"/>
+  <dimension ref="A1:AZ225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130084991</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130087789</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130091631</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1098,6 +1118,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130091751</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1204,6 +1229,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130092401</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1311,6 +1341,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130085198</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1427,6 +1462,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130083774</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1539,6 +1579,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130086497</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1645,6 +1690,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130092045</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1757,6 +1807,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130084138</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1869,6 +1924,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129972538</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1976,6 +2036,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130085288</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2077,6 +2142,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130091789</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2189,6 +2259,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129969625</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2296,6 +2371,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129969697</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2403,6 +2483,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129970487</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2510,6 +2595,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129970829</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2626,6 +2716,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129970888</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2733,6 +2828,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129971127</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2840,6 +2940,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129971290</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2952,6 +3057,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129971438</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3059,6 +3169,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129971589</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3166,6 +3281,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129971610</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3273,6 +3393,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129971741</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3380,6 +3505,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129971804</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3487,6 +3617,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129971832</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3594,6 +3729,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129972394</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3701,6 +3841,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129972457</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3813,6 +3958,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129972707</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3920,6 +4070,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129972800</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4027,6 +4182,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129972961</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4139,6 +4299,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129973137</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4246,6 +4411,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129973367</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4353,6 +4523,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129973535</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4460,6 +4635,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129973732</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4567,6 +4747,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129973851</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4674,6 +4859,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129973978</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4786,6 +4976,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130082682</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4893,6 +5088,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130082810</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5005,6 +5205,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130082967</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5112,6 +5317,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130083742</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5219,6 +5429,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130083753</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5326,6 +5541,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130083775</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5438,6 +5658,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130084189</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5550,6 +5775,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130084610</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5657,6 +5887,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130085210</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5769,6 +6004,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130086767</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5876,6 +6116,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130087798</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5983,6 +6228,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130087919</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6084,6 +6334,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130091626</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6185,6 +6440,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130091628</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6286,6 +6546,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130091745</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6387,6 +6652,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130091747</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6488,6 +6758,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130091761</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6589,6 +6864,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130091780</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6690,6 +6970,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130091785</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6791,6 +7076,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130091794</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6892,6 +7182,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130091832</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6993,6 +7288,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130091843</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7094,6 +7394,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130091872</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7195,6 +7500,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130091888</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7296,6 +7606,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130091979</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7397,6 +7712,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130092042</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7497,6 +7817,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130157508</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7598,6 +7923,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130157624</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7699,6 +8029,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130157632</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7800,6 +8135,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130157638</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7901,6 +8241,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130157644</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8002,6 +8347,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130157655</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8103,6 +8453,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130091754</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8210,6 +8565,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129970828</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8311,6 +8671,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130092026</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8418,6 +8783,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129970675</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8525,6 +8895,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129970738</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8632,6 +9007,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129970813</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8739,6 +9119,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129971608</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8846,6 +9231,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129971787</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8953,6 +9343,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129971802</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9060,6 +9455,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130083642</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9167,6 +9567,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130087915</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9279,6 +9684,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129969590</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9396,6 +9806,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129969692</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9508,6 +9923,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129971259</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9620,6 +10040,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129971585</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9732,6 +10157,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129971825</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9852,6 +10282,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129972233</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9964,6 +10399,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129972793</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10076,6 +10516,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129972983</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10188,6 +10633,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129973365</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10300,6 +10750,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129973829</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10417,6 +10872,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130083279</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10529,6 +10989,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130083972</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10641,6 +11106,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130085067</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10758,6 +11228,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130085149</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10870,6 +11345,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130085207</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10982,6 +11462,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130087794</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11087,6 +11572,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130091819</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11192,6 +11682,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130092006</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11297,6 +11792,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130157699</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11417,6 +11917,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129972392</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11534,6 +12039,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129972454</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11651,6 +12161,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129972955</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11771,6 +12286,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129973506</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11885,6 +12405,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130091841</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11995,6 +12520,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130091853</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12105,6 +12635,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130157713</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12215,6 +12750,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130157723</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12320,6 +12860,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130157740</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12438,6 +12983,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130083967</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12550,6 +13100,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129969658</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12662,6 +13217,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129971289</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12774,6 +13334,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129971587</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12886,6 +13451,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129971831</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12998,6 +13568,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129972234</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13110,6 +13685,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129972802</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13222,6 +13802,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129972990</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13334,6 +13919,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129973370</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13446,6 +14036,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129973534</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13558,6 +14153,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129973842</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13670,6 +14270,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130082759</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13777,6 +14382,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130083654</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13889,6 +14499,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130085157</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14001,6 +14616,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130085214</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14118,6 +14738,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130086721</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14225,6 +14850,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130091758</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14332,6 +14962,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130091767</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14439,6 +15074,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130091775</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14546,6 +15186,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130091798</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14653,6 +15298,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130091806</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14760,6 +15410,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130091811</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14867,6 +15522,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130091828</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14974,6 +15634,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130091883</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15081,6 +15746,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130091885</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15192,6 +15862,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130091914</t>
+        </is>
+      </c>
     </row>
    